--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saran\Documents\Academia\repository_clones\Bioindustrial-Park\biorefineries\isobutanol\analyses\full\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{946B5B05-DCC2-4EA2-AAF1-7F3D6BECADE4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9718E7DB-8ABD-45E8-920D-0585202443C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="169">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="184">
   <si>
     <t>Parameter name</t>
   </si>
@@ -209,9 +209,6 @@
     <t>V514.tau = x</t>
   </si>
   <si>
-    <t>Fermentation Kinetics</t>
-  </si>
-  <si>
     <t>V406.kinetic_reaction_system._te.k_2 = x</t>
   </si>
   <si>
@@ -299,250 +296,298 @@
     <t>V406.kinetic_reaction_system._te.k_11 = x</t>
   </si>
   <si>
+    <t>lime.price = x</t>
+  </si>
+  <si>
+    <t>sulfuric_acid.price = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_1l = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_1h = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_1i = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_1e = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_2 = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_2i = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_3 = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_4 = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_5 = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_5e = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_5i = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_6 = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_6e = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_7 = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_9 = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_9e = x</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_9i = x</t>
+  </si>
+  <si>
+    <t>steam.price = x</t>
+  </si>
+  <si>
+    <t>K_1l</t>
+  </si>
+  <si>
+    <t>K_1h</t>
+  </si>
+  <si>
+    <t>K_1i</t>
+  </si>
+  <si>
+    <t>K_1e</t>
+  </si>
+  <si>
+    <t>K_2</t>
+  </si>
+  <si>
+    <t>K_2i</t>
+  </si>
+  <si>
+    <t>K_3</t>
+  </si>
+  <si>
+    <t>K_4</t>
+  </si>
+  <si>
+    <t>K_5</t>
+  </si>
+  <si>
+    <t>K_5e</t>
+  </si>
+  <si>
+    <t>K_5i</t>
+  </si>
+  <si>
+    <t>K_6</t>
+  </si>
+  <si>
+    <t>K_6e</t>
+  </si>
+  <si>
+    <t>K_7</t>
+  </si>
+  <si>
+    <t>K_9</t>
+  </si>
+  <si>
+    <t>K_9e</t>
+  </si>
+  <si>
+    <t>K_9i</t>
+  </si>
+  <si>
+    <t>._k_1l</t>
+  </si>
+  <si>
+    <t>._k_1h</t>
+  </si>
+  <si>
+    <t>._k_1e</t>
+  </si>
+  <si>
+    <t>._k_1ie</t>
+  </si>
+  <si>
+    <t>._k_1ia</t>
+  </si>
+  <si>
+    <t>._k_1ii</t>
+  </si>
+  <si>
+    <t>._k_2</t>
+  </si>
+  <si>
+    <t>._k_3</t>
+  </si>
+  <si>
+    <t>._k_4</t>
+  </si>
+  <si>
+    <t>._k_4ie</t>
+  </si>
+  <si>
+    <t>._k_4ia</t>
+  </si>
+  <si>
+    <t>._k_4ii</t>
+  </si>
+  <si>
+    <t>._k_5</t>
+  </si>
+  <si>
+    <t>._k_5e</t>
+  </si>
+  <si>
+    <t>._k_6</t>
+  </si>
+  <si>
+    <t>._k_6r</t>
+  </si>
+  <si>
+    <t>._k_7</t>
+  </si>
+  <si>
+    <t>._k_7ie</t>
+  </si>
+  <si>
+    <t>._k_7ia</t>
+  </si>
+  <si>
+    <t>._k_7ii</t>
+  </si>
+  <si>
+    <t>._k_8</t>
+  </si>
+  <si>
+    <t>._k_9</t>
+  </si>
+  <si>
+    <t>._k_9e</t>
+  </si>
+  <si>
+    <t>._k_9c</t>
+  </si>
+  <si>
+    <t>._k_10</t>
+  </si>
+  <si>
+    <t>._k_11</t>
+  </si>
+  <si>
+    <t>Kinetics: Glycolysis</t>
+  </si>
+  <si>
+    <t>Kinetics: TCA Cycle</t>
+  </si>
+  <si>
+    <t>Kinetics: Pyruvate-to-Acetaldehyde</t>
+  </si>
+  <si>
+    <t>Kinetics: Acetaldehyde-to-Acetate</t>
+  </si>
+  <si>
+    <t>Kinetics: Acetaldyhede-to-Ethanol</t>
+  </si>
+  <si>
+    <t>Kinetics: Glucose-to-Biomass</t>
+  </si>
+  <si>
+    <t>Kinetics: Acetate-to-Biomass</t>
+  </si>
+  <si>
+    <t>Kinetics: Acetalhdyde compartment formation</t>
+  </si>
+  <si>
+    <t>Kinetics: Acetate respiration</t>
+  </si>
+  <si>
+    <t>Kinetics: Active compartment degradation</t>
+  </si>
+  <si>
+    <t>Kinetics: Acetaldehyde compartment degradation</t>
+  </si>
+  <si>
+    <t>._k_13</t>
+  </si>
+  <si>
     <t>V406.kinetic_reaction_system._te.k_13 = x</t>
   </si>
   <si>
+    <t>K_13</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_13 = x</t>
+  </si>
+  <si>
+    <t>._k_14</t>
+  </si>
+  <si>
     <t>V406.kinetic_reaction_system._te.k_14 = x</t>
   </si>
   <si>
+    <t>K_14</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_14 = x</t>
+  </si>
+  <si>
+    <t>._k_15</t>
+  </si>
+  <si>
     <t>V406.kinetic_reaction_system._te.k_15 = x</t>
   </si>
   <si>
+    <t>K_15</t>
+  </si>
+  <si>
+    <t>V406.kinetic_reaction_system._te.K_15 = x</t>
+  </si>
+  <si>
+    <t>._k_16</t>
+  </si>
+  <si>
     <t>V406.kinetic_reaction_system._te.k_16 = x</t>
   </si>
   <si>
+    <t>._k_16r</t>
+  </si>
+  <si>
     <t>V406.kinetic_reaction_system._te.k_16r = x</t>
   </si>
   <si>
-    <t>lime.price = x</t>
-  </si>
-  <si>
-    <t>sulfuric_acid.price = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_1l = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_1h = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_1i = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_1e = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_2 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_2i = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_3 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_4 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_5 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_5e = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_5i = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_6 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_6e = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_7 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_9 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_9e = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_9i = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_13 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_14 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_15 = x</t>
+    <t>K_16</t>
   </si>
   <si>
     <t>V406.kinetic_reaction_system._te.K_16 = x</t>
   </si>
   <si>
+    <t>K_16i</t>
+  </si>
+  <si>
     <t>V406.kinetic_reaction_system._te.K_16i = x</t>
   </si>
   <si>
-    <t>K_1l</t>
-  </si>
-  <si>
-    <t>K_1h</t>
-  </si>
-  <si>
-    <t>K_1i</t>
-  </si>
-  <si>
-    <t>K_1e</t>
-  </si>
-  <si>
-    <t>K_2</t>
-  </si>
-  <si>
-    <t>K_2i</t>
-  </si>
-  <si>
-    <t>K_3</t>
-  </si>
-  <si>
-    <t>K_4</t>
-  </si>
-  <si>
-    <t>K_5</t>
-  </si>
-  <si>
-    <t>K_5e</t>
-  </si>
-  <si>
-    <t>K_5i</t>
-  </si>
-  <si>
-    <t>K_6</t>
-  </si>
-  <si>
-    <t>K_6e</t>
-  </si>
-  <si>
-    <t>K_7</t>
-  </si>
-  <si>
-    <t>K_9</t>
-  </si>
-  <si>
-    <t>K_9e</t>
-  </si>
-  <si>
-    <t>K_9i</t>
-  </si>
-  <si>
-    <t>K_13</t>
-  </si>
-  <si>
-    <t>K_14</t>
-  </si>
-  <si>
-    <t>K_15</t>
-  </si>
-  <si>
-    <t>K_16</t>
-  </si>
-  <si>
-    <t>K_16i</t>
-  </si>
-  <si>
-    <t>._k_1l</t>
-  </si>
-  <si>
-    <t>._k_1h</t>
-  </si>
-  <si>
-    <t>._k_1e</t>
-  </si>
-  <si>
-    <t>._k_1ie</t>
-  </si>
-  <si>
-    <t>._k_1ia</t>
-  </si>
-  <si>
-    <t>._k_1ii</t>
-  </si>
-  <si>
-    <t>._k_2</t>
-  </si>
-  <si>
-    <t>._k_3</t>
-  </si>
-  <si>
-    <t>._k_4</t>
-  </si>
-  <si>
-    <t>._k_4ie</t>
-  </si>
-  <si>
-    <t>._k_4ia</t>
-  </si>
-  <si>
-    <t>._k_4ii</t>
-  </si>
-  <si>
-    <t>._k_5</t>
-  </si>
-  <si>
-    <t>._k_5e</t>
-  </si>
-  <si>
-    <t>._k_6</t>
-  </si>
-  <si>
-    <t>._k_6r</t>
-  </si>
-  <si>
-    <t>._k_7</t>
-  </si>
-  <si>
-    <t>._k_7ie</t>
-  </si>
-  <si>
-    <t>._k_7ia</t>
-  </si>
-  <si>
-    <t>._k_7ii</t>
-  </si>
-  <si>
-    <t>._k_8</t>
-  </si>
-  <si>
-    <t>._k_9</t>
-  </si>
-  <si>
-    <t>._k_9e</t>
-  </si>
-  <si>
-    <t>._k_9c</t>
-  </si>
-  <si>
-    <t>._k_10</t>
-  </si>
-  <si>
-    <t>._k_11</t>
-  </si>
-  <si>
-    <t>._k_13</t>
-  </si>
-  <si>
-    <t>._k_14</t>
-  </si>
-  <si>
-    <t>._k_15</t>
-  </si>
-  <si>
-    <t>._k_16</t>
-  </si>
-  <si>
-    <t>._k_16r</t>
+    <t>Kinetics: Pyruvate-to-Acetolactate</t>
+  </si>
+  <si>
+    <t>Kinetics: Acetolactate-to-DHI</t>
+  </si>
+  <si>
+    <t>Kinetics: DHI-to-Ketoisovalerate</t>
+  </si>
+  <si>
+    <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
   </si>
 </sst>
 </file>
@@ -566,7 +611,7 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="3">
+  <fills count="4">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -576,6 +621,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFF00"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC000"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -607,7 +658,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="6">
+  <cellXfs count="7">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -618,6 +669,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
     <xf numFmtId="11" fontId="0" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -902,7 +954,7 @@
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40.81640625" customWidth="1"/>
-    <col min="2" max="2" width="20.6328125" customWidth="1"/>
+    <col min="2" max="2" width="46" customWidth="1"/>
     <col min="4" max="4" width="12.1796875" customWidth="1"/>
     <col min="6" max="6" width="14.453125" customWidth="1"/>
     <col min="10" max="10" width="10.6328125" customWidth="1"/>
@@ -1012,70 +1064,70 @@
       </c>
     </row>
     <row r="4" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A4" s="3" t="s">
+      <c r="A4" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="B4" s="3" t="s">
+      <c r="B4" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C4" s="3" t="s">
+      <c r="C4" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D4" s="3" t="s">
+      <c r="D4" s="6" t="s">
         <v>9</v>
       </c>
-      <c r="E4" s="3">
+      <c r="E4" s="6">
         <v>0.13900000000000001</v>
       </c>
-      <c r="F4" s="3" t="s">
+      <c r="F4" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G4" s="3">
+      <c r="G4" s="6">
         <v>0.127</v>
       </c>
-      <c r="H4" s="3">
+      <c r="H4" s="6">
         <f>E4</f>
         <v>0.13900000000000001</v>
       </c>
-      <c r="I4" s="3">
+      <c r="I4" s="6">
         <v>0.15</v>
       </c>
-      <c r="J4" s="3"/>
-      <c r="K4" s="3" t="s">
+      <c r="J4" s="6"/>
+      <c r="K4" s="6" t="s">
         <v>24</v>
       </c>
     </row>
     <row r="5" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A5" s="3" t="s">
+      <c r="A5" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="B5" s="3" t="s">
+      <c r="B5" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C5" s="3" t="s">
+      <c r="C5" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D5" s="3" t="s">
+      <c r="D5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="E5" s="3">
+      <c r="E5" s="6">
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="F5" s="3" t="s">
+      <c r="F5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G5" s="3">
+      <c r="G5" s="6">
         <v>6.7000000000000004E-2</v>
       </c>
-      <c r="H5" s="3">
+      <c r="H5" s="6">
         <f>E5</f>
         <v>7.0000000000000007E-2</v>
       </c>
-      <c r="I5" s="3">
+      <c r="I5" s="6">
         <v>7.3999999999999996E-2</v>
       </c>
-      <c r="J5" s="3"/>
-      <c r="K5" s="3" t="s">
+      <c r="J5" s="6"/>
+      <c r="K5" s="6" t="s">
         <v>25</v>
       </c>
     </row>
@@ -1274,76 +1326,76 @@
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4" t="s">
-        <v>51</v>
+        <v>105</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="3" t="s">
+      <c r="A12" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="3" t="s">
+      <c r="B12" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="3" t="s">
+      <c r="C12" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="3" t="s">
+      <c r="D12" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="3">
+      <c r="E12" s="6">
         <v>0.28599999999999998</v>
       </c>
-      <c r="F12" s="3" t="s">
+      <c r="F12" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="3">
+      <c r="G12" s="6">
         <v>0.17499999999999999</v>
       </c>
-      <c r="H12" s="3">
+      <c r="H12" s="6">
         <v>0.28599999999999998</v>
       </c>
-      <c r="I12" s="3">
+      <c r="I12" s="6">
         <v>0.315</v>
       </c>
-      <c r="J12" s="3"/>
-      <c r="K12" s="3" t="s">
-        <v>92</v>
+      <c r="J12" s="6"/>
+      <c r="K12" s="6" t="s">
+        <v>86</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="3" t="s">
+      <c r="A13" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="3" t="s">
+      <c r="B13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="3" t="s">
+      <c r="C13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="3" t="s">
+      <c r="D13" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="3">
+      <c r="E13" s="6">
         <v>0.10355</v>
       </c>
-      <c r="F13" s="3" t="s">
+      <c r="F13" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G13" s="3">
+      <c r="G13" s="6">
         <f>E13*0.9</f>
         <v>9.3195E-2</v>
       </c>
-      <c r="H13" s="3">
+      <c r="H13" s="6">
         <f>E13</f>
         <v>0.10355</v>
       </c>
-      <c r="I13" s="3">
+      <c r="I13" s="6">
         <f>E13*1.1</f>
         <v>0.11390500000000001</v>
       </c>
-      <c r="J13" s="3"/>
-      <c r="K13" s="3" t="s">
-        <v>93</v>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6" t="s">
+        <v>87</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
@@ -1520,22 +1572,22 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>138</v>
+        <v>123</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E19" s="3">
         <v>1.43</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G19" s="3">
         <v>1.1439999999999999</v>
@@ -1548,27 +1600,27 @@
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>116</v>
+        <v>106</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E20" s="3">
         <v>0.94</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G20" s="3">
         <v>0.752</v>
@@ -1581,27 +1633,27 @@
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3" t="s">
-        <v>94</v>
+        <v>88</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>139</v>
+        <v>124</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E21" s="3">
         <v>0.58399999999999996</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G21" s="3">
         <v>0.4672</v>
@@ -1614,27 +1666,27 @@
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>117</v>
+        <v>107</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E22" s="3">
         <v>1.1599999999999999E-2</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G22" s="3">
         <v>9.2800000000000001E-3</v>
@@ -1647,27 +1699,27 @@
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>95</v>
+        <v>89</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>140</v>
+        <v>125</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E23" s="3">
         <v>47.1</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G23" s="3">
         <v>37.68</v>
@@ -1680,27 +1732,27 @@
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>118</v>
+        <v>108</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E24" s="3">
         <v>14.2</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G24" s="3">
         <v>11.36</v>
@@ -1713,27 +1765,27 @@
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3" t="s">
-        <v>96</v>
+        <v>90</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>119</v>
+        <v>109</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E25" s="3">
         <v>0.12</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G25" s="3">
         <v>9.6000000000000002E-2</v>
@@ -1746,27 +1798,27 @@
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3" t="s">
-        <v>97</v>
+        <v>91</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>141</v>
+        <v>126</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E26" s="3">
         <v>0.04</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G26" s="3">
         <v>3.2000000000000001E-2</v>
@@ -1779,27 +1831,27 @@
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>142</v>
+        <v>127</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E27" s="3">
         <v>0.12</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G27" s="3">
         <v>9.6000000000000002E-2</v>
@@ -1812,27 +1864,27 @@
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>143</v>
+        <v>128</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>57</v>
+        <v>149</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E28" s="3">
         <v>0.04</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G28" s="3">
         <v>3.2000000000000001E-2</v>
@@ -1845,27 +1897,27 @@
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>144</v>
+        <v>129</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E29" s="3">
         <v>0.501</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G29" s="3">
         <v>0.40079999999999999</v>
@@ -1878,27 +1930,27 @@
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>120</v>
+        <v>110</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E30" s="5">
         <v>2.0000000000000002E-5</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G30" s="5">
         <v>1.5999999999999999E-5</v>
@@ -1911,27 +1963,27 @@
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3" t="s">
-        <v>98</v>
+        <v>92</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>121</v>
+        <v>111</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>57</v>
+        <v>150</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E31" s="3">
         <v>0.10100000000000001</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G31" s="3">
         <v>8.0799999999999997E-2</v>
@@ -1944,27 +1996,27 @@
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3" t="s">
-        <v>99</v>
+        <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>145</v>
+        <v>130</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E32" s="3">
         <v>5.81</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G32" s="3">
         <v>4.6479999999999997</v>
@@ -1977,27 +2029,27 @@
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>122</v>
+        <v>112</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>57</v>
+        <v>151</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E33" s="5">
         <v>4.9999999999999998E-7</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G33" s="5">
         <v>3.9999999999999998E-7</v>
@@ -2010,27 +2062,27 @@
       </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3" t="s">
-        <v>100</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>146</v>
+        <v>131</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E34" s="3">
         <v>4.8</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G34" s="3">
         <v>3.84</v>
@@ -2043,27 +2095,27 @@
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>147</v>
+        <v>132</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E35" s="3">
         <v>0.04</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G35" s="3">
         <v>3.2000000000000001E-2</v>
@@ -2076,27 +2128,27 @@
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>148</v>
+        <v>133</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E36" s="3">
         <v>0.12</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G36" s="3">
         <v>9.6000000000000002E-2</v>
@@ -2109,27 +2161,27 @@
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>149</v>
+        <v>134</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E37" s="3">
         <v>0.04</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G37" s="3">
         <v>3.2000000000000001E-2</v>
@@ -2142,27 +2194,27 @@
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>123</v>
+        <v>113</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>57</v>
+        <v>152</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E38" s="3">
         <v>2.6400000000000002E-4</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G38" s="3">
         <v>2.1120000000000001E-4</v>
@@ -2175,27 +2227,27 @@
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>101</v>
+        <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>150</v>
+        <v>135</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E39" s="3">
         <v>1.04E-2</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G39" s="3">
         <v>8.3199999999999993E-3</v>
@@ -2208,27 +2260,27 @@
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>124</v>
+        <v>114</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E40" s="3">
         <v>1.0200000000000001E-2</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G40" s="3">
         <v>8.1600000000000006E-3</v>
@@ -2241,27 +2293,27 @@
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3" t="s">
-        <v>102</v>
+        <v>96</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>151</v>
+        <v>136</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E41" s="3">
         <v>0.77500000000000002</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G41" s="3">
         <v>0.62</v>
@@ -2274,27 +2326,27 @@
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>125</v>
+        <v>115</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E42" s="3">
         <v>0.1</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G42" s="3">
         <v>0.08</v>
@@ -2307,27 +2359,27 @@
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3" t="s">
-        <v>103</v>
+        <v>97</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>126</v>
+        <v>116</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>57</v>
+        <v>157</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E43" s="3">
         <v>440</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G43" s="3">
         <v>352</v>
@@ -2340,27 +2392,27 @@
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="3" t="s">
-        <v>104</v>
+        <v>98</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>152</v>
+        <v>137</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E44" s="3">
         <v>2.82</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G44" s="3">
         <v>2.2559999999999998</v>
@@ -2373,27 +2425,27 @@
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
+        <v>138</v>
+      </c>
+      <c r="B45" s="3" t="s">
         <v>153</v>
       </c>
-      <c r="B45" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="C45" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E45" s="3">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G45" s="3">
         <v>0.01</v>
@@ -2406,27 +2458,27 @@
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>127</v>
+        <v>117</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E46" s="3">
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G46" s="3">
         <v>2.7199999999999998E-2</v>
@@ -2439,27 +2491,27 @@
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>105</v>
+        <v>99</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>128</v>
+        <v>118</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>57</v>
+        <v>153</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E47" s="3">
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G47" s="3">
         <v>4.5600000000000002E-2</v>
@@ -2472,27 +2524,27 @@
       </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3" t="s">
-        <v>106</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="B48" s="3" t="s">
         <v>154</v>
       </c>
-      <c r="B48" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="C48" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E48" s="3">
         <v>1.2030000000000001</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G48" s="3">
         <v>0.96240000000000003</v>
@@ -2505,27 +2557,27 @@
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>155</v>
+        <v>140</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E49" s="3">
         <v>0.04</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G49" s="3">
         <v>3.2000000000000001E-2</v>
@@ -2538,27 +2590,27 @@
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>156</v>
+        <v>141</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E50" s="3">
         <v>0.12</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G50" s="3">
         <v>9.6000000000000002E-2</v>
@@ -2571,27 +2623,27 @@
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>157</v>
+        <v>142</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E51" s="3">
         <v>0.04</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G51" s="3">
         <v>3.2000000000000001E-2</v>
@@ -2604,27 +2656,27 @@
       </c>
       <c r="J51" s="3"/>
       <c r="K51" s="3" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
-        <v>129</v>
+        <v>119</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>57</v>
+        <v>154</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E52" s="3">
         <v>1.01E-2</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G52" s="3">
         <v>8.0800000000000004E-3</v>
@@ -2637,27 +2689,27 @@
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
-        <v>107</v>
+        <v>101</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>158</v>
+        <v>143</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>57</v>
+        <v>155</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E53" s="3">
         <v>0.58899999999999997</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G53" s="3">
         <v>0.47120000000000001</v>
@@ -2670,27 +2722,27 @@
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>159</v>
+        <v>144</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E54" s="3">
         <v>8.0000000000000002E-3</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G54" s="3">
         <v>6.4000000000000003E-3</v>
@@ -2703,27 +2755,27 @@
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>82</v>
+        <v>81</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>130</v>
+        <v>120</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E55" s="5">
         <v>9.9999999999999995E-7</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G55" s="5">
         <v>7.9999999999999996E-7</v>
@@ -2736,27 +2788,27 @@
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>108</v>
+        <v>102</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>160</v>
+        <v>145</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E56" s="3">
         <v>7.51E-2</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G56" s="3">
         <v>6.0080000000000001E-2</v>
@@ -2769,27 +2821,27 @@
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>131</v>
+        <v>121</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E57" s="3">
         <v>13</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G57" s="3">
         <v>10.4</v>
@@ -2802,27 +2854,27 @@
       </c>
       <c r="J57" s="3"/>
       <c r="K57" s="3" t="s">
-        <v>109</v>
+        <v>103</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>132</v>
+        <v>122</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E58" s="3">
         <v>25</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G58" s="3">
         <v>20</v>
@@ -2835,27 +2887,27 @@
       </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3" t="s">
-        <v>110</v>
+        <v>104</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>161</v>
+        <v>146</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>57</v>
+        <v>156</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E59" s="3">
         <v>3.9899999999999996E-3</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G59" s="3">
         <v>3.192E-3</v>
@@ -2868,27 +2920,27 @@
       </c>
       <c r="J59" s="3"/>
       <c r="K59" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>57</v>
+        <v>158</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E60" s="3">
         <v>0.06</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G60" s="3">
         <v>4.8000000000000001E-2</v>
@@ -2901,27 +2953,27 @@
       </c>
       <c r="J60" s="3"/>
       <c r="K60" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>163</v>
+        <v>148</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>57</v>
+        <v>159</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E61" s="3">
         <v>0.02</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G61" s="3">
         <v>1.6E-2</v>
@@ -2934,27 +2986,27 @@
       </c>
       <c r="J61" s="3"/>
       <c r="K61" s="3" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
-        <v>164</v>
+        <v>160</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E62" s="3">
         <v>5.81</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G62" s="3">
         <v>4.6479999999999997</v>
@@ -2967,27 +3019,27 @@
       </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3" t="s">
-        <v>87</v>
+        <v>161</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
-        <v>133</v>
+        <v>162</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>57</v>
+        <v>180</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E63" s="5">
         <v>4.9999999999999998E-7</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G63" s="5">
         <v>3.9999999999999998E-7</v>
@@ -3000,27 +3052,27 @@
       </c>
       <c r="J63" s="3"/>
       <c r="K63" s="3" t="s">
-        <v>111</v>
+        <v>163</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>57</v>
+        <v>181</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E64" s="3">
         <v>5.81</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G64" s="3">
         <v>4.6479999999999997</v>
@@ -3033,27 +3085,27 @@
       </c>
       <c r="J64" s="3"/>
       <c r="K64" s="3" t="s">
-        <v>88</v>
+        <v>165</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
-        <v>134</v>
+        <v>166</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>57</v>
+        <v>181</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E65" s="5">
         <v>4.9999999999999998E-7</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G65" s="5">
         <v>3.9999999999999998E-7</v>
@@ -3066,27 +3118,27 @@
       </c>
       <c r="J65" s="3"/>
       <c r="K65" s="3" t="s">
-        <v>112</v>
+        <v>167</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>57</v>
+        <v>182</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E66" s="3">
         <v>5.81</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G66" s="3">
         <v>4.6479999999999997</v>
@@ -3099,27 +3151,27 @@
       </c>
       <c r="J66" s="3"/>
       <c r="K66" s="3" t="s">
-        <v>89</v>
+        <v>169</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
-        <v>135</v>
+        <v>170</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>57</v>
+        <v>182</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E67" s="5">
         <v>4.9999999999999998E-7</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G67" s="5">
         <v>3.9999999999999998E-7</v>
@@ -3132,27 +3184,27 @@
       </c>
       <c r="J67" s="3"/>
       <c r="K67" s="3" t="s">
-        <v>113</v>
+        <v>171</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
-        <v>167</v>
+        <v>172</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>57</v>
+        <v>183</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E68" s="3">
         <v>2.82</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G68" s="3">
         <v>2.2559999999999998</v>
@@ -3165,27 +3217,27 @@
       </c>
       <c r="J68" s="3"/>
       <c r="K68" s="3" t="s">
-        <v>90</v>
+        <v>173</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>57</v>
+        <v>183</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="E69" s="3">
         <v>1.2500000000000001E-2</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G69" s="3">
         <v>0.01</v>
@@ -3198,27 +3250,27 @@
       </c>
       <c r="J69" s="3"/>
       <c r="K69" s="3" t="s">
-        <v>91</v>
+        <v>175</v>
       </c>
     </row>
     <row r="70" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
-        <v>136</v>
+        <v>176</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>57</v>
+        <v>183</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E70" s="3">
         <v>3.4000000000000002E-2</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G70" s="3">
         <v>2.7199999999999998E-2</v>
@@ -3231,27 +3283,27 @@
       </c>
       <c r="J70" s="3"/>
       <c r="K70" s="3" t="s">
-        <v>114</v>
+        <v>177</v>
       </c>
     </row>
     <row r="71" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
-        <v>137</v>
+        <v>178</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>57</v>
+        <v>183</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="E71" s="3">
         <v>5.7000000000000002E-2</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="G71" s="3">
         <v>4.5600000000000002E-2</v>
@@ -3264,7 +3316,7 @@
       </c>
       <c r="J71" s="3"/>
       <c r="K71" s="3" t="s">
-        <v>115</v>
+        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saran\Documents\Academia\repository_clones\Bioindustrial-Park\biorefineries\isobutanol\analyses\full\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9718E7DB-8ABD-45E8-920D-0585202443C3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DFA2F0-F27E-4C41-BAE0-91FE305C4645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -3008,14 +3008,17 @@
       <c r="F62" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G62" s="3">
+      <c r="G62" s="5">
+        <f>E62*0.8</f>
         <v>4.6479999999999997</v>
       </c>
-      <c r="H62" s="3">
+      <c r="H62" s="5">
+        <f>E62</f>
         <v>5.81</v>
       </c>
-      <c r="I62" s="3">
-        <v>6.9719999999999898</v>
+      <c r="I62" s="5">
+        <f>1.2*E62</f>
+        <v>6.9719999999999995</v>
       </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3" t="s">
@@ -3042,12 +3045,15 @@
         <v>67</v>
       </c>
       <c r="G63" s="5">
+        <f>E63*0.8</f>
         <v>3.9999999999999998E-7</v>
       </c>
       <c r="H63" s="5">
+        <f>E63</f>
         <v>4.9999999999999998E-7</v>
       </c>
       <c r="I63" s="5">
+        <f>1.2*E63</f>
         <v>5.9999999999999997E-7</v>
       </c>
       <c r="J63" s="3"/>
@@ -3069,19 +3075,22 @@
         <v>66</v>
       </c>
       <c r="E64" s="3">
-        <v>5.81</v>
+        <v>4.8</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G64" s="3">
-        <v>4.6479999999999997</v>
-      </c>
-      <c r="H64" s="3">
-        <v>5.81</v>
-      </c>
-      <c r="I64" s="3">
-        <v>6.9719999999999898</v>
+      <c r="G64" s="5">
+        <f t="shared" ref="G64:G71" si="2">E64*0.8</f>
+        <v>3.84</v>
+      </c>
+      <c r="H64" s="5">
+        <f t="shared" ref="H64:H71" si="3">E64</f>
+        <v>4.8</v>
+      </c>
+      <c r="I64" s="5">
+        <f t="shared" ref="I64:I71" si="4">1.2*E64</f>
+        <v>5.76</v>
       </c>
       <c r="J64" s="3"/>
       <c r="K64" s="3" t="s">
@@ -3102,19 +3111,22 @@
         <v>68</v>
       </c>
       <c r="E65" s="5">
-        <v>4.9999999999999998E-7</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G65" s="5">
-        <v>3.9999999999999998E-7</v>
+        <f t="shared" si="2"/>
+        <v>2.1120000000000004E-4</v>
       </c>
       <c r="H65" s="5">
-        <v>4.9999999999999998E-7</v>
+        <f t="shared" si="3"/>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="I65" s="5">
-        <v>5.9999999999999997E-7</v>
+        <f t="shared" si="4"/>
+        <v>3.168E-4</v>
       </c>
       <c r="J65" s="3"/>
       <c r="K65" s="3" t="s">
@@ -3135,19 +3147,22 @@
         <v>66</v>
       </c>
       <c r="E66" s="3">
-        <v>5.81</v>
+        <v>4.8</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G66" s="3">
-        <v>4.6479999999999997</v>
-      </c>
-      <c r="H66" s="3">
-        <v>5.81</v>
-      </c>
-      <c r="I66" s="3">
-        <v>6.9719999999999898</v>
+      <c r="G66" s="5">
+        <f t="shared" si="2"/>
+        <v>3.84</v>
+      </c>
+      <c r="H66" s="5">
+        <f t="shared" si="3"/>
+        <v>4.8</v>
+      </c>
+      <c r="I66" s="5">
+        <f t="shared" si="4"/>
+        <v>5.76</v>
       </c>
       <c r="J66" s="3"/>
       <c r="K66" s="3" t="s">
@@ -3168,19 +3183,22 @@
         <v>68</v>
       </c>
       <c r="E67" s="5">
-        <v>4.9999999999999998E-7</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G67" s="5">
-        <v>3.9999999999999998E-7</v>
+        <f t="shared" si="2"/>
+        <v>2.1120000000000004E-4</v>
       </c>
       <c r="H67" s="5">
-        <v>4.9999999999999998E-7</v>
+        <f t="shared" si="3"/>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="I67" s="5">
-        <v>5.9999999999999997E-7</v>
+        <f t="shared" si="4"/>
+        <v>3.168E-4</v>
       </c>
       <c r="J67" s="3"/>
       <c r="K67" s="3" t="s">
@@ -3206,13 +3224,16 @@
       <c r="F68" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G68" s="3">
+      <c r="G68" s="5">
+        <f t="shared" si="2"/>
         <v>2.2559999999999998</v>
       </c>
-      <c r="H68" s="3">
+      <c r="H68" s="5">
+        <f t="shared" si="3"/>
         <v>2.82</v>
       </c>
-      <c r="I68" s="3">
+      <c r="I68" s="5">
+        <f t="shared" si="4"/>
         <v>3.3839999999999999</v>
       </c>
       <c r="J68" s="3"/>
@@ -3239,13 +3260,16 @@
       <c r="F69" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G69" s="3">
-        <v>0.01</v>
-      </c>
-      <c r="H69" s="3">
+      <c r="G69" s="5">
+        <f t="shared" si="2"/>
+        <v>1.0000000000000002E-2</v>
+      </c>
+      <c r="H69" s="5">
+        <f t="shared" si="3"/>
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="I69" s="3">
+      <c r="I69" s="5">
+        <f t="shared" si="4"/>
         <v>1.4999999999999999E-2</v>
       </c>
       <c r="J69" s="3"/>
@@ -3272,13 +3296,16 @@
       <c r="F70" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G70" s="3">
-        <v>2.7199999999999998E-2</v>
-      </c>
-      <c r="H70" s="3">
+      <c r="G70" s="5">
+        <f t="shared" si="2"/>
+        <v>2.7200000000000002E-2</v>
+      </c>
+      <c r="H70" s="5">
+        <f t="shared" si="3"/>
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="I70" s="3">
+      <c r="I70" s="5">
+        <f t="shared" si="4"/>
         <v>4.0800000000000003E-2</v>
       </c>
       <c r="J70" s="3"/>
@@ -3305,13 +3332,16 @@
       <c r="F71" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G71" s="3">
+      <c r="G71" s="5">
+        <f t="shared" si="2"/>
         <v>4.5600000000000002E-2</v>
       </c>
-      <c r="H71" s="3">
+      <c r="H71" s="5">
+        <f t="shared" si="3"/>
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="I71" s="3">
+      <c r="I71" s="5">
+        <f t="shared" si="4"/>
         <v>6.8400000000000002E-2</v>
       </c>
       <c r="J71" s="3"/>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saran\Documents\Academia\repository_clones\Bioindustrial-Park\biorefineries\isobutanol\analyses\full\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F5DFA2F0-F27E-4C41-BAE0-91FE305C4645}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80504B7F-8307-4EBD-AD6D-9F15F4518404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="431" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="190">
   <si>
     <t>Parameter name</t>
   </si>
@@ -588,6 +588,24 @@
   </si>
   <si>
     <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
+  </si>
+  <si>
+    <t>DDGS price</t>
+  </si>
+  <si>
+    <t>DDGS.price =x</t>
+  </si>
+  <si>
+    <t>Isobutanol price</t>
+  </si>
+  <si>
+    <t>V514.isobutanol_price = x</t>
+  </si>
+  <si>
+    <t>Isopentyl acetate price</t>
+  </si>
+  <si>
+    <t>makeup_isopentyl_acetate.price = x</t>
   </si>
 </sst>
 </file>
@@ -950,7 +968,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K71"/>
+  <dimension ref="A1:K74"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40.81640625" customWidth="1"/>
@@ -1151,12 +1169,12 @@
         <v>18</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" ref="G6:G11" si="0">E6*0.8</f>
+        <f t="shared" ref="G6:G14" si="0">E6*0.8</f>
         <v>0.35920000000000002</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4">
-        <f t="shared" ref="I6:I11" si="1">1.2*E6</f>
+        <f t="shared" ref="I6:I14" si="1">1.2*E6</f>
         <v>0.53879999999999995</v>
       </c>
       <c r="J6" s="4"/>
@@ -1330,348 +1348,348 @@
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A12" s="6" t="s">
+      <c r="A12" s="4" t="s">
+        <v>184</v>
+      </c>
+      <c r="B12" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C12" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D12" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E12" s="4">
+        <v>0.12</v>
+      </c>
+      <c r="F12" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G12" s="4">
+        <f t="shared" si="0"/>
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="H12" s="4"/>
+      <c r="I12" s="4">
+        <f t="shared" si="1"/>
+        <v>0.14399999999999999</v>
+      </c>
+      <c r="J12" s="4"/>
+      <c r="K12" s="4" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A13" s="4" t="s">
+        <v>186</v>
+      </c>
+      <c r="B13" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C13" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D13" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E13" s="4">
+        <v>1.43</v>
+      </c>
+      <c r="F13" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G13" s="4">
+        <f t="shared" si="0"/>
+        <v>1.1439999999999999</v>
+      </c>
+      <c r="H13" s="4"/>
+      <c r="I13" s="4">
+        <f t="shared" si="1"/>
+        <v>1.716</v>
+      </c>
+      <c r="J13" s="4"/>
+      <c r="K13" s="4" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A14" s="4" t="s">
+        <v>188</v>
+      </c>
+      <c r="B14" s="4" t="s">
+        <v>7</v>
+      </c>
+      <c r="C14" s="4" t="s">
+        <v>20</v>
+      </c>
+      <c r="D14" s="4" t="s">
+        <v>10</v>
+      </c>
+      <c r="E14" s="4">
+        <v>3.2</v>
+      </c>
+      <c r="F14" s="4" t="s">
+        <v>18</v>
+      </c>
+      <c r="G14" s="4">
+        <f t="shared" si="0"/>
+        <v>2.5600000000000005</v>
+      </c>
+      <c r="H14" s="4"/>
+      <c r="I14" s="4">
+        <f t="shared" si="1"/>
+        <v>3.84</v>
+      </c>
+      <c r="J14" s="4"/>
+      <c r="K14" s="4" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A15" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="B12" s="6" t="s">
+      <c r="B15" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C12" s="6" t="s">
+      <c r="C15" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D12" s="6" t="s">
+      <c r="D15" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E12" s="6">
+      <c r="E15" s="6">
         <v>0.28599999999999998</v>
       </c>
-      <c r="F12" s="6" t="s">
+      <c r="F15" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G12" s="6">
+      <c r="G15" s="6">
         <v>0.17499999999999999</v>
       </c>
-      <c r="H12" s="6">
+      <c r="H15" s="6">
         <v>0.28599999999999998</v>
       </c>
-      <c r="I12" s="6">
+      <c r="I15" s="6">
         <v>0.315</v>
       </c>
-      <c r="J12" s="6"/>
-      <c r="K12" s="6" t="s">
+      <c r="J15" s="6"/>
+      <c r="K15" s="6" t="s">
         <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A13" s="6" t="s">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A16" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="B13" s="6" t="s">
+      <c r="B16" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="6" t="s">
+      <c r="C16" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="6" t="s">
+      <c r="D16" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="6">
+      <c r="E16" s="6">
         <v>0.10355</v>
       </c>
-      <c r="F13" s="6" t="s">
+      <c r="F16" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="G13" s="6">
-        <f>E13*0.9</f>
+      <c r="G16" s="6">
+        <f>E16*0.9</f>
         <v>9.3195E-2</v>
       </c>
-      <c r="H13" s="6">
-        <f>E13</f>
+      <c r="H16" s="6">
+        <f>E16</f>
         <v>0.10355</v>
       </c>
-      <c r="I13" s="6">
-        <f>E13*1.1</f>
+      <c r="I16" s="6">
+        <f>E16*1.1</f>
         <v>0.11390500000000001</v>
       </c>
-      <c r="J13" s="6"/>
-      <c r="K13" s="6" t="s">
+      <c r="J16" s="6"/>
+      <c r="K16" s="6" t="s">
         <v>87</v>
-      </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="3" t="s">
-        <v>31</v>
-      </c>
-      <c r="B14" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C14" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E14" s="3">
-        <v>0.21</v>
-      </c>
-      <c r="F14" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="H14" s="3"/>
-      <c r="I14" s="3">
-        <v>0.28000000000000003</v>
-      </c>
-      <c r="J14" s="3"/>
-      <c r="K14" s="3" t="s">
-        <v>34</v>
-      </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A15" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B15" s="3" t="s">
-        <v>7</v>
-      </c>
-      <c r="C15" s="3" t="s">
-        <v>20</v>
-      </c>
-      <c r="D15" s="3" t="s">
-        <v>8</v>
-      </c>
-      <c r="E15" s="3">
-        <v>0.15</v>
-      </c>
-      <c r="F15" s="3" t="s">
-        <v>18</v>
-      </c>
-      <c r="G15" s="3">
-        <f>0.8*E15</f>
-        <v>0.12</v>
-      </c>
-      <c r="H15" s="3"/>
-      <c r="I15" s="3">
-        <f>1.2*E15</f>
-        <v>0.18</v>
-      </c>
-      <c r="J15" s="3"/>
-      <c r="K15" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="3" t="s">
-        <v>38</v>
-      </c>
-      <c r="B16" s="3" t="s">
-        <v>39</v>
-      </c>
-      <c r="C16" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D16" s="3" t="s">
-        <v>40</v>
-      </c>
-      <c r="E16" s="3">
-        <v>56972</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="3">
-        <f>0.8*H16</f>
-        <v>45577.600000000006</v>
-      </c>
-      <c r="H16" s="3">
-        <f>E16</f>
-        <v>56972</v>
-      </c>
-      <c r="I16" s="3">
-        <f>1.2*H16</f>
-        <v>68366.399999999994</v>
-      </c>
-      <c r="J16" s="3"/>
-      <c r="K16" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>53</v>
+        <v>31</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E17" s="3">
-        <v>156</v>
+        <v>0.21</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G17" s="3">
-        <f>E17*0.8</f>
-        <v>124.80000000000001</v>
-      </c>
-      <c r="H17" s="3">
-        <f>E17</f>
-        <v>156</v>
-      </c>
+        <v>0.15</v>
+      </c>
+      <c r="H17" s="3"/>
       <c r="I17" s="3">
-        <f>E17*1.2</f>
-        <v>187.2</v>
+        <v>0.28000000000000003</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
-        <v>55</v>
+        <v>34</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>54</v>
+        <v>32</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>13</v>
+        <v>7</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="E18" s="3">
-        <v>156</v>
+        <v>0.15</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G18" s="3">
-        <f>E18*0.8</f>
-        <v>124.80000000000001</v>
-      </c>
-      <c r="H18" s="3">
-        <f>E18</f>
-        <v>156</v>
-      </c>
+        <f>0.8*E18</f>
+        <v>0.12</v>
+      </c>
+      <c r="H18" s="3"/>
       <c r="I18" s="3">
-        <f>E18*1.2</f>
-        <v>187.2</v>
+        <f>1.2*E18</f>
+        <v>0.18</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>56</v>
+        <v>33</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>123</v>
+        <v>38</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>149</v>
+        <v>39</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>66</v>
+        <v>40</v>
       </c>
       <c r="E19" s="3">
-        <v>1.43</v>
+        <v>56972</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3">
-        <v>1.1439999999999999</v>
+        <f>0.8*H19</f>
+        <v>45577.600000000006</v>
       </c>
       <c r="H19" s="3">
-        <v>1.43</v>
+        <f>E19</f>
+        <v>56972</v>
       </c>
       <c r="I19" s="3">
-        <v>1.716</v>
+        <f>1.2*H19</f>
+        <v>68366.399999999994</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
-        <v>63</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>106</v>
+        <v>53</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>149</v>
+        <v>13</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="E20" s="3">
-        <v>0.94</v>
+        <v>156</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3">
-        <v>0.752</v>
+        <f>E20*0.8</f>
+        <v>124.80000000000001</v>
       </c>
       <c r="H20" s="3">
-        <v>0.94</v>
+        <f>E20</f>
+        <v>156</v>
       </c>
       <c r="I20" s="3">
-        <v>1.1279999999999999</v>
+        <f>E20*1.2</f>
+        <v>187.2</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3" t="s">
-        <v>88</v>
+        <v>55</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>124</v>
+        <v>54</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>149</v>
+        <v>13</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="E21" s="3">
-        <v>0.58399999999999996</v>
+        <v>156</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="G21" s="3">
-        <v>0.4672</v>
+        <f>E21*0.8</f>
+        <v>124.80000000000001</v>
       </c>
       <c r="H21" s="3">
-        <v>0.58399999999999996</v>
+        <f>E21</f>
+        <v>156</v>
       </c>
       <c r="I21" s="3">
-        <v>0.70079999999999998</v>
+        <f>E21*1.2</f>
+        <v>187.2</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>149</v>
@@ -1680,31 +1698,31 @@
         <v>21</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E22" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>1.43</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G22" s="3">
-        <v>9.2800000000000001E-3</v>
+        <v>1.1439999999999999</v>
       </c>
       <c r="H22" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>1.43</v>
       </c>
       <c r="I22" s="3">
-        <v>1.3919999999999899E-2</v>
+        <v>1.716</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>89</v>
+        <v>63</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>149</v>
@@ -1713,31 +1731,31 @@
         <v>21</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E23" s="3">
-        <v>47.1</v>
+        <v>0.94</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G23" s="3">
-        <v>37.68</v>
+        <v>0.752</v>
       </c>
       <c r="H23" s="3">
-        <v>47.1</v>
+        <v>0.94</v>
       </c>
       <c r="I23" s="3">
-        <v>56.52</v>
+        <v>1.1279999999999999</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>108</v>
+        <v>124</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>149</v>
@@ -1746,31 +1764,31 @@
         <v>21</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E24" s="3">
-        <v>14.2</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G24" s="3">
-        <v>11.36</v>
+        <v>0.4672</v>
       </c>
       <c r="H24" s="3">
-        <v>14.2</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="I24" s="3">
-        <v>17.04</v>
+        <v>0.70079999999999998</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>109</v>
+        <v>107</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>149</v>
@@ -1782,28 +1800,28 @@
         <v>68</v>
       </c>
       <c r="E25" s="3">
-        <v>0.12</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G25" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>9.2800000000000001E-3</v>
       </c>
       <c r="H25" s="3">
-        <v>0.12</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="I25" s="3">
-        <v>0.14399999999999999</v>
+        <v>1.3919999999999899E-2</v>
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3" t="s">
-        <v>91</v>
+        <v>89</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>149</v>
@@ -1815,28 +1833,28 @@
         <v>66</v>
       </c>
       <c r="E26" s="3">
-        <v>0.04</v>
+        <v>47.1</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G26" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>37.68</v>
       </c>
       <c r="H26" s="3">
-        <v>0.04</v>
+        <v>47.1</v>
       </c>
       <c r="I26" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>56.52</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="s">
-        <v>60</v>
+        <v>58</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>149</v>
@@ -1845,31 +1863,31 @@
         <v>21</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E27" s="3">
-        <v>0.12</v>
+        <v>14.2</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G27" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>11.36</v>
       </c>
       <c r="H27" s="3">
-        <v>0.12</v>
+        <v>14.2</v>
       </c>
       <c r="I27" s="3">
-        <v>0.14399999999999999</v>
+        <v>17.04</v>
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3" t="s">
-        <v>61</v>
+        <v>90</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>128</v>
+        <v>109</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>149</v>
@@ -1878,34 +1896,34 @@
         <v>21</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E28" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G28" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H28" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I28" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>62</v>
+        <v>91</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>129</v>
+        <v>126</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>21</v>
@@ -1914,97 +1932,97 @@
         <v>66</v>
       </c>
       <c r="E29" s="3">
-        <v>0.501</v>
+        <v>0.04</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G29" s="3">
-        <v>0.40079999999999999</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H29" s="3">
-        <v>0.501</v>
+        <v>0.04</v>
       </c>
       <c r="I29" s="3">
-        <v>0.60119999999999996</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3" t="s">
-        <v>57</v>
+        <v>60</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>110</v>
+        <v>127</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E30" s="5">
-        <v>2.0000000000000002E-5</v>
+        <v>66</v>
+      </c>
+      <c r="E30" s="3">
+        <v>0.12</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G30" s="5">
-        <v>1.5999999999999999E-5</v>
-      </c>
-      <c r="H30" s="5">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="I30" s="5">
-        <v>2.4000000000000001E-5</v>
+      <c r="G30" s="3">
+        <v>9.6000000000000002E-2</v>
+      </c>
+      <c r="H30" s="3">
+        <v>0.12</v>
+      </c>
+      <c r="I30" s="3">
+        <v>0.14399999999999999</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3" t="s">
-        <v>92</v>
+        <v>61</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E31" s="3">
-        <v>0.10100000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G31" s="3">
-        <v>8.0799999999999997E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H31" s="3">
-        <v>0.10100000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="I31" s="3">
-        <v>0.1212</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3" t="s">
-        <v>93</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>21</v>
@@ -2013,31 +2031,31 @@
         <v>66</v>
       </c>
       <c r="E32" s="3">
-        <v>5.81</v>
+        <v>0.501</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G32" s="3">
-        <v>4.6479999999999997</v>
+        <v>0.40079999999999999</v>
       </c>
       <c r="H32" s="3">
-        <v>5.81</v>
+        <v>0.501</v>
       </c>
       <c r="I32" s="3">
-        <v>6.9719999999999898</v>
+        <v>0.60119999999999996</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3" t="s">
-        <v>64</v>
+        <v>57</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>112</v>
+        <v>110</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>21</v>
@@ -2046,64 +2064,64 @@
         <v>68</v>
       </c>
       <c r="E33" s="5">
-        <v>4.9999999999999998E-7</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G33" s="5">
-        <v>3.9999999999999998E-7</v>
+        <v>1.5999999999999999E-5</v>
       </c>
       <c r="H33" s="5">
-        <v>4.9999999999999998E-7</v>
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="I33" s="5">
-        <v>5.9999999999999997E-7</v>
+        <v>2.4000000000000001E-5</v>
       </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3" t="s">
-        <v>94</v>
+        <v>92</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>131</v>
+        <v>111</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E34" s="3">
-        <v>4.8</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G34" s="3">
-        <v>3.84</v>
+        <v>8.0799999999999997E-2</v>
       </c>
       <c r="H34" s="3">
-        <v>4.8</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="I34" s="3">
-        <v>5.76</v>
+        <v>0.1212</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>65</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>132</v>
+        <v>130</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>21</v>
@@ -2112,61 +2130,61 @@
         <v>66</v>
       </c>
       <c r="E35" s="3">
-        <v>0.04</v>
+        <v>5.81</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G35" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>4.6479999999999997</v>
       </c>
       <c r="H35" s="3">
-        <v>0.04</v>
+        <v>5.81</v>
       </c>
       <c r="I35" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>6.9719999999999898</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3" t="s">
-        <v>69</v>
+        <v>64</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E36" s="3">
-        <v>0.12</v>
+        <v>68</v>
+      </c>
+      <c r="E36" s="5">
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G36" s="3">
-        <v>9.6000000000000002E-2</v>
-      </c>
-      <c r="H36" s="3">
-        <v>0.12</v>
-      </c>
-      <c r="I36" s="3">
-        <v>0.14399999999999999</v>
+      <c r="G36" s="5">
+        <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="H36" s="5">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="I36" s="5">
+        <v>5.9999999999999997E-7</v>
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="3" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>134</v>
+        <v>131</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>152</v>
@@ -2178,28 +2196,28 @@
         <v>66</v>
       </c>
       <c r="E37" s="3">
-        <v>0.04</v>
+        <v>4.8</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G37" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>3.84</v>
       </c>
       <c r="H37" s="3">
-        <v>0.04</v>
+        <v>4.8</v>
       </c>
       <c r="I37" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>5.76</v>
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3" t="s">
-        <v>71</v>
+        <v>65</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>113</v>
+        <v>132</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>152</v>
@@ -2208,34 +2226,34 @@
         <v>21</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E38" s="3">
-        <v>2.6400000000000002E-4</v>
+        <v>0.04</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G38" s="3">
-        <v>2.1120000000000001E-4</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H38" s="3">
-        <v>2.6400000000000002E-4</v>
+        <v>0.04</v>
       </c>
       <c r="I38" s="3">
-        <v>3.168E-4</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>21</v>
@@ -2244,94 +2262,94 @@
         <v>66</v>
       </c>
       <c r="E39" s="3">
-        <v>1.04E-2</v>
+        <v>0.12</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G39" s="3">
-        <v>8.3199999999999993E-3</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H39" s="3">
-        <v>1.04E-2</v>
+        <v>0.12</v>
       </c>
       <c r="I39" s="3">
-        <v>1.248E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3" t="s">
-        <v>72</v>
+        <v>70</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E40" s="3">
-        <v>1.0200000000000001E-2</v>
+        <v>0.04</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G40" s="3">
-        <v>8.1600000000000006E-3</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H40" s="3">
-        <v>1.0200000000000001E-2</v>
+        <v>0.04</v>
       </c>
       <c r="I40" s="3">
-        <v>1.2239999999999999E-2</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3" t="s">
-        <v>96</v>
+        <v>71</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E41" s="3">
-        <v>0.77500000000000002</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G41" s="3">
-        <v>0.62</v>
+        <v>2.1120000000000001E-4</v>
       </c>
       <c r="H41" s="3">
-        <v>0.77500000000000002</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="I41" s="3">
-        <v>0.92999999999999905</v>
+        <v>3.168E-4</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>73</v>
+        <v>95</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>115</v>
+        <v>135</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>157</v>
@@ -2340,31 +2358,31 @@
         <v>21</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E42" s="3">
-        <v>0.1</v>
+        <v>1.04E-2</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G42" s="3">
-        <v>0.08</v>
+        <v>8.3199999999999993E-3</v>
       </c>
       <c r="H42" s="3">
-        <v>0.1</v>
+        <v>1.04E-2</v>
       </c>
       <c r="I42" s="3">
-        <v>0.12</v>
+        <v>1.248E-2</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3" t="s">
-        <v>97</v>
+        <v>72</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>157</v>
@@ -2376,31 +2394,31 @@
         <v>68</v>
       </c>
       <c r="E43" s="3">
-        <v>440</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G43" s="3">
-        <v>352</v>
+        <v>8.1600000000000006E-3</v>
       </c>
       <c r="H43" s="3">
-        <v>440</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="I43" s="3">
-        <v>528</v>
+        <v>1.2239999999999999E-2</v>
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>21</v>
@@ -2409,64 +2427,64 @@
         <v>66</v>
       </c>
       <c r="E44" s="3">
-        <v>2.82</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G44" s="3">
-        <v>2.2559999999999998</v>
+        <v>0.62</v>
       </c>
       <c r="H44" s="3">
-        <v>2.82</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="I44" s="3">
-        <v>3.3839999999999999</v>
+        <v>0.92999999999999905</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E45" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>0.1</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G45" s="3">
-        <v>0.01</v>
+        <v>0.08</v>
       </c>
       <c r="H45" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>0.1</v>
       </c>
       <c r="I45" s="3">
-        <v>1.4999999999999999E-2</v>
+        <v>0.12</v>
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3" t="s">
-        <v>75</v>
+        <v>97</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>21</v>
@@ -2475,28 +2493,28 @@
         <v>68</v>
       </c>
       <c r="E46" s="3">
-        <v>3.4000000000000002E-2</v>
+        <v>440</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G46" s="3">
-        <v>2.7199999999999998E-2</v>
+        <v>352</v>
       </c>
       <c r="H46" s="3">
-        <v>3.4000000000000002E-2</v>
+        <v>440</v>
       </c>
       <c r="I46" s="3">
-        <v>4.0800000000000003E-2</v>
+        <v>528</v>
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>153</v>
@@ -2505,34 +2523,34 @@
         <v>21</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E47" s="3">
-        <v>5.7000000000000002E-2</v>
+        <v>2.82</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G47" s="3">
-        <v>4.5600000000000002E-2</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="H47" s="3">
-        <v>5.7000000000000002E-2</v>
+        <v>2.82</v>
       </c>
       <c r="I47" s="3">
-        <v>6.8400000000000002E-2</v>
+        <v>3.3839999999999999</v>
       </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3" t="s">
-        <v>100</v>
+        <v>74</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>21</v>
@@ -2541,94 +2559,94 @@
         <v>66</v>
       </c>
       <c r="E48" s="3">
-        <v>1.2030000000000001</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G48" s="3">
-        <v>0.96240000000000003</v>
+        <v>0.01</v>
       </c>
       <c r="H48" s="3">
-        <v>1.2030000000000001</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="I48" s="3">
-        <v>1.4436</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="3" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E49" s="3">
-        <v>0.04</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G49" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>2.7199999999999998E-2</v>
       </c>
       <c r="H49" s="3">
-        <v>0.04</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="I49" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="3" t="s">
-        <v>77</v>
+        <v>99</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>141</v>
+        <v>118</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E50" s="3">
-        <v>0.12</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G50" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>4.5600000000000002E-2</v>
       </c>
       <c r="H50" s="3">
-        <v>0.12</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="I50" s="3">
-        <v>0.14399999999999999</v>
+        <v>6.8400000000000002E-2</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>142</v>
+        <v>139</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>154</v>
@@ -2640,28 +2658,28 @@
         <v>66</v>
       </c>
       <c r="E51" s="3">
-        <v>0.04</v>
+        <v>1.2030000000000001</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G51" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>0.96240000000000003</v>
       </c>
       <c r="H51" s="3">
-        <v>0.04</v>
+        <v>1.2030000000000001</v>
       </c>
       <c r="I51" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>1.4436</v>
       </c>
       <c r="J51" s="3"/>
       <c r="K51" s="3" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
-        <v>119</v>
+        <v>140</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>154</v>
@@ -2670,34 +2688,34 @@
         <v>21</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E52" s="3">
-        <v>1.01E-2</v>
+        <v>0.04</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G52" s="3">
-        <v>8.0800000000000004E-3</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H52" s="3">
-        <v>1.01E-2</v>
+        <v>0.04</v>
       </c>
       <c r="I52" s="3">
-        <v>1.21199999999999E-2</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
-        <v>101</v>
+        <v>77</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>21</v>
@@ -2706,31 +2724,31 @@
         <v>66</v>
       </c>
       <c r="E53" s="3">
-        <v>0.58899999999999997</v>
+        <v>0.12</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G53" s="3">
-        <v>0.47120000000000001</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H53" s="3">
-        <v>0.58899999999999997</v>
+        <v>0.12</v>
       </c>
       <c r="I53" s="3">
-        <v>0.70679999999999998</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>80</v>
+        <v>78</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>144</v>
+        <v>142</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>21</v>
@@ -2739,31 +2757,31 @@
         <v>66</v>
       </c>
       <c r="E54" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>0.04</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G54" s="3">
-        <v>6.4000000000000003E-3</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H54" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>0.04</v>
       </c>
       <c r="I54" s="3">
-        <v>9.5999999999999992E-3</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>81</v>
+        <v>79</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>21</v>
@@ -2771,32 +2789,32 @@
       <c r="D55" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E55" s="5">
-        <v>9.9999999999999995E-7</v>
+      <c r="E55" s="3">
+        <v>1.01E-2</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G55" s="5">
-        <v>7.9999999999999996E-7</v>
-      </c>
-      <c r="H55" s="5">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="I55" s="5">
-        <v>1.1999999999999999E-6</v>
+      <c r="G55" s="3">
+        <v>8.0800000000000004E-3</v>
+      </c>
+      <c r="H55" s="3">
+        <v>1.01E-2</v>
+      </c>
+      <c r="I55" s="3">
+        <v>1.21199999999999E-2</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>21</v>
@@ -2805,28 +2823,28 @@
         <v>66</v>
       </c>
       <c r="E56" s="3">
-        <v>7.51E-2</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G56" s="3">
-        <v>6.0080000000000001E-2</v>
+        <v>0.47120000000000001</v>
       </c>
       <c r="H56" s="3">
-        <v>7.51E-2</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="I56" s="3">
-        <v>9.0119999999999895E-2</v>
+        <v>0.70679999999999998</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>82</v>
+        <v>80</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>121</v>
+        <v>144</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>156</v>
@@ -2835,31 +2853,31 @@
         <v>21</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E57" s="3">
-        <v>13</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G57" s="3">
-        <v>10.4</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="H57" s="3">
-        <v>13</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="I57" s="3">
-        <v>15.6</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="J57" s="3"/>
       <c r="K57" s="3" t="s">
-        <v>103</v>
+        <v>81</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>122</v>
+        <v>120</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>156</v>
@@ -2870,29 +2888,29 @@
       <c r="D58" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E58" s="3">
-        <v>25</v>
+      <c r="E58" s="5">
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G58" s="3">
-        <v>20</v>
-      </c>
-      <c r="H58" s="3">
-        <v>25</v>
-      </c>
-      <c r="I58" s="3">
-        <v>30</v>
+      <c r="G58" s="5">
+        <v>7.9999999999999996E-7</v>
+      </c>
+      <c r="H58" s="5">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="I58" s="5">
+        <v>1.1999999999999999E-6</v>
       </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3" t="s">
-        <v>104</v>
+        <v>102</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>156</v>
@@ -2904,97 +2922,97 @@
         <v>66</v>
       </c>
       <c r="E59" s="3">
-        <v>3.9899999999999996E-3</v>
+        <v>7.51E-2</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G59" s="3">
-        <v>3.192E-3</v>
+        <v>6.0080000000000001E-2</v>
       </c>
       <c r="H59" s="3">
-        <v>3.9899999999999996E-3</v>
+        <v>7.51E-2</v>
       </c>
       <c r="I59" s="3">
-        <v>4.7879999999999997E-3</v>
+        <v>9.0119999999999895E-2</v>
       </c>
       <c r="J59" s="3"/>
       <c r="K59" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
-        <v>147</v>
+        <v>121</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E60" s="3">
-        <v>0.06</v>
+        <v>13</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G60" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>10.4</v>
       </c>
       <c r="H60" s="3">
-        <v>0.06</v>
+        <v>13</v>
       </c>
       <c r="I60" s="3">
-        <v>7.1999999999999995E-2</v>
+        <v>15.6</v>
       </c>
       <c r="J60" s="3"/>
       <c r="K60" s="3" t="s">
-        <v>84</v>
+        <v>103</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>148</v>
+        <v>122</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E61" s="3">
-        <v>0.02</v>
+        <v>25</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G61" s="3">
-        <v>1.6E-2</v>
+        <v>20</v>
       </c>
       <c r="H61" s="3">
-        <v>0.02</v>
+        <v>25</v>
       </c>
       <c r="I61" s="3">
-        <v>2.4E-2</v>
+        <v>30</v>
       </c>
       <c r="J61" s="3"/>
       <c r="K61" s="3" t="s">
-        <v>85</v>
+        <v>104</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
-        <v>160</v>
+        <v>146</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>180</v>
+        <v>156</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>21</v>
@@ -3003,70 +3021,64 @@
         <v>66</v>
       </c>
       <c r="E62" s="3">
-        <v>5.81</v>
+        <v>3.9899999999999996E-3</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G62" s="5">
-        <f>E62*0.8</f>
-        <v>4.6479999999999997</v>
-      </c>
-      <c r="H62" s="5">
-        <f>E62</f>
-        <v>5.81</v>
-      </c>
-      <c r="I62" s="5">
-        <f>1.2*E62</f>
-        <v>6.9719999999999995</v>
+      <c r="G62" s="3">
+        <v>3.192E-3</v>
+      </c>
+      <c r="H62" s="3">
+        <v>3.9899999999999996E-3</v>
+      </c>
+      <c r="I62" s="3">
+        <v>4.7879999999999997E-3</v>
       </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3" t="s">
-        <v>161</v>
+        <v>83</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
-        <v>162</v>
+        <v>147</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>180</v>
+        <v>158</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E63" s="5">
-        <v>4.9999999999999998E-7</v>
+        <v>66</v>
+      </c>
+      <c r="E63" s="3">
+        <v>0.06</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G63" s="5">
-        <f>E63*0.8</f>
-        <v>3.9999999999999998E-7</v>
-      </c>
-      <c r="H63" s="5">
-        <f>E63</f>
-        <v>4.9999999999999998E-7</v>
-      </c>
-      <c r="I63" s="5">
-        <f>1.2*E63</f>
-        <v>5.9999999999999997E-7</v>
+      <c r="G63" s="3">
+        <v>4.8000000000000001E-2</v>
+      </c>
+      <c r="H63" s="3">
+        <v>0.06</v>
+      </c>
+      <c r="I63" s="3">
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="J63" s="3"/>
       <c r="K63" s="3" t="s">
-        <v>163</v>
+        <v>84</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
-        <v>164</v>
+        <v>148</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>181</v>
+        <v>159</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>21</v>
@@ -3075,277 +3087,382 @@
         <v>66</v>
       </c>
       <c r="E64" s="3">
-        <v>4.8</v>
+        <v>0.02</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G64" s="5">
-        <f t="shared" ref="G64:G71" si="2">E64*0.8</f>
-        <v>3.84</v>
-      </c>
-      <c r="H64" s="5">
-        <f t="shared" ref="H64:H71" si="3">E64</f>
-        <v>4.8</v>
-      </c>
-      <c r="I64" s="5">
-        <f t="shared" ref="I64:I71" si="4">1.2*E64</f>
-        <v>5.76</v>
+      <c r="G64" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="H64" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I64" s="3">
+        <v>2.4E-2</v>
       </c>
       <c r="J64" s="3"/>
       <c r="K64" s="3" t="s">
-        <v>165</v>
+        <v>85</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
+        <v>160</v>
+      </c>
+      <c r="B65" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C65" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D65" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E65" s="3">
+        <v>5.81</v>
+      </c>
+      <c r="F65" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G65" s="5">
+        <f>E65*0.8</f>
+        <v>4.6479999999999997</v>
+      </c>
+      <c r="H65" s="5">
+        <f>E65</f>
+        <v>5.81</v>
+      </c>
+      <c r="I65" s="5">
+        <f>1.2*E65</f>
+        <v>6.9719999999999995</v>
+      </c>
+      <c r="J65" s="3"/>
+      <c r="K65" s="3" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A66" s="3" t="s">
+        <v>162</v>
+      </c>
+      <c r="B66" s="3" t="s">
+        <v>180</v>
+      </c>
+      <c r="C66" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D66" s="3" t="s">
+        <v>68</v>
+      </c>
+      <c r="E66" s="5">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="F66" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G66" s="5">
+        <f>E66*0.8</f>
+        <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="H66" s="5">
+        <f>E66</f>
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="I66" s="5">
+        <f>1.2*E66</f>
+        <v>5.9999999999999997E-7</v>
+      </c>
+      <c r="J66" s="3"/>
+      <c r="K66" s="3" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A67" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="B67" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C67" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D67" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E67" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="F67" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G67" s="5">
+        <f t="shared" ref="G67:G74" si="2">E67*0.8</f>
+        <v>3.84</v>
+      </c>
+      <c r="H67" s="5">
+        <f t="shared" ref="H67:H74" si="3">E67</f>
+        <v>4.8</v>
+      </c>
+      <c r="I67" s="5">
+        <f t="shared" ref="I67:I74" si="4">1.2*E67</f>
+        <v>5.76</v>
+      </c>
+      <c r="J67" s="3"/>
+      <c r="K67" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A68" s="3" t="s">
         <v>166</v>
       </c>
-      <c r="B65" s="3" t="s">
+      <c r="B68" s="3" t="s">
         <v>181</v>
       </c>
-      <c r="C65" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D65" s="3" t="s">
+      <c r="C68" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E65" s="5">
+      <c r="E68" s="5">
         <v>2.6400000000000002E-4</v>
       </c>
-      <c r="F65" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G65" s="5">
+      <c r="F68" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G68" s="5">
         <f t="shared" si="2"/>
         <v>2.1120000000000004E-4</v>
       </c>
-      <c r="H65" s="5">
+      <c r="H68" s="5">
         <f t="shared" si="3"/>
         <v>2.6400000000000002E-4</v>
       </c>
-      <c r="I65" s="5">
+      <c r="I68" s="5">
         <f t="shared" si="4"/>
         <v>3.168E-4</v>
       </c>
-      <c r="J65" s="3"/>
-      <c r="K65" s="3" t="s">
+      <c r="J68" s="3"/>
+      <c r="K68" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A66" s="3" t="s">
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A69" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B66" s="3" t="s">
+      <c r="B69" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C66" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D66" s="3" t="s">
+      <c r="C69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E66" s="3">
+      <c r="E69" s="3">
         <v>4.8</v>
       </c>
-      <c r="F66" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G66" s="5">
+      <c r="F69" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G69" s="5">
         <f t="shared" si="2"/>
         <v>3.84</v>
       </c>
-      <c r="H66" s="5">
+      <c r="H69" s="5">
         <f t="shared" si="3"/>
         <v>4.8</v>
       </c>
-      <c r="I66" s="5">
+      <c r="I69" s="5">
         <f t="shared" si="4"/>
         <v>5.76</v>
       </c>
-      <c r="J66" s="3"/>
-      <c r="K66" s="3" t="s">
+      <c r="J69" s="3"/>
+      <c r="K69" s="3" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A67" s="3" t="s">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A70" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B67" s="3" t="s">
+      <c r="B70" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C67" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D67" s="3" t="s">
+      <c r="C70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E67" s="5">
+      <c r="E70" s="5">
         <v>2.6400000000000002E-4</v>
       </c>
-      <c r="F67" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G67" s="5">
+      <c r="F70" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G70" s="5">
         <f t="shared" si="2"/>
         <v>2.1120000000000004E-4</v>
       </c>
-      <c r="H67" s="5">
+      <c r="H70" s="5">
         <f t="shared" si="3"/>
         <v>2.6400000000000002E-4</v>
       </c>
-      <c r="I67" s="5">
+      <c r="I70" s="5">
         <f t="shared" si="4"/>
         <v>3.168E-4</v>
       </c>
-      <c r="J67" s="3"/>
-      <c r="K67" s="3" t="s">
+      <c r="J70" s="3"/>
+      <c r="K70" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A68" s="3" t="s">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A71" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B68" s="3" t="s">
+      <c r="B71" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C68" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D68" s="3" t="s">
+      <c r="C71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E68" s="3">
+      <c r="E71" s="3">
         <v>2.82</v>
       </c>
-      <c r="F68" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G68" s="5">
+      <c r="F71" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G71" s="5">
         <f t="shared" si="2"/>
         <v>2.2559999999999998</v>
       </c>
-      <c r="H68" s="5">
+      <c r="H71" s="5">
         <f t="shared" si="3"/>
         <v>2.82</v>
       </c>
-      <c r="I68" s="5">
+      <c r="I71" s="5">
         <f t="shared" si="4"/>
         <v>3.3839999999999999</v>
       </c>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3" t="s">
+      <c r="J71" s="3"/>
+      <c r="K71" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="s">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A72" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B72" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D69" s="3" t="s">
+      <c r="C72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E69" s="3">
+      <c r="E72" s="3">
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="F69" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G69" s="5">
+      <c r="F72" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G72" s="5">
         <f t="shared" si="2"/>
         <v>1.0000000000000002E-2</v>
       </c>
-      <c r="H69" s="5">
+      <c r="H72" s="5">
         <f t="shared" si="3"/>
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="I69" s="5">
+      <c r="I72" s="5">
         <f t="shared" si="4"/>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3" t="s">
+      <c r="J72" s="3"/>
+      <c r="K72" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A70" s="3" t="s">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A73" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B73" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D70" s="3" t="s">
+      <c r="C73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E70" s="3">
+      <c r="E73" s="3">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G70" s="5">
+      <c r="F73" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G73" s="5">
         <f t="shared" si="2"/>
         <v>2.7200000000000002E-2</v>
       </c>
-      <c r="H70" s="5">
+      <c r="H73" s="5">
         <f t="shared" si="3"/>
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="I70" s="5">
+      <c r="I73" s="5">
         <f t="shared" si="4"/>
         <v>4.0800000000000003E-2</v>
       </c>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3" t="s">
+      <c r="J73" s="3"/>
+      <c r="K73" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B74" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D71" s="3" t="s">
+      <c r="C74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E71" s="3">
+      <c r="E74" s="3">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G71" s="5">
+      <c r="F74" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G74" s="5">
         <f t="shared" si="2"/>
         <v>4.5600000000000002E-2</v>
       </c>
-      <c r="H71" s="5">
+      <c r="H74" s="5">
         <f t="shared" si="3"/>
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="I71" s="5">
+      <c r="I74" s="5">
         <f t="shared" si="4"/>
         <v>6.8400000000000002E-2</v>
       </c>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3" t="s">
+      <c r="J74" s="3"/>
+      <c r="K74" s="3" t="s">
         <v>179</v>
       </c>
     </row>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saran\Documents\Academia\repository_clones\Bioindustrial-Park\biorefineries\isobutanol\analyses\full\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80504B7F-8307-4EBD-AD6D-9F15F4518404}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E62A783B-9F0A-4072-A673-39C0719C99D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="449" uniqueCount="190">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="193">
   <si>
     <t>Parameter name</t>
   </si>
@@ -606,6 +606,15 @@
   </si>
   <si>
     <t>makeup_isopentyl_acetate.price = x</t>
+  </si>
+  <si>
+    <t>Feedstock starch content</t>
+  </si>
+  <si>
+    <t>kg/kg-water</t>
+  </si>
+  <si>
+    <t>feedstock.imass['Starch'] =x * feedstock.imass['Water']</t>
   </si>
 </sst>
 </file>
@@ -968,7 +977,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K74"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40.81640625" customWidth="1"/>
@@ -1581,7 +1590,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>38</v>
+        <v>190</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -1590,70 +1599,70 @@
         <v>21</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>40</v>
+        <v>191</v>
       </c>
       <c r="E19" s="3">
-        <v>56972</v>
+        <v>4.08</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G19" s="3">
         <f>0.8*H19</f>
-        <v>45577.600000000006</v>
+        <v>3.2640000000000002</v>
       </c>
       <c r="H19" s="3">
         <f>E19</f>
-        <v>56972</v>
+        <v>4.08</v>
       </c>
       <c r="I19" s="3">
         <f>1.2*H19</f>
-        <v>68366.399999999994</v>
+        <v>4.8959999999999999</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
-        <v>41</v>
+        <v>192</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>53</v>
+        <v>38</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>13</v>
+        <v>39</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>14</v>
+        <v>40</v>
       </c>
       <c r="E20" s="3">
-        <v>156</v>
+        <v>56972</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G20" s="3">
-        <f>E20*0.8</f>
-        <v>124.80000000000001</v>
+        <f>0.8*H20</f>
+        <v>45577.600000000006</v>
       </c>
       <c r="H20" s="3">
         <f>E20</f>
-        <v>156</v>
+        <v>56972</v>
       </c>
       <c r="I20" s="3">
-        <f>E20*1.2</f>
-        <v>187.2</v>
+        <f>1.2*H20</f>
+        <v>68366.399999999994</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3" t="s">
-        <v>55</v>
+        <v>41</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>13</v>
@@ -1684,45 +1693,48 @@
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>149</v>
+        <v>13</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="E22" s="3">
-        <v>1.43</v>
+        <v>156</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="G22" s="3">
-        <v>1.1439999999999999</v>
+        <f>E22*0.8</f>
+        <v>124.80000000000001</v>
       </c>
       <c r="H22" s="3">
-        <v>1.43</v>
+        <f>E22</f>
+        <v>156</v>
       </c>
       <c r="I22" s="3">
-        <v>1.716</v>
+        <f>E22*1.2</f>
+        <v>187.2</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>149</v>
@@ -1731,31 +1743,31 @@
         <v>21</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E23" s="3">
-        <v>0.94</v>
+        <v>1.43</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G23" s="3">
-        <v>0.752</v>
+        <v>1.1439999999999999</v>
       </c>
       <c r="H23" s="3">
-        <v>0.94</v>
+        <v>1.43</v>
       </c>
       <c r="I23" s="3">
-        <v>1.1279999999999999</v>
+        <v>1.716</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>149</v>
@@ -1764,31 +1776,31 @@
         <v>21</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E24" s="3">
-        <v>0.58399999999999996</v>
+        <v>0.94</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G24" s="3">
-        <v>0.4672</v>
+        <v>0.752</v>
       </c>
       <c r="H24" s="3">
-        <v>0.58399999999999996</v>
+        <v>0.94</v>
       </c>
       <c r="I24" s="3">
-        <v>0.70079999999999998</v>
+        <v>1.1279999999999999</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>149</v>
@@ -1797,31 +1809,31 @@
         <v>21</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E25" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G25" s="3">
-        <v>9.2800000000000001E-3</v>
+        <v>0.4672</v>
       </c>
       <c r="H25" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="I25" s="3">
-        <v>1.3919999999999899E-2</v>
+        <v>0.70079999999999998</v>
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>149</v>
@@ -1830,31 +1842,31 @@
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E26" s="3">
-        <v>47.1</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G26" s="3">
-        <v>37.68</v>
+        <v>9.2800000000000001E-3</v>
       </c>
       <c r="H26" s="3">
-        <v>47.1</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="I26" s="3">
-        <v>56.52</v>
+        <v>1.3919999999999899E-2</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>149</v>
@@ -1863,31 +1875,31 @@
         <v>21</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E27" s="3">
-        <v>14.2</v>
+        <v>47.1</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G27" s="3">
-        <v>11.36</v>
+        <v>37.68</v>
       </c>
       <c r="H27" s="3">
-        <v>14.2</v>
+        <v>47.1</v>
       </c>
       <c r="I27" s="3">
-        <v>17.04</v>
+        <v>56.52</v>
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>149</v>
@@ -1899,28 +1911,28 @@
         <v>68</v>
       </c>
       <c r="E28" s="3">
-        <v>0.12</v>
+        <v>14.2</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G28" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>11.36</v>
       </c>
       <c r="H28" s="3">
-        <v>0.12</v>
+        <v>14.2</v>
       </c>
       <c r="I28" s="3">
-        <v>0.14399999999999999</v>
+        <v>17.04</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>149</v>
@@ -1929,31 +1941,31 @@
         <v>21</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E29" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G29" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H29" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I29" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>149</v>
@@ -1965,28 +1977,28 @@
         <v>66</v>
       </c>
       <c r="E30" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G30" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H30" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I30" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>149</v>
@@ -1998,31 +2010,31 @@
         <v>66</v>
       </c>
       <c r="E31" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G31" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H31" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I31" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>21</v>
@@ -2031,28 +2043,28 @@
         <v>66</v>
       </c>
       <c r="E32" s="3">
-        <v>0.501</v>
+        <v>0.04</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G32" s="3">
-        <v>0.40079999999999999</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H32" s="3">
-        <v>0.501</v>
+        <v>0.04</v>
       </c>
       <c r="I32" s="3">
-        <v>0.60119999999999996</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>150</v>
@@ -2061,31 +2073,31 @@
         <v>21</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E33" s="5">
-        <v>2.0000000000000002E-5</v>
+        <v>66</v>
+      </c>
+      <c r="E33" s="3">
+        <v>0.501</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G33" s="5">
-        <v>1.5999999999999999E-5</v>
-      </c>
-      <c r="H33" s="5">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="I33" s="5">
-        <v>2.4000000000000001E-5</v>
+      <c r="G33" s="3">
+        <v>0.40079999999999999</v>
+      </c>
+      <c r="H33" s="3">
+        <v>0.501</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0.60119999999999996</v>
       </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>150</v>
@@ -2096,62 +2108,62 @@
       <c r="D34" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E34" s="3">
-        <v>0.10100000000000001</v>
+      <c r="E34" s="5">
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G34" s="3">
-        <v>8.0799999999999997E-2</v>
-      </c>
-      <c r="H34" s="3">
-        <v>0.10100000000000001</v>
-      </c>
-      <c r="I34" s="3">
-        <v>0.1212</v>
+      <c r="G34" s="5">
+        <v>1.5999999999999999E-5</v>
+      </c>
+      <c r="H34" s="5">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="I34" s="5">
+        <v>2.4000000000000001E-5</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E35" s="3">
-        <v>5.81</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G35" s="3">
-        <v>4.6479999999999997</v>
+        <v>8.0799999999999997E-2</v>
       </c>
       <c r="H35" s="3">
-        <v>5.81</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="I35" s="3">
-        <v>6.9719999999999898</v>
+        <v>0.1212</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>151</v>
@@ -2160,64 +2172,64 @@
         <v>21</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E36" s="5">
-        <v>4.9999999999999998E-7</v>
+        <v>66</v>
+      </c>
+      <c r="E36" s="3">
+        <v>5.81</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G36" s="5">
-        <v>3.9999999999999998E-7</v>
-      </c>
-      <c r="H36" s="5">
-        <v>4.9999999999999998E-7</v>
-      </c>
-      <c r="I36" s="5">
-        <v>5.9999999999999997E-7</v>
+      <c r="G36" s="3">
+        <v>4.6479999999999997</v>
+      </c>
+      <c r="H36" s="3">
+        <v>5.81</v>
+      </c>
+      <c r="I36" s="3">
+        <v>6.9719999999999898</v>
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="3" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E37" s="3">
-        <v>4.8</v>
+        <v>68</v>
+      </c>
+      <c r="E37" s="5">
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G37" s="3">
-        <v>3.84</v>
-      </c>
-      <c r="H37" s="3">
-        <v>4.8</v>
-      </c>
-      <c r="I37" s="3">
-        <v>5.76</v>
+      <c r="G37" s="5">
+        <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="H37" s="5">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="I37" s="5">
+        <v>5.9999999999999997E-7</v>
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>152</v>
@@ -2229,28 +2241,28 @@
         <v>66</v>
       </c>
       <c r="E38" s="3">
-        <v>0.04</v>
+        <v>4.8</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G38" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>3.84</v>
       </c>
       <c r="H38" s="3">
-        <v>0.04</v>
+        <v>4.8</v>
       </c>
       <c r="I38" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>5.76</v>
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>152</v>
@@ -2262,28 +2274,28 @@
         <v>66</v>
       </c>
       <c r="E39" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G39" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H39" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I39" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>152</v>
@@ -2295,28 +2307,28 @@
         <v>66</v>
       </c>
       <c r="E40" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G40" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H40" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I40" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>152</v>
@@ -2325,64 +2337,64 @@
         <v>21</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E41" s="3">
-        <v>2.6400000000000002E-4</v>
+        <v>0.04</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G41" s="3">
-        <v>2.1120000000000001E-4</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H41" s="3">
-        <v>2.6400000000000002E-4</v>
+        <v>0.04</v>
       </c>
       <c r="I41" s="3">
-        <v>3.168E-4</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E42" s="3">
-        <v>1.04E-2</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G42" s="3">
-        <v>8.3199999999999993E-3</v>
+        <v>2.1120000000000001E-4</v>
       </c>
       <c r="H42" s="3">
-        <v>1.04E-2</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="I42" s="3">
-        <v>1.248E-2</v>
+        <v>3.168E-4</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>157</v>
@@ -2391,31 +2403,31 @@
         <v>21</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E43" s="3">
-        <v>1.0200000000000001E-2</v>
+        <v>1.04E-2</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G43" s="3">
-        <v>8.1600000000000006E-3</v>
+        <v>8.3199999999999993E-3</v>
       </c>
       <c r="H43" s="3">
-        <v>1.0200000000000001E-2</v>
+        <v>1.04E-2</v>
       </c>
       <c r="I43" s="3">
-        <v>1.2239999999999999E-2</v>
+        <v>1.248E-2</v>
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="3" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>157</v>
@@ -2424,31 +2436,31 @@
         <v>21</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E44" s="3">
-        <v>0.77500000000000002</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G44" s="3">
-        <v>0.62</v>
+        <v>8.1600000000000006E-3</v>
       </c>
       <c r="H44" s="3">
-        <v>0.77500000000000002</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="I44" s="3">
-        <v>0.92999999999999905</v>
+        <v>1.2239999999999999E-2</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>157</v>
@@ -2457,31 +2469,31 @@
         <v>21</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E45" s="3">
-        <v>0.1</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G45" s="3">
-        <v>0.08</v>
+        <v>0.62</v>
       </c>
       <c r="H45" s="3">
-        <v>0.1</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="I45" s="3">
-        <v>0.12</v>
+        <v>0.92999999999999905</v>
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>157</v>
@@ -2493,61 +2505,61 @@
         <v>68</v>
       </c>
       <c r="E46" s="3">
-        <v>440</v>
+        <v>0.1</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G46" s="3">
-        <v>352</v>
+        <v>0.08</v>
       </c>
       <c r="H46" s="3">
-        <v>440</v>
+        <v>0.1</v>
       </c>
       <c r="I46" s="3">
-        <v>528</v>
+        <v>0.12</v>
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E47" s="3">
-        <v>2.82</v>
+        <v>440</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G47" s="3">
-        <v>2.2559999999999998</v>
+        <v>352</v>
       </c>
       <c r="H47" s="3">
-        <v>2.82</v>
+        <v>440</v>
       </c>
       <c r="I47" s="3">
-        <v>3.3839999999999999</v>
+        <v>528</v>
       </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>153</v>
@@ -2559,28 +2571,28 @@
         <v>66</v>
       </c>
       <c r="E48" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>2.82</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G48" s="3">
-        <v>0.01</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="H48" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>2.82</v>
       </c>
       <c r="I48" s="3">
-        <v>1.4999999999999999E-2</v>
+        <v>3.3839999999999999</v>
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>153</v>
@@ -2589,31 +2601,31 @@
         <v>21</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E49" s="3">
-        <v>3.4000000000000002E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G49" s="3">
-        <v>2.7199999999999998E-2</v>
+        <v>0.01</v>
       </c>
       <c r="H49" s="3">
-        <v>3.4000000000000002E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="I49" s="3">
-        <v>4.0800000000000003E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="3" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>153</v>
@@ -2625,61 +2637,61 @@
         <v>68</v>
       </c>
       <c r="E50" s="3">
-        <v>5.7000000000000002E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G50" s="3">
-        <v>4.5600000000000002E-2</v>
+        <v>2.7199999999999998E-2</v>
       </c>
       <c r="H50" s="3">
-        <v>5.7000000000000002E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="I50" s="3">
-        <v>6.8400000000000002E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E51" s="3">
-        <v>1.2030000000000001</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G51" s="3">
-        <v>0.96240000000000003</v>
+        <v>4.5600000000000002E-2</v>
       </c>
       <c r="H51" s="3">
-        <v>1.2030000000000001</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="I51" s="3">
-        <v>1.4436</v>
+        <v>6.8400000000000002E-2</v>
       </c>
       <c r="J51" s="3"/>
       <c r="K51" s="3" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>154</v>
@@ -2691,28 +2703,28 @@
         <v>66</v>
       </c>
       <c r="E52" s="3">
-        <v>0.04</v>
+        <v>1.2030000000000001</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G52" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>0.96240000000000003</v>
       </c>
       <c r="H52" s="3">
-        <v>0.04</v>
+        <v>1.2030000000000001</v>
       </c>
       <c r="I52" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>1.4436</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>154</v>
@@ -2724,28 +2736,28 @@
         <v>66</v>
       </c>
       <c r="E53" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G53" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H53" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I53" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>154</v>
@@ -2757,28 +2769,28 @@
         <v>66</v>
       </c>
       <c r="E54" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G54" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H54" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I54" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>154</v>
@@ -2787,67 +2799,67 @@
         <v>21</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E55" s="3">
-        <v>1.01E-2</v>
+        <v>0.04</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G55" s="3">
-        <v>8.0800000000000004E-3</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H55" s="3">
-        <v>1.01E-2</v>
+        <v>0.04</v>
       </c>
       <c r="I55" s="3">
-        <v>1.21199999999999E-2</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E56" s="3">
-        <v>0.58899999999999997</v>
+        <v>1.01E-2</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G56" s="3">
-        <v>0.47120000000000001</v>
+        <v>8.0800000000000004E-3</v>
       </c>
       <c r="H56" s="3">
-        <v>0.58899999999999997</v>
+        <v>1.01E-2</v>
       </c>
       <c r="I56" s="3">
-        <v>0.70679999999999998</v>
+        <v>1.21199999999999E-2</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>21</v>
@@ -2856,28 +2868,28 @@
         <v>66</v>
       </c>
       <c r="E57" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G57" s="3">
-        <v>6.4000000000000003E-3</v>
+        <v>0.47120000000000001</v>
       </c>
       <c r="H57" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="I57" s="3">
-        <v>9.5999999999999992E-3</v>
+        <v>0.70679999999999998</v>
       </c>
       <c r="J57" s="3"/>
       <c r="K57" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>156</v>
@@ -2886,31 +2898,31 @@
         <v>21</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E58" s="5">
-        <v>9.9999999999999995E-7</v>
+        <v>66</v>
+      </c>
+      <c r="E58" s="3">
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G58" s="5">
-        <v>7.9999999999999996E-7</v>
-      </c>
-      <c r="H58" s="5">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="I58" s="5">
-        <v>1.1999999999999999E-6</v>
+      <c r="G58" s="3">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="H58" s="3">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I58" s="3">
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>156</v>
@@ -2919,31 +2931,31 @@
         <v>21</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E59" s="3">
-        <v>7.51E-2</v>
+        <v>68</v>
+      </c>
+      <c r="E59" s="5">
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G59" s="3">
-        <v>6.0080000000000001E-2</v>
-      </c>
-      <c r="H59" s="3">
-        <v>7.51E-2</v>
-      </c>
-      <c r="I59" s="3">
-        <v>9.0119999999999895E-2</v>
+      <c r="G59" s="5">
+        <v>7.9999999999999996E-7</v>
+      </c>
+      <c r="H59" s="5">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="I59" s="5">
+        <v>1.1999999999999999E-6</v>
       </c>
       <c r="J59" s="3"/>
       <c r="K59" s="3" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>156</v>
@@ -2952,31 +2964,31 @@
         <v>21</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E60" s="3">
-        <v>13</v>
+        <v>7.51E-2</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G60" s="3">
-        <v>10.4</v>
+        <v>6.0080000000000001E-2</v>
       </c>
       <c r="H60" s="3">
-        <v>13</v>
+        <v>7.51E-2</v>
       </c>
       <c r="I60" s="3">
-        <v>15.6</v>
+        <v>9.0119999999999895E-2</v>
       </c>
       <c r="J60" s="3"/>
       <c r="K60" s="3" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>156</v>
@@ -2988,28 +3000,28 @@
         <v>68</v>
       </c>
       <c r="E61" s="3">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G61" s="3">
-        <v>20</v>
+        <v>10.4</v>
       </c>
       <c r="H61" s="3">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="I61" s="3">
-        <v>30</v>
+        <v>15.6</v>
       </c>
       <c r="J61" s="3"/>
       <c r="K61" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>156</v>
@@ -3018,34 +3030,34 @@
         <v>21</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E62" s="3">
-        <v>3.9899999999999996E-3</v>
+        <v>25</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G62" s="3">
-        <v>3.192E-3</v>
+        <v>20</v>
       </c>
       <c r="H62" s="3">
-        <v>3.9899999999999996E-3</v>
+        <v>25</v>
       </c>
       <c r="I62" s="3">
-        <v>4.7879999999999997E-3</v>
+        <v>30</v>
       </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>21</v>
@@ -3054,31 +3066,31 @@
         <v>66</v>
       </c>
       <c r="E63" s="3">
-        <v>0.06</v>
+        <v>3.9899999999999996E-3</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G63" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>3.192E-3</v>
       </c>
       <c r="H63" s="3">
-        <v>0.06</v>
+        <v>3.9899999999999996E-3</v>
       </c>
       <c r="I63" s="3">
-        <v>7.1999999999999995E-2</v>
+        <v>4.7879999999999997E-3</v>
       </c>
       <c r="J63" s="3"/>
       <c r="K63" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>21</v>
@@ -3087,31 +3099,31 @@
         <v>66</v>
       </c>
       <c r="E64" s="3">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G64" s="3">
-        <v>1.6E-2</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="H64" s="3">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="I64" s="3">
-        <v>2.4E-2</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="J64" s="3"/>
       <c r="K64" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>21</v>
@@ -3120,31 +3132,28 @@
         <v>66</v>
       </c>
       <c r="E65" s="3">
-        <v>5.81</v>
+        <v>0.02</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G65" s="5">
-        <f>E65*0.8</f>
-        <v>4.6479999999999997</v>
-      </c>
-      <c r="H65" s="5">
-        <f>E65</f>
-        <v>5.81</v>
-      </c>
-      <c r="I65" s="5">
-        <f>1.2*E65</f>
-        <v>6.9719999999999995</v>
+      <c r="G65" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="H65" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I65" s="3">
+        <v>2.4E-2</v>
       </c>
       <c r="J65" s="3"/>
       <c r="K65" s="3" t="s">
-        <v>161</v>
+        <v>85</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>180</v>
@@ -3153,70 +3162,70 @@
         <v>21</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E66" s="5">
-        <v>4.9999999999999998E-7</v>
+        <v>66</v>
+      </c>
+      <c r="E66" s="3">
+        <v>5.81</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G66" s="5">
         <f>E66*0.8</f>
-        <v>3.9999999999999998E-7</v>
+        <v>4.6479999999999997</v>
       </c>
       <c r="H66" s="5">
         <f>E66</f>
-        <v>4.9999999999999998E-7</v>
+        <v>5.81</v>
       </c>
       <c r="I66" s="5">
         <f>1.2*E66</f>
-        <v>5.9999999999999997E-7</v>
+        <v>6.9719999999999995</v>
       </c>
       <c r="J66" s="3"/>
       <c r="K66" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E67" s="3">
-        <v>4.8</v>
+        <v>68</v>
+      </c>
+      <c r="E67" s="5">
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G67" s="5">
-        <f t="shared" ref="G67:G74" si="2">E67*0.8</f>
-        <v>3.84</v>
+        <f>E67*0.8</f>
+        <v>3.9999999999999998E-7</v>
       </c>
       <c r="H67" s="5">
-        <f t="shared" ref="H67:H74" si="3">E67</f>
-        <v>4.8</v>
+        <f>E67</f>
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="I67" s="5">
-        <f t="shared" ref="I67:I74" si="4">1.2*E67</f>
-        <v>5.76</v>
+        <f>1.2*E67</f>
+        <v>5.9999999999999997E-7</v>
       </c>
       <c r="J67" s="3"/>
       <c r="K67" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>181</v>
@@ -3225,244 +3234,280 @@
         <v>21</v>
       </c>
       <c r="D68" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E68" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="F68" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G68" s="5">
+        <f t="shared" ref="G68:G75" si="2">E68*0.8</f>
+        <v>3.84</v>
+      </c>
+      <c r="H68" s="5">
+        <f t="shared" ref="H68:H75" si="3">E68</f>
+        <v>4.8</v>
+      </c>
+      <c r="I68" s="5">
+        <f t="shared" ref="I68:I75" si="4">1.2*E68</f>
+        <v>5.76</v>
+      </c>
+      <c r="J68" s="3"/>
+      <c r="K68" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A69" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B69" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C69" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D69" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E68" s="5">
+      <c r="E69" s="5">
         <v>2.6400000000000002E-4</v>
       </c>
-      <c r="F68" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G68" s="5">
+      <c r="F69" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G69" s="5">
         <f t="shared" si="2"/>
         <v>2.1120000000000004E-4</v>
       </c>
-      <c r="H68" s="5">
+      <c r="H69" s="5">
         <f t="shared" si="3"/>
         <v>2.6400000000000002E-4</v>
       </c>
-      <c r="I68" s="5">
+      <c r="I69" s="5">
         <f t="shared" si="4"/>
         <v>3.168E-4</v>
       </c>
-      <c r="J68" s="3"/>
-      <c r="K68" s="3" t="s">
+      <c r="J69" s="3"/>
+      <c r="K69" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A69" s="3" t="s">
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A70" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B69" s="3" t="s">
+      <c r="B70" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C69" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D69" s="3" t="s">
+      <c r="C70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E69" s="3">
+      <c r="E70" s="3">
         <v>4.8</v>
       </c>
-      <c r="F69" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G69" s="5">
+      <c r="F70" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G70" s="5">
         <f t="shared" si="2"/>
         <v>3.84</v>
       </c>
-      <c r="H69" s="5">
+      <c r="H70" s="5">
         <f t="shared" si="3"/>
         <v>4.8</v>
       </c>
-      <c r="I69" s="5">
+      <c r="I70" s="5">
         <f t="shared" si="4"/>
         <v>5.76</v>
       </c>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3" t="s">
+      <c r="J70" s="3"/>
+      <c r="K70" s="3" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A70" s="3" t="s">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A71" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B71" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D70" s="3" t="s">
+      <c r="C71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E70" s="5">
+      <c r="E71" s="5">
         <v>2.6400000000000002E-4</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G70" s="5">
+      <c r="F71" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G71" s="5">
         <f t="shared" si="2"/>
         <v>2.1120000000000004E-4</v>
       </c>
-      <c r="H70" s="5">
+      <c r="H71" s="5">
         <f t="shared" si="3"/>
         <v>2.6400000000000002E-4</v>
       </c>
-      <c r="I70" s="5">
+      <c r="I71" s="5">
         <f t="shared" si="4"/>
         <v>3.168E-4</v>
       </c>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3" t="s">
+      <c r="J71" s="3"/>
+      <c r="K71" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A72" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B72" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D71" s="3" t="s">
+      <c r="C72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E71" s="3">
+      <c r="E72" s="3">
         <v>2.82</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G71" s="5">
+      <c r="F72" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G72" s="5">
         <f t="shared" si="2"/>
         <v>2.2559999999999998</v>
       </c>
-      <c r="H71" s="5">
+      <c r="H72" s="5">
         <f t="shared" si="3"/>
         <v>2.82</v>
       </c>
-      <c r="I71" s="5">
+      <c r="I72" s="5">
         <f t="shared" si="4"/>
         <v>3.3839999999999999</v>
       </c>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3" t="s">
+      <c r="J72" s="3"/>
+      <c r="K72" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A72" s="3" t="s">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A73" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B73" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D72" s="3" t="s">
+      <c r="C73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E73" s="3">
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G72" s="5">
+      <c r="F73" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G73" s="5">
         <f t="shared" si="2"/>
         <v>1.0000000000000002E-2</v>
       </c>
-      <c r="H72" s="5">
+      <c r="H73" s="5">
         <f t="shared" si="3"/>
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="I72" s="5">
+      <c r="I73" s="5">
         <f t="shared" si="4"/>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3" t="s">
+      <c r="J73" s="3"/>
+      <c r="K73" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A73" s="3" t="s">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B74" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D73" s="3" t="s">
+      <c r="C74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E73" s="3">
+      <c r="E74" s="3">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="F73" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G73" s="5">
+      <c r="F74" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G74" s="5">
         <f t="shared" si="2"/>
         <v>2.7200000000000002E-2</v>
       </c>
-      <c r="H73" s="5">
+      <c r="H74" s="5">
         <f t="shared" si="3"/>
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="I73" s="5">
+      <c r="I74" s="5">
         <f t="shared" si="4"/>
         <v>4.0800000000000003E-2</v>
       </c>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3" t="s">
+      <c r="J74" s="3"/>
+      <c r="K74" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A74" s="3" t="s">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A75" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B75" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D74" s="3" t="s">
+      <c r="C75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E74" s="3">
+      <c r="E75" s="3">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G74" s="5">
+      <c r="F75" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G75" s="5">
         <f t="shared" si="2"/>
         <v>4.5600000000000002E-2</v>
       </c>
-      <c r="H74" s="5">
+      <c r="H75" s="5">
         <f t="shared" si="3"/>
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="I74" s="5">
+      <c r="I75" s="5">
         <f t="shared" si="4"/>
         <v>6.8400000000000002E-2</v>
       </c>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3" t="s">
+      <c r="J75" s="3"/>
+      <c r="K75" s="3" t="s">
         <v>179</v>
       </c>
     </row>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saran\Documents\Academia\repository_clones\Bioindustrial-Park\biorefineries\isobutanol\analyses\full\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E62A783B-9F0A-4072-A673-39C0719C99D1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB87390A-2DAB-476E-90F1-11FEC7437ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -590,21 +590,12 @@
     <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
   </si>
   <si>
-    <t>DDGS price</t>
-  </si>
-  <si>
     <t>DDGS.price =x</t>
   </si>
   <si>
-    <t>Isobutanol price</t>
-  </si>
-  <si>
     <t>V514.isobutanol_price = x</t>
   </si>
   <si>
-    <t>Isopentyl acetate price</t>
-  </si>
-  <si>
     <t>makeup_isopentyl_acetate.price = x</t>
   </si>
   <si>
@@ -615,6 +606,15 @@
   </si>
   <si>
     <t>feedstock.imass['Starch'] =x * feedstock.imass['Water']</t>
+  </si>
+  <si>
+    <t>Isobutanol unit price</t>
+  </si>
+  <si>
+    <t>DDGS unit price</t>
+  </si>
+  <si>
+    <t>Isopentyl acetate unit price</t>
   </si>
 </sst>
 </file>
@@ -1358,7 +1358,7 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>184</v>
+        <v>191</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>7</v>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>7</v>
@@ -1403,28 +1403,28 @@
         <v>10</v>
       </c>
       <c r="E13" s="4">
-        <v>1.43</v>
+        <v>1.49</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>18</v>
       </c>
       <c r="G13" s="4">
         <f t="shared" si="0"/>
-        <v>1.1439999999999999</v>
+        <v>1.1919999999999999</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4">
         <f t="shared" si="1"/>
-        <v>1.716</v>
+        <v>1.788</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A14" s="4" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="B14" s="4" t="s">
         <v>7</v>
@@ -1452,7 +1452,7 @@
       </c>
       <c r="J14" s="4"/>
       <c r="K14" s="4" t="s">
-        <v>189</v>
+        <v>186</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
@@ -1590,7 +1590,7 @@
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>190</v>
+        <v>187</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -1599,7 +1599,7 @@
         <v>21</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>191</v>
+        <v>188</v>
       </c>
       <c r="E19" s="3">
         <v>4.08</v>
@@ -1621,7 +1621,7 @@
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
-        <v>192</v>
+        <v>189</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saran\Documents\Academia\repository_clones\Bioindustrial-Park\biorefineries\isobutanol\analyses\full\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EB87390A-2DAB-476E-90F1-11FEC7437ADC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBF3DC4-2269-42E5-BA07-C7F0AFB6684C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -1409,13 +1409,11 @@
         <v>18</v>
       </c>
       <c r="G13" s="4">
-        <f t="shared" si="0"/>
-        <v>1.1919999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4">
-        <f t="shared" si="1"/>
-        <v>1.788</v>
+        <v>1.7250000000000001</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4" t="s">

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saran\Documents\Academia\repository_clones\Bioindustrial-Park\biorefineries\isobutanol\analyses\full\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BBBF3DC4-2269-42E5-BA07-C7F0AFB6684C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B3EE8E-414D-4AE6-B4B5-B0137941DD4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="3720" yWindow="340" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="193">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="196">
   <si>
     <t>Parameter name</t>
   </si>
@@ -615,6 +615,15 @@
   </si>
   <si>
     <t>Isopentyl acetate unit price</t>
+  </si>
+  <si>
+    <t>Aeration rate safety factor</t>
+  </si>
+  <si>
+    <t>Fermentation</t>
+  </si>
+  <si>
+    <t>V406.aeration_safety_factor = x</t>
   </si>
 </sst>
 </file>
@@ -977,7 +986,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40.81640625" customWidth="1"/>
@@ -1660,43 +1669,38 @@
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>53</v>
+        <v>193</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>13</v>
+        <v>194</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="E21" s="3">
-        <v>156</v>
+        <v>2</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G21" s="3">
-        <f>E21*0.8</f>
-        <v>124.80000000000001</v>
-      </c>
-      <c r="H21" s="3">
-        <f>E21</f>
-        <v>156</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H21" s="3"/>
       <c r="I21" s="3">
-        <f>E21*1.2</f>
-        <v>187.2</v>
+        <v>3</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>55</v>
+        <v>195</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>13</v>
@@ -1727,45 +1731,48 @@
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>123</v>
+        <v>54</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>149</v>
+        <v>13</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>66</v>
+        <v>14</v>
       </c>
       <c r="E23" s="3">
-        <v>1.43</v>
+        <v>156</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>67</v>
+        <v>27</v>
       </c>
       <c r="G23" s="3">
-        <v>1.1439999999999999</v>
+        <f>E23*0.8</f>
+        <v>124.80000000000001</v>
       </c>
       <c r="H23" s="3">
-        <v>1.43</v>
+        <f>E23</f>
+        <v>156</v>
       </c>
       <c r="I23" s="3">
-        <v>1.716</v>
+        <f>E23*1.2</f>
+        <v>187.2</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3" t="s">
-        <v>63</v>
+        <v>56</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>106</v>
+        <v>123</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>149</v>
@@ -1774,31 +1781,31 @@
         <v>21</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E24" s="3">
-        <v>0.94</v>
+        <v>1.43</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G24" s="3">
-        <v>0.752</v>
+        <v>1.1439999999999999</v>
       </c>
       <c r="H24" s="3">
-        <v>0.94</v>
+        <v>1.43</v>
       </c>
       <c r="I24" s="3">
-        <v>1.1279999999999999</v>
+        <v>1.716</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3" t="s">
-        <v>88</v>
+        <v>63</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>124</v>
+        <v>106</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>149</v>
@@ -1807,31 +1814,31 @@
         <v>21</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E25" s="3">
-        <v>0.58399999999999996</v>
+        <v>0.94</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G25" s="3">
-        <v>0.4672</v>
+        <v>0.752</v>
       </c>
       <c r="H25" s="3">
-        <v>0.58399999999999996</v>
+        <v>0.94</v>
       </c>
       <c r="I25" s="3">
-        <v>0.70079999999999998</v>
+        <v>1.1279999999999999</v>
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>149</v>
@@ -1840,31 +1847,31 @@
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E26" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G26" s="3">
-        <v>9.2800000000000001E-3</v>
+        <v>0.4672</v>
       </c>
       <c r="H26" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="I26" s="3">
-        <v>1.3919999999999899E-2</v>
+        <v>0.70079999999999998</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="s">
-        <v>89</v>
+        <v>59</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>125</v>
+        <v>107</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>149</v>
@@ -1873,31 +1880,31 @@
         <v>21</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E27" s="3">
-        <v>47.1</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G27" s="3">
-        <v>37.68</v>
+        <v>9.2800000000000001E-3</v>
       </c>
       <c r="H27" s="3">
-        <v>47.1</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="I27" s="3">
-        <v>56.52</v>
+        <v>1.3919999999999899E-2</v>
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>108</v>
+        <v>125</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>149</v>
@@ -1906,31 +1913,31 @@
         <v>21</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E28" s="3">
-        <v>14.2</v>
+        <v>47.1</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G28" s="3">
-        <v>11.36</v>
+        <v>37.68</v>
       </c>
       <c r="H28" s="3">
-        <v>14.2</v>
+        <v>47.1</v>
       </c>
       <c r="I28" s="3">
-        <v>17.04</v>
+        <v>56.52</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>90</v>
+        <v>58</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>149</v>
@@ -1942,28 +1949,28 @@
         <v>68</v>
       </c>
       <c r="E29" s="3">
-        <v>0.12</v>
+        <v>14.2</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G29" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>11.36</v>
       </c>
       <c r="H29" s="3">
-        <v>0.12</v>
+        <v>14.2</v>
       </c>
       <c r="I29" s="3">
-        <v>0.14399999999999999</v>
+        <v>17.04</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>126</v>
+        <v>109</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>149</v>
@@ -1972,31 +1979,31 @@
         <v>21</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E30" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G30" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H30" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I30" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3" t="s">
-        <v>60</v>
+        <v>91</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>149</v>
@@ -2008,28 +2015,28 @@
         <v>66</v>
       </c>
       <c r="E31" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G31" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H31" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I31" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>149</v>
@@ -2041,31 +2048,31 @@
         <v>66</v>
       </c>
       <c r="E32" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G32" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H32" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I32" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>21</v>
@@ -2074,28 +2081,28 @@
         <v>66</v>
       </c>
       <c r="E33" s="3">
-        <v>0.501</v>
+        <v>0.04</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G33" s="3">
-        <v>0.40079999999999999</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H33" s="3">
-        <v>0.501</v>
+        <v>0.04</v>
       </c>
       <c r="I33" s="3">
-        <v>0.60119999999999996</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3" t="s">
-        <v>57</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>150</v>
@@ -2104,31 +2111,31 @@
         <v>21</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E34" s="5">
-        <v>2.0000000000000002E-5</v>
+        <v>66</v>
+      </c>
+      <c r="E34" s="3">
+        <v>0.501</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G34" s="5">
-        <v>1.5999999999999999E-5</v>
-      </c>
-      <c r="H34" s="5">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="I34" s="5">
-        <v>2.4000000000000001E-5</v>
+      <c r="G34" s="3">
+        <v>0.40079999999999999</v>
+      </c>
+      <c r="H34" s="3">
+        <v>0.501</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0.60119999999999996</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>92</v>
+        <v>57</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>111</v>
+        <v>110</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>150</v>
@@ -2139,62 +2146,62 @@
       <c r="D35" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E35" s="3">
-        <v>0.10100000000000001</v>
+      <c r="E35" s="5">
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G35" s="3">
-        <v>8.0799999999999997E-2</v>
-      </c>
-      <c r="H35" s="3">
-        <v>0.10100000000000001</v>
-      </c>
-      <c r="I35" s="3">
-        <v>0.1212</v>
+      <c r="G35" s="5">
+        <v>1.5999999999999999E-5</v>
+      </c>
+      <c r="H35" s="5">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="I35" s="5">
+        <v>2.4000000000000001E-5</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>130</v>
+        <v>111</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E36" s="3">
-        <v>5.81</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G36" s="3">
-        <v>4.6479999999999997</v>
+        <v>8.0799999999999997E-2</v>
       </c>
       <c r="H36" s="3">
-        <v>5.81</v>
+        <v>0.10100000000000001</v>
       </c>
       <c r="I36" s="3">
-        <v>6.9719999999999898</v>
+        <v>0.1212</v>
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="3" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>112</v>
+        <v>130</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>151</v>
@@ -2203,64 +2210,64 @@
         <v>21</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E37" s="5">
-        <v>4.9999999999999998E-7</v>
+        <v>66</v>
+      </c>
+      <c r="E37" s="3">
+        <v>5.81</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G37" s="5">
-        <v>3.9999999999999998E-7</v>
-      </c>
-      <c r="H37" s="5">
-        <v>4.9999999999999998E-7</v>
-      </c>
-      <c r="I37" s="5">
-        <v>5.9999999999999997E-7</v>
+      <c r="G37" s="3">
+        <v>4.6479999999999997</v>
+      </c>
+      <c r="H37" s="3">
+        <v>5.81</v>
+      </c>
+      <c r="I37" s="3">
+        <v>6.9719999999999898</v>
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>131</v>
+        <v>112</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E38" s="3">
-        <v>4.8</v>
+        <v>68</v>
+      </c>
+      <c r="E38" s="5">
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G38" s="3">
-        <v>3.84</v>
-      </c>
-      <c r="H38" s="3">
-        <v>4.8</v>
-      </c>
-      <c r="I38" s="3">
-        <v>5.76</v>
+      <c r="G38" s="5">
+        <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="H38" s="5">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="I38" s="5">
+        <v>5.9999999999999997E-7</v>
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>65</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>152</v>
@@ -2272,28 +2279,28 @@
         <v>66</v>
       </c>
       <c r="E39" s="3">
-        <v>0.04</v>
+        <v>4.8</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G39" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>3.84</v>
       </c>
       <c r="H39" s="3">
-        <v>0.04</v>
+        <v>4.8</v>
       </c>
       <c r="I39" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>5.76</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3" t="s">
-        <v>69</v>
+        <v>65</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>152</v>
@@ -2305,28 +2312,28 @@
         <v>66</v>
       </c>
       <c r="E40" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G40" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H40" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I40" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>152</v>
@@ -2338,28 +2345,28 @@
         <v>66</v>
       </c>
       <c r="E41" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G41" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H41" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I41" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>113</v>
+        <v>134</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>152</v>
@@ -2368,64 +2375,64 @@
         <v>21</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E42" s="3">
-        <v>2.6400000000000002E-4</v>
+        <v>0.04</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G42" s="3">
-        <v>2.1120000000000001E-4</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H42" s="3">
-        <v>2.6400000000000002E-4</v>
+        <v>0.04</v>
       </c>
       <c r="I42" s="3">
-        <v>3.168E-4</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>135</v>
+        <v>113</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>157</v>
+        <v>152</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E43" s="3">
-        <v>1.04E-2</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G43" s="3">
-        <v>8.3199999999999993E-3</v>
+        <v>2.1120000000000001E-4</v>
       </c>
       <c r="H43" s="3">
-        <v>1.04E-2</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="I43" s="3">
-        <v>1.248E-2</v>
+        <v>3.168E-4</v>
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="3" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>157</v>
@@ -2434,31 +2441,31 @@
         <v>21</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E44" s="3">
-        <v>1.0200000000000001E-2</v>
+        <v>1.04E-2</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G44" s="3">
-        <v>8.1600000000000006E-3</v>
+        <v>8.3199999999999993E-3</v>
       </c>
       <c r="H44" s="3">
-        <v>1.0200000000000001E-2</v>
+        <v>1.04E-2</v>
       </c>
       <c r="I44" s="3">
-        <v>1.2239999999999999E-2</v>
+        <v>1.248E-2</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>136</v>
+        <v>114</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>157</v>
@@ -2467,31 +2474,31 @@
         <v>21</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E45" s="3">
-        <v>0.77500000000000002</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G45" s="3">
-        <v>0.62</v>
+        <v>8.1600000000000006E-3</v>
       </c>
       <c r="H45" s="3">
-        <v>0.77500000000000002</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="I45" s="3">
-        <v>0.92999999999999905</v>
+        <v>1.2239999999999999E-2</v>
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>115</v>
+        <v>136</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>157</v>
@@ -2500,31 +2507,31 @@
         <v>21</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E46" s="3">
-        <v>0.1</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G46" s="3">
-        <v>0.08</v>
+        <v>0.62</v>
       </c>
       <c r="H46" s="3">
-        <v>0.1</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="I46" s="3">
-        <v>0.12</v>
+        <v>0.92999999999999905</v>
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>157</v>
@@ -2536,61 +2543,61 @@
         <v>68</v>
       </c>
       <c r="E47" s="3">
-        <v>440</v>
+        <v>0.1</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G47" s="3">
-        <v>352</v>
+        <v>0.08</v>
       </c>
       <c r="H47" s="3">
-        <v>440</v>
+        <v>0.1</v>
       </c>
       <c r="I47" s="3">
-        <v>528</v>
+        <v>0.12</v>
       </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>137</v>
+        <v>116</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E48" s="3">
-        <v>2.82</v>
+        <v>440</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G48" s="3">
-        <v>2.2559999999999998</v>
+        <v>352</v>
       </c>
       <c r="H48" s="3">
-        <v>2.82</v>
+        <v>440</v>
       </c>
       <c r="I48" s="3">
-        <v>3.3839999999999999</v>
+        <v>528</v>
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="3" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>153</v>
@@ -2602,28 +2609,28 @@
         <v>66</v>
       </c>
       <c r="E49" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>2.82</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G49" s="3">
-        <v>0.01</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="H49" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>2.82</v>
       </c>
       <c r="I49" s="3">
-        <v>1.4999999999999999E-2</v>
+        <v>3.3839999999999999</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>117</v>
+        <v>138</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>153</v>
@@ -2632,31 +2639,31 @@
         <v>21</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E50" s="3">
-        <v>3.4000000000000002E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G50" s="3">
-        <v>2.7199999999999998E-2</v>
+        <v>0.01</v>
       </c>
       <c r="H50" s="3">
-        <v>3.4000000000000002E-2</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="I50" s="3">
-        <v>4.0800000000000003E-2</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>153</v>
@@ -2668,61 +2675,61 @@
         <v>68</v>
       </c>
       <c r="E51" s="3">
-        <v>5.7000000000000002E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G51" s="3">
-        <v>4.5600000000000002E-2</v>
+        <v>2.7199999999999998E-2</v>
       </c>
       <c r="H51" s="3">
-        <v>5.7000000000000002E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="I51" s="3">
-        <v>6.8400000000000002E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="J51" s="3"/>
       <c r="K51" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
-        <v>139</v>
+        <v>118</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E52" s="3">
-        <v>1.2030000000000001</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G52" s="3">
-        <v>0.96240000000000003</v>
+        <v>4.5600000000000002E-2</v>
       </c>
       <c r="H52" s="3">
-        <v>1.2030000000000001</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="I52" s="3">
-        <v>1.4436</v>
+        <v>6.8400000000000002E-2</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
-        <v>76</v>
+        <v>100</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>154</v>
@@ -2734,28 +2741,28 @@
         <v>66</v>
       </c>
       <c r="E53" s="3">
-        <v>0.04</v>
+        <v>1.2030000000000001</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G53" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>0.96240000000000003</v>
       </c>
       <c r="H53" s="3">
-        <v>0.04</v>
+        <v>1.2030000000000001</v>
       </c>
       <c r="I53" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>1.4436</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>154</v>
@@ -2767,28 +2774,28 @@
         <v>66</v>
       </c>
       <c r="E54" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G54" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H54" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I54" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>154</v>
@@ -2800,28 +2807,28 @@
         <v>66</v>
       </c>
       <c r="E55" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G55" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H55" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I55" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>119</v>
+        <v>142</v>
       </c>
       <c r="B56" s="3" t="s">
         <v>154</v>
@@ -2830,67 +2837,67 @@
         <v>21</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E56" s="3">
-        <v>1.01E-2</v>
+        <v>0.04</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G56" s="3">
-        <v>8.0800000000000004E-3</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H56" s="3">
-        <v>1.01E-2</v>
+        <v>0.04</v>
       </c>
       <c r="I56" s="3">
-        <v>1.21199999999999E-2</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E57" s="3">
-        <v>0.58899999999999997</v>
+        <v>1.01E-2</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G57" s="3">
-        <v>0.47120000000000001</v>
+        <v>8.0800000000000004E-3</v>
       </c>
       <c r="H57" s="3">
-        <v>0.58899999999999997</v>
+        <v>1.01E-2</v>
       </c>
       <c r="I57" s="3">
-        <v>0.70679999999999998</v>
+        <v>1.21199999999999E-2</v>
       </c>
       <c r="J57" s="3"/>
       <c r="K57" s="3" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>21</v>
@@ -2899,28 +2906,28 @@
         <v>66</v>
       </c>
       <c r="E58" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G58" s="3">
-        <v>6.4000000000000003E-3</v>
+        <v>0.47120000000000001</v>
       </c>
       <c r="H58" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="I58" s="3">
-        <v>9.5999999999999992E-3</v>
+        <v>0.70679999999999998</v>
       </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>156</v>
@@ -2929,31 +2936,31 @@
         <v>21</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E59" s="5">
-        <v>9.9999999999999995E-7</v>
+        <v>66</v>
+      </c>
+      <c r="E59" s="3">
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G59" s="5">
-        <v>7.9999999999999996E-7</v>
-      </c>
-      <c r="H59" s="5">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="I59" s="5">
-        <v>1.1999999999999999E-6</v>
+      <c r="G59" s="3">
+        <v>6.4000000000000003E-3</v>
+      </c>
+      <c r="H59" s="3">
+        <v>8.0000000000000002E-3</v>
+      </c>
+      <c r="I59" s="3">
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="J59" s="3"/>
       <c r="K59" s="3" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
-        <v>145</v>
+        <v>120</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>156</v>
@@ -2962,31 +2969,31 @@
         <v>21</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E60" s="3">
-        <v>7.51E-2</v>
+        <v>68</v>
+      </c>
+      <c r="E60" s="5">
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G60" s="3">
-        <v>6.0080000000000001E-2</v>
-      </c>
-      <c r="H60" s="3">
-        <v>7.51E-2</v>
-      </c>
-      <c r="I60" s="3">
-        <v>9.0119999999999895E-2</v>
+      <c r="G60" s="5">
+        <v>7.9999999999999996E-7</v>
+      </c>
+      <c r="H60" s="5">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="I60" s="5">
+        <v>1.1999999999999999E-6</v>
       </c>
       <c r="J60" s="3"/>
       <c r="K60" s="3" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>121</v>
+        <v>145</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>156</v>
@@ -2995,31 +3002,31 @@
         <v>21</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="E61" s="3">
-        <v>13</v>
+        <v>7.51E-2</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G61" s="3">
-        <v>10.4</v>
+        <v>6.0080000000000001E-2</v>
       </c>
       <c r="H61" s="3">
-        <v>13</v>
+        <v>7.51E-2</v>
       </c>
       <c r="I61" s="3">
-        <v>15.6</v>
+        <v>9.0119999999999895E-2</v>
       </c>
       <c r="J61" s="3"/>
       <c r="K61" s="3" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>156</v>
@@ -3031,28 +3038,28 @@
         <v>68</v>
       </c>
       <c r="E62" s="3">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G62" s="3">
-        <v>20</v>
+        <v>10.4</v>
       </c>
       <c r="H62" s="3">
-        <v>25</v>
+        <v>13</v>
       </c>
       <c r="I62" s="3">
-        <v>30</v>
+        <v>15.6</v>
       </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
-        <v>146</v>
+        <v>122</v>
       </c>
       <c r="B63" s="3" t="s">
         <v>156</v>
@@ -3061,34 +3068,34 @@
         <v>21</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="E63" s="3">
-        <v>3.9899999999999996E-3</v>
+        <v>25</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G63" s="3">
-        <v>3.192E-3</v>
+        <v>20</v>
       </c>
       <c r="H63" s="3">
-        <v>3.9899999999999996E-3</v>
+        <v>25</v>
       </c>
       <c r="I63" s="3">
-        <v>4.7879999999999997E-3</v>
+        <v>30</v>
       </c>
       <c r="J63" s="3"/>
       <c r="K63" s="3" t="s">
-        <v>83</v>
+        <v>104</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>21</v>
@@ -3097,31 +3104,31 @@
         <v>66</v>
       </c>
       <c r="E64" s="3">
-        <v>0.06</v>
+        <v>3.9899999999999996E-3</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G64" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>3.192E-3</v>
       </c>
       <c r="H64" s="3">
-        <v>0.06</v>
+        <v>3.9899999999999996E-3</v>
       </c>
       <c r="I64" s="3">
-        <v>7.1999999999999995E-2</v>
+        <v>4.7879999999999997E-3</v>
       </c>
       <c r="J64" s="3"/>
       <c r="K64" s="3" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>21</v>
@@ -3130,31 +3137,31 @@
         <v>66</v>
       </c>
       <c r="E65" s="3">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G65" s="3">
-        <v>1.6E-2</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="H65" s="3">
-        <v>0.02</v>
+        <v>0.06</v>
       </c>
       <c r="I65" s="3">
-        <v>2.4E-2</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="J65" s="3"/>
       <c r="K65" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
-        <v>160</v>
+        <v>148</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>180</v>
+        <v>159</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>21</v>
@@ -3163,31 +3170,28 @@
         <v>66</v>
       </c>
       <c r="E66" s="3">
-        <v>5.81</v>
+        <v>0.02</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="G66" s="5">
-        <f>E66*0.8</f>
-        <v>4.6479999999999997</v>
-      </c>
-      <c r="H66" s="5">
-        <f>E66</f>
-        <v>5.81</v>
-      </c>
-      <c r="I66" s="5">
-        <f>1.2*E66</f>
-        <v>6.9719999999999995</v>
+      <c r="G66" s="3">
+        <v>1.6E-2</v>
+      </c>
+      <c r="H66" s="3">
+        <v>0.02</v>
+      </c>
+      <c r="I66" s="3">
+        <v>2.4E-2</v>
       </c>
       <c r="J66" s="3"/>
       <c r="K66" s="3" t="s">
-        <v>161</v>
+        <v>85</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>180</v>
@@ -3196,70 +3200,70 @@
         <v>21</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E67" s="5">
-        <v>4.9999999999999998E-7</v>
+        <v>66</v>
+      </c>
+      <c r="E67" s="3">
+        <v>5.81</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G67" s="5">
         <f>E67*0.8</f>
-        <v>3.9999999999999998E-7</v>
+        <v>4.6479999999999997</v>
       </c>
       <c r="H67" s="5">
         <f>E67</f>
-        <v>4.9999999999999998E-7</v>
+        <v>5.81</v>
       </c>
       <c r="I67" s="5">
         <f>1.2*E67</f>
-        <v>5.9999999999999997E-7</v>
+        <v>6.9719999999999995</v>
       </c>
       <c r="J67" s="3"/>
       <c r="K67" s="3" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
     </row>
     <row r="68" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E68" s="3">
-        <v>4.8</v>
+        <v>68</v>
+      </c>
+      <c r="E68" s="5">
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>67</v>
       </c>
       <c r="G68" s="5">
-        <f t="shared" ref="G68:G75" si="2">E68*0.8</f>
-        <v>3.84</v>
+        <f>E68*0.8</f>
+        <v>3.9999999999999998E-7</v>
       </c>
       <c r="H68" s="5">
-        <f t="shared" ref="H68:H75" si="3">E68</f>
-        <v>4.8</v>
+        <f>E68</f>
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="I68" s="5">
-        <f t="shared" ref="I68:I75" si="4">1.2*E68</f>
-        <v>5.76</v>
+        <f>1.2*E68</f>
+        <v>5.9999999999999997E-7</v>
       </c>
       <c r="J68" s="3"/>
       <c r="K68" s="3" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="69" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>181</v>
@@ -3268,244 +3272,280 @@
         <v>21</v>
       </c>
       <c r="D69" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="E69" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="F69" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G69" s="5">
+        <f t="shared" ref="G69:G76" si="2">E69*0.8</f>
+        <v>3.84</v>
+      </c>
+      <c r="H69" s="5">
+        <f t="shared" ref="H69:H76" si="3">E69</f>
+        <v>4.8</v>
+      </c>
+      <c r="I69" s="5">
+        <f t="shared" ref="I69:I76" si="4">1.2*E69</f>
+        <v>5.76</v>
+      </c>
+      <c r="J69" s="3"/>
+      <c r="K69" s="3" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A70" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="B70" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="C70" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D70" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E69" s="5">
+      <c r="E70" s="5">
         <v>2.6400000000000002E-4</v>
       </c>
-      <c r="F69" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G69" s="5">
+      <c r="F70" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G70" s="5">
         <f t="shared" si="2"/>
         <v>2.1120000000000004E-4</v>
       </c>
-      <c r="H69" s="5">
+      <c r="H70" s="5">
         <f t="shared" si="3"/>
         <v>2.6400000000000002E-4</v>
       </c>
-      <c r="I69" s="5">
+      <c r="I70" s="5">
         <f t="shared" si="4"/>
         <v>3.168E-4</v>
       </c>
-      <c r="J69" s="3"/>
-      <c r="K69" s="3" t="s">
+      <c r="J70" s="3"/>
+      <c r="K70" s="3" t="s">
         <v>167</v>
       </c>
     </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A70" s="3" t="s">
+    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A71" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="B70" s="3" t="s">
+      <c r="B71" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C70" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D70" s="3" t="s">
+      <c r="C71" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D71" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E70" s="3">
+      <c r="E71" s="3">
         <v>4.8</v>
       </c>
-      <c r="F70" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G70" s="5">
+      <c r="F71" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G71" s="5">
         <f t="shared" si="2"/>
         <v>3.84</v>
       </c>
-      <c r="H70" s="5">
+      <c r="H71" s="5">
         <f t="shared" si="3"/>
         <v>4.8</v>
       </c>
-      <c r="I70" s="5">
+      <c r="I71" s="5">
         <f t="shared" si="4"/>
         <v>5.76</v>
       </c>
-      <c r="J70" s="3"/>
-      <c r="K70" s="3" t="s">
+      <c r="J71" s="3"/>
+      <c r="K71" s="3" t="s">
         <v>169</v>
       </c>
     </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A71" s="3" t="s">
+    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A72" s="3" t="s">
         <v>170</v>
       </c>
-      <c r="B71" s="3" t="s">
+      <c r="B72" s="3" t="s">
         <v>182</v>
       </c>
-      <c r="C71" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D71" s="3" t="s">
+      <c r="C72" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D72" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E71" s="5">
+      <c r="E72" s="5">
         <v>2.6400000000000002E-4</v>
       </c>
-      <c r="F71" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G71" s="5">
+      <c r="F72" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G72" s="5">
         <f t="shared" si="2"/>
         <v>2.1120000000000004E-4</v>
       </c>
-      <c r="H71" s="5">
+      <c r="H72" s="5">
         <f t="shared" si="3"/>
         <v>2.6400000000000002E-4</v>
       </c>
-      <c r="I71" s="5">
+      <c r="I72" s="5">
         <f t="shared" si="4"/>
         <v>3.168E-4</v>
       </c>
-      <c r="J71" s="3"/>
-      <c r="K71" s="3" t="s">
+      <c r="J72" s="3"/>
+      <c r="K72" s="3" t="s">
         <v>171</v>
       </c>
     </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A72" s="3" t="s">
+    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A73" s="3" t="s">
         <v>172</v>
       </c>
-      <c r="B72" s="3" t="s">
+      <c r="B73" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C72" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D72" s="3" t="s">
+      <c r="C73" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D73" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E72" s="3">
+      <c r="E73" s="3">
         <v>2.82</v>
       </c>
-      <c r="F72" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G72" s="5">
+      <c r="F73" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G73" s="5">
         <f t="shared" si="2"/>
         <v>2.2559999999999998</v>
       </c>
-      <c r="H72" s="5">
+      <c r="H73" s="5">
         <f t="shared" si="3"/>
         <v>2.82</v>
       </c>
-      <c r="I72" s="5">
+      <c r="I73" s="5">
         <f t="shared" si="4"/>
         <v>3.3839999999999999</v>
       </c>
-      <c r="J72" s="3"/>
-      <c r="K72" s="3" t="s">
+      <c r="J73" s="3"/>
+      <c r="K73" s="3" t="s">
         <v>173</v>
       </c>
     </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A73" s="3" t="s">
+    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A74" s="3" t="s">
         <v>174</v>
       </c>
-      <c r="B73" s="3" t="s">
+      <c r="B74" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C73" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D73" s="3" t="s">
+      <c r="C74" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D74" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="E73" s="3">
+      <c r="E74" s="3">
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="F73" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G73" s="5">
+      <c r="F74" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G74" s="5">
         <f t="shared" si="2"/>
         <v>1.0000000000000002E-2</v>
       </c>
-      <c r="H73" s="5">
+      <c r="H74" s="5">
         <f t="shared" si="3"/>
         <v>1.2500000000000001E-2</v>
       </c>
-      <c r="I73" s="5">
+      <c r="I74" s="5">
         <f t="shared" si="4"/>
         <v>1.4999999999999999E-2</v>
       </c>
-      <c r="J73" s="3"/>
-      <c r="K73" s="3" t="s">
+      <c r="J74" s="3"/>
+      <c r="K74" s="3" t="s">
         <v>175</v>
       </c>
     </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A74" s="3" t="s">
+    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A75" s="3" t="s">
         <v>176</v>
       </c>
-      <c r="B74" s="3" t="s">
+      <c r="B75" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D74" s="3" t="s">
+      <c r="C75" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D75" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E74" s="3">
+      <c r="E75" s="3">
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="F74" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G74" s="5">
+      <c r="F75" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G75" s="5">
         <f t="shared" si="2"/>
         <v>2.7200000000000002E-2</v>
       </c>
-      <c r="H74" s="5">
+      <c r="H75" s="5">
         <f t="shared" si="3"/>
         <v>3.4000000000000002E-2</v>
       </c>
-      <c r="I74" s="5">
+      <c r="I75" s="5">
         <f t="shared" si="4"/>
         <v>4.0800000000000003E-2</v>
       </c>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3" t="s">
+      <c r="J75" s="3"/>
+      <c r="K75" s="3" t="s">
         <v>177</v>
       </c>
     </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A75" s="3" t="s">
+    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="A76" s="3" t="s">
         <v>178</v>
       </c>
-      <c r="B75" s="3" t="s">
+      <c r="B76" s="3" t="s">
         <v>183</v>
       </c>
-      <c r="C75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D75" s="3" t="s">
+      <c r="C76" s="3" t="s">
+        <v>21</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="E75" s="3">
+      <c r="E76" s="3">
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="F75" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G75" s="5">
+      <c r="F76" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="G76" s="5">
         <f t="shared" si="2"/>
         <v>4.5600000000000002E-2</v>
       </c>
-      <c r="H75" s="5">
+      <c r="H76" s="5">
         <f t="shared" si="3"/>
         <v>5.7000000000000002E-2</v>
       </c>
-      <c r="I75" s="5">
+      <c r="I76" s="5">
         <f t="shared" si="4"/>
         <v>6.8400000000000002E-2</v>
       </c>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3" t="s">
+      <c r="J76" s="3"/>
+      <c r="K76" s="3" t="s">
         <v>179</v>
       </c>
     </row>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saran\Documents\Academia\repository_clones\Bioindustrial-Park\biorefineries\isobutanol\analyses\full\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{55B3EE8E-414D-4AE6-B4B5-B0137941DD4C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF3A6AF-CA6E-4CE5-BE3F-94D8BF95F734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="3720" yWindow="340" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="461" uniqueCount="196">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="455" uniqueCount="194">
   <si>
     <t>Parameter name</t>
   </si>
@@ -194,9 +194,6 @@
     <t>denaturant.price = x</t>
   </si>
   <si>
-    <t>Steam jet cooking unit price</t>
-  </si>
-  <si>
     <t>Product ethanol storage time</t>
   </si>
   <si>
@@ -353,9 +350,6 @@
     <t>V406.kinetic_reaction_system._te.K_9i = x</t>
   </si>
   <si>
-    <t>steam.price = x</t>
-  </si>
-  <si>
     <t>K_1l</t>
   </si>
   <si>
@@ -608,12 +602,6 @@
     <t>feedstock.imass['Starch'] =x * feedstock.imass['Water']</t>
   </si>
   <si>
-    <t>Isobutanol unit price</t>
-  </si>
-  <si>
-    <t>DDGS unit price</t>
-  </si>
-  <si>
     <t>Isopentyl acetate unit price</t>
   </si>
   <si>
@@ -624,6 +612,12 @@
   </si>
   <si>
     <t>V406.aeration_safety_factor = x</t>
+  </si>
+  <si>
+    <t>DDGS unit price (sale)</t>
+  </si>
+  <si>
+    <t>Isobutanol selling unit price (sale)</t>
   </si>
 </sst>
 </file>
@@ -986,7 +980,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K76"/>
+  <dimension ref="A1:K75"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40.81640625" customWidth="1"/>
@@ -1187,12 +1181,12 @@
         <v>18</v>
       </c>
       <c r="G6" s="4">
-        <f t="shared" ref="G6:G14" si="0">E6*0.8</f>
+        <f t="shared" ref="G6:G13" si="0">E6*0.8</f>
         <v>0.35920000000000002</v>
       </c>
       <c r="H6" s="4"/>
       <c r="I6" s="4">
-        <f t="shared" ref="I6:I14" si="1">1.2*E6</f>
+        <f t="shared" ref="I6:I13" si="1">1.2*E6</f>
         <v>0.53879999999999995</v>
       </c>
       <c r="J6" s="4"/>
@@ -1334,7 +1328,7 @@
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>52</v>
+        <v>192</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>7</v>
@@ -1346,28 +1340,28 @@
         <v>10</v>
       </c>
       <c r="E11" s="4">
-        <v>1.2999999999999999E-2</v>
+        <v>0.12</v>
       </c>
       <c r="F11" s="4" t="s">
         <v>18</v>
       </c>
       <c r="G11" s="4">
         <f t="shared" si="0"/>
-        <v>1.04E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H11" s="4"/>
       <c r="I11" s="4">
         <f t="shared" si="1"/>
-        <v>1.5599999999999999E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J11" s="4"/>
       <c r="K11" s="4" t="s">
-        <v>105</v>
+        <v>182</v>
       </c>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>191</v>
+        <v>193</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>7</v>
@@ -1379,28 +1373,29 @@
         <v>10</v>
       </c>
       <c r="E12" s="4">
-        <v>0.12</v>
+        <v>1.49</v>
       </c>
       <c r="F12" s="4" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
-        <v>9.6000000000000002E-2</v>
-      </c>
-      <c r="H12" s="4"/>
+        <v>0.95</v>
+      </c>
+      <c r="H12" s="4">
+        <f>E12</f>
+        <v>1.49</v>
+      </c>
       <c r="I12" s="4">
-        <f t="shared" si="1"/>
-        <v>0.14399999999999999</v>
+        <v>1.7250000000000001</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>7</v>
@@ -1412,59 +1407,61 @@
         <v>10</v>
       </c>
       <c r="E13" s="4">
-        <v>1.49</v>
+        <v>3.2</v>
       </c>
       <c r="F13" s="4" t="s">
         <v>18</v>
       </c>
       <c r="G13" s="4">
-        <v>0.95</v>
+        <f t="shared" si="0"/>
+        <v>2.5600000000000005</v>
       </c>
       <c r="H13" s="4"/>
       <c r="I13" s="4">
-        <v>1.7250000000000001</v>
+        <f t="shared" si="1"/>
+        <v>3.84</v>
       </c>
       <c r="J13" s="4"/>
       <c r="K13" s="4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A14" s="4" t="s">
-        <v>192</v>
-      </c>
-      <c r="B14" s="4" t="s">
+      <c r="A14" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B14" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C14" s="4" t="s">
+      <c r="C14" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D14" s="4" t="s">
+      <c r="D14" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E14" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="F14" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G14" s="4">
-        <f t="shared" si="0"/>
-        <v>2.5600000000000005</v>
-      </c>
-      <c r="H14" s="4"/>
-      <c r="I14" s="4">
-        <f t="shared" si="1"/>
-        <v>3.84</v>
-      </c>
-      <c r="J14" s="4"/>
-      <c r="K14" s="4" t="s">
-        <v>186</v>
+      <c r="E14" s="6">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="F14" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G14" s="6">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="H14" s="6">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="I14" s="6">
+        <v>0.315</v>
+      </c>
+      <c r="J14" s="6"/>
+      <c r="K14" s="6" t="s">
+        <v>85</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B15" s="6" t="s">
         <v>7</v>
@@ -1476,19 +1473,22 @@
         <v>10</v>
       </c>
       <c r="E15" s="6">
-        <v>0.28599999999999998</v>
+        <v>0.10355</v>
       </c>
       <c r="F15" s="6" t="s">
         <v>27</v>
       </c>
       <c r="G15" s="6">
-        <v>0.17499999999999999</v>
+        <f>E15*0.9</f>
+        <v>9.3195E-2</v>
       </c>
       <c r="H15" s="6">
-        <v>0.28599999999999998</v>
+        <f>E15</f>
+        <v>0.10355</v>
       </c>
       <c r="I15" s="6">
-        <v>0.315</v>
+        <f>E15*1.1</f>
+        <v>0.11390500000000001</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6" t="s">
@@ -1496,44 +1496,39 @@
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A16" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B16" s="6" t="s">
+      <c r="A16" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B16" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C16" s="6" t="s">
+      <c r="C16" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D16" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E16" s="6">
-        <v>0.10355</v>
-      </c>
-      <c r="F16" s="6" t="s">
-        <v>27</v>
-      </c>
-      <c r="G16" s="6">
-        <f>E16*0.9</f>
-        <v>9.3195E-2</v>
-      </c>
-      <c r="H16" s="6">
-        <f>E16</f>
-        <v>0.10355</v>
-      </c>
-      <c r="I16" s="6">
-        <f>E16*1.1</f>
-        <v>0.11390500000000001</v>
-      </c>
-      <c r="J16" s="6"/>
-      <c r="K16" s="6" t="s">
-        <v>87</v>
+      <c r="D16" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E16" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="F16" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="G16" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="H16" s="3"/>
+      <c r="I16" s="3">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J16" s="3"/>
+      <c r="K16" s="3" t="s">
+        <v>34</v>
       </c>
     </row>
     <row r="17" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>7</v>
@@ -1545,59 +1540,64 @@
         <v>8</v>
       </c>
       <c r="E17" s="3">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>18</v>
       </c>
       <c r="G17" s="3">
-        <v>0.15</v>
+        <f>0.8*E17</f>
+        <v>0.12</v>
       </c>
       <c r="H17" s="3"/>
       <c r="I17" s="3">
-        <v>0.28000000000000003</v>
+        <f>1.2*E17</f>
+        <v>0.18</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
     </row>
     <row r="18" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>32</v>
+        <v>185</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C18" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>8</v>
+        <v>186</v>
       </c>
       <c r="E18" s="3">
-        <v>0.15</v>
+        <v>4.08</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G18" s="3">
-        <f>0.8*E18</f>
-        <v>0.12</v>
-      </c>
-      <c r="H18" s="3"/>
+        <f>0.8*H18</f>
+        <v>3.2640000000000002</v>
+      </c>
+      <c r="H18" s="3">
+        <f>E18</f>
+        <v>4.08</v>
+      </c>
       <c r="I18" s="3">
-        <f>1.2*E18</f>
-        <v>0.18</v>
+        <f>1.2*H18</f>
+        <v>4.8959999999999999</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>33</v>
+        <v>187</v>
       </c>
     </row>
     <row r="19" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>187</v>
+        <v>38</v>
       </c>
       <c r="B19" s="3" t="s">
         <v>39</v>
@@ -1606,96 +1606,96 @@
         <v>21</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>188</v>
+        <v>40</v>
       </c>
       <c r="E19" s="3">
-        <v>4.08</v>
+        <v>56972</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G19" s="3">
         <f>0.8*H19</f>
-        <v>3.2640000000000002</v>
+        <v>45577.600000000006</v>
       </c>
       <c r="H19" s="3">
         <f>E19</f>
-        <v>4.08</v>
+        <v>56972</v>
       </c>
       <c r="I19" s="3">
         <f>1.2*H19</f>
-        <v>4.8959999999999999</v>
+        <v>68366.399999999994</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
-        <v>189</v>
+        <v>41</v>
       </c>
     </row>
     <row r="20" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>38</v>
+        <v>189</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>39</v>
+        <v>190</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E20" s="3">
-        <v>56972</v>
+        <v>2</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G20" s="3">
-        <f>0.8*H20</f>
-        <v>45577.600000000006</v>
-      </c>
-      <c r="H20" s="3">
-        <f>E20</f>
-        <v>56972</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H20" s="3"/>
       <c r="I20" s="3">
-        <f>1.2*H20</f>
-        <v>68366.399999999994</v>
+        <v>3</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3" t="s">
-        <v>41</v>
+        <v>191</v>
       </c>
     </row>
     <row r="21" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>193</v>
+        <v>52</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>194</v>
+        <v>13</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E21" s="3">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G21" s="3">
-        <v>1</v>
-      </c>
-      <c r="H21" s="3"/>
+        <f>E21*0.8</f>
+        <v>124.80000000000001</v>
+      </c>
+      <c r="H21" s="3">
+        <f>E21</f>
+        <v>156</v>
+      </c>
       <c r="I21" s="3">
-        <v>3</v>
+        <f>E21*1.2</f>
+        <v>187.2</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>195</v>
+        <v>54</v>
       </c>
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.35">
@@ -1736,232 +1736,229 @@
     </row>
     <row r="23" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>54</v>
+        <v>121</v>
       </c>
       <c r="B23" s="3" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="E23" s="3">
-        <v>156</v>
+        <v>1.43</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="G23" s="3">
-        <f>E23*0.8</f>
-        <v>124.80000000000001</v>
+        <v>1.1439999999999999</v>
       </c>
       <c r="H23" s="3">
-        <f>E23</f>
-        <v>156</v>
+        <v>1.43</v>
       </c>
       <c r="I23" s="3">
-        <f>E23*1.2</f>
-        <v>187.2</v>
+        <v>1.716</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3" t="s">
-        <v>56</v>
+        <v>62</v>
       </c>
     </row>
     <row r="24" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>123</v>
+        <v>104</v>
       </c>
       <c r="B24" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E24" s="3">
-        <v>1.43</v>
+        <v>0.94</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G24" s="3">
-        <v>1.1439999999999999</v>
+        <v>0.752</v>
       </c>
       <c r="H24" s="3">
-        <v>1.43</v>
+        <v>0.94</v>
       </c>
       <c r="I24" s="3">
-        <v>1.716</v>
+        <v>1.1279999999999999</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3" t="s">
-        <v>63</v>
+        <v>87</v>
       </c>
     </row>
     <row r="25" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>106</v>
+        <v>122</v>
       </c>
       <c r="B25" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E25" s="3">
-        <v>0.94</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G25" s="3">
-        <v>0.752</v>
+        <v>0.4672</v>
       </c>
       <c r="H25" s="3">
-        <v>0.94</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="I25" s="3">
-        <v>1.1279999999999999</v>
+        <v>0.70079999999999998</v>
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3" t="s">
-        <v>88</v>
+        <v>58</v>
       </c>
     </row>
     <row r="26" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>124</v>
+        <v>105</v>
       </c>
       <c r="B26" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E26" s="3">
-        <v>0.58399999999999996</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="F26" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G26" s="3">
-        <v>0.4672</v>
+        <v>9.2800000000000001E-3</v>
       </c>
       <c r="H26" s="3">
-        <v>0.58399999999999996</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="I26" s="3">
-        <v>0.70079999999999998</v>
+        <v>1.3919999999999899E-2</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="s">
-        <v>59</v>
+        <v>88</v>
       </c>
     </row>
     <row r="27" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>107</v>
+        <v>123</v>
       </c>
       <c r="B27" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C27" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E27" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>47.1</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G27" s="3">
-        <v>9.2800000000000001E-3</v>
+        <v>37.68</v>
       </c>
       <c r="H27" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>47.1</v>
       </c>
       <c r="I27" s="3">
-        <v>1.3919999999999899E-2</v>
+        <v>56.52</v>
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3" t="s">
-        <v>89</v>
+        <v>57</v>
       </c>
     </row>
     <row r="28" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>125</v>
+        <v>106</v>
       </c>
       <c r="B28" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C28" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E28" s="3">
-        <v>47.1</v>
+        <v>14.2</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G28" s="3">
-        <v>37.68</v>
+        <v>11.36</v>
       </c>
       <c r="H28" s="3">
-        <v>47.1</v>
+        <v>14.2</v>
       </c>
       <c r="I28" s="3">
-        <v>56.52</v>
+        <v>17.04</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>58</v>
+        <v>89</v>
       </c>
     </row>
     <row r="29" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="B29" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C29" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E29" s="3">
-        <v>14.2</v>
+        <v>0.12</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G29" s="3">
-        <v>11.36</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H29" s="3">
-        <v>14.2</v>
+        <v>0.12</v>
       </c>
       <c r="I29" s="3">
-        <v>17.04</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3" t="s">
@@ -1970,64 +1967,64 @@
     </row>
     <row r="30" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>109</v>
+        <v>124</v>
       </c>
       <c r="B30" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C30" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D30" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E30" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G30" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H30" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I30" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3" t="s">
-        <v>91</v>
+        <v>59</v>
       </c>
     </row>
     <row r="31" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D31" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E31" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G31" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H31" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I31" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3" t="s">
@@ -2036,31 +2033,31 @@
     </row>
     <row r="32" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E32" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F32" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G32" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H32" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I32" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3" t="s">
@@ -2069,97 +2066,97 @@
     </row>
     <row r="33" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="B33" s="3" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E33" s="3">
-        <v>0.04</v>
+        <v>0.501</v>
       </c>
       <c r="F33" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G33" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>0.40079999999999999</v>
       </c>
       <c r="H33" s="3">
-        <v>0.04</v>
+        <v>0.501</v>
       </c>
       <c r="I33" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.60119999999999996</v>
       </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3" t="s">
-        <v>62</v>
+        <v>56</v>
       </c>
     </row>
     <row r="34" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>129</v>
+        <v>108</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E34" s="3">
-        <v>0.501</v>
+        <v>67</v>
+      </c>
+      <c r="E34" s="5">
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G34" s="3">
-        <v>0.40079999999999999</v>
-      </c>
-      <c r="H34" s="3">
-        <v>0.501</v>
-      </c>
-      <c r="I34" s="3">
-        <v>0.60119999999999996</v>
+        <v>66</v>
+      </c>
+      <c r="G34" s="5">
+        <v>1.5999999999999999E-5</v>
+      </c>
+      <c r="H34" s="5">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="I34" s="5">
+        <v>2.4000000000000001E-5</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>57</v>
+        <v>91</v>
       </c>
     </row>
     <row r="35" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E35" s="5">
-        <v>2.0000000000000002E-5</v>
+        <v>67</v>
+      </c>
+      <c r="E35" s="3">
+        <v>0.10100000000000001</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G35" s="5">
-        <v>1.5999999999999999E-5</v>
-      </c>
-      <c r="H35" s="5">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="I35" s="5">
-        <v>2.4000000000000001E-5</v>
+        <v>66</v>
+      </c>
+      <c r="G35" s="3">
+        <v>8.0799999999999997E-2</v>
+      </c>
+      <c r="H35" s="3">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="I35" s="3">
+        <v>0.1212</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3" t="s">
@@ -2168,163 +2165,163 @@
     </row>
     <row r="36" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>111</v>
+        <v>128</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E36" s="3">
-        <v>0.10100000000000001</v>
+        <v>5.81</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G36" s="3">
-        <v>8.0799999999999997E-2</v>
+        <v>4.6479999999999997</v>
       </c>
       <c r="H36" s="3">
-        <v>0.10100000000000001</v>
+        <v>5.81</v>
       </c>
       <c r="I36" s="3">
-        <v>0.1212</v>
+        <v>6.9719999999999898</v>
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="3" t="s">
-        <v>93</v>
+        <v>63</v>
       </c>
     </row>
     <row r="37" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>130</v>
+        <v>110</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E37" s="3">
-        <v>5.81</v>
+        <v>67</v>
+      </c>
+      <c r="E37" s="5">
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G37" s="3">
-        <v>4.6479999999999997</v>
-      </c>
-      <c r="H37" s="3">
-        <v>5.81</v>
-      </c>
-      <c r="I37" s="3">
-        <v>6.9719999999999898</v>
+        <v>66</v>
+      </c>
+      <c r="G37" s="5">
+        <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="H37" s="5">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="I37" s="5">
+        <v>5.9999999999999997E-7</v>
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3" t="s">
-        <v>64</v>
+        <v>93</v>
       </c>
     </row>
     <row r="38" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>112</v>
+        <v>129</v>
       </c>
       <c r="B38" s="3" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D38" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E38" s="5">
-        <v>4.9999999999999998E-7</v>
+        <v>65</v>
+      </c>
+      <c r="E38" s="3">
+        <v>4.8</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G38" s="5">
-        <v>3.9999999999999998E-7</v>
-      </c>
-      <c r="H38" s="5">
-        <v>4.9999999999999998E-7</v>
-      </c>
-      <c r="I38" s="5">
-        <v>5.9999999999999997E-7</v>
+        <v>66</v>
+      </c>
+      <c r="G38" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="H38" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="I38" s="3">
+        <v>5.76</v>
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>94</v>
+        <v>64</v>
       </c>
     </row>
     <row r="39" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="B39" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D39" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E39" s="3">
-        <v>4.8</v>
+        <v>0.04</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G39" s="3">
-        <v>3.84</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H39" s="3">
-        <v>4.8</v>
+        <v>0.04</v>
       </c>
       <c r="I39" s="3">
-        <v>5.76</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3" t="s">
-        <v>65</v>
+        <v>68</v>
       </c>
     </row>
     <row r="40" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="B40" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E40" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G40" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H40" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I40" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3" t="s">
@@ -2333,31 +2330,31 @@
     </row>
     <row r="41" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E41" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G41" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H41" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I41" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
@@ -2366,196 +2363,196 @@
     </row>
     <row r="42" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>134</v>
+        <v>111</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E42" s="3">
-        <v>0.04</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G42" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>2.1120000000000001E-4</v>
       </c>
       <c r="H42" s="3">
-        <v>0.04</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="I42" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>3.168E-4</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3" t="s">
-        <v>71</v>
+        <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>113</v>
+        <v>133</v>
       </c>
       <c r="B43" s="3" t="s">
-        <v>152</v>
+        <v>155</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E43" s="3">
-        <v>2.6400000000000002E-4</v>
+        <v>1.04E-2</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G43" s="3">
-        <v>2.1120000000000001E-4</v>
+        <v>8.3199999999999993E-3</v>
       </c>
       <c r="H43" s="3">
-        <v>2.6400000000000002E-4</v>
+        <v>1.04E-2</v>
       </c>
       <c r="I43" s="3">
-        <v>3.168E-4</v>
+        <v>1.248E-2</v>
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="3" t="s">
-        <v>95</v>
+        <v>71</v>
       </c>
     </row>
     <row r="44" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>135</v>
+        <v>112</v>
       </c>
       <c r="B44" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E44" s="3">
-        <v>1.04E-2</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G44" s="3">
-        <v>8.3199999999999993E-3</v>
+        <v>8.1600000000000006E-3</v>
       </c>
       <c r="H44" s="3">
-        <v>1.04E-2</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="I44" s="3">
-        <v>1.248E-2</v>
+        <v>1.2239999999999999E-2</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>72</v>
+        <v>95</v>
       </c>
     </row>
     <row r="45" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>114</v>
+        <v>134</v>
       </c>
       <c r="B45" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E45" s="3">
-        <v>1.0200000000000001E-2</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G45" s="3">
-        <v>8.1600000000000006E-3</v>
+        <v>0.62</v>
       </c>
       <c r="H45" s="3">
-        <v>1.0200000000000001E-2</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="I45" s="3">
-        <v>1.2239999999999999E-2</v>
+        <v>0.92999999999999905</v>
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3" t="s">
-        <v>96</v>
+        <v>72</v>
       </c>
     </row>
     <row r="46" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>136</v>
+        <v>113</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E46" s="3">
-        <v>0.77500000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="F46" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G46" s="3">
-        <v>0.62</v>
+        <v>0.08</v>
       </c>
       <c r="H46" s="3">
-        <v>0.77500000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="I46" s="3">
-        <v>0.92999999999999905</v>
+        <v>0.12</v>
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>73</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>115</v>
+        <v>114</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E47" s="3">
-        <v>0.1</v>
+        <v>440</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G47" s="3">
-        <v>0.08</v>
+        <v>352</v>
       </c>
       <c r="H47" s="3">
-        <v>0.1</v>
+        <v>440</v>
       </c>
       <c r="I47" s="3">
-        <v>0.12</v>
+        <v>528</v>
       </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3" t="s">
@@ -2564,64 +2561,64 @@
     </row>
     <row r="48" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>116</v>
+        <v>135</v>
       </c>
       <c r="B48" s="3" t="s">
-        <v>157</v>
+        <v>151</v>
       </c>
       <c r="C48" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E48" s="3">
-        <v>440</v>
+        <v>2.82</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G48" s="3">
-        <v>352</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="H48" s="3">
-        <v>440</v>
+        <v>2.82</v>
       </c>
       <c r="I48" s="3">
-        <v>528</v>
+        <v>3.3839999999999999</v>
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="3" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
     </row>
     <row r="49" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
       <c r="B49" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C49" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E49" s="3">
-        <v>2.82</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G49" s="3">
-        <v>2.2559999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="H49" s="3">
-        <v>2.82</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="I49" s="3">
-        <v>3.3839999999999999</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="3" t="s">
@@ -2630,64 +2627,64 @@
     </row>
     <row r="50" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>138</v>
+        <v>115</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E50" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G50" s="3">
-        <v>0.01</v>
+        <v>2.7199999999999998E-2</v>
       </c>
       <c r="H50" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="I50" s="3">
-        <v>1.4999999999999999E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3" t="s">
-        <v>75</v>
+        <v>98</v>
       </c>
     </row>
     <row r="51" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>117</v>
+        <v>116</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E51" s="3">
-        <v>3.4000000000000002E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G51" s="3">
-        <v>2.7199999999999998E-2</v>
+        <v>4.5600000000000002E-2</v>
       </c>
       <c r="H51" s="3">
-        <v>3.4000000000000002E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="I51" s="3">
-        <v>4.0800000000000003E-2</v>
+        <v>6.8400000000000002E-2</v>
       </c>
       <c r="J51" s="3"/>
       <c r="K51" s="3" t="s">
@@ -2696,64 +2693,64 @@
     </row>
     <row r="52" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
-        <v>118</v>
+        <v>137</v>
       </c>
       <c r="B52" s="3" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D52" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E52" s="3">
-        <v>5.7000000000000002E-2</v>
+        <v>1.2030000000000001</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G52" s="3">
-        <v>4.5600000000000002E-2</v>
+        <v>0.96240000000000003</v>
       </c>
       <c r="H52" s="3">
-        <v>5.7000000000000002E-2</v>
+        <v>1.2030000000000001</v>
       </c>
       <c r="I52" s="3">
-        <v>6.8400000000000002E-2</v>
+        <v>1.4436</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
-        <v>100</v>
+        <v>75</v>
       </c>
     </row>
     <row r="53" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="B53" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D53" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E53" s="3">
-        <v>1.2030000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G53" s="3">
-        <v>0.96240000000000003</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H53" s="3">
-        <v>1.2030000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="I53" s="3">
-        <v>1.4436</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
@@ -2762,31 +2759,31 @@
     </row>
     <row r="54" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
       <c r="B54" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E54" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G54" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H54" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I54" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
@@ -2795,31 +2792,31 @@
     </row>
     <row r="55" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E55" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G55" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H55" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I55" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
@@ -2828,97 +2825,97 @@
     </row>
     <row r="56" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>142</v>
+        <v>117</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E56" s="3">
-        <v>0.04</v>
+        <v>1.01E-2</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G56" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>8.0800000000000004E-3</v>
       </c>
       <c r="H56" s="3">
-        <v>0.04</v>
+        <v>1.01E-2</v>
       </c>
       <c r="I56" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>1.21199999999999E-2</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>79</v>
+        <v>100</v>
       </c>
     </row>
     <row r="57" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>119</v>
+        <v>141</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E57" s="3">
-        <v>1.01E-2</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G57" s="3">
-        <v>8.0800000000000004E-3</v>
+        <v>0.47120000000000001</v>
       </c>
       <c r="H57" s="3">
-        <v>1.01E-2</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="I57" s="3">
-        <v>1.21199999999999E-2</v>
+        <v>0.70679999999999998</v>
       </c>
       <c r="J57" s="3"/>
       <c r="K57" s="3" t="s">
-        <v>101</v>
+        <v>79</v>
       </c>
     </row>
     <row r="58" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="B58" s="3" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E58" s="3">
-        <v>0.58899999999999997</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G58" s="3">
-        <v>0.47120000000000001</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="H58" s="3">
-        <v>0.58899999999999997</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="I58" s="3">
-        <v>0.70679999999999998</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3" t="s">
@@ -2927,130 +2924,130 @@
     </row>
     <row r="59" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>144</v>
+        <v>118</v>
       </c>
       <c r="B59" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E59" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>67</v>
+      </c>
+      <c r="E59" s="5">
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G59" s="3">
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="H59" s="3">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="I59" s="3">
-        <v>9.5999999999999992E-3</v>
+        <v>66</v>
+      </c>
+      <c r="G59" s="5">
+        <v>7.9999999999999996E-7</v>
+      </c>
+      <c r="H59" s="5">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="I59" s="5">
+        <v>1.1999999999999999E-6</v>
       </c>
       <c r="J59" s="3"/>
       <c r="K59" s="3" t="s">
-        <v>81</v>
+        <v>101</v>
       </c>
     </row>
     <row r="60" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
-        <v>120</v>
+        <v>143</v>
       </c>
       <c r="B60" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E60" s="5">
-        <v>9.9999999999999995E-7</v>
+        <v>65</v>
+      </c>
+      <c r="E60" s="3">
+        <v>7.51E-2</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G60" s="5">
-        <v>7.9999999999999996E-7</v>
-      </c>
-      <c r="H60" s="5">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="I60" s="5">
-        <v>1.1999999999999999E-6</v>
+        <v>66</v>
+      </c>
+      <c r="G60" s="3">
+        <v>6.0080000000000001E-2</v>
+      </c>
+      <c r="H60" s="3">
+        <v>7.51E-2</v>
+      </c>
+      <c r="I60" s="3">
+        <v>9.0119999999999895E-2</v>
       </c>
       <c r="J60" s="3"/>
       <c r="K60" s="3" t="s">
-        <v>102</v>
+        <v>81</v>
       </c>
     </row>
     <row r="61" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>145</v>
+        <v>119</v>
       </c>
       <c r="B61" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E61" s="3">
-        <v>7.51E-2</v>
+        <v>13</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G61" s="3">
-        <v>6.0080000000000001E-2</v>
+        <v>10.4</v>
       </c>
       <c r="H61" s="3">
-        <v>7.51E-2</v>
+        <v>13</v>
       </c>
       <c r="I61" s="3">
-        <v>9.0119999999999895E-2</v>
+        <v>15.6</v>
       </c>
       <c r="J61" s="3"/>
       <c r="K61" s="3" t="s">
-        <v>82</v>
+        <v>102</v>
       </c>
     </row>
     <row r="62" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E62" s="3">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G62" s="3">
-        <v>10.4</v>
+        <v>20</v>
       </c>
       <c r="H62" s="3">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I62" s="3">
-        <v>15.6</v>
+        <v>30</v>
       </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3" t="s">
@@ -3059,40 +3056,40 @@
     </row>
     <row r="63" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
-        <v>122</v>
+        <v>144</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D63" s="3" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="E63" s="3">
-        <v>25</v>
+        <v>3.9899999999999996E-3</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G63" s="3">
-        <v>20</v>
+        <v>3.192E-3</v>
       </c>
       <c r="H63" s="3">
-        <v>25</v>
+        <v>3.9899999999999996E-3</v>
       </c>
       <c r="I63" s="3">
-        <v>30</v>
+        <v>4.7879999999999997E-3</v>
       </c>
       <c r="J63" s="3"/>
       <c r="K63" s="3" t="s">
-        <v>104</v>
+        <v>82</v>
       </c>
     </row>
     <row r="64" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="B64" s="3" t="s">
         <v>156</v>
@@ -3101,22 +3098,22 @@
         <v>21</v>
       </c>
       <c r="D64" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E64" s="3">
-        <v>3.9899999999999996E-3</v>
+        <v>0.06</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G64" s="3">
-        <v>3.192E-3</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="H64" s="3">
-        <v>3.9899999999999996E-3</v>
+        <v>0.06</v>
       </c>
       <c r="I64" s="3">
-        <v>4.7879999999999997E-3</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="J64" s="3"/>
       <c r="K64" s="3" t="s">
@@ -3125,31 +3122,31 @@
     </row>
     <row r="65" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E65" s="3">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G65" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="H65" s="3">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I65" s="3">
-        <v>7.1999999999999995E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="J65" s="3"/>
       <c r="K65" s="3" t="s">
@@ -3158,35 +3155,38 @@
     </row>
     <row r="66" spans="1:11" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
-        <v>148</v>
+        <v>158</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>159</v>
+        <v>178</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E66" s="3">
-        <v>0.02</v>
+        <v>5.81</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G66" s="3">
-        <v>1.6E-2</v>
-      </c>
-      <c r="H66" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="I66" s="3">
-        <v>2.4E-2</v>
+        <v>66</v>
+      </c>
+      <c r="G66" s="5">
+        <f>E66*0.8</f>
+        <v>4.6479999999999997</v>
+      </c>
+      <c r="H66" s="5">
+        <f>E66</f>
+        <v>5.81</v>
+      </c>
+      <c r="I66" s="5">
+        <f>1.2*E66</f>
+        <v>6.9719999999999995</v>
       </c>
       <c r="J66" s="3"/>
       <c r="K66" s="3" t="s">
-        <v>85</v>
+        <v>159</v>
       </c>
     </row>
     <row r="67" spans="1:11" x14ac:dyDescent="0.35">
@@ -3194,31 +3194,31 @@
         <v>160</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E67" s="3">
-        <v>5.81</v>
+        <v>67</v>
+      </c>
+      <c r="E67" s="5">
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G67" s="5">
         <f>E67*0.8</f>
-        <v>4.6479999999999997</v>
+        <v>3.9999999999999998E-7</v>
       </c>
       <c r="H67" s="5">
         <f>E67</f>
-        <v>5.81</v>
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="I67" s="5">
         <f>1.2*E67</f>
-        <v>6.9719999999999995</v>
+        <v>5.9999999999999997E-7</v>
       </c>
       <c r="J67" s="3"/>
       <c r="K67" s="3" t="s">
@@ -3230,31 +3230,31 @@
         <v>162</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E68" s="5">
-        <v>4.9999999999999998E-7</v>
+        <v>65</v>
+      </c>
+      <c r="E68" s="3">
+        <v>4.8</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G68" s="5">
-        <f>E68*0.8</f>
-        <v>3.9999999999999998E-7</v>
+        <f t="shared" ref="G68:G75" si="2">E68*0.8</f>
+        <v>3.84</v>
       </c>
       <c r="H68" s="5">
-        <f>E68</f>
-        <v>4.9999999999999998E-7</v>
+        <f t="shared" ref="H68:H75" si="3">E68</f>
+        <v>4.8</v>
       </c>
       <c r="I68" s="5">
-        <f>1.2*E68</f>
-        <v>5.9999999999999997E-7</v>
+        <f t="shared" ref="I68:I75" si="4">1.2*E68</f>
+        <v>5.76</v>
       </c>
       <c r="J68" s="3"/>
       <c r="K68" s="3" t="s">
@@ -3266,31 +3266,31 @@
         <v>164</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E69" s="3">
-        <v>4.8</v>
+        <v>67</v>
+      </c>
+      <c r="E69" s="5">
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G69" s="5">
-        <f t="shared" ref="G69:G76" si="2">E69*0.8</f>
-        <v>3.84</v>
+        <f t="shared" si="2"/>
+        <v>2.1120000000000004E-4</v>
       </c>
       <c r="H69" s="5">
-        <f t="shared" ref="H69:H76" si="3">E69</f>
-        <v>4.8</v>
+        <f t="shared" si="3"/>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="I69" s="5">
-        <f t="shared" ref="I69:I76" si="4">1.2*E69</f>
-        <v>5.76</v>
+        <f t="shared" si="4"/>
+        <v>3.168E-4</v>
       </c>
       <c r="J69" s="3"/>
       <c r="K69" s="3" t="s">
@@ -3302,31 +3302,31 @@
         <v>166</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E70" s="5">
-        <v>2.6400000000000002E-4</v>
+        <v>65</v>
+      </c>
+      <c r="E70" s="3">
+        <v>4.8</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G70" s="5">
         <f t="shared" si="2"/>
-        <v>2.1120000000000004E-4</v>
+        <v>3.84</v>
       </c>
       <c r="H70" s="5">
         <f t="shared" si="3"/>
-        <v>2.6400000000000002E-4</v>
+        <v>4.8</v>
       </c>
       <c r="I70" s="5">
         <f t="shared" si="4"/>
-        <v>3.168E-4</v>
+        <v>5.76</v>
       </c>
       <c r="J70" s="3"/>
       <c r="K70" s="3" t="s">
@@ -3338,31 +3338,31 @@
         <v>168</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="E71" s="3">
-        <v>4.8</v>
+        <v>67</v>
+      </c>
+      <c r="E71" s="5">
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G71" s="5">
         <f t="shared" si="2"/>
-        <v>3.84</v>
+        <v>2.1120000000000004E-4</v>
       </c>
       <c r="H71" s="5">
         <f t="shared" si="3"/>
-        <v>4.8</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="I71" s="5">
         <f t="shared" si="4"/>
-        <v>5.76</v>
+        <v>3.168E-4</v>
       </c>
       <c r="J71" s="3"/>
       <c r="K71" s="3" t="s">
@@ -3374,31 +3374,31 @@
         <v>170</v>
       </c>
       <c r="B72" s="3" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="C72" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E72" s="5">
-        <v>2.6400000000000002E-4</v>
+        <v>65</v>
+      </c>
+      <c r="E72" s="3">
+        <v>2.82</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G72" s="5">
         <f t="shared" si="2"/>
-        <v>2.1120000000000004E-4</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="H72" s="5">
         <f t="shared" si="3"/>
-        <v>2.6400000000000002E-4</v>
+        <v>2.82</v>
       </c>
       <c r="I72" s="5">
         <f t="shared" si="4"/>
-        <v>3.168E-4</v>
+        <v>3.3839999999999999</v>
       </c>
       <c r="J72" s="3"/>
       <c r="K72" s="3" t="s">
@@ -3410,31 +3410,31 @@
         <v>172</v>
       </c>
       <c r="B73" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C73" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="E73" s="3">
-        <v>2.82</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G73" s="5">
         <f t="shared" si="2"/>
-        <v>2.2559999999999998</v>
+        <v>1.0000000000000002E-2</v>
       </c>
       <c r="H73" s="5">
         <f t="shared" si="3"/>
-        <v>2.82</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="I73" s="5">
         <f t="shared" si="4"/>
-        <v>3.3839999999999999</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="J73" s="3"/>
       <c r="K73" s="3" t="s">
@@ -3446,31 +3446,31 @@
         <v>174</v>
       </c>
       <c r="B74" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C74" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D74" s="3" t="s">
-        <v>66</v>
+        <v>67</v>
       </c>
       <c r="E74" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="F74" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G74" s="5">
         <f t="shared" si="2"/>
-        <v>1.0000000000000002E-2</v>
+        <v>2.7200000000000002E-2</v>
       </c>
       <c r="H74" s="5">
         <f t="shared" si="3"/>
-        <v>1.2500000000000001E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="I74" s="5">
         <f t="shared" si="4"/>
-        <v>1.4999999999999999E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="J74" s="3"/>
       <c r="K74" s="3" t="s">
@@ -3482,71 +3482,35 @@
         <v>176</v>
       </c>
       <c r="B75" s="3" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="C75" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D75" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="E75" s="3">
-        <v>3.4000000000000002E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="F75" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="G75" s="5">
         <f t="shared" si="2"/>
-        <v>2.7200000000000002E-2</v>
+        <v>4.5600000000000002E-2</v>
       </c>
       <c r="H75" s="5">
         <f t="shared" si="3"/>
-        <v>3.4000000000000002E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="I75" s="5">
         <f t="shared" si="4"/>
-        <v>4.0800000000000003E-2</v>
+        <v>6.8400000000000002E-2</v>
       </c>
       <c r="J75" s="3"/>
       <c r="K75" s="3" t="s">
         <v>177</v>
-      </c>
-    </row>
-    <row r="76" spans="1:11" x14ac:dyDescent="0.35">
-      <c r="A76" s="3" t="s">
-        <v>178</v>
-      </c>
-      <c r="B76" s="3" t="s">
-        <v>183</v>
-      </c>
-      <c r="C76" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D76" s="3" t="s">
-        <v>68</v>
-      </c>
-      <c r="E76" s="3">
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="F76" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="G76" s="5">
-        <f t="shared" si="2"/>
-        <v>4.5600000000000002E-2</v>
-      </c>
-      <c r="H76" s="5">
-        <f t="shared" si="3"/>
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="I76" s="5">
-        <f t="shared" si="4"/>
-        <v>6.8400000000000002E-2</v>
-      </c>
-      <c r="J76" s="3"/>
-      <c r="K76" s="3" t="s">
-        <v>179</v>
       </c>
     </row>
   </sheetData>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -8,13 +8,16 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saran\Documents\Academia\repository_clones\Bioindustrial-Park\biorefineries\isobutanol\analyses\full\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7DF3A6AF-CA6E-4CE5-BE3F-94D8BF95F734}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7189EE-26EF-4DE6-9BA5-179C71AF3E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1520" yWindow="1520" windowWidth="19200" windowHeight="11170" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
+  <externalReferences>
+    <externalReference r:id="rId2"/>
+  </externalReferences>
   <calcPr calcId="191029"/>
   <extLst>
     <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{140A7094-0E35-4892-8432-C4D2E57EDEB5}">
@@ -715,6 +718,1078 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/externalLinks/externalLink1.xml><?xml version="1.0" encoding="utf-8"?>
+<externalLink xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xxl21="http://schemas.microsoft.com/office/spreadsheetml/2021/extlinks2021" mc:Ignorable="x14 xxl21">
+  <externalBook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1">
+    <xxl21:alternateUrls>
+      <xxl21:absoluteUrl r:id="rId2"/>
+    </xxl21:alternateUrls>
+    <sheetNames>
+      <sheetName val="Sheet1"/>
+    </sheetNames>
+    <sheetDataSet>
+      <sheetData sheetId="0">
+        <row r="2">
+          <cell r="E2">
+            <v>1</v>
+          </cell>
+          <cell r="F2" t="str">
+            <v>Uniform</v>
+          </cell>
+          <cell r="G2">
+            <v>0.9</v>
+          </cell>
+          <cell r="I2">
+            <v>1.1000000000000001</v>
+          </cell>
+        </row>
+        <row r="3">
+          <cell r="E3">
+            <v>330</v>
+          </cell>
+          <cell r="F3" t="str">
+            <v>Triangular</v>
+          </cell>
+          <cell r="G3">
+            <v>297</v>
+          </cell>
+          <cell r="H3">
+            <v>330</v>
+          </cell>
+          <cell r="I3">
+            <v>363.00000000000006</v>
+          </cell>
+        </row>
+        <row r="4">
+          <cell r="E4">
+            <v>0.13900000000000001</v>
+          </cell>
+          <cell r="F4" t="str">
+            <v>Triangular</v>
+          </cell>
+          <cell r="G4">
+            <v>0.127</v>
+          </cell>
+          <cell r="H4">
+            <v>0.13900000000000001</v>
+          </cell>
+          <cell r="I4">
+            <v>0.15</v>
+          </cell>
+        </row>
+        <row r="5">
+          <cell r="E5">
+            <v>7.0000000000000007E-2</v>
+          </cell>
+          <cell r="F5" t="str">
+            <v>Triangular</v>
+          </cell>
+          <cell r="G5">
+            <v>6.7000000000000004E-2</v>
+          </cell>
+          <cell r="H5">
+            <v>7.0000000000000007E-2</v>
+          </cell>
+          <cell r="I5">
+            <v>7.3999999999999996E-2</v>
+          </cell>
+        </row>
+        <row r="6">
+          <cell r="E6">
+            <v>0.44900000000000001</v>
+          </cell>
+          <cell r="F6" t="str">
+            <v>Uniform</v>
+          </cell>
+          <cell r="G6">
+            <v>0.35920000000000002</v>
+          </cell>
+          <cell r="I6">
+            <v>0.53879999999999995</v>
+          </cell>
+        </row>
+        <row r="7">
+          <cell r="E7">
+            <v>1.86</v>
+          </cell>
+          <cell r="F7" t="str">
+            <v>Uniform</v>
+          </cell>
+          <cell r="G7">
+            <v>1.4880000000000002</v>
+          </cell>
+          <cell r="I7">
+            <v>2.2320000000000002</v>
+          </cell>
+        </row>
+        <row r="8">
+          <cell r="E8">
+            <v>2.25</v>
+          </cell>
+          <cell r="F8" t="str">
+            <v>Uniform</v>
+          </cell>
+          <cell r="G8">
+            <v>1.8</v>
+          </cell>
+          <cell r="I8">
+            <v>2.6999999999999997</v>
+          </cell>
+        </row>
+        <row r="9">
+          <cell r="E9">
+            <v>2.25</v>
+          </cell>
+          <cell r="F9" t="str">
+            <v>Uniform</v>
+          </cell>
+          <cell r="G9">
+            <v>1.8</v>
+          </cell>
+          <cell r="I9">
+            <v>2.6999999999999997</v>
+          </cell>
+        </row>
+        <row r="10">
+          <cell r="E10">
+            <v>0.436</v>
+          </cell>
+          <cell r="F10" t="str">
+            <v>Uniform</v>
+          </cell>
+          <cell r="G10">
+            <v>0.3488</v>
+          </cell>
+          <cell r="I10">
+            <v>0.5232</v>
+          </cell>
+        </row>
+        <row r="11">
+          <cell r="E11">
+            <v>0.12</v>
+          </cell>
+          <cell r="F11" t="str">
+            <v>Uniform</v>
+          </cell>
+          <cell r="G11">
+            <v>9.6000000000000002E-2</v>
+          </cell>
+          <cell r="I11">
+            <v>0.14399999999999999</v>
+          </cell>
+        </row>
+        <row r="12">
+          <cell r="E12">
+            <v>1.49</v>
+          </cell>
+          <cell r="F12" t="str">
+            <v>Triangular</v>
+          </cell>
+          <cell r="G12">
+            <v>1.1919999999999999</v>
+          </cell>
+          <cell r="H12">
+            <v>1.49</v>
+          </cell>
+          <cell r="I12">
+            <v>1.788</v>
+          </cell>
+        </row>
+        <row r="13">
+          <cell r="E13">
+            <v>3.2</v>
+          </cell>
+          <cell r="F13" t="str">
+            <v>Uniform</v>
+          </cell>
+          <cell r="G13">
+            <v>2.5600000000000005</v>
+          </cell>
+          <cell r="I13">
+            <v>3.84</v>
+          </cell>
+        </row>
+        <row r="14">
+          <cell r="E14">
+            <v>0.28599999999999998</v>
+          </cell>
+          <cell r="F14" t="str">
+            <v>Triangular</v>
+          </cell>
+          <cell r="G14">
+            <v>0.17499999999999999</v>
+          </cell>
+          <cell r="H14">
+            <v>0.28599999999999998</v>
+          </cell>
+          <cell r="I14">
+            <v>0.315</v>
+          </cell>
+        </row>
+        <row r="15">
+          <cell r="E15">
+            <v>0.10355</v>
+          </cell>
+          <cell r="F15" t="str">
+            <v>Triangular</v>
+          </cell>
+          <cell r="G15">
+            <v>9.3195E-2</v>
+          </cell>
+          <cell r="H15">
+            <v>0.10355</v>
+          </cell>
+          <cell r="I15">
+            <v>0.11390500000000001</v>
+          </cell>
+        </row>
+        <row r="16">
+          <cell r="E16">
+            <v>0.21</v>
+          </cell>
+          <cell r="F16" t="str">
+            <v>Uniform</v>
+          </cell>
+          <cell r="G16">
+            <v>0.15</v>
+          </cell>
+          <cell r="I16">
+            <v>0.28000000000000003</v>
+          </cell>
+        </row>
+        <row r="17">
+          <cell r="E17">
+            <v>0.15</v>
+          </cell>
+          <cell r="F17" t="str">
+            <v>Uniform</v>
+          </cell>
+          <cell r="G17">
+            <v>0.12</v>
+          </cell>
+          <cell r="I17">
+            <v>0.18</v>
+          </cell>
+        </row>
+        <row r="18">
+          <cell r="E18">
+            <v>4.08</v>
+          </cell>
+          <cell r="F18" t="str">
+            <v>Triangular</v>
+          </cell>
+          <cell r="G18">
+            <v>3.2640000000000002</v>
+          </cell>
+          <cell r="H18">
+            <v>4.08</v>
+          </cell>
+          <cell r="I18">
+            <v>4.8959999999999999</v>
+          </cell>
+        </row>
+        <row r="19">
+          <cell r="E19">
+            <v>56972</v>
+          </cell>
+          <cell r="F19" t="str">
+            <v>Triangular</v>
+          </cell>
+          <cell r="G19">
+            <v>45577.600000000006</v>
+          </cell>
+          <cell r="H19">
+            <v>56972</v>
+          </cell>
+          <cell r="I19">
+            <v>68366.399999999994</v>
+          </cell>
+        </row>
+        <row r="20">
+          <cell r="E20">
+            <v>2</v>
+          </cell>
+          <cell r="F20" t="str">
+            <v>Uniform</v>
+          </cell>
+          <cell r="G20">
+            <v>1</v>
+          </cell>
+          <cell r="I20">
+            <v>3</v>
+          </cell>
+        </row>
+        <row r="21">
+          <cell r="E21">
+            <v>156</v>
+          </cell>
+          <cell r="F21" t="str">
+            <v>Triangular</v>
+          </cell>
+          <cell r="G21">
+            <v>124.80000000000001</v>
+          </cell>
+          <cell r="H21">
+            <v>156</v>
+          </cell>
+          <cell r="I21">
+            <v>187.2</v>
+          </cell>
+        </row>
+        <row r="22">
+          <cell r="E22">
+            <v>156</v>
+          </cell>
+          <cell r="F22" t="str">
+            <v>Triangular</v>
+          </cell>
+          <cell r="G22">
+            <v>124.80000000000001</v>
+          </cell>
+          <cell r="H22">
+            <v>156</v>
+          </cell>
+          <cell r="I22">
+            <v>187.2</v>
+          </cell>
+        </row>
+        <row r="23">
+          <cell r="E23">
+            <v>1.43</v>
+          </cell>
+          <cell r="F23" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G23">
+            <v>1.1439999999999999</v>
+          </cell>
+          <cell r="H23">
+            <v>1.43</v>
+          </cell>
+          <cell r="I23">
+            <v>1.716</v>
+          </cell>
+        </row>
+        <row r="24">
+          <cell r="E24">
+            <v>0.94</v>
+          </cell>
+          <cell r="F24" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G24">
+            <v>0.752</v>
+          </cell>
+          <cell r="H24">
+            <v>0.94</v>
+          </cell>
+          <cell r="I24">
+            <v>1.1279999999999999</v>
+          </cell>
+        </row>
+        <row r="25">
+          <cell r="E25">
+            <v>0.58399999999999996</v>
+          </cell>
+          <cell r="F25" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G25">
+            <v>0.4672</v>
+          </cell>
+          <cell r="H25">
+            <v>0.58399999999999996</v>
+          </cell>
+          <cell r="I25">
+            <v>0.70079999999999998</v>
+          </cell>
+        </row>
+        <row r="26">
+          <cell r="E26">
+            <v>1.1599999999999999E-2</v>
+          </cell>
+          <cell r="F26" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G26">
+            <v>9.2800000000000001E-3</v>
+          </cell>
+          <cell r="H26">
+            <v>1.1599999999999999E-2</v>
+          </cell>
+          <cell r="I26">
+            <v>1.3919999999999899E-2</v>
+          </cell>
+        </row>
+        <row r="27">
+          <cell r="E27">
+            <v>47.1</v>
+          </cell>
+          <cell r="F27" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G27">
+            <v>37.68</v>
+          </cell>
+          <cell r="H27">
+            <v>47.1</v>
+          </cell>
+          <cell r="I27">
+            <v>56.52</v>
+          </cell>
+        </row>
+        <row r="28">
+          <cell r="E28">
+            <v>14.2</v>
+          </cell>
+          <cell r="F28" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G28">
+            <v>11.36</v>
+          </cell>
+          <cell r="H28">
+            <v>14.2</v>
+          </cell>
+          <cell r="I28">
+            <v>17.04</v>
+          </cell>
+        </row>
+        <row r="29">
+          <cell r="E29">
+            <v>0.12</v>
+          </cell>
+          <cell r="F29" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G29">
+            <v>9.6000000000000002E-2</v>
+          </cell>
+          <cell r="H29">
+            <v>0.12</v>
+          </cell>
+          <cell r="I29">
+            <v>0.14399999999999999</v>
+          </cell>
+        </row>
+        <row r="30">
+          <cell r="E30">
+            <v>0.04</v>
+          </cell>
+          <cell r="F30" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G30">
+            <v>3.2000000000000001E-2</v>
+          </cell>
+          <cell r="H30">
+            <v>0.04</v>
+          </cell>
+          <cell r="I30">
+            <v>4.8000000000000001E-2</v>
+          </cell>
+        </row>
+        <row r="31">
+          <cell r="E31">
+            <v>0.12</v>
+          </cell>
+          <cell r="F31" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G31">
+            <v>9.6000000000000002E-2</v>
+          </cell>
+          <cell r="H31">
+            <v>0.12</v>
+          </cell>
+          <cell r="I31">
+            <v>0.14399999999999999</v>
+          </cell>
+        </row>
+        <row r="32">
+          <cell r="E32">
+            <v>0.04</v>
+          </cell>
+          <cell r="F32" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G32">
+            <v>3.2000000000000001E-2</v>
+          </cell>
+          <cell r="H32">
+            <v>0.04</v>
+          </cell>
+          <cell r="I32">
+            <v>4.8000000000000001E-2</v>
+          </cell>
+        </row>
+        <row r="33">
+          <cell r="E33">
+            <v>0.501</v>
+          </cell>
+          <cell r="F33" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G33">
+            <v>0.40079999999999999</v>
+          </cell>
+          <cell r="H33">
+            <v>0.501</v>
+          </cell>
+          <cell r="I33">
+            <v>0.60119999999999996</v>
+          </cell>
+        </row>
+        <row r="34">
+          <cell r="E34">
+            <v>2.0000000000000002E-5</v>
+          </cell>
+          <cell r="F34" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G34">
+            <v>1.5999999999999999E-5</v>
+          </cell>
+          <cell r="H34">
+            <v>2.0000000000000002E-5</v>
+          </cell>
+          <cell r="I34">
+            <v>2.4000000000000001E-5</v>
+          </cell>
+        </row>
+        <row r="35">
+          <cell r="E35">
+            <v>0.10100000000000001</v>
+          </cell>
+          <cell r="F35" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G35">
+            <v>8.0799999999999997E-2</v>
+          </cell>
+          <cell r="H35">
+            <v>0.10100000000000001</v>
+          </cell>
+          <cell r="I35">
+            <v>0.1212</v>
+          </cell>
+        </row>
+        <row r="36">
+          <cell r="E36">
+            <v>5.81</v>
+          </cell>
+          <cell r="F36" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G36">
+            <v>4.6479999999999997</v>
+          </cell>
+          <cell r="H36">
+            <v>5.81</v>
+          </cell>
+          <cell r="I36">
+            <v>6.9719999999999898</v>
+          </cell>
+        </row>
+        <row r="37">
+          <cell r="E37">
+            <v>4.9999999999999998E-7</v>
+          </cell>
+          <cell r="F37" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G37">
+            <v>3.9999999999999998E-7</v>
+          </cell>
+          <cell r="H37">
+            <v>4.9999999999999998E-7</v>
+          </cell>
+          <cell r="I37">
+            <v>5.9999999999999997E-7</v>
+          </cell>
+        </row>
+        <row r="38">
+          <cell r="E38">
+            <v>4.8</v>
+          </cell>
+          <cell r="F38" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G38">
+            <v>3.84</v>
+          </cell>
+          <cell r="H38">
+            <v>4.8</v>
+          </cell>
+          <cell r="I38">
+            <v>5.76</v>
+          </cell>
+        </row>
+        <row r="39">
+          <cell r="E39">
+            <v>0.04</v>
+          </cell>
+          <cell r="F39" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G39">
+            <v>3.2000000000000001E-2</v>
+          </cell>
+          <cell r="H39">
+            <v>0.04</v>
+          </cell>
+          <cell r="I39">
+            <v>4.8000000000000001E-2</v>
+          </cell>
+        </row>
+        <row r="40">
+          <cell r="E40">
+            <v>0.12</v>
+          </cell>
+          <cell r="F40" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G40">
+            <v>9.6000000000000002E-2</v>
+          </cell>
+          <cell r="H40">
+            <v>0.12</v>
+          </cell>
+          <cell r="I40">
+            <v>0.14399999999999999</v>
+          </cell>
+        </row>
+        <row r="41">
+          <cell r="E41">
+            <v>0.04</v>
+          </cell>
+          <cell r="F41" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G41">
+            <v>3.2000000000000001E-2</v>
+          </cell>
+          <cell r="H41">
+            <v>0.04</v>
+          </cell>
+          <cell r="I41">
+            <v>4.8000000000000001E-2</v>
+          </cell>
+        </row>
+        <row r="42">
+          <cell r="E42">
+            <v>2.6400000000000002E-4</v>
+          </cell>
+          <cell r="F42" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G42">
+            <v>2.1120000000000001E-4</v>
+          </cell>
+          <cell r="H42">
+            <v>2.6400000000000002E-4</v>
+          </cell>
+          <cell r="I42">
+            <v>3.168E-4</v>
+          </cell>
+        </row>
+        <row r="43">
+          <cell r="E43">
+            <v>1.04E-2</v>
+          </cell>
+          <cell r="F43" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G43">
+            <v>8.3199999999999993E-3</v>
+          </cell>
+          <cell r="H43">
+            <v>1.04E-2</v>
+          </cell>
+          <cell r="I43">
+            <v>1.248E-2</v>
+          </cell>
+        </row>
+        <row r="44">
+          <cell r="E44">
+            <v>1.0200000000000001E-2</v>
+          </cell>
+          <cell r="F44" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G44">
+            <v>8.1600000000000006E-3</v>
+          </cell>
+          <cell r="H44">
+            <v>1.0200000000000001E-2</v>
+          </cell>
+          <cell r="I44">
+            <v>1.2239999999999999E-2</v>
+          </cell>
+        </row>
+        <row r="45">
+          <cell r="E45">
+            <v>0.77500000000000002</v>
+          </cell>
+          <cell r="F45" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G45">
+            <v>0.62</v>
+          </cell>
+          <cell r="H45">
+            <v>0.77500000000000002</v>
+          </cell>
+          <cell r="I45">
+            <v>0.92999999999999905</v>
+          </cell>
+        </row>
+        <row r="46">
+          <cell r="E46">
+            <v>0.1</v>
+          </cell>
+          <cell r="F46" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G46">
+            <v>0.08</v>
+          </cell>
+          <cell r="H46">
+            <v>0.1</v>
+          </cell>
+          <cell r="I46">
+            <v>0.12</v>
+          </cell>
+        </row>
+        <row r="47">
+          <cell r="E47">
+            <v>440</v>
+          </cell>
+          <cell r="F47" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G47">
+            <v>352</v>
+          </cell>
+          <cell r="H47">
+            <v>440</v>
+          </cell>
+          <cell r="I47">
+            <v>528</v>
+          </cell>
+        </row>
+        <row r="48">
+          <cell r="E48">
+            <v>2.82</v>
+          </cell>
+          <cell r="F48" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G48">
+            <v>2.2559999999999998</v>
+          </cell>
+          <cell r="H48">
+            <v>2.82</v>
+          </cell>
+          <cell r="I48">
+            <v>3.3839999999999999</v>
+          </cell>
+        </row>
+        <row r="49">
+          <cell r="E49">
+            <v>1.2500000000000001E-2</v>
+          </cell>
+          <cell r="F49" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G49">
+            <v>0.01</v>
+          </cell>
+          <cell r="H49">
+            <v>1.2500000000000001E-2</v>
+          </cell>
+          <cell r="I49">
+            <v>1.4999999999999999E-2</v>
+          </cell>
+        </row>
+        <row r="50">
+          <cell r="E50">
+            <v>3.4000000000000002E-2</v>
+          </cell>
+          <cell r="F50" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G50">
+            <v>2.7199999999999998E-2</v>
+          </cell>
+          <cell r="H50">
+            <v>3.4000000000000002E-2</v>
+          </cell>
+          <cell r="I50">
+            <v>4.0800000000000003E-2</v>
+          </cell>
+        </row>
+        <row r="51">
+          <cell r="E51">
+            <v>5.7000000000000002E-2</v>
+          </cell>
+          <cell r="F51" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G51">
+            <v>4.5600000000000002E-2</v>
+          </cell>
+          <cell r="H51">
+            <v>5.7000000000000002E-2</v>
+          </cell>
+          <cell r="I51">
+            <v>6.8400000000000002E-2</v>
+          </cell>
+        </row>
+        <row r="52">
+          <cell r="E52">
+            <v>1.2030000000000001</v>
+          </cell>
+          <cell r="F52" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G52">
+            <v>0.96240000000000003</v>
+          </cell>
+          <cell r="H52">
+            <v>1.2030000000000001</v>
+          </cell>
+          <cell r="I52">
+            <v>1.4436</v>
+          </cell>
+        </row>
+        <row r="53">
+          <cell r="E53">
+            <v>0.04</v>
+          </cell>
+          <cell r="F53" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G53">
+            <v>3.2000000000000001E-2</v>
+          </cell>
+          <cell r="H53">
+            <v>0.04</v>
+          </cell>
+          <cell r="I53">
+            <v>4.8000000000000001E-2</v>
+          </cell>
+        </row>
+        <row r="54">
+          <cell r="E54">
+            <v>0.12</v>
+          </cell>
+          <cell r="F54" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G54">
+            <v>9.6000000000000002E-2</v>
+          </cell>
+          <cell r="H54">
+            <v>0.12</v>
+          </cell>
+          <cell r="I54">
+            <v>0.14399999999999999</v>
+          </cell>
+        </row>
+        <row r="55">
+          <cell r="E55">
+            <v>0.04</v>
+          </cell>
+          <cell r="F55" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G55">
+            <v>3.2000000000000001E-2</v>
+          </cell>
+          <cell r="H55">
+            <v>0.04</v>
+          </cell>
+          <cell r="I55">
+            <v>4.8000000000000001E-2</v>
+          </cell>
+        </row>
+        <row r="56">
+          <cell r="E56">
+            <v>1.01E-2</v>
+          </cell>
+          <cell r="F56" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G56">
+            <v>8.0800000000000004E-3</v>
+          </cell>
+          <cell r="H56">
+            <v>1.01E-2</v>
+          </cell>
+          <cell r="I56">
+            <v>1.21199999999999E-2</v>
+          </cell>
+        </row>
+        <row r="57">
+          <cell r="E57">
+            <v>0.58899999999999997</v>
+          </cell>
+          <cell r="F57" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G57">
+            <v>0.47120000000000001</v>
+          </cell>
+          <cell r="H57">
+            <v>0.58899999999999997</v>
+          </cell>
+          <cell r="I57">
+            <v>0.70679999999999998</v>
+          </cell>
+        </row>
+        <row r="58">
+          <cell r="E58">
+            <v>8.0000000000000002E-3</v>
+          </cell>
+          <cell r="F58" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G58">
+            <v>6.4000000000000003E-3</v>
+          </cell>
+          <cell r="H58">
+            <v>8.0000000000000002E-3</v>
+          </cell>
+          <cell r="I58">
+            <v>9.5999999999999992E-3</v>
+          </cell>
+        </row>
+        <row r="59">
+          <cell r="E59">
+            <v>9.9999999999999995E-7</v>
+          </cell>
+          <cell r="F59" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G59">
+            <v>7.9999999999999996E-7</v>
+          </cell>
+          <cell r="H59">
+            <v>9.9999999999999995E-7</v>
+          </cell>
+          <cell r="I59">
+            <v>1.1999999999999999E-6</v>
+          </cell>
+        </row>
+        <row r="60">
+          <cell r="E60">
+            <v>7.51E-2</v>
+          </cell>
+          <cell r="F60" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G60">
+            <v>6.0080000000000001E-2</v>
+          </cell>
+          <cell r="H60">
+            <v>7.51E-2</v>
+          </cell>
+          <cell r="I60">
+            <v>9.0119999999999895E-2</v>
+          </cell>
+        </row>
+        <row r="61">
+          <cell r="E61">
+            <v>13</v>
+          </cell>
+          <cell r="F61" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G61">
+            <v>10.4</v>
+          </cell>
+          <cell r="H61">
+            <v>13</v>
+          </cell>
+          <cell r="I61">
+            <v>15.6</v>
+          </cell>
+        </row>
+        <row r="62">
+          <cell r="E62">
+            <v>25</v>
+          </cell>
+          <cell r="F62" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G62">
+            <v>20</v>
+          </cell>
+          <cell r="H62">
+            <v>25</v>
+          </cell>
+          <cell r="I62">
+            <v>30</v>
+          </cell>
+        </row>
+        <row r="63">
+          <cell r="E63">
+            <v>3.9899999999999996E-3</v>
+          </cell>
+          <cell r="F63" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G63">
+            <v>3.192E-3</v>
+          </cell>
+          <cell r="H63">
+            <v>3.9899999999999996E-3</v>
+          </cell>
+          <cell r="I63">
+            <v>4.7879999999999997E-3</v>
+          </cell>
+        </row>
+        <row r="64">
+          <cell r="E64">
+            <v>0.06</v>
+          </cell>
+          <cell r="F64" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G64">
+            <v>4.8000000000000001E-2</v>
+          </cell>
+          <cell r="H64">
+            <v>0.06</v>
+          </cell>
+          <cell r="I64">
+            <v>7.1999999999999995E-2</v>
+          </cell>
+        </row>
+        <row r="65">
+          <cell r="E65">
+            <v>0.02</v>
+          </cell>
+          <cell r="F65" t="str">
+            <v>triangular</v>
+          </cell>
+          <cell r="G65">
+            <v>1.6E-2</v>
+          </cell>
+          <cell r="H65">
+            <v>0.02</v>
+          </cell>
+          <cell r="I65">
+            <v>2.4E-2</v>
+          </cell>
+        </row>
+      </sheetData>
+    </sheetDataSet>
+  </externalBook>
+</externalLink>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -980,18 +2055,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K75"/>
+  <dimension ref="A1:T75"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40.81640625" customWidth="1"/>
-    <col min="2" max="2" width="46" customWidth="1"/>
+    <col min="2" max="2" width="16.90625" customWidth="1"/>
     <col min="4" max="4" width="12.1796875" customWidth="1"/>
     <col min="6" max="6" width="14.453125" customWidth="1"/>
     <col min="10" max="10" width="10.6328125" customWidth="1"/>
     <col min="11" max="11" width="19.08984375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="1" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
+    <row r="1" spans="1:20" s="1" customFormat="1" ht="22.25" customHeight="1" x14ac:dyDescent="0.35">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -1026,7 +2101,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.35">
+    <row r="2" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A2" s="3" t="s">
         <v>17</v>
       </c>
@@ -1056,8 +2131,28 @@
       <c r="K2" s="3" t="s">
         <v>23</v>
       </c>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P2">
+        <f>IF(E2=[1]Sheet1!E2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q2">
+        <f>IF(F2=[1]Sheet1!F2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R2">
+        <f>IF(G2=[1]Sheet1!G2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S2">
+        <f>IF(H2=[1]Sheet1!H2,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T2">
+        <f>IF(I2=[1]Sheet1!I2,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A3" s="3" t="s">
         <v>28</v>
       </c>
@@ -1092,8 +2187,28 @@
       <c r="K3" s="3" t="s">
         <v>29</v>
       </c>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P3">
+        <f>IF(E3=[1]Sheet1!E3,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q3">
+        <f>IF(F3=[1]Sheet1!F3,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R3">
+        <f>IF(G3=[1]Sheet1!G3,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S3">
+        <f>IF(H3=[1]Sheet1!H3,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T3">
+        <f>IF(I3=[1]Sheet1!I3,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A4" s="6" t="s">
         <v>15</v>
       </c>
@@ -1126,8 +2241,28 @@
       <c r="K4" s="6" t="s">
         <v>24</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P4">
+        <f>IF(E4=[1]Sheet1!E4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q4">
+        <f>IF(F4=[1]Sheet1!F4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R4">
+        <f>IF(G4=[1]Sheet1!G4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S4">
+        <f>IF(H4=[1]Sheet1!H4,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T4">
+        <f>IF(I4=[1]Sheet1!I4,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A5" s="6" t="s">
         <v>16</v>
       </c>
@@ -1160,8 +2295,28 @@
       <c r="K5" s="6" t="s">
         <v>25</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P5">
+        <f>IF(E5=[1]Sheet1!E5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q5">
+        <f>IF(F5=[1]Sheet1!F5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R5">
+        <f>IF(G5=[1]Sheet1!G5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S5">
+        <f>IF(H5=[1]Sheet1!H5,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T5">
+        <f>IF(I5=[1]Sheet1!I5,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A6" s="4" t="s">
         <v>42</v>
       </c>
@@ -1193,8 +2348,28 @@
       <c r="K6" s="4" t="s">
         <v>43</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P6">
+        <f>IF(E6=[1]Sheet1!E6,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q6">
+        <f>IF(F6=[1]Sheet1!F6,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R6">
+        <f>IF(G6=[1]Sheet1!G6,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S6">
+        <f>IF(H6=[1]Sheet1!H6,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T6">
+        <f>IF(I6=[1]Sheet1!I6,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A7" s="4" t="s">
         <v>45</v>
       </c>
@@ -1226,8 +2401,28 @@
       <c r="K7" s="4" t="s">
         <v>44</v>
       </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P7">
+        <f>IF(E7=[1]Sheet1!E7,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q7">
+        <f>IF(F7=[1]Sheet1!F7,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R7">
+        <f>IF(G7=[1]Sheet1!G7,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S7">
+        <f>IF(H7=[1]Sheet1!H7,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T7">
+        <f>IF(I7=[1]Sheet1!I7,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="8" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A8" s="4" t="s">
         <v>46</v>
       </c>
@@ -1259,8 +2454,28 @@
       <c r="K8" s="4" t="s">
         <v>47</v>
       </c>
-    </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P8">
+        <f>IF(E8=[1]Sheet1!E8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q8">
+        <f>IF(F8=[1]Sheet1!F8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R8">
+        <f>IF(G8=[1]Sheet1!G8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S8">
+        <f>IF(H8=[1]Sheet1!H8,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T8">
+        <f>IF(I8=[1]Sheet1!I8,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="9" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A9" s="4" t="s">
         <v>48</v>
       </c>
@@ -1292,8 +2507,28 @@
       <c r="K9" s="4" t="s">
         <v>49</v>
       </c>
-    </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P9">
+        <f>IF(E9=[1]Sheet1!E9,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q9">
+        <f>IF(F9=[1]Sheet1!F9,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R9">
+        <f>IF(G9=[1]Sheet1!G9,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S9">
+        <f>IF(H9=[1]Sheet1!H9,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T9">
+        <f>IF(I9=[1]Sheet1!I9,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="10" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A10" s="4" t="s">
         <v>50</v>
       </c>
@@ -1325,8 +2560,28 @@
       <c r="K10" s="4" t="s">
         <v>51</v>
       </c>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P10">
+        <f>IF(E10=[1]Sheet1!E10,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q10">
+        <f>IF(F10=[1]Sheet1!F10,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R10">
+        <f>IF(G10=[1]Sheet1!G10,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S10">
+        <f>IF(H10=[1]Sheet1!H10,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T10">
+        <f>IF(I10=[1]Sheet1!I10,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
         <v>192</v>
       </c>
@@ -1358,8 +2613,28 @@
       <c r="K11" s="4" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P11">
+        <f>IF(E11=[1]Sheet1!E11,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q11">
+        <f>IF(F11=[1]Sheet1!F11,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R11">
+        <f>IF(G11=[1]Sheet1!G11,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S11">
+        <f>IF(H11=[1]Sheet1!H11,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T11">
+        <f>IF(I11=[1]Sheet1!I11,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
         <v>193</v>
       </c>
@@ -1379,21 +2654,43 @@
         <v>27</v>
       </c>
       <c r="G12" s="4">
-        <v>0.95</v>
+        <f t="shared" si="0"/>
+        <v>1.1919999999999999</v>
       </c>
       <c r="H12" s="4">
         <f>E12</f>
         <v>1.49</v>
       </c>
       <c r="I12" s="4">
-        <v>1.7250000000000001</v>
+        <f>1.2*E12</f>
+        <v>1.788</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P12">
+        <f>IF(E12=[1]Sheet1!E12,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q12">
+        <f>IF(F12=[1]Sheet1!F12,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R12">
+        <f>IF(G12=[1]Sheet1!G12,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S12">
+        <f>IF(H12=[1]Sheet1!H12,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T12">
+        <f>IF(I12=[1]Sheet1!I12,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
         <v>188</v>
       </c>
@@ -1425,8 +2722,28 @@
       <c r="K13" s="4" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P13">
+        <f>IF(E13=[1]Sheet1!E13,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q13">
+        <f>IF(F13=[1]Sheet1!F13,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R13">
+        <f>IF(G13=[1]Sheet1!G13,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S13">
+        <f>IF(H13=[1]Sheet1!H13,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T13">
+        <f>IF(I13=[1]Sheet1!I13,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
         <v>35</v>
       </c>
@@ -1458,8 +2775,28 @@
       <c r="K14" s="6" t="s">
         <v>85</v>
       </c>
-    </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P14">
+        <f>IF(E14=[1]Sheet1!E14,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q14">
+        <f>IF(F14=[1]Sheet1!F14,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R14">
+        <f>IF(G14=[1]Sheet1!G14,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S14">
+        <f>IF(H14=[1]Sheet1!H14,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T14">
+        <f>IF(I14=[1]Sheet1!I14,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="15" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A15" s="6" t="s">
         <v>36</v>
       </c>
@@ -1494,8 +2831,28 @@
       <c r="K15" s="6" t="s">
         <v>86</v>
       </c>
-    </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P15">
+        <f>IF(E15=[1]Sheet1!E15,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q15">
+        <f>IF(F15=[1]Sheet1!F15,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R15">
+        <f>IF(G15=[1]Sheet1!G15,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S15">
+        <f>IF(H15=[1]Sheet1!H15,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T15">
+        <f>IF(I15=[1]Sheet1!I15,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
         <v>31</v>
       </c>
@@ -1525,8 +2882,28 @@
       <c r="K16" s="3" t="s">
         <v>34</v>
       </c>
-    </row>
-    <row r="17" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P16">
+        <f>IF(E16=[1]Sheet1!E16,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q16">
+        <f>IF(F16=[1]Sheet1!F16,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R16">
+        <f>IF(G16=[1]Sheet1!G16,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S16">
+        <f>IF(H16=[1]Sheet1!H16,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T16">
+        <f>IF(I16=[1]Sheet1!I16,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
         <v>32</v>
       </c>
@@ -1558,8 +2935,28 @@
       <c r="K17" s="3" t="s">
         <v>33</v>
       </c>
-    </row>
-    <row r="18" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P17">
+        <f>IF(E17=[1]Sheet1!E17,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q17">
+        <f>IF(F17=[1]Sheet1!F17,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R17">
+        <f>IF(G17=[1]Sheet1!G17,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S17">
+        <f>IF(H17=[1]Sheet1!H17,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T17">
+        <f>IF(I17=[1]Sheet1!I17,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
         <v>185</v>
       </c>
@@ -1594,8 +2991,28 @@
       <c r="K18" s="3" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="19" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P18">
+        <f>IF(E18=[1]Sheet1!E18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q18">
+        <f>IF(F18=[1]Sheet1!F18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R18">
+        <f>IF(G18=[1]Sheet1!G18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S18">
+        <f>IF(H18=[1]Sheet1!H18,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T18">
+        <f>IF(I18=[1]Sheet1!I18,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
         <v>38</v>
       </c>
@@ -1630,8 +3047,28 @@
       <c r="K19" s="3" t="s">
         <v>41</v>
       </c>
-    </row>
-    <row r="20" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P19">
+        <f>IF(E19=[1]Sheet1!E19,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q19">
+        <f>IF(F19=[1]Sheet1!F19,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R19">
+        <f>IF(G19=[1]Sheet1!G19,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S19">
+        <f>IF(H19=[1]Sheet1!H19,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T19">
+        <f>IF(I19=[1]Sheet1!I19,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
         <v>189</v>
       </c>
@@ -1661,8 +3098,28 @@
       <c r="K20" s="3" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="21" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P20">
+        <f>IF(E20=[1]Sheet1!E20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q20">
+        <f>IF(F20=[1]Sheet1!F20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R20">
+        <f>IF(G20=[1]Sheet1!G20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S20">
+        <f>IF(H20=[1]Sheet1!H20,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T20">
+        <f>IF(I20=[1]Sheet1!I20,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
         <v>52</v>
       </c>
@@ -1697,8 +3154,28 @@
       <c r="K21" s="3" t="s">
         <v>54</v>
       </c>
-    </row>
-    <row r="22" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P21">
+        <f>IF(E21=[1]Sheet1!E21,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q21">
+        <f>IF(F21=[1]Sheet1!F21,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R21">
+        <f>IF(G21=[1]Sheet1!G21,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S21">
+        <f>IF(H21=[1]Sheet1!H21,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T21">
+        <f>IF(I21=[1]Sheet1!I21,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
         <v>53</v>
       </c>
@@ -1733,8 +3210,28 @@
       <c r="K22" s="3" t="s">
         <v>55</v>
       </c>
-    </row>
-    <row r="23" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P22">
+        <f>IF(E22=[1]Sheet1!E22,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q22">
+        <f>IF(F22=[1]Sheet1!F22,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R22">
+        <f>IF(G22=[1]Sheet1!G22,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S22">
+        <f>IF(H22=[1]Sheet1!H22,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T22">
+        <f>IF(I22=[1]Sheet1!I22,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
         <v>121</v>
       </c>
@@ -1766,8 +3263,28 @@
       <c r="K23" s="3" t="s">
         <v>62</v>
       </c>
-    </row>
-    <row r="24" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P23">
+        <f>IF(E23=[1]Sheet1!E23,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q23">
+        <f>IF(F23=[1]Sheet1!F23,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R23">
+        <f>IF(G23=[1]Sheet1!G23,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S23">
+        <f>IF(H23=[1]Sheet1!H23,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T23">
+        <f>IF(I23=[1]Sheet1!I23,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
         <v>104</v>
       </c>
@@ -1799,8 +3316,28 @@
       <c r="K24" s="3" t="s">
         <v>87</v>
       </c>
-    </row>
-    <row r="25" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P24">
+        <f>IF(E24=[1]Sheet1!E24,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q24">
+        <f>IF(F24=[1]Sheet1!F24,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R24">
+        <f>IF(G24=[1]Sheet1!G24,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S24">
+        <f>IF(H24=[1]Sheet1!H24,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T24">
+        <f>IF(I24=[1]Sheet1!I24,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
         <v>122</v>
       </c>
@@ -1832,8 +3369,28 @@
       <c r="K25" s="3" t="s">
         <v>58</v>
       </c>
-    </row>
-    <row r="26" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P25">
+        <f>IF(E25=[1]Sheet1!E25,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q25">
+        <f>IF(F25=[1]Sheet1!F25,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R25">
+        <f>IF(G25=[1]Sheet1!G25,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S25">
+        <f>IF(H25=[1]Sheet1!H25,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T25">
+        <f>IF(I25=[1]Sheet1!I25,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
         <v>105</v>
       </c>
@@ -1865,8 +3422,28 @@
       <c r="K26" s="3" t="s">
         <v>88</v>
       </c>
-    </row>
-    <row r="27" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P26">
+        <f>IF(E26=[1]Sheet1!E26,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q26">
+        <f>IF(F26=[1]Sheet1!F26,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R26">
+        <f>IF(G26=[1]Sheet1!G26,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S26">
+        <f>IF(H26=[1]Sheet1!H26,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T26">
+        <f>IF(I26=[1]Sheet1!I26,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
         <v>123</v>
       </c>
@@ -1898,8 +3475,28 @@
       <c r="K27" s="3" t="s">
         <v>57</v>
       </c>
-    </row>
-    <row r="28" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P27">
+        <f>IF(E27=[1]Sheet1!E27,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q27">
+        <f>IF(F27=[1]Sheet1!F27,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R27">
+        <f>IF(G27=[1]Sheet1!G27,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S27">
+        <f>IF(H27=[1]Sheet1!H27,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T27">
+        <f>IF(I27=[1]Sheet1!I27,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
         <v>106</v>
       </c>
@@ -1931,8 +3528,28 @@
       <c r="K28" s="3" t="s">
         <v>89</v>
       </c>
-    </row>
-    <row r="29" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P28">
+        <f>IF(E28=[1]Sheet1!E28,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q28">
+        <f>IF(F28=[1]Sheet1!F28,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R28">
+        <f>IF(G28=[1]Sheet1!G28,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S28">
+        <f>IF(H28=[1]Sheet1!H28,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T28">
+        <f>IF(I28=[1]Sheet1!I28,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
         <v>107</v>
       </c>
@@ -1964,8 +3581,28 @@
       <c r="K29" s="3" t="s">
         <v>90</v>
       </c>
-    </row>
-    <row r="30" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P29">
+        <f>IF(E29=[1]Sheet1!E29,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q29">
+        <f>IF(F29=[1]Sheet1!F29,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R29">
+        <f>IF(G29=[1]Sheet1!G29,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S29">
+        <f>IF(H29=[1]Sheet1!H29,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T29">
+        <f>IF(I29=[1]Sheet1!I29,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
         <v>124</v>
       </c>
@@ -1997,8 +3634,28 @@
       <c r="K30" s="3" t="s">
         <v>59</v>
       </c>
-    </row>
-    <row r="31" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P30">
+        <f>IF(E30=[1]Sheet1!E30,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q30">
+        <f>IF(F30=[1]Sheet1!F30,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R30">
+        <f>IF(G30=[1]Sheet1!G30,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S30">
+        <f>IF(H30=[1]Sheet1!H30,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T30">
+        <f>IF(I30=[1]Sheet1!I30,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
         <v>125</v>
       </c>
@@ -2030,8 +3687,28 @@
       <c r="K31" s="3" t="s">
         <v>60</v>
       </c>
-    </row>
-    <row r="32" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P31">
+        <f>IF(E31=[1]Sheet1!E31,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q31">
+        <f>IF(F31=[1]Sheet1!F31,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R31">
+        <f>IF(G31=[1]Sheet1!G31,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S31">
+        <f>IF(H31=[1]Sheet1!H31,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T31">
+        <f>IF(I31=[1]Sheet1!I31,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
         <v>126</v>
       </c>
@@ -2063,8 +3740,28 @@
       <c r="K32" s="3" t="s">
         <v>61</v>
       </c>
-    </row>
-    <row r="33" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P32">
+        <f>IF(E32=[1]Sheet1!E32,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q32">
+        <f>IF(F32=[1]Sheet1!F32,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R32">
+        <f>IF(G32=[1]Sheet1!G32,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S32">
+        <f>IF(H32=[1]Sheet1!H32,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T32">
+        <f>IF(I32=[1]Sheet1!I32,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="33" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
         <v>127</v>
       </c>
@@ -2096,8 +3793,28 @@
       <c r="K33" s="3" t="s">
         <v>56</v>
       </c>
-    </row>
-    <row r="34" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P33">
+        <f>IF(E33=[1]Sheet1!E33,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q33">
+        <f>IF(F33=[1]Sheet1!F33,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R33">
+        <f>IF(G33=[1]Sheet1!G33,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S33">
+        <f>IF(H33=[1]Sheet1!H33,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T33">
+        <f>IF(I33=[1]Sheet1!I33,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="34" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
         <v>108</v>
       </c>
@@ -2129,8 +3846,28 @@
       <c r="K34" s="3" t="s">
         <v>91</v>
       </c>
-    </row>
-    <row r="35" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P34">
+        <f>IF(E34=[1]Sheet1!E34,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q34">
+        <f>IF(F34=[1]Sheet1!F34,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R34">
+        <f>IF(G34=[1]Sheet1!G34,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S34">
+        <f>IF(H34=[1]Sheet1!H34,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T34">
+        <f>IF(I34=[1]Sheet1!I34,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="35" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
         <v>109</v>
       </c>
@@ -2162,8 +3899,28 @@
       <c r="K35" s="3" t="s">
         <v>92</v>
       </c>
-    </row>
-    <row r="36" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P35">
+        <f>IF(E35=[1]Sheet1!E35,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q35">
+        <f>IF(F35=[1]Sheet1!F35,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R35">
+        <f>IF(G35=[1]Sheet1!G35,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S35">
+        <f>IF(H35=[1]Sheet1!H35,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T35">
+        <f>IF(I35=[1]Sheet1!I35,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="36" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
         <v>128</v>
       </c>
@@ -2195,8 +3952,28 @@
       <c r="K36" s="3" t="s">
         <v>63</v>
       </c>
-    </row>
-    <row r="37" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P36">
+        <f>IF(E36=[1]Sheet1!E36,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q36">
+        <f>IF(F36=[1]Sheet1!F36,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R36">
+        <f>IF(G36=[1]Sheet1!G36,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S36">
+        <f>IF(H36=[1]Sheet1!H36,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T36">
+        <f>IF(I36=[1]Sheet1!I36,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="37" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
         <v>110</v>
       </c>
@@ -2228,8 +4005,28 @@
       <c r="K37" s="3" t="s">
         <v>93</v>
       </c>
-    </row>
-    <row r="38" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P37">
+        <f>IF(E37=[1]Sheet1!E37,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q37">
+        <f>IF(F37=[1]Sheet1!F37,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R37">
+        <f>IF(G37=[1]Sheet1!G37,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S37">
+        <f>IF(H37=[1]Sheet1!H37,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T37">
+        <f>IF(I37=[1]Sheet1!I37,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
         <v>129</v>
       </c>
@@ -2261,8 +4058,28 @@
       <c r="K38" s="3" t="s">
         <v>64</v>
       </c>
-    </row>
-    <row r="39" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P38">
+        <f>IF(E38=[1]Sheet1!E38,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q38">
+        <f>IF(F38=[1]Sheet1!F38,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R38">
+        <f>IF(G38=[1]Sheet1!G38,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S38">
+        <f>IF(H38=[1]Sheet1!H38,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T38">
+        <f>IF(I38=[1]Sheet1!I38,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
         <v>130</v>
       </c>
@@ -2294,8 +4111,28 @@
       <c r="K39" s="3" t="s">
         <v>68</v>
       </c>
-    </row>
-    <row r="40" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P39">
+        <f>IF(E39=[1]Sheet1!E39,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q39">
+        <f>IF(F39=[1]Sheet1!F39,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R39">
+        <f>IF(G39=[1]Sheet1!G39,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S39">
+        <f>IF(H39=[1]Sheet1!H39,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T39">
+        <f>IF(I39=[1]Sheet1!I39,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="40" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
         <v>131</v>
       </c>
@@ -2327,8 +4164,28 @@
       <c r="K40" s="3" t="s">
         <v>69</v>
       </c>
-    </row>
-    <row r="41" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P40">
+        <f>IF(E40=[1]Sheet1!E40,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q40">
+        <f>IF(F40=[1]Sheet1!F40,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R40">
+        <f>IF(G40=[1]Sheet1!G40,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S40">
+        <f>IF(H40=[1]Sheet1!H40,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T40">
+        <f>IF(I40=[1]Sheet1!I40,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="41" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
         <v>132</v>
       </c>
@@ -2360,8 +4217,28 @@
       <c r="K41" s="3" t="s">
         <v>70</v>
       </c>
-    </row>
-    <row r="42" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P41">
+        <f>IF(E41=[1]Sheet1!E41,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q41">
+        <f>IF(F41=[1]Sheet1!F41,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R41">
+        <f>IF(G41=[1]Sheet1!G41,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S41">
+        <f>IF(H41=[1]Sheet1!H41,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T41">
+        <f>IF(I41=[1]Sheet1!I41,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="42" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
         <v>111</v>
       </c>
@@ -2393,8 +4270,28 @@
       <c r="K42" s="3" t="s">
         <v>94</v>
       </c>
-    </row>
-    <row r="43" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P42">
+        <f>IF(E42=[1]Sheet1!E42,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q42">
+        <f>IF(F42=[1]Sheet1!F42,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R42">
+        <f>IF(G42=[1]Sheet1!G42,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S42">
+        <f>IF(H42=[1]Sheet1!H42,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T42">
+        <f>IF(I42=[1]Sheet1!I42,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
         <v>133</v>
       </c>
@@ -2426,8 +4323,28 @@
       <c r="K43" s="3" t="s">
         <v>71</v>
       </c>
-    </row>
-    <row r="44" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P43">
+        <f>IF(E43=[1]Sheet1!E43,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q43">
+        <f>IF(F43=[1]Sheet1!F43,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R43">
+        <f>IF(G43=[1]Sheet1!G43,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S43">
+        <f>IF(H43=[1]Sheet1!H43,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T43">
+        <f>IF(I43=[1]Sheet1!I43,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
         <v>112</v>
       </c>
@@ -2459,8 +4376,28 @@
       <c r="K44" s="3" t="s">
         <v>95</v>
       </c>
-    </row>
-    <row r="45" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P44">
+        <f>IF(E44=[1]Sheet1!E44,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q44">
+        <f>IF(F44=[1]Sheet1!F44,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R44">
+        <f>IF(G44=[1]Sheet1!G44,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S44">
+        <f>IF(H44=[1]Sheet1!H44,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T44">
+        <f>IF(I44=[1]Sheet1!I44,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
         <v>134</v>
       </c>
@@ -2492,8 +4429,28 @@
       <c r="K45" s="3" t="s">
         <v>72</v>
       </c>
-    </row>
-    <row r="46" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P45">
+        <f>IF(E45=[1]Sheet1!E45,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q45">
+        <f>IF(F45=[1]Sheet1!F45,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R45">
+        <f>IF(G45=[1]Sheet1!G45,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S45">
+        <f>IF(H45=[1]Sheet1!H45,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T45">
+        <f>IF(I45=[1]Sheet1!I45,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
         <v>113</v>
       </c>
@@ -2525,8 +4482,28 @@
       <c r="K46" s="3" t="s">
         <v>96</v>
       </c>
-    </row>
-    <row r="47" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P46">
+        <f>IF(E46=[1]Sheet1!E46,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q46">
+        <f>IF(F46=[1]Sheet1!F46,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R46">
+        <f>IF(G46=[1]Sheet1!G46,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S46">
+        <f>IF(H46=[1]Sheet1!H46,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T46">
+        <f>IF(I46=[1]Sheet1!I46,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="47" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
         <v>114</v>
       </c>
@@ -2558,8 +4535,28 @@
       <c r="K47" s="3" t="s">
         <v>97</v>
       </c>
-    </row>
-    <row r="48" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P47">
+        <f>IF(E47=[1]Sheet1!E47,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q47">
+        <f>IF(F47=[1]Sheet1!F47,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R47">
+        <f>IF(G47=[1]Sheet1!G47,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S47">
+        <f>IF(H47=[1]Sheet1!H47,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T47">
+        <f>IF(I47=[1]Sheet1!I47,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="48" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
         <v>135</v>
       </c>
@@ -2591,8 +4588,28 @@
       <c r="K48" s="3" t="s">
         <v>73</v>
       </c>
-    </row>
-    <row r="49" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P48">
+        <f>IF(E48=[1]Sheet1!E48,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q48">
+        <f>IF(F48=[1]Sheet1!F48,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R48">
+        <f>IF(G48=[1]Sheet1!G48,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S48">
+        <f>IF(H48=[1]Sheet1!H48,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T48">
+        <f>IF(I48=[1]Sheet1!I48,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="49" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
         <v>136</v>
       </c>
@@ -2624,8 +4641,28 @@
       <c r="K49" s="3" t="s">
         <v>74</v>
       </c>
-    </row>
-    <row r="50" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P49">
+        <f>IF(E49=[1]Sheet1!E49,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q49">
+        <f>IF(F49=[1]Sheet1!F49,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R49">
+        <f>IF(G49=[1]Sheet1!G49,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S49">
+        <f>IF(H49=[1]Sheet1!H49,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T49">
+        <f>IF(I49=[1]Sheet1!I49,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="50" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
         <v>115</v>
       </c>
@@ -2657,8 +4694,28 @@
       <c r="K50" s="3" t="s">
         <v>98</v>
       </c>
-    </row>
-    <row r="51" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P50">
+        <f>IF(E50=[1]Sheet1!E50,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q50">
+        <f>IF(F50=[1]Sheet1!F50,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R50">
+        <f>IF(G50=[1]Sheet1!G50,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S50">
+        <f>IF(H50=[1]Sheet1!H50,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T50">
+        <f>IF(I50=[1]Sheet1!I50,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="51" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
         <v>116</v>
       </c>
@@ -2690,8 +4747,28 @@
       <c r="K51" s="3" t="s">
         <v>99</v>
       </c>
-    </row>
-    <row r="52" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P51">
+        <f>IF(E51=[1]Sheet1!E51,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q51">
+        <f>IF(F51=[1]Sheet1!F51,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R51">
+        <f>IF(G51=[1]Sheet1!G51,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S51">
+        <f>IF(H51=[1]Sheet1!H51,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T51">
+        <f>IF(I51=[1]Sheet1!I51,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="52" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
         <v>137</v>
       </c>
@@ -2723,8 +4800,28 @@
       <c r="K52" s="3" t="s">
         <v>75</v>
       </c>
-    </row>
-    <row r="53" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P52">
+        <f>IF(E52=[1]Sheet1!E52,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q52">
+        <f>IF(F52=[1]Sheet1!F52,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R52">
+        <f>IF(G52=[1]Sheet1!G52,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S52">
+        <f>IF(H52=[1]Sheet1!H52,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T52">
+        <f>IF(I52=[1]Sheet1!I52,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="53" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
         <v>138</v>
       </c>
@@ -2756,8 +4853,28 @@
       <c r="K53" s="3" t="s">
         <v>76</v>
       </c>
-    </row>
-    <row r="54" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P53">
+        <f>IF(E53=[1]Sheet1!E53,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q53">
+        <f>IF(F53=[1]Sheet1!F53,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R53">
+        <f>IF(G53=[1]Sheet1!G53,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S53">
+        <f>IF(H53=[1]Sheet1!H53,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T53">
+        <f>IF(I53=[1]Sheet1!I53,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="54" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
         <v>139</v>
       </c>
@@ -2789,8 +4906,28 @@
       <c r="K54" s="3" t="s">
         <v>77</v>
       </c>
-    </row>
-    <row r="55" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P54">
+        <f>IF(E54=[1]Sheet1!E54,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q54">
+        <f>IF(F54=[1]Sheet1!F54,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R54">
+        <f>IF(G54=[1]Sheet1!G54,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S54">
+        <f>IF(H54=[1]Sheet1!H54,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T54">
+        <f>IF(I54=[1]Sheet1!I54,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="55" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
         <v>140</v>
       </c>
@@ -2822,8 +4959,28 @@
       <c r="K55" s="3" t="s">
         <v>78</v>
       </c>
-    </row>
-    <row r="56" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P55">
+        <f>IF(E55=[1]Sheet1!E55,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q55">
+        <f>IF(F55=[1]Sheet1!F55,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R55">
+        <f>IF(G55=[1]Sheet1!G55,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S55">
+        <f>IF(H55=[1]Sheet1!H55,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T55">
+        <f>IF(I55=[1]Sheet1!I55,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="56" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
         <v>117</v>
       </c>
@@ -2855,8 +5012,28 @@
       <c r="K56" s="3" t="s">
         <v>100</v>
       </c>
-    </row>
-    <row r="57" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P56">
+        <f>IF(E56=[1]Sheet1!E56,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q56">
+        <f>IF(F56=[1]Sheet1!F56,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R56">
+        <f>IF(G56=[1]Sheet1!G56,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S56">
+        <f>IF(H56=[1]Sheet1!H56,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T56">
+        <f>IF(I56=[1]Sheet1!I56,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="57" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
         <v>141</v>
       </c>
@@ -2888,8 +5065,28 @@
       <c r="K57" s="3" t="s">
         <v>79</v>
       </c>
-    </row>
-    <row r="58" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P57">
+        <f>IF(E57=[1]Sheet1!E57,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q57">
+        <f>IF(F57=[1]Sheet1!F57,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R57">
+        <f>IF(G57=[1]Sheet1!G57,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S57">
+        <f>IF(H57=[1]Sheet1!H57,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T57">
+        <f>IF(I57=[1]Sheet1!I57,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="58" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
         <v>142</v>
       </c>
@@ -2921,8 +5118,28 @@
       <c r="K58" s="3" t="s">
         <v>80</v>
       </c>
-    </row>
-    <row r="59" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P58">
+        <f>IF(E58=[1]Sheet1!E58,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q58">
+        <f>IF(F58=[1]Sheet1!F58,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R58">
+        <f>IF(G58=[1]Sheet1!G58,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S58">
+        <f>IF(H58=[1]Sheet1!H58,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T58">
+        <f>IF(I58=[1]Sheet1!I58,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="59" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
         <v>118</v>
       </c>
@@ -2954,8 +5171,28 @@
       <c r="K59" s="3" t="s">
         <v>101</v>
       </c>
-    </row>
-    <row r="60" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P59">
+        <f>IF(E59=[1]Sheet1!E59,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q59">
+        <f>IF(F59=[1]Sheet1!F59,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R59">
+        <f>IF(G59=[1]Sheet1!G59,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S59">
+        <f>IF(H59=[1]Sheet1!H59,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T59">
+        <f>IF(I59=[1]Sheet1!I59,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="60" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
         <v>143</v>
       </c>
@@ -2987,8 +5224,28 @@
       <c r="K60" s="3" t="s">
         <v>81</v>
       </c>
-    </row>
-    <row r="61" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P60">
+        <f>IF(E60=[1]Sheet1!E60,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q60">
+        <f>IF(F60=[1]Sheet1!F60,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R60">
+        <f>IF(G60=[1]Sheet1!G60,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S60">
+        <f>IF(H60=[1]Sheet1!H60,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T60">
+        <f>IF(I60=[1]Sheet1!I60,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="61" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
         <v>119</v>
       </c>
@@ -3020,8 +5277,28 @@
       <c r="K61" s="3" t="s">
         <v>102</v>
       </c>
-    </row>
-    <row r="62" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P61">
+        <f>IF(E61=[1]Sheet1!E61,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q61">
+        <f>IF(F61=[1]Sheet1!F61,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R61">
+        <f>IF(G61=[1]Sheet1!G61,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S61">
+        <f>IF(H61=[1]Sheet1!H61,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T61">
+        <f>IF(I61=[1]Sheet1!I61,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="62" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
         <v>120</v>
       </c>
@@ -3053,8 +5330,28 @@
       <c r="K62" s="3" t="s">
         <v>103</v>
       </c>
-    </row>
-    <row r="63" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P62">
+        <f>IF(E62=[1]Sheet1!E62,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q62">
+        <f>IF(F62=[1]Sheet1!F62,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R62">
+        <f>IF(G62=[1]Sheet1!G62,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S62">
+        <f>IF(H62=[1]Sheet1!H62,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T62">
+        <f>IF(I62=[1]Sheet1!I62,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="63" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
         <v>144</v>
       </c>
@@ -3086,8 +5383,28 @@
       <c r="K63" s="3" t="s">
         <v>82</v>
       </c>
-    </row>
-    <row r="64" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P63">
+        <f>IF(E63=[1]Sheet1!E63,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q63">
+        <f>IF(F63=[1]Sheet1!F63,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R63">
+        <f>IF(G63=[1]Sheet1!G63,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S63">
+        <f>IF(H63=[1]Sheet1!H63,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T63">
+        <f>IF(I63=[1]Sheet1!I63,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="64" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
         <v>145</v>
       </c>
@@ -3119,8 +5436,28 @@
       <c r="K64" s="3" t="s">
         <v>83</v>
       </c>
-    </row>
-    <row r="65" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P64">
+        <f>IF(E64=[1]Sheet1!E64,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q64">
+        <f>IF(F64=[1]Sheet1!F64,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R64">
+        <f>IF(G64=[1]Sheet1!G64,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S64">
+        <f>IF(H64=[1]Sheet1!H64,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T64">
+        <f>IF(I64=[1]Sheet1!I64,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="65" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
         <v>146</v>
       </c>
@@ -3152,8 +5489,28 @@
       <c r="K65" s="3" t="s">
         <v>84</v>
       </c>
-    </row>
-    <row r="66" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P65">
+        <f>IF(E65=[1]Sheet1!E65,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="Q65">
+        <f>IF(F65=[1]Sheet1!F65,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="R65">
+        <f>IF(G65=[1]Sheet1!G65,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="S65">
+        <f>IF(H65=[1]Sheet1!H65,1,0)</f>
+        <v>1</v>
+      </c>
+      <c r="T65">
+        <f>IF(I65=[1]Sheet1!I65,1,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="66" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
         <v>158</v>
       </c>
@@ -3188,8 +5545,28 @@
       <c r="K66" s="3" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="67" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P66">
+        <f>IF(E66=[1]Sheet1!E66,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q66">
+        <f>IF(F66=[1]Sheet1!F66,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R66">
+        <f>IF(G66=[1]Sheet1!G66,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S66">
+        <f>IF(H66=[1]Sheet1!H66,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T66">
+        <f>IF(I66=[1]Sheet1!I66,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="67" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
         <v>160</v>
       </c>
@@ -3224,8 +5601,28 @@
       <c r="K67" s="3" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="68" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P67">
+        <f>IF(E67=[1]Sheet1!E67,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q67">
+        <f>IF(F67=[1]Sheet1!F67,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R67">
+        <f>IF(G67=[1]Sheet1!G67,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S67">
+        <f>IF(H67=[1]Sheet1!H67,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T67">
+        <f>IF(I67=[1]Sheet1!I67,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="68" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
         <v>162</v>
       </c>
@@ -3260,8 +5657,28 @@
       <c r="K68" s="3" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="69" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P68">
+        <f>IF(E68=[1]Sheet1!E68,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q68">
+        <f>IF(F68=[1]Sheet1!F68,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R68">
+        <f>IF(G68=[1]Sheet1!G68,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S68">
+        <f>IF(H68=[1]Sheet1!H68,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T68">
+        <f>IF(I68=[1]Sheet1!I68,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="69" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
         <v>164</v>
       </c>
@@ -3296,8 +5713,28 @@
       <c r="K69" s="3" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="70" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P69">
+        <f>IF(E69=[1]Sheet1!E69,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q69">
+        <f>IF(F69=[1]Sheet1!F69,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R69">
+        <f>IF(G69=[1]Sheet1!G69,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S69">
+        <f>IF(H69=[1]Sheet1!H69,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T69">
+        <f>IF(I69=[1]Sheet1!I69,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="70" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
         <v>166</v>
       </c>
@@ -3332,8 +5769,28 @@
       <c r="K70" s="3" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="71" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P70">
+        <f>IF(E70=[1]Sheet1!E70,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q70">
+        <f>IF(F70=[1]Sheet1!F70,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R70">
+        <f>IF(G70=[1]Sheet1!G70,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S70">
+        <f>IF(H70=[1]Sheet1!H70,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T70">
+        <f>IF(I70=[1]Sheet1!I70,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="71" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
         <v>168</v>
       </c>
@@ -3368,8 +5825,28 @@
       <c r="K71" s="3" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="72" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P71">
+        <f>IF(E71=[1]Sheet1!E71,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q71">
+        <f>IF(F71=[1]Sheet1!F71,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R71">
+        <f>IF(G71=[1]Sheet1!G71,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S71">
+        <f>IF(H71=[1]Sheet1!H71,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T71">
+        <f>IF(I71=[1]Sheet1!I71,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="72" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
         <v>170</v>
       </c>
@@ -3404,8 +5881,28 @@
       <c r="K72" s="3" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="73" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P72">
+        <f>IF(E72=[1]Sheet1!E72,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q72">
+        <f>IF(F72=[1]Sheet1!F72,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R72">
+        <f>IF(G72=[1]Sheet1!G72,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S72">
+        <f>IF(H72=[1]Sheet1!H72,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T72">
+        <f>IF(I72=[1]Sheet1!I72,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="73" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
         <v>172</v>
       </c>
@@ -3440,8 +5937,28 @@
       <c r="K73" s="3" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="74" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P73">
+        <f>IF(E73=[1]Sheet1!E73,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q73">
+        <f>IF(F73=[1]Sheet1!F73,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R73">
+        <f>IF(G73=[1]Sheet1!G73,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S73">
+        <f>IF(H73=[1]Sheet1!H73,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T73">
+        <f>IF(I73=[1]Sheet1!I73,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="74" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
         <v>174</v>
       </c>
@@ -3476,8 +5993,28 @@
       <c r="K74" s="3" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="75" spans="1:11" x14ac:dyDescent="0.35">
+      <c r="P74">
+        <f>IF(E74=[1]Sheet1!E74,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q74">
+        <f>IF(F74=[1]Sheet1!F74,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R74">
+        <f>IF(G74=[1]Sheet1!G74,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S74">
+        <f>IF(H74=[1]Sheet1!H74,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T74">
+        <f>IF(I74=[1]Sheet1!I74,1,0)</f>
+        <v>0</v>
+      </c>
+    </row>
+    <row r="75" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A75" s="3" t="s">
         <v>176</v>
       </c>
@@ -3511,6 +6048,26 @@
       <c r="J75" s="3"/>
       <c r="K75" s="3" t="s">
         <v>177</v>
+      </c>
+      <c r="P75">
+        <f>IF(E75=[1]Sheet1!E75,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="Q75">
+        <f>IF(F75=[1]Sheet1!F75,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="R75">
+        <f>IF(G75=[1]Sheet1!G75,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="S75">
+        <f>IF(H75=[1]Sheet1!H75,1,0)</f>
+        <v>0</v>
+      </c>
+      <c r="T75">
+        <f>IF(I75=[1]Sheet1!I75,1,0)</f>
+        <v>0</v>
       </c>
     </row>
   </sheetData>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29725"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="30228"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saran\Documents\Academia\repository_clones\Bioindustrial-Park\biorefineries\isobutanol\analyses\full\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7B7189EE-26EF-4DE6-9BA5-179C71AF3E3C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40ED91F-AD3F-46A8-AE1A-1EA828B2D5D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -599,12 +599,6 @@
     <t>Feedstock starch content</t>
   </si>
   <si>
-    <t>kg/kg-water</t>
-  </si>
-  <si>
-    <t>feedstock.imass['Starch'] =x * feedstock.imass['Water']</t>
-  </si>
-  <si>
     <t>Isopentyl acetate unit price</t>
   </si>
   <si>
@@ -621,6 +615,12 @@
   </si>
   <si>
     <t>Isobutanol selling unit price (sale)</t>
+  </si>
+  <si>
+    <t>kg/dry-kg</t>
+  </si>
+  <si>
+    <t>fixed_F_mass = feedstock.F_mass; feedstock.imass['Starch'] = x * (fixed_F_mass - feedstock.imass['Water']); feedstock.F_mass = fixed_F_mass</t>
   </si>
 </sst>
 </file>
@@ -882,279 +882,282 @@
         </row>
         <row r="12">
           <cell r="E12">
-            <v>1.49</v>
+            <v>0.28599999999999998</v>
           </cell>
           <cell r="F12" t="str">
             <v>Triangular</v>
           </cell>
           <cell r="G12">
-            <v>1.1919999999999999</v>
+            <v>0.17499999999999999</v>
           </cell>
           <cell r="H12">
-            <v>1.49</v>
+            <v>0.28599999999999998</v>
           </cell>
           <cell r="I12">
-            <v>1.788</v>
+            <v>0.315</v>
           </cell>
         </row>
         <row r="13">
           <cell r="E13">
-            <v>3.2</v>
+            <v>0.10355</v>
           </cell>
           <cell r="F13" t="str">
-            <v>Uniform</v>
+            <v>Triangular</v>
           </cell>
           <cell r="G13">
-            <v>2.5600000000000005</v>
+            <v>9.3195E-2</v>
+          </cell>
+          <cell r="H13">
+            <v>0.10355</v>
           </cell>
           <cell r="I13">
-            <v>3.84</v>
+            <v>0.11390500000000001</v>
           </cell>
         </row>
         <row r="14">
           <cell r="E14">
-            <v>0.28599999999999998</v>
+            <v>0.21</v>
           </cell>
           <cell r="F14" t="str">
-            <v>Triangular</v>
+            <v>Uniform</v>
           </cell>
           <cell r="G14">
-            <v>0.17499999999999999</v>
-          </cell>
-          <cell r="H14">
-            <v>0.28599999999999998</v>
+            <v>0.15</v>
           </cell>
           <cell r="I14">
-            <v>0.315</v>
+            <v>0.28000000000000003</v>
           </cell>
         </row>
         <row r="15">
           <cell r="E15">
-            <v>0.10355</v>
+            <v>0.15</v>
           </cell>
           <cell r="F15" t="str">
-            <v>Triangular</v>
+            <v>Uniform</v>
           </cell>
           <cell r="G15">
-            <v>9.3195E-2</v>
-          </cell>
-          <cell r="H15">
-            <v>0.10355</v>
+            <v>0.12</v>
           </cell>
           <cell r="I15">
-            <v>0.11390500000000001</v>
+            <v>0.18</v>
           </cell>
         </row>
         <row r="16">
           <cell r="E16">
-            <v>0.21</v>
+            <v>0.72</v>
           </cell>
           <cell r="F16" t="str">
-            <v>Uniform</v>
+            <v>Triangular</v>
           </cell>
           <cell r="G16">
-            <v>0.15</v>
+            <v>0.57599999999999996</v>
+          </cell>
+          <cell r="H16">
+            <v>0.72</v>
           </cell>
           <cell r="I16">
-            <v>0.28000000000000003</v>
+            <v>0.86399999999999999</v>
           </cell>
         </row>
         <row r="17">
           <cell r="E17">
-            <v>0.15</v>
+            <v>56972</v>
           </cell>
           <cell r="F17" t="str">
-            <v>Uniform</v>
+            <v>Triangular</v>
           </cell>
           <cell r="G17">
-            <v>0.12</v>
+            <v>45577.600000000006</v>
+          </cell>
+          <cell r="H17">
+            <v>56972</v>
           </cell>
           <cell r="I17">
-            <v>0.18</v>
+            <v>68366.399999999994</v>
           </cell>
         </row>
         <row r="18">
           <cell r="E18">
-            <v>4.08</v>
+            <v>2</v>
           </cell>
           <cell r="F18" t="str">
-            <v>Triangular</v>
+            <v>Uniform</v>
           </cell>
           <cell r="G18">
-            <v>3.2640000000000002</v>
-          </cell>
-          <cell r="H18">
-            <v>4.08</v>
+            <v>1</v>
           </cell>
           <cell r="I18">
-            <v>4.8959999999999999</v>
+            <v>3</v>
           </cell>
         </row>
         <row r="19">
           <cell r="E19">
-            <v>56972</v>
+            <v>156</v>
           </cell>
           <cell r="F19" t="str">
             <v>Triangular</v>
           </cell>
           <cell r="G19">
-            <v>45577.600000000006</v>
+            <v>124.80000000000001</v>
           </cell>
           <cell r="H19">
-            <v>56972</v>
+            <v>156</v>
           </cell>
           <cell r="I19">
-            <v>68366.399999999994</v>
+            <v>187.2</v>
           </cell>
         </row>
         <row r="20">
           <cell r="E20">
-            <v>2</v>
+            <v>156</v>
           </cell>
           <cell r="F20" t="str">
-            <v>Uniform</v>
+            <v>Triangular</v>
           </cell>
           <cell r="G20">
-            <v>1</v>
+            <v>124.80000000000001</v>
+          </cell>
+          <cell r="H20">
+            <v>156</v>
           </cell>
           <cell r="I20">
-            <v>3</v>
+            <v>187.2</v>
           </cell>
         </row>
         <row r="21">
           <cell r="E21">
-            <v>156</v>
+            <v>1.43</v>
           </cell>
           <cell r="F21" t="str">
-            <v>Triangular</v>
+            <v>triangular</v>
           </cell>
           <cell r="G21">
-            <v>124.80000000000001</v>
+            <v>1.1439999999999999</v>
           </cell>
           <cell r="H21">
-            <v>156</v>
+            <v>1.43</v>
           </cell>
           <cell r="I21">
-            <v>187.2</v>
+            <v>1.716</v>
           </cell>
         </row>
         <row r="22">
           <cell r="E22">
-            <v>156</v>
+            <v>0.94</v>
           </cell>
           <cell r="F22" t="str">
-            <v>Triangular</v>
+            <v>triangular</v>
           </cell>
           <cell r="G22">
-            <v>124.80000000000001</v>
+            <v>0.752</v>
           </cell>
           <cell r="H22">
-            <v>156</v>
+            <v>0.94</v>
           </cell>
           <cell r="I22">
-            <v>187.2</v>
+            <v>1.1279999999999999</v>
           </cell>
         </row>
         <row r="23">
           <cell r="E23">
-            <v>1.43</v>
+            <v>0.58399999999999996</v>
           </cell>
           <cell r="F23" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G23">
-            <v>1.1439999999999999</v>
+            <v>0.4672</v>
           </cell>
           <cell r="H23">
-            <v>1.43</v>
+            <v>0.58399999999999996</v>
           </cell>
           <cell r="I23">
-            <v>1.716</v>
+            <v>0.70079999999999998</v>
           </cell>
         </row>
         <row r="24">
           <cell r="E24">
-            <v>0.94</v>
+            <v>1.1599999999999999E-2</v>
           </cell>
           <cell r="F24" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G24">
-            <v>0.752</v>
+            <v>9.2800000000000001E-3</v>
           </cell>
           <cell r="H24">
-            <v>0.94</v>
+            <v>1.1599999999999999E-2</v>
           </cell>
           <cell r="I24">
-            <v>1.1279999999999999</v>
+            <v>1.3919999999999899E-2</v>
           </cell>
         </row>
         <row r="25">
           <cell r="E25">
-            <v>0.58399999999999996</v>
+            <v>47.1</v>
           </cell>
           <cell r="F25" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G25">
-            <v>0.4672</v>
+            <v>37.68</v>
           </cell>
           <cell r="H25">
-            <v>0.58399999999999996</v>
+            <v>47.1</v>
           </cell>
           <cell r="I25">
-            <v>0.70079999999999998</v>
+            <v>56.52</v>
           </cell>
         </row>
         <row r="26">
           <cell r="E26">
-            <v>1.1599999999999999E-2</v>
+            <v>14.2</v>
           </cell>
           <cell r="F26" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G26">
-            <v>9.2800000000000001E-3</v>
+            <v>11.36</v>
           </cell>
           <cell r="H26">
-            <v>1.1599999999999999E-2</v>
+            <v>14.2</v>
           </cell>
           <cell r="I26">
-            <v>1.3919999999999899E-2</v>
+            <v>17.04</v>
           </cell>
         </row>
         <row r="27">
           <cell r="E27">
-            <v>47.1</v>
+            <v>0.12</v>
           </cell>
           <cell r="F27" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G27">
-            <v>37.68</v>
+            <v>9.6000000000000002E-2</v>
           </cell>
           <cell r="H27">
-            <v>47.1</v>
+            <v>0.12</v>
           </cell>
           <cell r="I27">
-            <v>56.52</v>
+            <v>0.14399999999999999</v>
           </cell>
         </row>
         <row r="28">
           <cell r="E28">
-            <v>14.2</v>
+            <v>0.04</v>
           </cell>
           <cell r="F28" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G28">
-            <v>11.36</v>
+            <v>3.2000000000000001E-2</v>
           </cell>
           <cell r="H28">
-            <v>14.2</v>
+            <v>0.04</v>
           </cell>
           <cell r="I28">
-            <v>17.04</v>
+            <v>4.8000000000000001E-2</v>
           </cell>
         </row>
         <row r="29">
@@ -1193,138 +1196,138 @@
         </row>
         <row r="31">
           <cell r="E31">
-            <v>0.12</v>
+            <v>0.501</v>
           </cell>
           <cell r="F31" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G31">
-            <v>9.6000000000000002E-2</v>
+            <v>0.40079999999999999</v>
           </cell>
           <cell r="H31">
-            <v>0.12</v>
+            <v>0.501</v>
           </cell>
           <cell r="I31">
-            <v>0.14399999999999999</v>
+            <v>0.60119999999999996</v>
           </cell>
         </row>
         <row r="32">
           <cell r="E32">
-            <v>0.04</v>
+            <v>2.0000000000000002E-5</v>
           </cell>
           <cell r="F32" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G32">
-            <v>3.2000000000000001E-2</v>
+            <v>1.5999999999999999E-5</v>
           </cell>
           <cell r="H32">
-            <v>0.04</v>
+            <v>2.0000000000000002E-5</v>
           </cell>
           <cell r="I32">
-            <v>4.8000000000000001E-2</v>
+            <v>2.4000000000000001E-5</v>
           </cell>
         </row>
         <row r="33">
           <cell r="E33">
-            <v>0.501</v>
+            <v>0.10100000000000001</v>
           </cell>
           <cell r="F33" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G33">
-            <v>0.40079999999999999</v>
+            <v>8.0799999999999997E-2</v>
           </cell>
           <cell r="H33">
-            <v>0.501</v>
+            <v>0.10100000000000001</v>
           </cell>
           <cell r="I33">
-            <v>0.60119999999999996</v>
+            <v>0.1212</v>
           </cell>
         </row>
         <row r="34">
           <cell r="E34">
-            <v>2.0000000000000002E-5</v>
+            <v>5.81</v>
           </cell>
           <cell r="F34" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G34">
-            <v>1.5999999999999999E-5</v>
+            <v>4.6479999999999997</v>
           </cell>
           <cell r="H34">
-            <v>2.0000000000000002E-5</v>
+            <v>5.81</v>
           </cell>
           <cell r="I34">
-            <v>2.4000000000000001E-5</v>
+            <v>6.9719999999999898</v>
           </cell>
         </row>
         <row r="35">
           <cell r="E35">
-            <v>0.10100000000000001</v>
+            <v>4.9999999999999998E-7</v>
           </cell>
           <cell r="F35" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G35">
-            <v>8.0799999999999997E-2</v>
+            <v>3.9999999999999998E-7</v>
           </cell>
           <cell r="H35">
-            <v>0.10100000000000001</v>
+            <v>4.9999999999999998E-7</v>
           </cell>
           <cell r="I35">
-            <v>0.1212</v>
+            <v>5.9999999999999997E-7</v>
           </cell>
         </row>
         <row r="36">
           <cell r="E36">
-            <v>5.81</v>
+            <v>4.8</v>
           </cell>
           <cell r="F36" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G36">
-            <v>4.6479999999999997</v>
+            <v>3.84</v>
           </cell>
           <cell r="H36">
-            <v>5.81</v>
+            <v>4.8</v>
           </cell>
           <cell r="I36">
-            <v>6.9719999999999898</v>
+            <v>5.76</v>
           </cell>
         </row>
         <row r="37">
           <cell r="E37">
-            <v>4.9999999999999998E-7</v>
+            <v>0.04</v>
           </cell>
           <cell r="F37" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G37">
-            <v>3.9999999999999998E-7</v>
+            <v>3.2000000000000001E-2</v>
           </cell>
           <cell r="H37">
-            <v>4.9999999999999998E-7</v>
+            <v>0.04</v>
           </cell>
           <cell r="I37">
-            <v>5.9999999999999997E-7</v>
+            <v>4.8000000000000001E-2</v>
           </cell>
         </row>
         <row r="38">
           <cell r="E38">
-            <v>4.8</v>
+            <v>0.12</v>
           </cell>
           <cell r="F38" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G38">
-            <v>3.84</v>
+            <v>9.6000000000000002E-2</v>
           </cell>
           <cell r="H38">
-            <v>4.8</v>
+            <v>0.12</v>
           </cell>
           <cell r="I38">
-            <v>5.76</v>
+            <v>0.14399999999999999</v>
           </cell>
         </row>
         <row r="39">
@@ -1346,223 +1349,223 @@
         </row>
         <row r="40">
           <cell r="E40">
-            <v>0.12</v>
+            <v>2.6400000000000002E-4</v>
           </cell>
           <cell r="F40" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G40">
-            <v>9.6000000000000002E-2</v>
+            <v>2.1120000000000001E-4</v>
           </cell>
           <cell r="H40">
-            <v>0.12</v>
+            <v>2.6400000000000002E-4</v>
           </cell>
           <cell r="I40">
-            <v>0.14399999999999999</v>
+            <v>3.168E-4</v>
           </cell>
         </row>
         <row r="41">
           <cell r="E41">
-            <v>0.04</v>
+            <v>1.04E-2</v>
           </cell>
           <cell r="F41" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G41">
-            <v>3.2000000000000001E-2</v>
+            <v>8.3199999999999993E-3</v>
           </cell>
           <cell r="H41">
-            <v>0.04</v>
+            <v>1.04E-2</v>
           </cell>
           <cell r="I41">
-            <v>4.8000000000000001E-2</v>
+            <v>1.248E-2</v>
           </cell>
         </row>
         <row r="42">
           <cell r="E42">
-            <v>2.6400000000000002E-4</v>
+            <v>1.0200000000000001E-2</v>
           </cell>
           <cell r="F42" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G42">
-            <v>2.1120000000000001E-4</v>
+            <v>8.1600000000000006E-3</v>
           </cell>
           <cell r="H42">
-            <v>2.6400000000000002E-4</v>
+            <v>1.0200000000000001E-2</v>
           </cell>
           <cell r="I42">
-            <v>3.168E-4</v>
+            <v>1.2239999999999999E-2</v>
           </cell>
         </row>
         <row r="43">
           <cell r="E43">
-            <v>1.04E-2</v>
+            <v>0.77500000000000002</v>
           </cell>
           <cell r="F43" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G43">
-            <v>8.3199999999999993E-3</v>
+            <v>0.62</v>
           </cell>
           <cell r="H43">
-            <v>1.04E-2</v>
+            <v>0.77500000000000002</v>
           </cell>
           <cell r="I43">
-            <v>1.248E-2</v>
+            <v>0.92999999999999905</v>
           </cell>
         </row>
         <row r="44">
           <cell r="E44">
-            <v>1.0200000000000001E-2</v>
+            <v>0.1</v>
           </cell>
           <cell r="F44" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G44">
-            <v>8.1600000000000006E-3</v>
+            <v>0.08</v>
           </cell>
           <cell r="H44">
-            <v>1.0200000000000001E-2</v>
+            <v>0.1</v>
           </cell>
           <cell r="I44">
-            <v>1.2239999999999999E-2</v>
+            <v>0.12</v>
           </cell>
         </row>
         <row r="45">
           <cell r="E45">
-            <v>0.77500000000000002</v>
+            <v>440</v>
           </cell>
           <cell r="F45" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G45">
-            <v>0.62</v>
+            <v>352</v>
           </cell>
           <cell r="H45">
-            <v>0.77500000000000002</v>
+            <v>440</v>
           </cell>
           <cell r="I45">
-            <v>0.92999999999999905</v>
+            <v>528</v>
           </cell>
         </row>
         <row r="46">
           <cell r="E46">
-            <v>0.1</v>
+            <v>2.82</v>
           </cell>
           <cell r="F46" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G46">
-            <v>0.08</v>
+            <v>2.2559999999999998</v>
           </cell>
           <cell r="H46">
-            <v>0.1</v>
+            <v>2.82</v>
           </cell>
           <cell r="I46">
-            <v>0.12</v>
+            <v>3.3839999999999999</v>
           </cell>
         </row>
         <row r="47">
           <cell r="E47">
-            <v>440</v>
+            <v>1.2500000000000001E-2</v>
           </cell>
           <cell r="F47" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G47">
-            <v>352</v>
+            <v>0.01</v>
           </cell>
           <cell r="H47">
-            <v>440</v>
+            <v>1.2500000000000001E-2</v>
           </cell>
           <cell r="I47">
-            <v>528</v>
+            <v>1.4999999999999999E-2</v>
           </cell>
         </row>
         <row r="48">
           <cell r="E48">
-            <v>2.82</v>
+            <v>3.4000000000000002E-2</v>
           </cell>
           <cell r="F48" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G48">
-            <v>2.2559999999999998</v>
+            <v>2.7199999999999998E-2</v>
           </cell>
           <cell r="H48">
-            <v>2.82</v>
+            <v>3.4000000000000002E-2</v>
           </cell>
           <cell r="I48">
-            <v>3.3839999999999999</v>
+            <v>4.0800000000000003E-2</v>
           </cell>
         </row>
         <row r="49">
           <cell r="E49">
-            <v>1.2500000000000001E-2</v>
+            <v>5.7000000000000002E-2</v>
           </cell>
           <cell r="F49" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G49">
-            <v>0.01</v>
+            <v>4.5600000000000002E-2</v>
           </cell>
           <cell r="H49">
-            <v>1.2500000000000001E-2</v>
+            <v>5.7000000000000002E-2</v>
           </cell>
           <cell r="I49">
-            <v>1.4999999999999999E-2</v>
+            <v>6.8400000000000002E-2</v>
           </cell>
         </row>
         <row r="50">
           <cell r="E50">
-            <v>3.4000000000000002E-2</v>
+            <v>1.2030000000000001</v>
           </cell>
           <cell r="F50" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G50">
-            <v>2.7199999999999998E-2</v>
+            <v>0.96240000000000003</v>
           </cell>
           <cell r="H50">
-            <v>3.4000000000000002E-2</v>
+            <v>1.2030000000000001</v>
           </cell>
           <cell r="I50">
-            <v>4.0800000000000003E-2</v>
+            <v>1.4436</v>
           </cell>
         </row>
         <row r="51">
           <cell r="E51">
-            <v>5.7000000000000002E-2</v>
+            <v>0.04</v>
           </cell>
           <cell r="F51" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G51">
-            <v>4.5600000000000002E-2</v>
+            <v>3.2000000000000001E-2</v>
           </cell>
           <cell r="H51">
-            <v>5.7000000000000002E-2</v>
+            <v>0.04</v>
           </cell>
           <cell r="I51">
-            <v>6.8400000000000002E-2</v>
+            <v>4.8000000000000001E-2</v>
           </cell>
         </row>
         <row r="52">
           <cell r="E52">
-            <v>1.2030000000000001</v>
+            <v>0.12</v>
           </cell>
           <cell r="F52" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G52">
-            <v>0.96240000000000003</v>
+            <v>9.6000000000000002E-2</v>
           </cell>
           <cell r="H52">
-            <v>1.2030000000000001</v>
+            <v>0.12</v>
           </cell>
           <cell r="I52">
-            <v>1.4436</v>
+            <v>0.14399999999999999</v>
           </cell>
         </row>
         <row r="53">
@@ -1584,205 +1587,171 @@
         </row>
         <row r="54">
           <cell r="E54">
-            <v>0.12</v>
+            <v>1.01E-2</v>
           </cell>
           <cell r="F54" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G54">
-            <v>9.6000000000000002E-2</v>
+            <v>8.0800000000000004E-3</v>
           </cell>
           <cell r="H54">
-            <v>0.12</v>
+            <v>1.01E-2</v>
           </cell>
           <cell r="I54">
-            <v>0.14399999999999999</v>
+            <v>1.21199999999999E-2</v>
           </cell>
         </row>
         <row r="55">
           <cell r="E55">
-            <v>0.04</v>
+            <v>0.58899999999999997</v>
           </cell>
           <cell r="F55" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G55">
-            <v>3.2000000000000001E-2</v>
+            <v>0.47120000000000001</v>
           </cell>
           <cell r="H55">
-            <v>0.04</v>
+            <v>0.58899999999999997</v>
           </cell>
           <cell r="I55">
-            <v>4.8000000000000001E-2</v>
+            <v>0.70679999999999998</v>
           </cell>
         </row>
         <row r="56">
           <cell r="E56">
-            <v>1.01E-2</v>
+            <v>8.0000000000000002E-3</v>
           </cell>
           <cell r="F56" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G56">
-            <v>8.0800000000000004E-3</v>
+            <v>6.4000000000000003E-3</v>
           </cell>
           <cell r="H56">
-            <v>1.01E-2</v>
+            <v>8.0000000000000002E-3</v>
           </cell>
           <cell r="I56">
-            <v>1.21199999999999E-2</v>
+            <v>9.5999999999999992E-3</v>
           </cell>
         </row>
         <row r="57">
           <cell r="E57">
-            <v>0.58899999999999997</v>
+            <v>9.9999999999999995E-7</v>
           </cell>
           <cell r="F57" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G57">
-            <v>0.47120000000000001</v>
+            <v>7.9999999999999996E-7</v>
           </cell>
           <cell r="H57">
-            <v>0.58899999999999997</v>
+            <v>9.9999999999999995E-7</v>
           </cell>
           <cell r="I57">
-            <v>0.70679999999999998</v>
+            <v>1.1999999999999999E-6</v>
           </cell>
         </row>
         <row r="58">
           <cell r="E58">
-            <v>8.0000000000000002E-3</v>
+            <v>7.51E-2</v>
           </cell>
           <cell r="F58" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G58">
-            <v>6.4000000000000003E-3</v>
+            <v>6.0080000000000001E-2</v>
           </cell>
           <cell r="H58">
-            <v>8.0000000000000002E-3</v>
+            <v>7.51E-2</v>
           </cell>
           <cell r="I58">
-            <v>9.5999999999999992E-3</v>
+            <v>9.0119999999999895E-2</v>
           </cell>
         </row>
         <row r="59">
           <cell r="E59">
-            <v>9.9999999999999995E-7</v>
+            <v>13</v>
           </cell>
           <cell r="F59" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G59">
-            <v>7.9999999999999996E-7</v>
+            <v>10.4</v>
           </cell>
           <cell r="H59">
-            <v>9.9999999999999995E-7</v>
+            <v>13</v>
           </cell>
           <cell r="I59">
-            <v>1.1999999999999999E-6</v>
+            <v>15.6</v>
           </cell>
         </row>
         <row r="60">
           <cell r="E60">
-            <v>7.51E-2</v>
+            <v>25</v>
           </cell>
           <cell r="F60" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G60">
-            <v>6.0080000000000001E-2</v>
+            <v>20</v>
           </cell>
           <cell r="H60">
-            <v>7.51E-2</v>
+            <v>25</v>
           </cell>
           <cell r="I60">
-            <v>9.0119999999999895E-2</v>
+            <v>30</v>
           </cell>
         </row>
         <row r="61">
           <cell r="E61">
-            <v>13</v>
+            <v>3.9899999999999996E-3</v>
           </cell>
           <cell r="F61" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G61">
-            <v>10.4</v>
+            <v>3.192E-3</v>
           </cell>
           <cell r="H61">
-            <v>13</v>
+            <v>3.9899999999999996E-3</v>
           </cell>
           <cell r="I61">
-            <v>15.6</v>
+            <v>4.7879999999999997E-3</v>
           </cell>
         </row>
         <row r="62">
           <cell r="E62">
-            <v>25</v>
+            <v>0.06</v>
           </cell>
           <cell r="F62" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G62">
-            <v>20</v>
+            <v>4.8000000000000001E-2</v>
           </cell>
           <cell r="H62">
-            <v>25</v>
+            <v>0.06</v>
           </cell>
           <cell r="I62">
-            <v>30</v>
+            <v>7.1999999999999995E-2</v>
           </cell>
         </row>
         <row r="63">
           <cell r="E63">
-            <v>3.9899999999999996E-3</v>
+            <v>0.02</v>
           </cell>
           <cell r="F63" t="str">
             <v>triangular</v>
           </cell>
           <cell r="G63">
-            <v>3.192E-3</v>
+            <v>1.6E-2</v>
           </cell>
           <cell r="H63">
-            <v>3.9899999999999996E-3</v>
+            <v>0.02</v>
           </cell>
           <cell r="I63">
-            <v>4.7879999999999997E-3</v>
-          </cell>
-        </row>
-        <row r="64">
-          <cell r="E64">
-            <v>0.06</v>
-          </cell>
-          <cell r="F64" t="str">
-            <v>triangular</v>
-          </cell>
-          <cell r="G64">
-            <v>4.8000000000000001E-2</v>
-          </cell>
-          <cell r="H64">
-            <v>0.06</v>
-          </cell>
-          <cell r="I64">
-            <v>7.1999999999999995E-2</v>
-          </cell>
-        </row>
-        <row r="65">
-          <cell r="E65">
-            <v>0.02</v>
-          </cell>
-          <cell r="F65" t="str">
-            <v>triangular</v>
-          </cell>
-          <cell r="G65">
-            <v>1.6E-2</v>
-          </cell>
-          <cell r="H65">
-            <v>0.02</v>
-          </cell>
-          <cell r="I65">
             <v>2.4E-2</v>
           </cell>
         </row>
@@ -2583,7 +2552,7 @@
     </row>
     <row r="11" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A11" s="4" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B11" s="4" t="s">
         <v>7</v>
@@ -2636,7 +2605,7 @@
     </row>
     <row r="12" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A12" s="4" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="B12" s="4" t="s">
         <v>7</v>
@@ -2671,7 +2640,7 @@
       </c>
       <c r="P12">
         <f>IF(E12=[1]Sheet1!E12,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q12">
         <f>IF(F12=[1]Sheet1!F12,1,0)</f>
@@ -2679,20 +2648,20 @@
       </c>
       <c r="R12">
         <f>IF(G12=[1]Sheet1!G12,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S12">
         <f>IF(H12=[1]Sheet1!H12,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T12">
         <f>IF(I12=[1]Sheet1!I12,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A13" s="4" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B13" s="4" t="s">
         <v>7</v>
@@ -2724,23 +2693,23 @@
       </c>
       <c r="P13">
         <f>IF(E13=[1]Sheet1!E13,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q13">
         <f>IF(F13=[1]Sheet1!F13,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13">
         <f>IF(G13=[1]Sheet1!G13,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S13">
         <f>IF(H13=[1]Sheet1!H13,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13">
         <f>IF(I13=[1]Sheet1!I13,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
@@ -2777,23 +2746,23 @@
       </c>
       <c r="P14">
         <f>IF(E14=[1]Sheet1!E14,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q14">
         <f>IF(F14=[1]Sheet1!F14,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R14">
         <f>IF(G14=[1]Sheet1!G14,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S14">
         <f>IF(H14=[1]Sheet1!H14,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T14">
         <f>IF(I14=[1]Sheet1!I14,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.35">
@@ -2833,23 +2802,23 @@
       </c>
       <c r="P15">
         <f>IF(E15=[1]Sheet1!E15,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q15">
         <f>IF(F15=[1]Sheet1!F15,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15">
         <f>IF(G15=[1]Sheet1!G15,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S15">
         <f>IF(H15=[1]Sheet1!H15,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15">
         <f>IF(I15=[1]Sheet1!I15,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.35">
@@ -2884,23 +2853,23 @@
       </c>
       <c r="P16">
         <f>IF(E16=[1]Sheet1!E16,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q16">
         <f>IF(F16=[1]Sheet1!F16,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R16">
         <f>IF(G16=[1]Sheet1!G16,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S16">
         <f>IF(H16=[1]Sheet1!H16,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T16">
         <f>IF(I16=[1]Sheet1!I16,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.35">
@@ -2937,23 +2906,23 @@
       </c>
       <c r="P17">
         <f>IF(E17=[1]Sheet1!E17,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q17">
         <f>IF(F17=[1]Sheet1!F17,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R17">
         <f>IF(G17=[1]Sheet1!G17,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S17">
         <f>IF(H17=[1]Sheet1!H17,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T17">
         <f>IF(I17=[1]Sheet1!I17,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.35">
@@ -2967,49 +2936,49 @@
         <v>21</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="E18" s="3">
-        <v>4.08</v>
+        <v>0.72</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G18" s="3">
         <f>0.8*H18</f>
-        <v>3.2640000000000002</v>
+        <v>0.57599999999999996</v>
       </c>
       <c r="H18" s="3">
         <f>E18</f>
-        <v>4.08</v>
+        <v>0.72</v>
       </c>
       <c r="I18" s="3">
         <f>1.2*H18</f>
-        <v>4.8959999999999999</v>
+        <v>0.86399999999999999</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="P18">
         <f>IF(E18=[1]Sheet1!E18,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q18">
         <f>IF(F18=[1]Sheet1!F18,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18">
         <f>IF(G18=[1]Sheet1!G18,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S18">
         <f>IF(H18=[1]Sheet1!H18,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T18">
         <f>IF(I18=[1]Sheet1!I18,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.35">
@@ -3049,7 +3018,7 @@
       </c>
       <c r="P19">
         <f>IF(E19=[1]Sheet1!E19,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q19">
         <f>IF(F19=[1]Sheet1!F19,1,0)</f>
@@ -3057,23 +3026,23 @@
       </c>
       <c r="R19">
         <f>IF(G19=[1]Sheet1!G19,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S19">
         <f>IF(H19=[1]Sheet1!H19,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T19">
         <f>IF(I19=[1]Sheet1!I19,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
@@ -3096,27 +3065,27 @@
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="P20">
         <f>IF(E20=[1]Sheet1!E20,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q20">
         <f>IF(F20=[1]Sheet1!F20,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R20">
         <f>IF(G20=[1]Sheet1!G20,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S20">
         <f>IF(H20=[1]Sheet1!H20,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T20">
         <f>IF(I20=[1]Sheet1!I20,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.35">
@@ -3156,7 +3125,7 @@
       </c>
       <c r="P21">
         <f>IF(E21=[1]Sheet1!E21,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q21">
         <f>IF(F21=[1]Sheet1!F21,1,0)</f>
@@ -3164,15 +3133,15 @@
       </c>
       <c r="R21">
         <f>IF(G21=[1]Sheet1!G21,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S21">
         <f>IF(H21=[1]Sheet1!H21,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T21">
         <f>IF(I21=[1]Sheet1!I21,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.35">
@@ -3212,7 +3181,7 @@
       </c>
       <c r="P22">
         <f>IF(E22=[1]Sheet1!E22,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q22">
         <f>IF(F22=[1]Sheet1!F22,1,0)</f>
@@ -3220,15 +3189,15 @@
       </c>
       <c r="R22">
         <f>IF(G22=[1]Sheet1!G22,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S22">
         <f>IF(H22=[1]Sheet1!H22,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T22">
         <f>IF(I22=[1]Sheet1!I22,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.35">
@@ -3265,7 +3234,7 @@
       </c>
       <c r="P23">
         <f>IF(E23=[1]Sheet1!E23,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q23">
         <f>IF(F23=[1]Sheet1!F23,1,0)</f>
@@ -3273,15 +3242,15 @@
       </c>
       <c r="R23">
         <f>IF(G23=[1]Sheet1!G23,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S23">
         <f>IF(H23=[1]Sheet1!H23,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T23">
         <f>IF(I23=[1]Sheet1!I23,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.35">
@@ -3318,7 +3287,7 @@
       </c>
       <c r="P24">
         <f>IF(E24=[1]Sheet1!E24,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q24">
         <f>IF(F24=[1]Sheet1!F24,1,0)</f>
@@ -3326,15 +3295,15 @@
       </c>
       <c r="R24">
         <f>IF(G24=[1]Sheet1!G24,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S24">
         <f>IF(H24=[1]Sheet1!H24,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T24">
         <f>IF(I24=[1]Sheet1!I24,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.35">
@@ -3371,7 +3340,7 @@
       </c>
       <c r="P25">
         <f>IF(E25=[1]Sheet1!E25,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q25">
         <f>IF(F25=[1]Sheet1!F25,1,0)</f>
@@ -3379,15 +3348,15 @@
       </c>
       <c r="R25">
         <f>IF(G25=[1]Sheet1!G25,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S25">
         <f>IF(H25=[1]Sheet1!H25,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T25">
         <f>IF(I25=[1]Sheet1!I25,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.35">
@@ -3424,7 +3393,7 @@
       </c>
       <c r="P26">
         <f>IF(E26=[1]Sheet1!E26,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q26">
         <f>IF(F26=[1]Sheet1!F26,1,0)</f>
@@ -3432,15 +3401,15 @@
       </c>
       <c r="R26">
         <f>IF(G26=[1]Sheet1!G26,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S26">
         <f>IF(H26=[1]Sheet1!H26,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T26">
         <f>IF(I26=[1]Sheet1!I26,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.35">
@@ -3477,7 +3446,7 @@
       </c>
       <c r="P27">
         <f>IF(E27=[1]Sheet1!E27,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q27">
         <f>IF(F27=[1]Sheet1!F27,1,0)</f>
@@ -3485,15 +3454,15 @@
       </c>
       <c r="R27">
         <f>IF(G27=[1]Sheet1!G27,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S27">
         <f>IF(H27=[1]Sheet1!H27,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T27">
         <f>IF(I27=[1]Sheet1!I27,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.35">
@@ -3530,7 +3499,7 @@
       </c>
       <c r="P28">
         <f>IF(E28=[1]Sheet1!E28,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q28">
         <f>IF(F28=[1]Sheet1!F28,1,0)</f>
@@ -3538,15 +3507,15 @@
       </c>
       <c r="R28">
         <f>IF(G28=[1]Sheet1!G28,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S28">
         <f>IF(H28=[1]Sheet1!H28,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T28">
         <f>IF(I28=[1]Sheet1!I28,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.35">
@@ -3689,7 +3658,7 @@
       </c>
       <c r="P31">
         <f>IF(E31=[1]Sheet1!E31,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q31">
         <f>IF(F31=[1]Sheet1!F31,1,0)</f>
@@ -3697,15 +3666,15 @@
       </c>
       <c r="R31">
         <f>IF(G31=[1]Sheet1!G31,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S31">
         <f>IF(H31=[1]Sheet1!H31,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T31">
         <f>IF(I31=[1]Sheet1!I31,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.35">
@@ -3742,7 +3711,7 @@
       </c>
       <c r="P32">
         <f>IF(E32=[1]Sheet1!E32,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q32">
         <f>IF(F32=[1]Sheet1!F32,1,0)</f>
@@ -3750,15 +3719,15 @@
       </c>
       <c r="R32">
         <f>IF(G32=[1]Sheet1!G32,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S32">
         <f>IF(H32=[1]Sheet1!H32,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T32">
         <f>IF(I32=[1]Sheet1!I32,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.35">
@@ -3795,7 +3764,7 @@
       </c>
       <c r="P33">
         <f>IF(E33=[1]Sheet1!E33,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q33">
         <f>IF(F33=[1]Sheet1!F33,1,0)</f>
@@ -3803,15 +3772,15 @@
       </c>
       <c r="R33">
         <f>IF(G33=[1]Sheet1!G33,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S33">
         <f>IF(H33=[1]Sheet1!H33,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T33">
         <f>IF(I33=[1]Sheet1!I33,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.35">
@@ -3848,7 +3817,7 @@
       </c>
       <c r="P34">
         <f>IF(E34=[1]Sheet1!E34,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q34">
         <f>IF(F34=[1]Sheet1!F34,1,0)</f>
@@ -3856,15 +3825,15 @@
       </c>
       <c r="R34">
         <f>IF(G34=[1]Sheet1!G34,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S34">
         <f>IF(H34=[1]Sheet1!H34,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T34">
         <f>IF(I34=[1]Sheet1!I34,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.35">
@@ -3901,7 +3870,7 @@
       </c>
       <c r="P35">
         <f>IF(E35=[1]Sheet1!E35,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q35">
         <f>IF(F35=[1]Sheet1!F35,1,0)</f>
@@ -3909,15 +3878,15 @@
       </c>
       <c r="R35">
         <f>IF(G35=[1]Sheet1!G35,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S35">
         <f>IF(H35=[1]Sheet1!H35,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T35">
         <f>IF(I35=[1]Sheet1!I35,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.35">
@@ -3954,7 +3923,7 @@
       </c>
       <c r="P36">
         <f>IF(E36=[1]Sheet1!E36,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q36">
         <f>IF(F36=[1]Sheet1!F36,1,0)</f>
@@ -3962,15 +3931,15 @@
       </c>
       <c r="R36">
         <f>IF(G36=[1]Sheet1!G36,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S36">
         <f>IF(H36=[1]Sheet1!H36,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T36">
         <f>IF(I36=[1]Sheet1!I36,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.35">
@@ -4007,7 +3976,7 @@
       </c>
       <c r="P37">
         <f>IF(E37=[1]Sheet1!E37,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q37">
         <f>IF(F37=[1]Sheet1!F37,1,0)</f>
@@ -4015,15 +3984,15 @@
       </c>
       <c r="R37">
         <f>IF(G37=[1]Sheet1!G37,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S37">
         <f>IF(H37=[1]Sheet1!H37,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T37">
         <f>IF(I37=[1]Sheet1!I37,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.35">
@@ -4060,7 +4029,7 @@
       </c>
       <c r="P38">
         <f>IF(E38=[1]Sheet1!E38,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <f>IF(F38=[1]Sheet1!F38,1,0)</f>
@@ -4068,15 +4037,15 @@
       </c>
       <c r="R38">
         <f>IF(G38=[1]Sheet1!G38,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <f>IF(H38=[1]Sheet1!H38,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38">
         <f>IF(I38=[1]Sheet1!I38,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.35">
@@ -4166,7 +4135,7 @@
       </c>
       <c r="P40">
         <f>IF(E40=[1]Sheet1!E40,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q40">
         <f>IF(F40=[1]Sheet1!F40,1,0)</f>
@@ -4174,15 +4143,15 @@
       </c>
       <c r="R40">
         <f>IF(G40=[1]Sheet1!G40,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S40">
         <f>IF(H40=[1]Sheet1!H40,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T40">
         <f>IF(I40=[1]Sheet1!I40,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.35">
@@ -4219,7 +4188,7 @@
       </c>
       <c r="P41">
         <f>IF(E41=[1]Sheet1!E41,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q41">
         <f>IF(F41=[1]Sheet1!F41,1,0)</f>
@@ -4227,15 +4196,15 @@
       </c>
       <c r="R41">
         <f>IF(G41=[1]Sheet1!G41,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S41">
         <f>IF(H41=[1]Sheet1!H41,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T41">
         <f>IF(I41=[1]Sheet1!I41,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.35">
@@ -4272,7 +4241,7 @@
       </c>
       <c r="P42">
         <f>IF(E42=[1]Sheet1!E42,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q42">
         <f>IF(F42=[1]Sheet1!F42,1,0)</f>
@@ -4280,15 +4249,15 @@
       </c>
       <c r="R42">
         <f>IF(G42=[1]Sheet1!G42,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S42">
         <f>IF(H42=[1]Sheet1!H42,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T42">
         <f>IF(I42=[1]Sheet1!I42,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.35">
@@ -4325,7 +4294,7 @@
       </c>
       <c r="P43">
         <f>IF(E43=[1]Sheet1!E43,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q43">
         <f>IF(F43=[1]Sheet1!F43,1,0)</f>
@@ -4333,15 +4302,15 @@
       </c>
       <c r="R43">
         <f>IF(G43=[1]Sheet1!G43,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S43">
         <f>IF(H43=[1]Sheet1!H43,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T43">
         <f>IF(I43=[1]Sheet1!I43,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.35">
@@ -4378,7 +4347,7 @@
       </c>
       <c r="P44">
         <f>IF(E44=[1]Sheet1!E44,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q44">
         <f>IF(F44=[1]Sheet1!F44,1,0)</f>
@@ -4386,15 +4355,15 @@
       </c>
       <c r="R44">
         <f>IF(G44=[1]Sheet1!G44,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S44">
         <f>IF(H44=[1]Sheet1!H44,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T44">
         <f>IF(I44=[1]Sheet1!I44,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.35">
@@ -4431,7 +4400,7 @@
       </c>
       <c r="P45">
         <f>IF(E45=[1]Sheet1!E45,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q45">
         <f>IF(F45=[1]Sheet1!F45,1,0)</f>
@@ -4439,15 +4408,15 @@
       </c>
       <c r="R45">
         <f>IF(G45=[1]Sheet1!G45,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S45">
         <f>IF(H45=[1]Sheet1!H45,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T45">
         <f>IF(I45=[1]Sheet1!I45,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.35">
@@ -4484,7 +4453,7 @@
       </c>
       <c r="P46">
         <f>IF(E46=[1]Sheet1!E46,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q46">
         <f>IF(F46=[1]Sheet1!F46,1,0)</f>
@@ -4492,15 +4461,15 @@
       </c>
       <c r="R46">
         <f>IF(G46=[1]Sheet1!G46,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S46">
         <f>IF(H46=[1]Sheet1!H46,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T46">
         <f>IF(I46=[1]Sheet1!I46,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.35">
@@ -4537,7 +4506,7 @@
       </c>
       <c r="P47">
         <f>IF(E47=[1]Sheet1!E47,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q47">
         <f>IF(F47=[1]Sheet1!F47,1,0)</f>
@@ -4545,15 +4514,15 @@
       </c>
       <c r="R47">
         <f>IF(G47=[1]Sheet1!G47,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S47">
         <f>IF(H47=[1]Sheet1!H47,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T47">
         <f>IF(I47=[1]Sheet1!I47,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.35">
@@ -4590,7 +4559,7 @@
       </c>
       <c r="P48">
         <f>IF(E48=[1]Sheet1!E48,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q48">
         <f>IF(F48=[1]Sheet1!F48,1,0)</f>
@@ -4598,15 +4567,15 @@
       </c>
       <c r="R48">
         <f>IF(G48=[1]Sheet1!G48,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S48">
         <f>IF(H48=[1]Sheet1!H48,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T48">
         <f>IF(I48=[1]Sheet1!I48,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.35">
@@ -4643,7 +4612,7 @@
       </c>
       <c r="P49">
         <f>IF(E49=[1]Sheet1!E49,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q49">
         <f>IF(F49=[1]Sheet1!F49,1,0)</f>
@@ -4651,15 +4620,15 @@
       </c>
       <c r="R49">
         <f>IF(G49=[1]Sheet1!G49,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S49">
         <f>IF(H49=[1]Sheet1!H49,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T49">
         <f>IF(I49=[1]Sheet1!I49,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.35">
@@ -4696,7 +4665,7 @@
       </c>
       <c r="P50">
         <f>IF(E50=[1]Sheet1!E50,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q50">
         <f>IF(F50=[1]Sheet1!F50,1,0)</f>
@@ -4704,15 +4673,15 @@
       </c>
       <c r="R50">
         <f>IF(G50=[1]Sheet1!G50,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S50">
         <f>IF(H50=[1]Sheet1!H50,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T50">
         <f>IF(I50=[1]Sheet1!I50,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.35">
@@ -4749,7 +4718,7 @@
       </c>
       <c r="P51">
         <f>IF(E51=[1]Sheet1!E51,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q51">
         <f>IF(F51=[1]Sheet1!F51,1,0)</f>
@@ -4757,15 +4726,15 @@
       </c>
       <c r="R51">
         <f>IF(G51=[1]Sheet1!G51,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S51">
         <f>IF(H51=[1]Sheet1!H51,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T51">
         <f>IF(I51=[1]Sheet1!I51,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.35">
@@ -4802,7 +4771,7 @@
       </c>
       <c r="P52">
         <f>IF(E52=[1]Sheet1!E52,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q52">
         <f>IF(F52=[1]Sheet1!F52,1,0)</f>
@@ -4810,15 +4779,15 @@
       </c>
       <c r="R52">
         <f>IF(G52=[1]Sheet1!G52,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52">
         <f>IF(H52=[1]Sheet1!H52,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T52">
         <f>IF(I52=[1]Sheet1!I52,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.35">
@@ -4908,7 +4877,7 @@
       </c>
       <c r="P54">
         <f>IF(E54=[1]Sheet1!E54,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q54">
         <f>IF(F54=[1]Sheet1!F54,1,0)</f>
@@ -4916,15 +4885,15 @@
       </c>
       <c r="R54">
         <f>IF(G54=[1]Sheet1!G54,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S54">
         <f>IF(H54=[1]Sheet1!H54,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T54">
         <f>IF(I54=[1]Sheet1!I54,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.35">
@@ -4961,7 +4930,7 @@
       </c>
       <c r="P55">
         <f>IF(E55=[1]Sheet1!E55,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q55">
         <f>IF(F55=[1]Sheet1!F55,1,0)</f>
@@ -4969,15 +4938,15 @@
       </c>
       <c r="R55">
         <f>IF(G55=[1]Sheet1!G55,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S55">
         <f>IF(H55=[1]Sheet1!H55,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T55">
         <f>IF(I55=[1]Sheet1!I55,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.35">
@@ -5014,7 +4983,7 @@
       </c>
       <c r="P56">
         <f>IF(E56=[1]Sheet1!E56,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q56">
         <f>IF(F56=[1]Sheet1!F56,1,0)</f>
@@ -5022,15 +4991,15 @@
       </c>
       <c r="R56">
         <f>IF(G56=[1]Sheet1!G56,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S56">
         <f>IF(H56=[1]Sheet1!H56,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T56">
         <f>IF(I56=[1]Sheet1!I56,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.35">
@@ -5067,7 +5036,7 @@
       </c>
       <c r="P57">
         <f>IF(E57=[1]Sheet1!E57,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q57">
         <f>IF(F57=[1]Sheet1!F57,1,0)</f>
@@ -5075,15 +5044,15 @@
       </c>
       <c r="R57">
         <f>IF(G57=[1]Sheet1!G57,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S57">
         <f>IF(H57=[1]Sheet1!H57,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T57">
         <f>IF(I57=[1]Sheet1!I57,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.35">
@@ -5120,7 +5089,7 @@
       </c>
       <c r="P58">
         <f>IF(E58=[1]Sheet1!E58,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q58">
         <f>IF(F58=[1]Sheet1!F58,1,0)</f>
@@ -5128,15 +5097,15 @@
       </c>
       <c r="R58">
         <f>IF(G58=[1]Sheet1!G58,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S58">
         <f>IF(H58=[1]Sheet1!H58,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T58">
         <f>IF(I58=[1]Sheet1!I58,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.35">
@@ -5173,7 +5142,7 @@
       </c>
       <c r="P59">
         <f>IF(E59=[1]Sheet1!E59,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q59">
         <f>IF(F59=[1]Sheet1!F59,1,0)</f>
@@ -5181,15 +5150,15 @@
       </c>
       <c r="R59">
         <f>IF(G59=[1]Sheet1!G59,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S59">
         <f>IF(H59=[1]Sheet1!H59,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T59">
         <f>IF(I59=[1]Sheet1!I59,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.35">
@@ -5226,7 +5195,7 @@
       </c>
       <c r="P60">
         <f>IF(E60=[1]Sheet1!E60,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q60">
         <f>IF(F60=[1]Sheet1!F60,1,0)</f>
@@ -5234,15 +5203,15 @@
       </c>
       <c r="R60">
         <f>IF(G60=[1]Sheet1!G60,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S60">
         <f>IF(H60=[1]Sheet1!H60,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T60">
         <f>IF(I60=[1]Sheet1!I60,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.35">
@@ -5279,7 +5248,7 @@
       </c>
       <c r="P61">
         <f>IF(E61=[1]Sheet1!E61,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q61">
         <f>IF(F61=[1]Sheet1!F61,1,0)</f>
@@ -5287,15 +5256,15 @@
       </c>
       <c r="R61">
         <f>IF(G61=[1]Sheet1!G61,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S61">
         <f>IF(H61=[1]Sheet1!H61,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T61">
         <f>IF(I61=[1]Sheet1!I61,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.35">
@@ -5332,7 +5301,7 @@
       </c>
       <c r="P62">
         <f>IF(E62=[1]Sheet1!E62,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q62">
         <f>IF(F62=[1]Sheet1!F62,1,0)</f>
@@ -5340,15 +5309,15 @@
       </c>
       <c r="R62">
         <f>IF(G62=[1]Sheet1!G62,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S62">
         <f>IF(H62=[1]Sheet1!H62,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T62">
         <f>IF(I62=[1]Sheet1!I62,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.35">
@@ -5385,7 +5354,7 @@
       </c>
       <c r="P63">
         <f>IF(E63=[1]Sheet1!E63,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q63">
         <f>IF(F63=[1]Sheet1!F63,1,0)</f>
@@ -5393,15 +5362,15 @@
       </c>
       <c r="R63">
         <f>IF(G63=[1]Sheet1!G63,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S63">
         <f>IF(H63=[1]Sheet1!H63,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T63">
         <f>IF(I63=[1]Sheet1!I63,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.35">
@@ -5438,23 +5407,23 @@
       </c>
       <c r="P64">
         <f>IF(E64=[1]Sheet1!E64,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q64">
         <f>IF(F64=[1]Sheet1!F64,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R64">
         <f>IF(G64=[1]Sheet1!G64,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S64">
         <f>IF(H64=[1]Sheet1!H64,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T64">
         <f>IF(I64=[1]Sheet1!I64,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.35">
@@ -5491,23 +5460,23 @@
       </c>
       <c r="P65">
         <f>IF(E65=[1]Sheet1!E65,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q65">
         <f>IF(F65=[1]Sheet1!F65,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R65">
         <f>IF(G65=[1]Sheet1!G65,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S65">
         <f>IF(H65=[1]Sheet1!H65,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T65">
         <f>IF(I65=[1]Sheet1!I65,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.35">

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saran\Documents\Academia\repository_clones\Bioindustrial-Park\biorefineries\isobutanol\analyses\full\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F40ED91F-AD3F-46A8-AE1A-1EA828B2D5D8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CF6066-72BA-4EA6-BCB0-6AAFC0083865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -2623,16 +2623,14 @@
         <v>27</v>
       </c>
       <c r="G12" s="4">
-        <f t="shared" si="0"/>
-        <v>1.1919999999999999</v>
+        <v>0.95</v>
       </c>
       <c r="H12" s="4">
         <f>E12</f>
         <v>1.49</v>
       </c>
       <c r="I12" s="4">
-        <f>1.2*E12</f>
-        <v>1.788</v>
+        <v>1.7250000000000001</v>
       </c>
       <c r="J12" s="4"/>
       <c r="K12" s="4" t="s">

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saran\Documents\Academia\repository_clones\Bioindustrial-Park\biorefineries\isobutanol\analyses\full\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D3CF6066-72BA-4EA6-BCB0-6AAFC0083865}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0857B1B-D11D-4F66-B900-42A32C376EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -905,13 +905,13 @@
             <v>Triangular</v>
           </cell>
           <cell r="G13">
-            <v>9.3195E-2</v>
+            <v>8.2840000000000011E-2</v>
           </cell>
           <cell r="H13">
             <v>0.10355</v>
           </cell>
           <cell r="I13">
-            <v>0.11390500000000001</v>
+            <v>0.12426</v>
           </cell>
         </row>
         <row r="14">
@@ -2780,19 +2780,19 @@
         <v>0.10355</v>
       </c>
       <c r="F15" s="6" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G15" s="6">
-        <f>E15*0.9</f>
-        <v>9.3195E-2</v>
+        <f>E15*0.8</f>
+        <v>8.2840000000000011E-2</v>
       </c>
       <c r="H15" s="6">
         <f>E15</f>
         <v>0.10355</v>
       </c>
       <c r="I15" s="6">
-        <f>E15*1.1</f>
-        <v>0.11390500000000001</v>
+        <f>E15*1.2</f>
+        <v>0.12426</v>
       </c>
       <c r="J15" s="6"/>
       <c r="K15" s="6" t="s">
@@ -2804,7 +2804,7 @@
       </c>
       <c r="Q15">
         <f>IF(F15=[1]Sheet1!F15,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R15">
         <f>IF(G15=[1]Sheet1!G15,1,0)</f>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saran\Documents\Academia\repository_clones\Bioindustrial-Park\biorefineries\isobutanol\analyses\full\parameter_distributions\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{E0857B1B-D11D-4F66-B900-42A32C376EFB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F5BD481-464D-4160-B6D3-98D4223FAAFD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="25820" windowHeight="15500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -902,13 +902,10 @@
             <v>0.10355</v>
           </cell>
           <cell r="F13" t="str">
-            <v>Triangular</v>
+            <v>Uniform</v>
           </cell>
           <cell r="G13">
             <v>8.2840000000000011E-2</v>
-          </cell>
-          <cell r="H13">
-            <v>0.10355</v>
           </cell>
           <cell r="I13">
             <v>0.12426</v>
@@ -2695,7 +2692,7 @@
       </c>
       <c r="Q13">
         <f>IF(F13=[1]Sheet1!F13,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R13">
         <f>IF(G13=[1]Sheet1!G13,1,0)</f>
@@ -2703,7 +2700,7 @@
       </c>
       <c r="S13">
         <f>IF(H13=[1]Sheet1!H13,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T13">
         <f>IF(I13=[1]Sheet1!I13,1,0)</f>
@@ -2786,10 +2783,7 @@
         <f>E15*0.8</f>
         <v>8.2840000000000011E-2</v>
       </c>
-      <c r="H15" s="6">
-        <f>E15</f>
-        <v>0.10355</v>
-      </c>
+      <c r="H15" s="6"/>
       <c r="I15" s="6">
         <f>E15*1.2</f>
         <v>0.12426</v>
@@ -2812,7 +2806,7 @@
       </c>
       <c r="S15">
         <f>IF(H15=[1]Sheet1!H15,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T15">
         <f>IF(I15=[1]Sheet1!I15,1,0)</f>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -209,31 +209,31 @@
     <t>V514.tau = x</t>
   </si>
   <si>
-    <t>V406.kinetic_reaction_system._te.k_2 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_1e = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_1h = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_1ie = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_1ia = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_1ii = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_1l = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_3 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_4 = x</t>
+    <t>V406.nsk_kinetic_model._te.k_2 = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_1e = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_1h = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_1ie = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_1ia = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_1ii = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_1l = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_3 = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_4 = x</t>
   </si>
   <si>
     <t>g_per_l_per_h</t>
@@ -245,55 +245,55 @@
     <t>g_per_l</t>
   </si>
   <si>
-    <t>V406.kinetic_reaction_system._te.k_4ie = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_4ia = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_4ii = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_5 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_5e = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_6 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_6r = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_7 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_7ie = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_7ia = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_7ii = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_8 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_9 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_9e = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_9c = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_10 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.k_11 = x</t>
+    <t>V406.nsk_kinetic_model._te.k_4ie = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_4ia = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_4ii = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_5 = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_5e = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_6 = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_6r = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_7 = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_7ie = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_7ia = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_7ii = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_8 = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_9 = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_9e = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_9c = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_10 = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.k_11 = x</t>
   </si>
   <si>
     <t>lime.price = x</t>
@@ -302,55 +302,55 @@
     <t>sulfuric_acid.price = x</t>
   </si>
   <si>
-    <t>V406.kinetic_reaction_system._te.K_1l = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_1h = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_1i = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_1e = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_2 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_2i = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_3 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_4 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_5 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_5e = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_5i = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_6 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_6e = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_7 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_9 = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_9e = x</t>
-  </si>
-  <si>
-    <t>V406.kinetic_reaction_system._te.K_9i = x</t>
+    <t>V406.nsk_kinetic_model._te.K_1l = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_1h = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_1i = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_1e = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_2 = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_2i = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_3 = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_4 = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_5 = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_5e = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_5i = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_6 = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_6e = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_7 = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_9 = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_9e = x</t>
+  </si>
+  <si>
+    <t>V406.nsk_kinetic_model._te.K_9i = x</t>
   </si>
   <si>
     <t>K_1l</t>
@@ -518,61 +518,61 @@
     <t>._k_13</t>
   </si>
   <si>
-    <t>V406.kinetic_reaction_system._te.k_13 = x</t>
+    <t>V406.nsk_kinetic_model._te.k_13 = x</t>
   </si>
   <si>
     <t>K_13</t>
   </si>
   <si>
-    <t>V406.kinetic_reaction_system._te.K_13 = x</t>
+    <t>V406.nsk_kinetic_model._te.K_13 = x</t>
   </si>
   <si>
     <t>._k_14</t>
   </si>
   <si>
-    <t>V406.kinetic_reaction_system._te.k_14 = x</t>
+    <t>V406.nsk_kinetic_model._te.k_14 = x</t>
   </si>
   <si>
     <t>K_14</t>
   </si>
   <si>
-    <t>V406.kinetic_reaction_system._te.K_14 = x</t>
+    <t>V406.nsk_kinetic_model._te.K_14 = x</t>
   </si>
   <si>
     <t>._k_15</t>
   </si>
   <si>
-    <t>V406.kinetic_reaction_system._te.k_15 = x</t>
+    <t>V406.nsk_kinetic_model._te.k_15 = x</t>
   </si>
   <si>
     <t>K_15</t>
   </si>
   <si>
-    <t>V406.kinetic_reaction_system._te.K_15 = x</t>
+    <t>V406.nsk_kinetic_model._te.K_15 = x</t>
   </si>
   <si>
     <t>._k_16</t>
   </si>
   <si>
-    <t>V406.kinetic_reaction_system._te.k_16 = x</t>
+    <t>V406.nsk_kinetic_model._te.k_16 = x</t>
   </si>
   <si>
     <t>._k_16r</t>
   </si>
   <si>
-    <t>V406.kinetic_reaction_system._te.k_16r = x</t>
+    <t>V406.nsk_kinetic_model._te.k_16r = x</t>
   </si>
   <si>
     <t>K_16</t>
   </si>
   <si>
-    <t>V406.kinetic_reaction_system._te.K_16 = x</t>
+    <t>V406.nsk_kinetic_model._te.K_16 = x</t>
   </si>
   <si>
     <t>K_16i</t>
   </si>
   <si>
-    <t>V406.kinetic_reaction_system._te.K_16i = x</t>
+    <t>V406.nsk_kinetic_model._te.K_16i = x</t>
   </si>
   <si>
     <t>Kinetics: Pyruvate-to-Acetolactate</t>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -2021,7 +2021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T75"/>
+  <dimension ref="A1:T74"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40.81640625" customWidth="1"/>
@@ -2655,36 +2655,36 @@
       </c>
     </row>
     <row r="13" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A13" s="4" t="s">
-        <v>186</v>
-      </c>
-      <c r="B13" s="4" t="s">
+      <c r="A13" s="6" t="s">
+        <v>35</v>
+      </c>
+      <c r="B13" s="6" t="s">
         <v>7</v>
       </c>
-      <c r="C13" s="4" t="s">
+      <c r="C13" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D13" s="4" t="s">
+      <c r="D13" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="E13" s="4">
-        <v>3.2</v>
-      </c>
-      <c r="F13" s="4" t="s">
-        <v>18</v>
-      </c>
-      <c r="G13" s="4">
-        <f t="shared" si="0"/>
-        <v>2.5600000000000005</v>
-      </c>
-      <c r="H13" s="4"/>
-      <c r="I13" s="4">
-        <f t="shared" si="1"/>
-        <v>3.84</v>
-      </c>
-      <c r="J13" s="4"/>
-      <c r="K13" s="4" t="s">
-        <v>184</v>
+      <c r="E13" s="6">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="F13" s="6" t="s">
+        <v>27</v>
+      </c>
+      <c r="G13" s="6">
+        <v>0.17499999999999999</v>
+      </c>
+      <c r="H13" s="6">
+        <v>0.28599999999999998</v>
+      </c>
+      <c r="I13" s="6">
+        <v>0.315</v>
+      </c>
+      <c r="J13" s="6"/>
+      <c r="K13" s="6" t="s">
+        <v>85</v>
       </c>
       <c r="P13">
         <f>IF(E13=[1]Sheet1!E13,1,0)</f>
@@ -2692,7 +2692,7 @@
       </c>
       <c r="Q13">
         <f>IF(F13=[1]Sheet1!F13,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R13">
         <f>IF(G13=[1]Sheet1!G13,1,0)</f>
@@ -2700,7 +2700,7 @@
       </c>
       <c r="S13">
         <f>IF(H13=[1]Sheet1!H13,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T13">
         <f>IF(I13=[1]Sheet1!I13,1,0)</f>
@@ -2709,7 +2709,7 @@
     </row>
     <row r="14" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A14" s="6" t="s">
-        <v>35</v>
+        <v>36</v>
       </c>
       <c r="B14" s="6" t="s">
         <v>7</v>
@@ -2721,23 +2721,23 @@
         <v>10</v>
       </c>
       <c r="E14" s="6">
-        <v>0.28599999999999998</v>
+        <v>0.10355</v>
       </c>
       <c r="F14" s="6" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G14" s="6">
-        <v>0.17499999999999999</v>
-      </c>
-      <c r="H14" s="6">
-        <v>0.28599999999999998</v>
-      </c>
+        <f>E14*0.8</f>
+        <v>8.2840000000000011E-2</v>
+      </c>
+      <c r="H14" s="6"/>
       <c r="I14" s="6">
-        <v>0.315</v>
+        <f>E14*1.2</f>
+        <v>0.12426</v>
       </c>
       <c r="J14" s="6"/>
       <c r="K14" s="6" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="P14">
         <f>IF(E14=[1]Sheet1!E14,1,0)</f>
@@ -2745,7 +2745,7 @@
       </c>
       <c r="Q14">
         <f>IF(F14=[1]Sheet1!F14,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R14">
         <f>IF(G14=[1]Sheet1!G14,1,0)</f>
@@ -2753,7 +2753,7 @@
       </c>
       <c r="S14">
         <f>IF(H14=[1]Sheet1!H14,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T14">
         <f>IF(I14=[1]Sheet1!I14,1,0)</f>
@@ -2761,36 +2761,34 @@
       </c>
     </row>
     <row r="15" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A15" s="6" t="s">
-        <v>36</v>
-      </c>
-      <c r="B15" s="6" t="s">
+      <c r="A15" s="3" t="s">
+        <v>31</v>
+      </c>
+      <c r="B15" s="3" t="s">
         <v>7</v>
       </c>
-      <c r="C15" s="6" t="s">
+      <c r="C15" s="3" t="s">
         <v>20</v>
       </c>
-      <c r="D15" s="6" t="s">
-        <v>10</v>
-      </c>
-      <c r="E15" s="6">
-        <v>0.10355</v>
-      </c>
-      <c r="F15" s="6" t="s">
+      <c r="D15" s="3" t="s">
+        <v>8</v>
+      </c>
+      <c r="E15" s="3">
+        <v>0.21</v>
+      </c>
+      <c r="F15" s="3" t="s">
         <v>18</v>
       </c>
-      <c r="G15" s="6">
-        <f>E15*0.8</f>
-        <v>8.2840000000000011E-2</v>
-      </c>
-      <c r="H15" s="6"/>
-      <c r="I15" s="6">
-        <f>E15*1.2</f>
-        <v>0.12426</v>
-      </c>
-      <c r="J15" s="6"/>
-      <c r="K15" s="6" t="s">
-        <v>86</v>
+      <c r="G15" s="3">
+        <v>0.15</v>
+      </c>
+      <c r="H15" s="3"/>
+      <c r="I15" s="3">
+        <v>0.28000000000000003</v>
+      </c>
+      <c r="J15" s="3"/>
+      <c r="K15" s="3" t="s">
+        <v>34</v>
       </c>
       <c r="P15">
         <f>IF(E15=[1]Sheet1!E15,1,0)</f>
@@ -2798,7 +2796,7 @@
       </c>
       <c r="Q15">
         <f>IF(F15=[1]Sheet1!F15,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R15">
         <f>IF(G15=[1]Sheet1!G15,1,0)</f>
@@ -2806,7 +2804,7 @@
       </c>
       <c r="S15">
         <f>IF(H15=[1]Sheet1!H15,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T15">
         <f>IF(I15=[1]Sheet1!I15,1,0)</f>
@@ -2815,7 +2813,7 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>31</v>
+        <v>32</v>
       </c>
       <c r="B16" s="3" t="s">
         <v>7</v>
@@ -2827,21 +2825,23 @@
         <v>8</v>
       </c>
       <c r="E16" s="3">
-        <v>0.21</v>
+        <v>0.15</v>
       </c>
       <c r="F16" s="3" t="s">
         <v>18</v>
       </c>
       <c r="G16" s="3">
-        <v>0.15</v>
+        <f>0.8*E16</f>
+        <v>0.12</v>
       </c>
       <c r="H16" s="3"/>
       <c r="I16" s="3">
-        <v>0.28000000000000003</v>
+        <f>1.2*E16</f>
+        <v>0.18</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="P16">
         <f>IF(E16=[1]Sheet1!E16,1,0)</f>
@@ -2866,35 +2866,38 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>32</v>
+        <v>185</v>
       </c>
       <c r="B17" s="3" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C17" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="E17" s="3">
-        <v>0.15</v>
+        <v>0.72</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G17" s="3">
-        <f>0.8*E17</f>
-        <v>0.12</v>
-      </c>
-      <c r="H17" s="3"/>
+        <f>0.8*H17</f>
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="H17" s="3">
+        <f>E17</f>
+        <v>0.72</v>
+      </c>
       <c r="I17" s="3">
-        <f>1.2*E17</f>
-        <v>0.18</v>
+        <f>1.2*H17</f>
+        <v>0.86399999999999999</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
-        <v>33</v>
+        <v>193</v>
       </c>
       <c r="P17">
         <f>IF(E17=[1]Sheet1!E17,1,0)</f>
@@ -2919,7 +2922,7 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>185</v>
+        <v>38</v>
       </c>
       <c r="B18" s="3" t="s">
         <v>39</v>
@@ -2928,29 +2931,29 @@
         <v>21</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>192</v>
+        <v>40</v>
       </c>
       <c r="E18" s="3">
-        <v>0.72</v>
+        <v>56972</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G18" s="3">
         <f>0.8*H18</f>
-        <v>0.57599999999999996</v>
+        <v>45577.600000000006</v>
       </c>
       <c r="H18" s="3">
         <f>E18</f>
-        <v>0.72</v>
+        <v>56972</v>
       </c>
       <c r="I18" s="3">
         <f>1.2*H18</f>
-        <v>0.86399999999999999</v>
+        <v>68366.399999999994</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>193</v>
+        <v>41</v>
       </c>
       <c r="P18">
         <f>IF(E18=[1]Sheet1!E18,1,0)</f>
@@ -2958,7 +2961,7 @@
       </c>
       <c r="Q18">
         <f>IF(F18=[1]Sheet1!F18,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R18">
         <f>IF(G18=[1]Sheet1!G18,1,0)</f>
@@ -2975,38 +2978,33 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>38</v>
+        <v>187</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>39</v>
+        <v>188</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E19" s="3">
-        <v>56972</v>
+        <v>2</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G19" s="3">
-        <f>0.8*H19</f>
-        <v>45577.600000000006</v>
-      </c>
-      <c r="H19" s="3">
-        <f>E19</f>
-        <v>56972</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H19" s="3"/>
       <c r="I19" s="3">
-        <f>1.2*H19</f>
-        <v>68366.399999999994</v>
+        <v>3</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="P19">
         <f>IF(E19=[1]Sheet1!E19,1,0)</f>
@@ -3014,7 +3012,7 @@
       </c>
       <c r="Q19">
         <f>IF(F19=[1]Sheet1!F19,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R19">
         <f>IF(G19=[1]Sheet1!G19,1,0)</f>
@@ -3031,33 +3029,38 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>187</v>
+        <v>52</v>
       </c>
       <c r="B20" s="3" t="s">
-        <v>188</v>
+        <v>13</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D20" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E20" s="3">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G20" s="3">
-        <v>1</v>
-      </c>
-      <c r="H20" s="3"/>
+        <f>E20*0.8</f>
+        <v>124.80000000000001</v>
+      </c>
+      <c r="H20" s="3">
+        <f>E20</f>
+        <v>156</v>
+      </c>
       <c r="I20" s="3">
-        <v>3</v>
+        <f>E20*1.2</f>
+        <v>187.2</v>
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3" t="s">
-        <v>189</v>
+        <v>54</v>
       </c>
       <c r="P20">
         <f>IF(E20=[1]Sheet1!E20,1,0)</f>
@@ -3065,7 +3068,7 @@
       </c>
       <c r="Q20">
         <f>IF(F20=[1]Sheet1!F20,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R20">
         <f>IF(G20=[1]Sheet1!G20,1,0)</f>
@@ -3082,7 +3085,7 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B21" s="3" t="s">
         <v>13</v>
@@ -3113,7 +3116,7 @@
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P21">
         <f>IF(E21=[1]Sheet1!E21,1,0)</f>
@@ -3138,38 +3141,35 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="B22" s="3" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="E22" s="3">
-        <v>156</v>
+        <v>1.43</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="G22" s="3">
-        <f>E22*0.8</f>
-        <v>124.80000000000001</v>
+        <v>1.1439999999999999</v>
       </c>
       <c r="H22" s="3">
-        <f>E22</f>
-        <v>156</v>
+        <v>1.43</v>
       </c>
       <c r="I22" s="3">
-        <f>E22*1.2</f>
-        <v>187.2</v>
+        <v>1.716</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="P22">
         <f>IF(E22=[1]Sheet1!E22,1,0)</f>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>147</v>
@@ -3203,26 +3203,26 @@
         <v>21</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E23" s="3">
-        <v>1.43</v>
+        <v>0.94</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G23" s="3">
-        <v>1.1439999999999999</v>
+        <v>0.752</v>
       </c>
       <c r="H23" s="3">
-        <v>1.43</v>
+        <v>0.94</v>
       </c>
       <c r="I23" s="3">
-        <v>1.716</v>
+        <v>1.1279999999999999</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="P23">
         <f>IF(E23=[1]Sheet1!E23,1,0)</f>
@@ -3247,7 +3247,7 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>147</v>
@@ -3256,26 +3256,26 @@
         <v>21</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E24" s="3">
-        <v>0.94</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G24" s="3">
-        <v>0.752</v>
+        <v>0.4672</v>
       </c>
       <c r="H24" s="3">
-        <v>0.94</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="I24" s="3">
-        <v>1.1279999999999999</v>
+        <v>0.70079999999999998</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="P24">
         <f>IF(E24=[1]Sheet1!E24,1,0)</f>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>147</v>
@@ -3309,26 +3309,26 @@
         <v>21</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E25" s="3">
-        <v>0.58399999999999996</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G25" s="3">
-        <v>0.4672</v>
+        <v>9.2800000000000001E-3</v>
       </c>
       <c r="H25" s="3">
-        <v>0.58399999999999996</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="I25" s="3">
-        <v>0.70079999999999998</v>
+        <v>1.3919999999999899E-2</v>
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="P25">
         <f>IF(E25=[1]Sheet1!E25,1,0)</f>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>147</v>
@@ -3362,26 +3362,26 @@
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E26" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>47.1</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G26" s="3">
-        <v>9.2800000000000001E-3</v>
+        <v>37.68</v>
       </c>
       <c r="H26" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>47.1</v>
       </c>
       <c r="I26" s="3">
-        <v>1.3919999999999899E-2</v>
+        <v>56.52</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="P26">
         <f>IF(E26=[1]Sheet1!E26,1,0)</f>
@@ -3406,7 +3406,7 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>147</v>
@@ -3415,26 +3415,26 @@
         <v>21</v>
       </c>
       <c r="D27" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E27" s="3">
-        <v>47.1</v>
+        <v>14.2</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G27" s="3">
-        <v>37.68</v>
+        <v>11.36</v>
       </c>
       <c r="H27" s="3">
-        <v>47.1</v>
+        <v>14.2</v>
       </c>
       <c r="I27" s="3">
-        <v>56.52</v>
+        <v>17.04</v>
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="P27">
         <f>IF(E27=[1]Sheet1!E27,1,0)</f>
@@ -3459,7 +3459,7 @@
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>147</v>
@@ -3471,27 +3471,27 @@
         <v>67</v>
       </c>
       <c r="E28" s="3">
-        <v>14.2</v>
+        <v>0.12</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G28" s="3">
-        <v>11.36</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H28" s="3">
-        <v>14.2</v>
+        <v>0.12</v>
       </c>
       <c r="I28" s="3">
-        <v>17.04</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P28">
         <f>IF(E28=[1]Sheet1!E28,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q28">
         <f>IF(F28=[1]Sheet1!F28,1,0)</f>
@@ -3499,20 +3499,20 @@
       </c>
       <c r="R28">
         <f>IF(G28=[1]Sheet1!G28,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S28">
         <f>IF(H28=[1]Sheet1!H28,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T28">
         <f>IF(I28=[1]Sheet1!I28,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>147</v>
@@ -3521,26 +3521,26 @@
         <v>21</v>
       </c>
       <c r="D29" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E29" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G29" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H29" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I29" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="P29">
         <f>IF(E29=[1]Sheet1!E29,1,0)</f>
@@ -3565,7 +3565,7 @@
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>147</v>
@@ -3577,27 +3577,27 @@
         <v>65</v>
       </c>
       <c r="E30" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G30" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H30" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I30" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P30">
         <f>IF(E30=[1]Sheet1!E30,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q30">
         <f>IF(F30=[1]Sheet1!F30,1,0)</f>
@@ -3605,20 +3605,20 @@
       </c>
       <c r="R30">
         <f>IF(G30=[1]Sheet1!G30,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S30">
         <f>IF(H30=[1]Sheet1!H30,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T30">
         <f>IF(I30=[1]Sheet1!I30,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B31" s="3" t="s">
         <v>147</v>
@@ -3630,23 +3630,23 @@
         <v>65</v>
       </c>
       <c r="E31" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H31" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I31" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P31">
         <f>IF(E31=[1]Sheet1!E31,1,0)</f>
@@ -3671,10 +3671,10 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B32" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C32" s="3" t="s">
         <v>21</v>
@@ -3683,23 +3683,23 @@
         <v>65</v>
       </c>
       <c r="E32" s="3">
-        <v>0.04</v>
+        <v>0.501</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G32" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>0.40079999999999999</v>
       </c>
       <c r="H32" s="3">
-        <v>0.04</v>
+        <v>0.501</v>
       </c>
       <c r="I32" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.60119999999999996</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="P32">
         <f>IF(E32=[1]Sheet1!E32,1,0)</f>
@@ -3724,7 +3724,7 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>148</v>
@@ -3733,26 +3733,26 @@
         <v>21</v>
       </c>
       <c r="D33" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E33" s="3">
-        <v>0.501</v>
+        <v>67</v>
+      </c>
+      <c r="E33" s="5">
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G33" s="3">
-        <v>0.40079999999999999</v>
-      </c>
-      <c r="H33" s="3">
-        <v>0.501</v>
-      </c>
-      <c r="I33" s="3">
-        <v>0.60119999999999996</v>
+      <c r="G33" s="5">
+        <v>1.5999999999999999E-5</v>
+      </c>
+      <c r="H33" s="5">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="I33" s="5">
+        <v>2.4000000000000001E-5</v>
       </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="P33">
         <f>IF(E33=[1]Sheet1!E33,1,0)</f>
@@ -3777,7 +3777,7 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B34" s="3" t="s">
         <v>148</v>
@@ -3788,24 +3788,24 @@
       <c r="D34" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E34" s="5">
-        <v>2.0000000000000002E-5</v>
+      <c r="E34" s="3">
+        <v>0.10100000000000001</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G34" s="5">
-        <v>1.5999999999999999E-5</v>
-      </c>
-      <c r="H34" s="5">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="I34" s="5">
-        <v>2.4000000000000001E-5</v>
+      <c r="G34" s="3">
+        <v>8.0799999999999997E-2</v>
+      </c>
+      <c r="H34" s="3">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="I34" s="3">
+        <v>0.1212</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P34">
         <f>IF(E34=[1]Sheet1!E34,1,0)</f>
@@ -3830,35 +3830,35 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="B35" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E35" s="3">
-        <v>0.10100000000000001</v>
+        <v>5.81</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G35" s="3">
-        <v>8.0799999999999997E-2</v>
+        <v>4.6479999999999997</v>
       </c>
       <c r="H35" s="3">
-        <v>0.10100000000000001</v>
+        <v>5.81</v>
       </c>
       <c r="I35" s="3">
-        <v>0.1212</v>
+        <v>6.9719999999999898</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="P35">
         <f>IF(E35=[1]Sheet1!E35,1,0)</f>
@@ -3883,7 +3883,7 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B36" s="3" t="s">
         <v>149</v>
@@ -3892,26 +3892,26 @@
         <v>21</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E36" s="3">
-        <v>5.81</v>
+        <v>67</v>
+      </c>
+      <c r="E36" s="5">
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G36" s="3">
-        <v>4.6479999999999997</v>
-      </c>
-      <c r="H36" s="3">
-        <v>5.81</v>
-      </c>
-      <c r="I36" s="3">
-        <v>6.9719999999999898</v>
+      <c r="G36" s="5">
+        <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="H36" s="5">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="I36" s="5">
+        <v>5.9999999999999997E-7</v>
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="3" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="P36">
         <f>IF(E36=[1]Sheet1!E36,1,0)</f>
@@ -3936,35 +3936,35 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="B37" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D37" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E37" s="5">
-        <v>4.9999999999999998E-7</v>
+        <v>65</v>
+      </c>
+      <c r="E37" s="3">
+        <v>4.8</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G37" s="5">
-        <v>3.9999999999999998E-7</v>
-      </c>
-      <c r="H37" s="5">
-        <v>4.9999999999999998E-7</v>
-      </c>
-      <c r="I37" s="5">
-        <v>5.9999999999999997E-7</v>
+      <c r="G37" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="H37" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="I37" s="3">
+        <v>5.76</v>
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="P37">
         <f>IF(E37=[1]Sheet1!E37,1,0)</f>
@@ -3989,7 +3989,7 @@
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>150</v>
@@ -4001,27 +4001,27 @@
         <v>65</v>
       </c>
       <c r="E38" s="3">
-        <v>4.8</v>
+        <v>0.04</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G38" s="3">
-        <v>3.84</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H38" s="3">
-        <v>4.8</v>
+        <v>0.04</v>
       </c>
       <c r="I38" s="3">
-        <v>5.76</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P38">
         <f>IF(E38=[1]Sheet1!E38,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q38">
         <f>IF(F38=[1]Sheet1!F38,1,0)</f>
@@ -4029,20 +4029,20 @@
       </c>
       <c r="R38">
         <f>IF(G38=[1]Sheet1!G38,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S38">
         <f>IF(H38=[1]Sheet1!H38,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T38">
         <f>IF(I38=[1]Sheet1!I38,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>150</v>
@@ -4054,27 +4054,27 @@
         <v>65</v>
       </c>
       <c r="E39" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G39" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H39" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I39" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P39">
         <f>IF(E39=[1]Sheet1!E39,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q39">
         <f>IF(F39=[1]Sheet1!F39,1,0)</f>
@@ -4082,20 +4082,20 @@
       </c>
       <c r="R39">
         <f>IF(G39=[1]Sheet1!G39,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S39">
         <f>IF(H39=[1]Sheet1!H39,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T39">
         <f>IF(I39=[1]Sheet1!I39,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>150</v>
@@ -4107,23 +4107,23 @@
         <v>65</v>
       </c>
       <c r="E40" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G40" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H40" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I40" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P40">
         <f>IF(E40=[1]Sheet1!E40,1,0)</f>
@@ -4148,7 +4148,7 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="B41" s="3" t="s">
         <v>150</v>
@@ -4157,26 +4157,26 @@
         <v>21</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E41" s="3">
-        <v>0.04</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G41" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>2.1120000000000001E-4</v>
       </c>
       <c r="H41" s="3">
-        <v>0.04</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="I41" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>3.168E-4</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="P41">
         <f>IF(E41=[1]Sheet1!E41,1,0)</f>
@@ -4201,35 +4201,35 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="B42" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E42" s="3">
-        <v>2.6400000000000002E-4</v>
+        <v>1.04E-2</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G42" s="3">
-        <v>2.1120000000000001E-4</v>
+        <v>8.3199999999999993E-3</v>
       </c>
       <c r="H42" s="3">
-        <v>2.6400000000000002E-4</v>
+        <v>1.04E-2</v>
       </c>
       <c r="I42" s="3">
-        <v>3.168E-4</v>
+        <v>1.248E-2</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P42">
         <f>IF(E42=[1]Sheet1!E42,1,0)</f>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>155</v>
@@ -4263,26 +4263,26 @@
         <v>21</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E43" s="3">
-        <v>1.04E-2</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="3">
-        <v>8.3199999999999993E-3</v>
+        <v>8.1600000000000006E-3</v>
       </c>
       <c r="H43" s="3">
-        <v>1.04E-2</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="I43" s="3">
-        <v>1.248E-2</v>
+        <v>1.2239999999999999E-2</v>
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="3" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="P43">
         <f>IF(E43=[1]Sheet1!E43,1,0)</f>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>155</v>
@@ -4316,26 +4316,26 @@
         <v>21</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E44" s="3">
-        <v>1.0200000000000001E-2</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G44" s="3">
-        <v>8.1600000000000006E-3</v>
+        <v>0.62</v>
       </c>
       <c r="H44" s="3">
-        <v>1.0200000000000001E-2</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="I44" s="3">
-        <v>1.2239999999999999E-2</v>
+        <v>0.92999999999999905</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="P44">
         <f>IF(E44=[1]Sheet1!E44,1,0)</f>
@@ -4360,7 +4360,7 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>155</v>
@@ -4369,26 +4369,26 @@
         <v>21</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E45" s="3">
-        <v>0.77500000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G45" s="3">
-        <v>0.62</v>
+        <v>0.08</v>
       </c>
       <c r="H45" s="3">
-        <v>0.77500000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="I45" s="3">
-        <v>0.92999999999999905</v>
+        <v>0.12</v>
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="P45">
         <f>IF(E45=[1]Sheet1!E45,1,0)</f>
@@ -4413,7 +4413,7 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B46" s="3" t="s">
         <v>155</v>
@@ -4425,23 +4425,23 @@
         <v>67</v>
       </c>
       <c r="E46" s="3">
-        <v>0.1</v>
+        <v>440</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G46" s="3">
-        <v>0.08</v>
+        <v>352</v>
       </c>
       <c r="H46" s="3">
-        <v>0.1</v>
+        <v>440</v>
       </c>
       <c r="I46" s="3">
-        <v>0.12</v>
+        <v>528</v>
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P46">
         <f>IF(E46=[1]Sheet1!E46,1,0)</f>
@@ -4466,35 +4466,35 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="B47" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C47" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D47" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E47" s="3">
-        <v>440</v>
+        <v>2.82</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G47" s="3">
-        <v>352</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="H47" s="3">
-        <v>440</v>
+        <v>2.82</v>
       </c>
       <c r="I47" s="3">
-        <v>528</v>
+        <v>3.3839999999999999</v>
       </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="P47">
         <f>IF(E47=[1]Sheet1!E47,1,0)</f>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>151</v>
@@ -4531,23 +4531,23 @@
         <v>65</v>
       </c>
       <c r="E48" s="3">
-        <v>2.82</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G48" s="3">
-        <v>2.2559999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="H48" s="3">
-        <v>2.82</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="I48" s="3">
-        <v>3.3839999999999999</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P48">
         <f>IF(E48=[1]Sheet1!E48,1,0)</f>
@@ -4572,7 +4572,7 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>151</v>
@@ -4581,26 +4581,26 @@
         <v>21</v>
       </c>
       <c r="D49" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E49" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G49" s="3">
-        <v>0.01</v>
+        <v>2.7199999999999998E-2</v>
       </c>
       <c r="H49" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="I49" s="3">
-        <v>1.4999999999999999E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="3" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="P49">
         <f>IF(E49=[1]Sheet1!E49,1,0)</f>
@@ -4625,7 +4625,7 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B50" s="3" t="s">
         <v>151</v>
@@ -4637,23 +4637,23 @@
         <v>67</v>
       </c>
       <c r="E50" s="3">
-        <v>3.4000000000000002E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G50" s="3">
-        <v>2.7199999999999998E-2</v>
+        <v>4.5600000000000002E-2</v>
       </c>
       <c r="H50" s="3">
-        <v>3.4000000000000002E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="I50" s="3">
-        <v>4.0800000000000003E-2</v>
+        <v>6.8400000000000002E-2</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P50">
         <f>IF(E50=[1]Sheet1!E50,1,0)</f>
@@ -4678,35 +4678,35 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="B51" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D51" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E51" s="3">
-        <v>5.7000000000000002E-2</v>
+        <v>1.2030000000000001</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G51" s="3">
-        <v>4.5600000000000002E-2</v>
+        <v>0.96240000000000003</v>
       </c>
       <c r="H51" s="3">
-        <v>5.7000000000000002E-2</v>
+        <v>1.2030000000000001</v>
       </c>
       <c r="I51" s="3">
-        <v>6.8400000000000002E-2</v>
+        <v>1.4436</v>
       </c>
       <c r="J51" s="3"/>
       <c r="K51" s="3" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="P51">
         <f>IF(E51=[1]Sheet1!E51,1,0)</f>
@@ -4731,7 +4731,7 @@
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>152</v>
@@ -4743,27 +4743,27 @@
         <v>65</v>
       </c>
       <c r="E52" s="3">
-        <v>1.2030000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G52" s="3">
-        <v>0.96240000000000003</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H52" s="3">
-        <v>1.2030000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="I52" s="3">
-        <v>1.4436</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P52">
         <f>IF(E52=[1]Sheet1!E52,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q52">
         <f>IF(F52=[1]Sheet1!F52,1,0)</f>
@@ -4771,20 +4771,20 @@
       </c>
       <c r="R52">
         <f>IF(G52=[1]Sheet1!G52,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S52">
         <f>IF(H52=[1]Sheet1!H52,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T52">
         <f>IF(I52=[1]Sheet1!I52,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>152</v>
@@ -4796,27 +4796,27 @@
         <v>65</v>
       </c>
       <c r="E53" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G53" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H53" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I53" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P53">
         <f>IF(E53=[1]Sheet1!E53,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q53">
         <f>IF(F53=[1]Sheet1!F53,1,0)</f>
@@ -4824,20 +4824,20 @@
       </c>
       <c r="R53">
         <f>IF(G53=[1]Sheet1!G53,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S53">
         <f>IF(H53=[1]Sheet1!H53,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T53">
         <f>IF(I53=[1]Sheet1!I53,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>152</v>
@@ -4849,23 +4849,23 @@
         <v>65</v>
       </c>
       <c r="E54" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G54" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H54" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I54" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P54">
         <f>IF(E54=[1]Sheet1!E54,1,0)</f>
@@ -4890,7 +4890,7 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="B55" s="3" t="s">
         <v>152</v>
@@ -4899,26 +4899,26 @@
         <v>21</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E55" s="3">
-        <v>0.04</v>
+        <v>1.01E-2</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>8.0800000000000004E-3</v>
       </c>
       <c r="H55" s="3">
-        <v>0.04</v>
+        <v>1.01E-2</v>
       </c>
       <c r="I55" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>1.21199999999999E-2</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="P55">
         <f>IF(E55=[1]Sheet1!E55,1,0)</f>
@@ -4943,35 +4943,35 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D56" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E56" s="3">
-        <v>1.01E-2</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G56" s="3">
-        <v>8.0800000000000004E-3</v>
+        <v>0.47120000000000001</v>
       </c>
       <c r="H56" s="3">
-        <v>1.01E-2</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="I56" s="3">
-        <v>1.21199999999999E-2</v>
+        <v>0.70679999999999998</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="P56">
         <f>IF(E56=[1]Sheet1!E56,1,0)</f>
@@ -4996,10 +4996,10 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B57" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>21</v>
@@ -5008,23 +5008,23 @@
         <v>65</v>
       </c>
       <c r="E57" s="3">
-        <v>0.58899999999999997</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G57" s="3">
-        <v>0.47120000000000001</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="H57" s="3">
-        <v>0.58899999999999997</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="I57" s="3">
-        <v>0.70679999999999998</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="J57" s="3"/>
       <c r="K57" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P57">
         <f>IF(E57=[1]Sheet1!E57,1,0)</f>
@@ -5049,7 +5049,7 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>154</v>
@@ -5058,26 +5058,26 @@
         <v>21</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E58" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>67</v>
+      </c>
+      <c r="E58" s="5">
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G58" s="3">
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="H58" s="3">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="I58" s="3">
-        <v>9.5999999999999992E-3</v>
+      <c r="G58" s="5">
+        <v>7.9999999999999996E-7</v>
+      </c>
+      <c r="H58" s="5">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="I58" s="5">
+        <v>1.1999999999999999E-6</v>
       </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="P58">
         <f>IF(E58=[1]Sheet1!E58,1,0)</f>
@@ -5102,7 +5102,7 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>154</v>
@@ -5111,26 +5111,26 @@
         <v>21</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E59" s="5">
-        <v>9.9999999999999995E-7</v>
+        <v>65</v>
+      </c>
+      <c r="E59" s="3">
+        <v>7.51E-2</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G59" s="5">
-        <v>7.9999999999999996E-7</v>
-      </c>
-      <c r="H59" s="5">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="I59" s="5">
-        <v>1.1999999999999999E-6</v>
+      <c r="G59" s="3">
+        <v>6.0080000000000001E-2</v>
+      </c>
+      <c r="H59" s="3">
+        <v>7.51E-2</v>
+      </c>
+      <c r="I59" s="3">
+        <v>9.0119999999999895E-2</v>
       </c>
       <c r="J59" s="3"/>
       <c r="K59" s="3" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="P59">
         <f>IF(E59=[1]Sheet1!E59,1,0)</f>
@@ -5155,7 +5155,7 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>154</v>
@@ -5164,26 +5164,26 @@
         <v>21</v>
       </c>
       <c r="D60" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E60" s="3">
-        <v>7.51E-2</v>
+        <v>13</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G60" s="3">
-        <v>6.0080000000000001E-2</v>
+        <v>10.4</v>
       </c>
       <c r="H60" s="3">
-        <v>7.51E-2</v>
+        <v>13</v>
       </c>
       <c r="I60" s="3">
-        <v>9.0119999999999895E-2</v>
+        <v>15.6</v>
       </c>
       <c r="J60" s="3"/>
       <c r="K60" s="3" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="P60">
         <f>IF(E60=[1]Sheet1!E60,1,0)</f>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>154</v>
@@ -5220,23 +5220,23 @@
         <v>67</v>
       </c>
       <c r="E61" s="3">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G61" s="3">
-        <v>10.4</v>
+        <v>20</v>
       </c>
       <c r="H61" s="3">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I61" s="3">
-        <v>15.6</v>
+        <v>30</v>
       </c>
       <c r="J61" s="3"/>
       <c r="K61" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P61">
         <f>IF(E61=[1]Sheet1!E61,1,0)</f>
@@ -5261,7 +5261,7 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="B62" s="3" t="s">
         <v>154</v>
@@ -5270,26 +5270,26 @@
         <v>21</v>
       </c>
       <c r="D62" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E62" s="3">
-        <v>25</v>
+        <v>3.9899999999999996E-3</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G62" s="3">
-        <v>20</v>
+        <v>3.192E-3</v>
       </c>
       <c r="H62" s="3">
-        <v>25</v>
+        <v>3.9899999999999996E-3</v>
       </c>
       <c r="I62" s="3">
-        <v>30</v>
+        <v>4.7879999999999997E-3</v>
       </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="P62">
         <f>IF(E62=[1]Sheet1!E62,1,0)</f>
@@ -5314,10 +5314,10 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>21</v>
@@ -5326,23 +5326,23 @@
         <v>65</v>
       </c>
       <c r="E63" s="3">
-        <v>3.9899999999999996E-3</v>
+        <v>0.06</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G63" s="3">
-        <v>3.192E-3</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="H63" s="3">
-        <v>3.9899999999999996E-3</v>
+        <v>0.06</v>
       </c>
       <c r="I63" s="3">
-        <v>4.7879999999999997E-3</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="J63" s="3"/>
       <c r="K63" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P63">
         <f>IF(E63=[1]Sheet1!E63,1,0)</f>
@@ -5350,7 +5350,7 @@
       </c>
       <c r="Q63">
         <f>IF(F63=[1]Sheet1!F63,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R63">
         <f>IF(G63=[1]Sheet1!G63,1,0)</f>
@@ -5367,10 +5367,10 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>21</v>
@@ -5379,23 +5379,23 @@
         <v>65</v>
       </c>
       <c r="E64" s="3">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G64" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="H64" s="3">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I64" s="3">
-        <v>7.1999999999999995E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="J64" s="3"/>
       <c r="K64" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P64">
         <f>IF(E64=[1]Sheet1!E64,1,0)</f>
@@ -5420,10 +5420,10 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="B65" s="3" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>21</v>
@@ -5432,23 +5432,26 @@
         <v>65</v>
       </c>
       <c r="E65" s="3">
-        <v>0.02</v>
+        <v>5.81</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G65" s="3">
-        <v>1.6E-2</v>
-      </c>
-      <c r="H65" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="I65" s="3">
-        <v>2.4E-2</v>
+      <c r="G65" s="5">
+        <f>E65*0.8</f>
+        <v>4.6479999999999997</v>
+      </c>
+      <c r="H65" s="5">
+        <f>E65</f>
+        <v>5.81</v>
+      </c>
+      <c r="I65" s="5">
+        <f>1.2*E65</f>
+        <v>6.9719999999999995</v>
       </c>
       <c r="J65" s="3"/>
       <c r="K65" s="3" t="s">
-        <v>84</v>
+        <v>159</v>
       </c>
       <c r="P65">
         <f>IF(E65=[1]Sheet1!E65,1,0)</f>
@@ -5473,7 +5476,7 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B66" s="3" t="s">
         <v>178</v>
@@ -5482,29 +5485,29 @@
         <v>21</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E66" s="3">
-        <v>5.81</v>
+        <v>67</v>
+      </c>
+      <c r="E66" s="5">
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G66" s="5">
         <f>E66*0.8</f>
-        <v>4.6479999999999997</v>
+        <v>3.9999999999999998E-7</v>
       </c>
       <c r="H66" s="5">
         <f>E66</f>
-        <v>5.81</v>
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="I66" s="5">
         <f>1.2*E66</f>
-        <v>6.9719999999999995</v>
+        <v>5.9999999999999997E-7</v>
       </c>
       <c r="J66" s="3"/>
       <c r="K66" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P66">
         <f>IF(E66=[1]Sheet1!E66,1,0)</f>
@@ -5529,38 +5532,38 @@
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B67" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E67" s="5">
-        <v>4.9999999999999998E-7</v>
+        <v>65</v>
+      </c>
+      <c r="E67" s="3">
+        <v>4.8</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G67" s="5">
-        <f>E67*0.8</f>
-        <v>3.9999999999999998E-7</v>
+        <f t="shared" ref="G68:G75" si="2">E67*0.8</f>
+        <v>3.84</v>
       </c>
       <c r="H67" s="5">
-        <f>E67</f>
-        <v>4.9999999999999998E-7</v>
+        <f t="shared" ref="H68:H75" si="3">E67</f>
+        <v>4.8</v>
       </c>
       <c r="I67" s="5">
-        <f>1.2*E67</f>
-        <v>5.9999999999999997E-7</v>
+        <f t="shared" ref="I68:I75" si="4">1.2*E67</f>
+        <v>5.76</v>
       </c>
       <c r="J67" s="3"/>
       <c r="K67" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="P67">
         <f>IF(E67=[1]Sheet1!E67,1,0)</f>
@@ -5585,7 +5588,7 @@
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B68" s="3" t="s">
         <v>179</v>
@@ -5594,29 +5597,29 @@
         <v>21</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E68" s="3">
-        <v>4.8</v>
+        <v>67</v>
+      </c>
+      <c r="E68" s="5">
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="5">
-        <f t="shared" ref="G68:G75" si="2">E68*0.8</f>
-        <v>3.84</v>
+        <f t="shared" si="2"/>
+        <v>2.1120000000000004E-4</v>
       </c>
       <c r="H68" s="5">
-        <f t="shared" ref="H68:H75" si="3">E68</f>
-        <v>4.8</v>
+        <f t="shared" si="3"/>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="I68" s="5">
-        <f t="shared" ref="I68:I75" si="4">1.2*E68</f>
-        <v>5.76</v>
+        <f t="shared" si="4"/>
+        <v>3.168E-4</v>
       </c>
       <c r="J68" s="3"/>
       <c r="K68" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P68">
         <f>IF(E68=[1]Sheet1!E68,1,0)</f>
@@ -5641,38 +5644,38 @@
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B69" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E69" s="5">
-        <v>2.6400000000000002E-4</v>
+        <v>65</v>
+      </c>
+      <c r="E69" s="3">
+        <v>4.8</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G69" s="5">
         <f t="shared" si="2"/>
-        <v>2.1120000000000004E-4</v>
+        <v>3.84</v>
       </c>
       <c r="H69" s="5">
         <f t="shared" si="3"/>
-        <v>2.6400000000000002E-4</v>
+        <v>4.8</v>
       </c>
       <c r="I69" s="5">
         <f t="shared" si="4"/>
-        <v>3.168E-4</v>
+        <v>5.76</v>
       </c>
       <c r="J69" s="3"/>
       <c r="K69" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P69">
         <f>IF(E69=[1]Sheet1!E69,1,0)</f>
@@ -5697,7 +5700,7 @@
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B70" s="3" t="s">
         <v>180</v>
@@ -5706,29 +5709,29 @@
         <v>21</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E70" s="3">
-        <v>4.8</v>
+        <v>67</v>
+      </c>
+      <c r="E70" s="5">
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G70" s="5">
         <f t="shared" si="2"/>
-        <v>3.84</v>
+        <v>2.1120000000000004E-4</v>
       </c>
       <c r="H70" s="5">
         <f t="shared" si="3"/>
-        <v>4.8</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="I70" s="5">
         <f t="shared" si="4"/>
-        <v>5.76</v>
+        <v>3.168E-4</v>
       </c>
       <c r="J70" s="3"/>
       <c r="K70" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="P70">
         <f>IF(E70=[1]Sheet1!E70,1,0)</f>
@@ -5753,38 +5756,38 @@
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B71" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C71" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E71" s="5">
-        <v>2.6400000000000002E-4</v>
+        <v>65</v>
+      </c>
+      <c r="E71" s="3">
+        <v>2.82</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G71" s="5">
         <f t="shared" si="2"/>
-        <v>2.1120000000000004E-4</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="H71" s="5">
         <f t="shared" si="3"/>
-        <v>2.6400000000000002E-4</v>
+        <v>2.82</v>
       </c>
       <c r="I71" s="5">
         <f t="shared" si="4"/>
-        <v>3.168E-4</v>
+        <v>3.3839999999999999</v>
       </c>
       <c r="J71" s="3"/>
       <c r="K71" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="P71">
         <f>IF(E71=[1]Sheet1!E71,1,0)</f>
@@ -5809,7 +5812,7 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>181</v>
@@ -5821,26 +5824,26 @@
         <v>65</v>
       </c>
       <c r="E72" s="3">
-        <v>2.82</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G72" s="5">
         <f t="shared" si="2"/>
-        <v>2.2559999999999998</v>
+        <v>1.0000000000000002E-2</v>
       </c>
       <c r="H72" s="5">
         <f t="shared" si="3"/>
-        <v>2.82</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="I72" s="5">
         <f t="shared" si="4"/>
-        <v>3.3839999999999999</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="J72" s="3"/>
       <c r="K72" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P72">
         <f>IF(E72=[1]Sheet1!E72,1,0)</f>
@@ -5865,7 +5868,7 @@
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>181</v>
@@ -5874,29 +5877,29 @@
         <v>21</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E73" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G73" s="5">
         <f t="shared" si="2"/>
-        <v>1.0000000000000002E-2</v>
+        <v>2.7200000000000002E-2</v>
       </c>
       <c r="H73" s="5">
         <f t="shared" si="3"/>
-        <v>1.2500000000000001E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="I73" s="5">
         <f t="shared" si="4"/>
-        <v>1.4999999999999999E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="J73" s="3"/>
       <c r="K73" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="P73">
         <f>IF(E73=[1]Sheet1!E73,1,0)</f>
@@ -5921,7 +5924,7 @@
     </row>
     <row r="74" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A74" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B74" s="3" t="s">
         <v>181</v>
@@ -5933,26 +5936,26 @@
         <v>67</v>
       </c>
       <c r="E74" s="3">
-        <v>3.4000000000000002E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="F74" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G74" s="5">
         <f t="shared" si="2"/>
-        <v>2.7200000000000002E-2</v>
+        <v>4.5600000000000002E-2</v>
       </c>
       <c r="H74" s="5">
         <f t="shared" si="3"/>
-        <v>3.4000000000000002E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="I74" s="5">
         <f t="shared" si="4"/>
-        <v>4.0800000000000003E-2</v>
+        <v>6.8400000000000002E-2</v>
       </c>
       <c r="J74" s="3"/>
       <c r="K74" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P74">
         <f>IF(E74=[1]Sheet1!E74,1,0)</f>
@@ -5972,62 +5975,6 @@
       </c>
       <c r="T74">
         <f>IF(I74=[1]Sheet1!I74,1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="75" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A75" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B75" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E75" s="3">
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G75" s="5">
-        <f t="shared" si="2"/>
-        <v>4.5600000000000002E-2</v>
-      </c>
-      <c r="H75" s="5">
-        <f t="shared" si="3"/>
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="I75" s="5">
-        <f t="shared" si="4"/>
-        <v>6.8400000000000002E-2</v>
-      </c>
-      <c r="J75" s="3"/>
-      <c r="K75" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="P75">
-        <f>IF(E75=[1]Sheet1!E75,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q75">
-        <f>IF(F75=[1]Sheet1!F75,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R75">
-        <f>IF(G75=[1]Sheet1!G75,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S75">
-        <f>IF(H75=[1]Sheet1!H75,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T75">
-        <f>IF(I75=[1]Sheet1!I75,1,0)</f>
         <v>0</v>
       </c>
     </row>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -2021,7 +2021,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:T74"/>
+  <dimension ref="A1:T73"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <cols>
     <col min="1" max="1" width="40.81640625" customWidth="1"/>
@@ -2813,35 +2813,38 @@
     </row>
     <row r="16" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A16" s="3" t="s">
-        <v>32</v>
+        <v>185</v>
       </c>
       <c r="B16" s="3" t="s">
-        <v>7</v>
+        <v>39</v>
       </c>
       <c r="C16" s="3" t="s">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="D16" s="3" t="s">
-        <v>8</v>
+        <v>192</v>
       </c>
       <c r="E16" s="3">
-        <v>0.15</v>
+        <v>0.72</v>
       </c>
       <c r="F16" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G16" s="3">
-        <f>0.8*E16</f>
-        <v>0.12</v>
-      </c>
-      <c r="H16" s="3"/>
+        <f>0.8*H16</f>
+        <v>0.57599999999999996</v>
+      </c>
+      <c r="H16" s="3">
+        <f>E16</f>
+        <v>0.72</v>
+      </c>
       <c r="I16" s="3">
-        <f>1.2*E16</f>
-        <v>0.18</v>
+        <f>1.2*H16</f>
+        <v>0.86399999999999999</v>
       </c>
       <c r="J16" s="3"/>
       <c r="K16" s="3" t="s">
-        <v>33</v>
+        <v>193</v>
       </c>
       <c r="P16">
         <f>IF(E16=[1]Sheet1!E16,1,0)</f>
@@ -2866,7 +2869,7 @@
     </row>
     <row r="17" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A17" s="3" t="s">
-        <v>185</v>
+        <v>38</v>
       </c>
       <c r="B17" s="3" t="s">
         <v>39</v>
@@ -2875,29 +2878,29 @@
         <v>21</v>
       </c>
       <c r="D17" s="3" t="s">
-        <v>192</v>
+        <v>40</v>
       </c>
       <c r="E17" s="3">
-        <v>0.72</v>
+        <v>56972</v>
       </c>
       <c r="F17" s="3" t="s">
         <v>27</v>
       </c>
       <c r="G17" s="3">
         <f>0.8*H17</f>
-        <v>0.57599999999999996</v>
+        <v>45577.600000000006</v>
       </c>
       <c r="H17" s="3">
         <f>E17</f>
-        <v>0.72</v>
+        <v>56972</v>
       </c>
       <c r="I17" s="3">
         <f>1.2*H17</f>
-        <v>0.86399999999999999</v>
+        <v>68366.399999999994</v>
       </c>
       <c r="J17" s="3"/>
       <c r="K17" s="3" t="s">
-        <v>193</v>
+        <v>41</v>
       </c>
       <c r="P17">
         <f>IF(E17=[1]Sheet1!E17,1,0)</f>
@@ -2905,7 +2908,7 @@
       </c>
       <c r="Q17">
         <f>IF(F17=[1]Sheet1!F17,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R17">
         <f>IF(G17=[1]Sheet1!G17,1,0)</f>
@@ -2922,38 +2925,33 @@
     </row>
     <row r="18" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A18" s="3" t="s">
-        <v>38</v>
+        <v>187</v>
       </c>
       <c r="B18" s="3" t="s">
-        <v>39</v>
+        <v>188</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D18" s="3" t="s">
-        <v>40</v>
+        <v>12</v>
       </c>
       <c r="E18" s="3">
-        <v>56972</v>
+        <v>2</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="G18" s="3">
-        <f>0.8*H18</f>
-        <v>45577.600000000006</v>
-      </c>
-      <c r="H18" s="3">
-        <f>E18</f>
-        <v>56972</v>
-      </c>
+        <v>1</v>
+      </c>
+      <c r="H18" s="3"/>
       <c r="I18" s="3">
-        <f>1.2*H18</f>
-        <v>68366.399999999994</v>
+        <v>3</v>
       </c>
       <c r="J18" s="3"/>
       <c r="K18" s="3" t="s">
-        <v>41</v>
+        <v>189</v>
       </c>
       <c r="P18">
         <f>IF(E18=[1]Sheet1!E18,1,0)</f>
@@ -2961,7 +2959,7 @@
       </c>
       <c r="Q18">
         <f>IF(F18=[1]Sheet1!F18,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R18">
         <f>IF(G18=[1]Sheet1!G18,1,0)</f>
@@ -2978,33 +2976,38 @@
     </row>
     <row r="19" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A19" s="3" t="s">
-        <v>187</v>
+        <v>52</v>
       </c>
       <c r="B19" s="3" t="s">
-        <v>188</v>
+        <v>13</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D19" s="3" t="s">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="E19" s="3">
-        <v>2</v>
+        <v>156</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>18</v>
+        <v>27</v>
       </c>
       <c r="G19" s="3">
-        <v>1</v>
-      </c>
-      <c r="H19" s="3"/>
+        <f>E19*0.8</f>
+        <v>124.80000000000001</v>
+      </c>
+      <c r="H19" s="3">
+        <f>E19</f>
+        <v>156</v>
+      </c>
       <c r="I19" s="3">
-        <v>3</v>
+        <f>E19*1.2</f>
+        <v>187.2</v>
       </c>
       <c r="J19" s="3"/>
       <c r="K19" s="3" t="s">
-        <v>189</v>
+        <v>54</v>
       </c>
       <c r="P19">
         <f>IF(E19=[1]Sheet1!E19,1,0)</f>
@@ -3012,7 +3015,7 @@
       </c>
       <c r="Q19">
         <f>IF(F19=[1]Sheet1!F19,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R19">
         <f>IF(G19=[1]Sheet1!G19,1,0)</f>
@@ -3029,7 +3032,7 @@
     </row>
     <row r="20" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A20" s="3" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B20" s="3" t="s">
         <v>13</v>
@@ -3060,7 +3063,7 @@
       </c>
       <c r="J20" s="3"/>
       <c r="K20" s="3" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="P20">
         <f>IF(E20=[1]Sheet1!E20,1,0)</f>
@@ -3085,38 +3088,35 @@
     </row>
     <row r="21" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A21" s="3" t="s">
-        <v>53</v>
+        <v>121</v>
       </c>
       <c r="B21" s="3" t="s">
-        <v>13</v>
+        <v>147</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D21" s="3" t="s">
-        <v>14</v>
+        <v>65</v>
       </c>
       <c r="E21" s="3">
-        <v>156</v>
+        <v>1.43</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>27</v>
+        <v>66</v>
       </c>
       <c r="G21" s="3">
-        <f>E21*0.8</f>
-        <v>124.80000000000001</v>
+        <v>1.1439999999999999</v>
       </c>
       <c r="H21" s="3">
-        <f>E21</f>
-        <v>156</v>
+        <v>1.43</v>
       </c>
       <c r="I21" s="3">
-        <f>E21*1.2</f>
-        <v>187.2</v>
+        <v>1.716</v>
       </c>
       <c r="J21" s="3"/>
       <c r="K21" s="3" t="s">
-        <v>55</v>
+        <v>62</v>
       </c>
       <c r="P21">
         <f>IF(E21=[1]Sheet1!E21,1,0)</f>
@@ -3141,7 +3141,7 @@
     </row>
     <row r="22" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A22" s="3" t="s">
-        <v>121</v>
+        <v>104</v>
       </c>
       <c r="B22" s="3" t="s">
         <v>147</v>
@@ -3150,26 +3150,26 @@
         <v>21</v>
       </c>
       <c r="D22" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E22" s="3">
-        <v>1.43</v>
+        <v>0.94</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G22" s="3">
-        <v>1.1439999999999999</v>
+        <v>0.752</v>
       </c>
       <c r="H22" s="3">
-        <v>1.43</v>
+        <v>0.94</v>
       </c>
       <c r="I22" s="3">
-        <v>1.716</v>
+        <v>1.1279999999999999</v>
       </c>
       <c r="J22" s="3"/>
       <c r="K22" s="3" t="s">
-        <v>62</v>
+        <v>87</v>
       </c>
       <c r="P22">
         <f>IF(E22=[1]Sheet1!E22,1,0)</f>
@@ -3194,7 +3194,7 @@
     </row>
     <row r="23" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A23" s="3" t="s">
-        <v>104</v>
+        <v>122</v>
       </c>
       <c r="B23" s="3" t="s">
         <v>147</v>
@@ -3203,26 +3203,26 @@
         <v>21</v>
       </c>
       <c r="D23" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E23" s="3">
-        <v>0.94</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G23" s="3">
-        <v>0.752</v>
+        <v>0.4672</v>
       </c>
       <c r="H23" s="3">
-        <v>0.94</v>
+        <v>0.58399999999999996</v>
       </c>
       <c r="I23" s="3">
-        <v>1.1279999999999999</v>
+        <v>0.70079999999999998</v>
       </c>
       <c r="J23" s="3"/>
       <c r="K23" s="3" t="s">
-        <v>87</v>
+        <v>58</v>
       </c>
       <c r="P23">
         <f>IF(E23=[1]Sheet1!E23,1,0)</f>
@@ -3247,7 +3247,7 @@
     </row>
     <row r="24" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A24" s="3" t="s">
-        <v>122</v>
+        <v>105</v>
       </c>
       <c r="B24" s="3" t="s">
         <v>147</v>
@@ -3256,26 +3256,26 @@
         <v>21</v>
       </c>
       <c r="D24" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E24" s="3">
-        <v>0.58399999999999996</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G24" s="3">
-        <v>0.4672</v>
+        <v>9.2800000000000001E-3</v>
       </c>
       <c r="H24" s="3">
-        <v>0.58399999999999996</v>
+        <v>1.1599999999999999E-2</v>
       </c>
       <c r="I24" s="3">
-        <v>0.70079999999999998</v>
+        <v>1.3919999999999899E-2</v>
       </c>
       <c r="J24" s="3"/>
       <c r="K24" s="3" t="s">
-        <v>58</v>
+        <v>88</v>
       </c>
       <c r="P24">
         <f>IF(E24=[1]Sheet1!E24,1,0)</f>
@@ -3300,7 +3300,7 @@
     </row>
     <row r="25" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A25" s="3" t="s">
-        <v>105</v>
+        <v>123</v>
       </c>
       <c r="B25" s="3" t="s">
         <v>147</v>
@@ -3309,26 +3309,26 @@
         <v>21</v>
       </c>
       <c r="D25" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E25" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>47.1</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G25" s="3">
-        <v>9.2800000000000001E-3</v>
+        <v>37.68</v>
       </c>
       <c r="H25" s="3">
-        <v>1.1599999999999999E-2</v>
+        <v>47.1</v>
       </c>
       <c r="I25" s="3">
-        <v>1.3919999999999899E-2</v>
+        <v>56.52</v>
       </c>
       <c r="J25" s="3"/>
       <c r="K25" s="3" t="s">
-        <v>88</v>
+        <v>57</v>
       </c>
       <c r="P25">
         <f>IF(E25=[1]Sheet1!E25,1,0)</f>
@@ -3353,7 +3353,7 @@
     </row>
     <row r="26" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A26" s="3" t="s">
-        <v>123</v>
+        <v>106</v>
       </c>
       <c r="B26" s="3" t="s">
         <v>147</v>
@@ -3362,26 +3362,26 @@
         <v>21</v>
       </c>
       <c r="D26" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E26" s="3">
-        <v>47.1</v>
+        <v>14.2</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G26" s="3">
-        <v>37.68</v>
+        <v>11.36</v>
       </c>
       <c r="H26" s="3">
-        <v>47.1</v>
+        <v>14.2</v>
       </c>
       <c r="I26" s="3">
-        <v>56.52</v>
+        <v>17.04</v>
       </c>
       <c r="J26" s="3"/>
       <c r="K26" s="3" t="s">
-        <v>57</v>
+        <v>89</v>
       </c>
       <c r="P26">
         <f>IF(E26=[1]Sheet1!E26,1,0)</f>
@@ -3406,7 +3406,7 @@
     </row>
     <row r="27" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A27" s="3" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
       <c r="B27" s="3" t="s">
         <v>147</v>
@@ -3418,27 +3418,27 @@
         <v>67</v>
       </c>
       <c r="E27" s="3">
-        <v>14.2</v>
+        <v>0.12</v>
       </c>
       <c r="F27" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G27" s="3">
-        <v>11.36</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H27" s="3">
-        <v>14.2</v>
+        <v>0.12</v>
       </c>
       <c r="I27" s="3">
-        <v>17.04</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J27" s="3"/>
       <c r="K27" s="3" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="P27">
         <f>IF(E27=[1]Sheet1!E27,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q27">
         <f>IF(F27=[1]Sheet1!F27,1,0)</f>
@@ -3446,20 +3446,20 @@
       </c>
       <c r="R27">
         <f>IF(G27=[1]Sheet1!G27,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S27">
         <f>IF(H27=[1]Sheet1!H27,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T27">
         <f>IF(I27=[1]Sheet1!I27,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="28" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A28" s="3" t="s">
-        <v>107</v>
+        <v>124</v>
       </c>
       <c r="B28" s="3" t="s">
         <v>147</v>
@@ -3468,26 +3468,26 @@
         <v>21</v>
       </c>
       <c r="D28" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E28" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F28" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G28" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H28" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I28" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J28" s="3"/>
       <c r="K28" s="3" t="s">
-        <v>90</v>
+        <v>59</v>
       </c>
       <c r="P28">
         <f>IF(E28=[1]Sheet1!E28,1,0)</f>
@@ -3512,7 +3512,7 @@
     </row>
     <row r="29" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A29" s="3" t="s">
-        <v>124</v>
+        <v>125</v>
       </c>
       <c r="B29" s="3" t="s">
         <v>147</v>
@@ -3524,27 +3524,27 @@
         <v>65</v>
       </c>
       <c r="E29" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F29" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G29" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H29" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I29" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J29" s="3"/>
       <c r="K29" s="3" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
       <c r="P29">
         <f>IF(E29=[1]Sheet1!E29,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q29">
         <f>IF(F29=[1]Sheet1!F29,1,0)</f>
@@ -3552,20 +3552,20 @@
       </c>
       <c r="R29">
         <f>IF(G29=[1]Sheet1!G29,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S29">
         <f>IF(H29=[1]Sheet1!H29,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T29">
         <f>IF(I29=[1]Sheet1!I29,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="30" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A30" s="3" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
       <c r="B30" s="3" t="s">
         <v>147</v>
@@ -3577,23 +3577,23 @@
         <v>65</v>
       </c>
       <c r="E30" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F30" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G30" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H30" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I30" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J30" s="3"/>
       <c r="K30" s="3" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="P30">
         <f>IF(E30=[1]Sheet1!E30,1,0)</f>
@@ -3618,10 +3618,10 @@
     </row>
     <row r="31" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A31" s="3" t="s">
-        <v>126</v>
+        <v>127</v>
       </c>
       <c r="B31" s="3" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="C31" s="3" t="s">
         <v>21</v>
@@ -3630,23 +3630,23 @@
         <v>65</v>
       </c>
       <c r="E31" s="3">
-        <v>0.04</v>
+        <v>0.501</v>
       </c>
       <c r="F31" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G31" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>0.40079999999999999</v>
       </c>
       <c r="H31" s="3">
-        <v>0.04</v>
+        <v>0.501</v>
       </c>
       <c r="I31" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.60119999999999996</v>
       </c>
       <c r="J31" s="3"/>
       <c r="K31" s="3" t="s">
-        <v>61</v>
+        <v>56</v>
       </c>
       <c r="P31">
         <f>IF(E31=[1]Sheet1!E31,1,0)</f>
@@ -3671,7 +3671,7 @@
     </row>
     <row r="32" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A32" s="3" t="s">
-        <v>127</v>
+        <v>108</v>
       </c>
       <c r="B32" s="3" t="s">
         <v>148</v>
@@ -3680,26 +3680,26 @@
         <v>21</v>
       </c>
       <c r="D32" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E32" s="3">
-        <v>0.501</v>
+        <v>67</v>
+      </c>
+      <c r="E32" s="5">
+        <v>2.0000000000000002E-5</v>
       </c>
       <c r="F32" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G32" s="3">
-        <v>0.40079999999999999</v>
-      </c>
-      <c r="H32" s="3">
-        <v>0.501</v>
-      </c>
-      <c r="I32" s="3">
-        <v>0.60119999999999996</v>
+      <c r="G32" s="5">
+        <v>1.5999999999999999E-5</v>
+      </c>
+      <c r="H32" s="5">
+        <v>2.0000000000000002E-5</v>
+      </c>
+      <c r="I32" s="5">
+        <v>2.4000000000000001E-5</v>
       </c>
       <c r="J32" s="3"/>
       <c r="K32" s="3" t="s">
-        <v>56</v>
+        <v>91</v>
       </c>
       <c r="P32">
         <f>IF(E32=[1]Sheet1!E32,1,0)</f>
@@ -3724,7 +3724,7 @@
     </row>
     <row r="33" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A33" s="3" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
       <c r="B33" s="3" t="s">
         <v>148</v>
@@ -3735,24 +3735,24 @@
       <c r="D33" s="3" t="s">
         <v>67</v>
       </c>
-      <c r="E33" s="5">
-        <v>2.0000000000000002E-5</v>
+      <c r="E33" s="3">
+        <v>0.10100000000000001</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G33" s="5">
-        <v>1.5999999999999999E-5</v>
-      </c>
-      <c r="H33" s="5">
-        <v>2.0000000000000002E-5</v>
-      </c>
-      <c r="I33" s="5">
-        <v>2.4000000000000001E-5</v>
+      <c r="G33" s="3">
+        <v>8.0799999999999997E-2</v>
+      </c>
+      <c r="H33" s="3">
+        <v>0.10100000000000001</v>
+      </c>
+      <c r="I33" s="3">
+        <v>0.1212</v>
       </c>
       <c r="J33" s="3"/>
       <c r="K33" s="3" t="s">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="P33">
         <f>IF(E33=[1]Sheet1!E33,1,0)</f>
@@ -3777,35 +3777,35 @@
     </row>
     <row r="34" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A34" s="3" t="s">
-        <v>109</v>
+        <v>128</v>
       </c>
       <c r="B34" s="3" t="s">
-        <v>148</v>
+        <v>149</v>
       </c>
       <c r="C34" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D34" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E34" s="3">
-        <v>0.10100000000000001</v>
+        <v>5.81</v>
       </c>
       <c r="F34" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G34" s="3">
-        <v>8.0799999999999997E-2</v>
+        <v>4.6479999999999997</v>
       </c>
       <c r="H34" s="3">
-        <v>0.10100000000000001</v>
+        <v>5.81</v>
       </c>
       <c r="I34" s="3">
-        <v>0.1212</v>
+        <v>6.9719999999999898</v>
       </c>
       <c r="J34" s="3"/>
       <c r="K34" s="3" t="s">
-        <v>92</v>
+        <v>63</v>
       </c>
       <c r="P34">
         <f>IF(E34=[1]Sheet1!E34,1,0)</f>
@@ -3830,7 +3830,7 @@
     </row>
     <row r="35" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A35" s="3" t="s">
-        <v>128</v>
+        <v>110</v>
       </c>
       <c r="B35" s="3" t="s">
         <v>149</v>
@@ -3839,26 +3839,26 @@
         <v>21</v>
       </c>
       <c r="D35" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E35" s="3">
-        <v>5.81</v>
+        <v>67</v>
+      </c>
+      <c r="E35" s="5">
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G35" s="3">
-        <v>4.6479999999999997</v>
-      </c>
-      <c r="H35" s="3">
-        <v>5.81</v>
-      </c>
-      <c r="I35" s="3">
-        <v>6.9719999999999898</v>
+      <c r="G35" s="5">
+        <v>3.9999999999999998E-7</v>
+      </c>
+      <c r="H35" s="5">
+        <v>4.9999999999999998E-7</v>
+      </c>
+      <c r="I35" s="5">
+        <v>5.9999999999999997E-7</v>
       </c>
       <c r="J35" s="3"/>
       <c r="K35" s="3" t="s">
-        <v>63</v>
+        <v>93</v>
       </c>
       <c r="P35">
         <f>IF(E35=[1]Sheet1!E35,1,0)</f>
@@ -3883,35 +3883,35 @@
     </row>
     <row r="36" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A36" s="3" t="s">
-        <v>110</v>
+        <v>129</v>
       </c>
       <c r="B36" s="3" t="s">
-        <v>149</v>
+        <v>150</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D36" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E36" s="5">
-        <v>4.9999999999999998E-7</v>
+        <v>65</v>
+      </c>
+      <c r="E36" s="3">
+        <v>4.8</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G36" s="5">
-        <v>3.9999999999999998E-7</v>
-      </c>
-      <c r="H36" s="5">
-        <v>4.9999999999999998E-7</v>
-      </c>
-      <c r="I36" s="5">
-        <v>5.9999999999999997E-7</v>
+      <c r="G36" s="3">
+        <v>3.84</v>
+      </c>
+      <c r="H36" s="3">
+        <v>4.8</v>
+      </c>
+      <c r="I36" s="3">
+        <v>5.76</v>
       </c>
       <c r="J36" s="3"/>
       <c r="K36" s="3" t="s">
-        <v>93</v>
+        <v>64</v>
       </c>
       <c r="P36">
         <f>IF(E36=[1]Sheet1!E36,1,0)</f>
@@ -3936,7 +3936,7 @@
     </row>
     <row r="37" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A37" s="3" t="s">
-        <v>129</v>
+        <v>130</v>
       </c>
       <c r="B37" s="3" t="s">
         <v>150</v>
@@ -3948,27 +3948,27 @@
         <v>65</v>
       </c>
       <c r="E37" s="3">
-        <v>4.8</v>
+        <v>0.04</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G37" s="3">
-        <v>3.84</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H37" s="3">
-        <v>4.8</v>
+        <v>0.04</v>
       </c>
       <c r="I37" s="3">
-        <v>5.76</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J37" s="3"/>
       <c r="K37" s="3" t="s">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="P37">
         <f>IF(E37=[1]Sheet1!E37,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q37">
         <f>IF(F37=[1]Sheet1!F37,1,0)</f>
@@ -3976,20 +3976,20 @@
       </c>
       <c r="R37">
         <f>IF(G37=[1]Sheet1!G37,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S37">
         <f>IF(H37=[1]Sheet1!H37,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T37">
         <f>IF(I37=[1]Sheet1!I37,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="38" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A38" s="3" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
       <c r="B38" s="3" t="s">
         <v>150</v>
@@ -4001,27 +4001,27 @@
         <v>65</v>
       </c>
       <c r="E38" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G38" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H38" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I38" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J38" s="3"/>
       <c r="K38" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
       </c>
       <c r="P38">
         <f>IF(E38=[1]Sheet1!E38,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q38">
         <f>IF(F38=[1]Sheet1!F38,1,0)</f>
@@ -4029,20 +4029,20 @@
       </c>
       <c r="R38">
         <f>IF(G38=[1]Sheet1!G38,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S38">
         <f>IF(H38=[1]Sheet1!H38,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T38">
         <f>IF(I38=[1]Sheet1!I38,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="39" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A39" s="3" t="s">
-        <v>131</v>
+        <v>132</v>
       </c>
       <c r="B39" s="3" t="s">
         <v>150</v>
@@ -4054,23 +4054,23 @@
         <v>65</v>
       </c>
       <c r="E39" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G39" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H39" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I39" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J39" s="3"/>
       <c r="K39" s="3" t="s">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="P39">
         <f>IF(E39=[1]Sheet1!E39,1,0)</f>
@@ -4095,7 +4095,7 @@
     </row>
     <row r="40" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A40" s="3" t="s">
-        <v>132</v>
+        <v>111</v>
       </c>
       <c r="B40" s="3" t="s">
         <v>150</v>
@@ -4104,26 +4104,26 @@
         <v>21</v>
       </c>
       <c r="D40" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E40" s="3">
-        <v>0.04</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G40" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>2.1120000000000001E-4</v>
       </c>
       <c r="H40" s="3">
-        <v>0.04</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="I40" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>3.168E-4</v>
       </c>
       <c r="J40" s="3"/>
       <c r="K40" s="3" t="s">
-        <v>70</v>
+        <v>94</v>
       </c>
       <c r="P40">
         <f>IF(E40=[1]Sheet1!E40,1,0)</f>
@@ -4148,35 +4148,35 @@
     </row>
     <row r="41" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A41" s="3" t="s">
-        <v>111</v>
+        <v>133</v>
       </c>
       <c r="B41" s="3" t="s">
-        <v>150</v>
+        <v>155</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D41" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E41" s="3">
-        <v>2.6400000000000002E-4</v>
+        <v>1.04E-2</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G41" s="3">
-        <v>2.1120000000000001E-4</v>
+        <v>8.3199999999999993E-3</v>
       </c>
       <c r="H41" s="3">
-        <v>2.6400000000000002E-4</v>
+        <v>1.04E-2</v>
       </c>
       <c r="I41" s="3">
-        <v>3.168E-4</v>
+        <v>1.248E-2</v>
       </c>
       <c r="J41" s="3"/>
       <c r="K41" s="3" t="s">
-        <v>94</v>
+        <v>71</v>
       </c>
       <c r="P41">
         <f>IF(E41=[1]Sheet1!E41,1,0)</f>
@@ -4201,7 +4201,7 @@
     </row>
     <row r="42" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A42" s="3" t="s">
-        <v>133</v>
+        <v>112</v>
       </c>
       <c r="B42" s="3" t="s">
         <v>155</v>
@@ -4210,26 +4210,26 @@
         <v>21</v>
       </c>
       <c r="D42" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E42" s="3">
-        <v>1.04E-2</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G42" s="3">
-        <v>8.3199999999999993E-3</v>
+        <v>8.1600000000000006E-3</v>
       </c>
       <c r="H42" s="3">
-        <v>1.04E-2</v>
+        <v>1.0200000000000001E-2</v>
       </c>
       <c r="I42" s="3">
-        <v>1.248E-2</v>
+        <v>1.2239999999999999E-2</v>
       </c>
       <c r="J42" s="3"/>
       <c r="K42" s="3" t="s">
-        <v>71</v>
+        <v>95</v>
       </c>
       <c r="P42">
         <f>IF(E42=[1]Sheet1!E42,1,0)</f>
@@ -4254,7 +4254,7 @@
     </row>
     <row r="43" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A43" s="3" t="s">
-        <v>112</v>
+        <v>134</v>
       </c>
       <c r="B43" s="3" t="s">
         <v>155</v>
@@ -4263,26 +4263,26 @@
         <v>21</v>
       </c>
       <c r="D43" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E43" s="3">
-        <v>1.0200000000000001E-2</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G43" s="3">
-        <v>8.1600000000000006E-3</v>
+        <v>0.62</v>
       </c>
       <c r="H43" s="3">
-        <v>1.0200000000000001E-2</v>
+        <v>0.77500000000000002</v>
       </c>
       <c r="I43" s="3">
-        <v>1.2239999999999999E-2</v>
+        <v>0.92999999999999905</v>
       </c>
       <c r="J43" s="3"/>
       <c r="K43" s="3" t="s">
-        <v>95</v>
+        <v>72</v>
       </c>
       <c r="P43">
         <f>IF(E43=[1]Sheet1!E43,1,0)</f>
@@ -4307,7 +4307,7 @@
     </row>
     <row r="44" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A44" s="3" t="s">
-        <v>134</v>
+        <v>113</v>
       </c>
       <c r="B44" s="3" t="s">
         <v>155</v>
@@ -4316,26 +4316,26 @@
         <v>21</v>
       </c>
       <c r="D44" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E44" s="3">
-        <v>0.77500000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G44" s="3">
-        <v>0.62</v>
+        <v>0.08</v>
       </c>
       <c r="H44" s="3">
-        <v>0.77500000000000002</v>
+        <v>0.1</v>
       </c>
       <c r="I44" s="3">
-        <v>0.92999999999999905</v>
+        <v>0.12</v>
       </c>
       <c r="J44" s="3"/>
       <c r="K44" s="3" t="s">
-        <v>72</v>
+        <v>96</v>
       </c>
       <c r="P44">
         <f>IF(E44=[1]Sheet1!E44,1,0)</f>
@@ -4360,7 +4360,7 @@
     </row>
     <row r="45" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A45" s="3" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B45" s="3" t="s">
         <v>155</v>
@@ -4372,23 +4372,23 @@
         <v>67</v>
       </c>
       <c r="E45" s="3">
-        <v>0.1</v>
+        <v>440</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G45" s="3">
-        <v>0.08</v>
+        <v>352</v>
       </c>
       <c r="H45" s="3">
-        <v>0.1</v>
+        <v>440</v>
       </c>
       <c r="I45" s="3">
-        <v>0.12</v>
+        <v>528</v>
       </c>
       <c r="J45" s="3"/>
       <c r="K45" s="3" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="P45">
         <f>IF(E45=[1]Sheet1!E45,1,0)</f>
@@ -4413,35 +4413,35 @@
     </row>
     <row r="46" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A46" s="3" t="s">
-        <v>114</v>
+        <v>135</v>
       </c>
       <c r="B46" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D46" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E46" s="3">
-        <v>440</v>
+        <v>2.82</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G46" s="3">
-        <v>352</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="H46" s="3">
-        <v>440</v>
+        <v>2.82</v>
       </c>
       <c r="I46" s="3">
-        <v>528</v>
+        <v>3.3839999999999999</v>
       </c>
       <c r="J46" s="3"/>
       <c r="K46" s="3" t="s">
-        <v>97</v>
+        <v>73</v>
       </c>
       <c r="P46">
         <f>IF(E46=[1]Sheet1!E46,1,0)</f>
@@ -4466,7 +4466,7 @@
     </row>
     <row r="47" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A47" s="3" t="s">
-        <v>135</v>
+        <v>136</v>
       </c>
       <c r="B47" s="3" t="s">
         <v>151</v>
@@ -4478,23 +4478,23 @@
         <v>65</v>
       </c>
       <c r="E47" s="3">
-        <v>2.82</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="F47" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G47" s="3">
-        <v>2.2559999999999998</v>
+        <v>0.01</v>
       </c>
       <c r="H47" s="3">
-        <v>2.82</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="I47" s="3">
-        <v>3.3839999999999999</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="J47" s="3"/>
       <c r="K47" s="3" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="P47">
         <f>IF(E47=[1]Sheet1!E47,1,0)</f>
@@ -4519,7 +4519,7 @@
     </row>
     <row r="48" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A48" s="3" t="s">
-        <v>136</v>
+        <v>115</v>
       </c>
       <c r="B48" s="3" t="s">
         <v>151</v>
@@ -4528,26 +4528,26 @@
         <v>21</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E48" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="F48" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G48" s="3">
-        <v>0.01</v>
+        <v>2.7199999999999998E-2</v>
       </c>
       <c r="H48" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="I48" s="3">
-        <v>1.4999999999999999E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="J48" s="3"/>
       <c r="K48" s="3" t="s">
-        <v>74</v>
+        <v>98</v>
       </c>
       <c r="P48">
         <f>IF(E48=[1]Sheet1!E48,1,0)</f>
@@ -4572,7 +4572,7 @@
     </row>
     <row r="49" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A49" s="3" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B49" s="3" t="s">
         <v>151</v>
@@ -4584,23 +4584,23 @@
         <v>67</v>
       </c>
       <c r="E49" s="3">
-        <v>3.4000000000000002E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="F49" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G49" s="3">
-        <v>2.7199999999999998E-2</v>
+        <v>4.5600000000000002E-2</v>
       </c>
       <c r="H49" s="3">
-        <v>3.4000000000000002E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="I49" s="3">
-        <v>4.0800000000000003E-2</v>
+        <v>6.8400000000000002E-2</v>
       </c>
       <c r="J49" s="3"/>
       <c r="K49" s="3" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="P49">
         <f>IF(E49=[1]Sheet1!E49,1,0)</f>
@@ -4625,35 +4625,35 @@
     </row>
     <row r="50" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A50" s="3" t="s">
-        <v>116</v>
+        <v>137</v>
       </c>
       <c r="B50" s="3" t="s">
-        <v>151</v>
+        <v>152</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D50" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E50" s="3">
-        <v>5.7000000000000002E-2</v>
+        <v>1.2030000000000001</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G50" s="3">
-        <v>4.5600000000000002E-2</v>
+        <v>0.96240000000000003</v>
       </c>
       <c r="H50" s="3">
-        <v>5.7000000000000002E-2</v>
+        <v>1.2030000000000001</v>
       </c>
       <c r="I50" s="3">
-        <v>6.8400000000000002E-2</v>
+        <v>1.4436</v>
       </c>
       <c r="J50" s="3"/>
       <c r="K50" s="3" t="s">
-        <v>99</v>
+        <v>75</v>
       </c>
       <c r="P50">
         <f>IF(E50=[1]Sheet1!E50,1,0)</f>
@@ -4678,7 +4678,7 @@
     </row>
     <row r="51" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A51" s="3" t="s">
-        <v>137</v>
+        <v>138</v>
       </c>
       <c r="B51" s="3" t="s">
         <v>152</v>
@@ -4690,27 +4690,27 @@
         <v>65</v>
       </c>
       <c r="E51" s="3">
-        <v>1.2030000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G51" s="3">
-        <v>0.96240000000000003</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H51" s="3">
-        <v>1.2030000000000001</v>
+        <v>0.04</v>
       </c>
       <c r="I51" s="3">
-        <v>1.4436</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J51" s="3"/>
       <c r="K51" s="3" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="P51">
         <f>IF(E51=[1]Sheet1!E51,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q51">
         <f>IF(F51=[1]Sheet1!F51,1,0)</f>
@@ -4718,20 +4718,20 @@
       </c>
       <c r="R51">
         <f>IF(G51=[1]Sheet1!G51,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S51">
         <f>IF(H51=[1]Sheet1!H51,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T51">
         <f>IF(I51=[1]Sheet1!I51,1,0)</f>
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="52" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A52" s="3" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
       <c r="B52" s="3" t="s">
         <v>152</v>
@@ -4743,27 +4743,27 @@
         <v>65</v>
       </c>
       <c r="E52" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G52" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>9.6000000000000002E-2</v>
       </c>
       <c r="H52" s="3">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I52" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>0.14399999999999999</v>
       </c>
       <c r="J52" s="3"/>
       <c r="K52" s="3" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="P52">
         <f>IF(E52=[1]Sheet1!E52,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="Q52">
         <f>IF(F52=[1]Sheet1!F52,1,0)</f>
@@ -4771,20 +4771,20 @@
       </c>
       <c r="R52">
         <f>IF(G52=[1]Sheet1!G52,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="S52">
         <f>IF(H52=[1]Sheet1!H52,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T52">
         <f>IF(I52=[1]Sheet1!I52,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="53" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A53" s="3" t="s">
-        <v>139</v>
+        <v>140</v>
       </c>
       <c r="B53" s="3" t="s">
         <v>152</v>
@@ -4796,23 +4796,23 @@
         <v>65</v>
       </c>
       <c r="E53" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G53" s="3">
-        <v>9.6000000000000002E-2</v>
+        <v>3.2000000000000001E-2</v>
       </c>
       <c r="H53" s="3">
-        <v>0.12</v>
+        <v>0.04</v>
       </c>
       <c r="I53" s="3">
-        <v>0.14399999999999999</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="J53" s="3"/>
       <c r="K53" s="3" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="P53">
         <f>IF(E53=[1]Sheet1!E53,1,0)</f>
@@ -4837,7 +4837,7 @@
     </row>
     <row r="54" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A54" s="3" t="s">
-        <v>140</v>
+        <v>117</v>
       </c>
       <c r="B54" s="3" t="s">
         <v>152</v>
@@ -4846,26 +4846,26 @@
         <v>21</v>
       </c>
       <c r="D54" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E54" s="3">
-        <v>0.04</v>
+        <v>1.01E-2</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G54" s="3">
-        <v>3.2000000000000001E-2</v>
+        <v>8.0800000000000004E-3</v>
       </c>
       <c r="H54" s="3">
-        <v>0.04</v>
+        <v>1.01E-2</v>
       </c>
       <c r="I54" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>1.21199999999999E-2</v>
       </c>
       <c r="J54" s="3"/>
       <c r="K54" s="3" t="s">
-        <v>78</v>
+        <v>100</v>
       </c>
       <c r="P54">
         <f>IF(E54=[1]Sheet1!E54,1,0)</f>
@@ -4890,35 +4890,35 @@
     </row>
     <row r="55" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A55" s="3" t="s">
-        <v>117</v>
+        <v>141</v>
       </c>
       <c r="B55" s="3" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D55" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E55" s="3">
-        <v>1.01E-2</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G55" s="3">
-        <v>8.0800000000000004E-3</v>
+        <v>0.47120000000000001</v>
       </c>
       <c r="H55" s="3">
-        <v>1.01E-2</v>
+        <v>0.58899999999999997</v>
       </c>
       <c r="I55" s="3">
-        <v>1.21199999999999E-2</v>
+        <v>0.70679999999999998</v>
       </c>
       <c r="J55" s="3"/>
       <c r="K55" s="3" t="s">
-        <v>100</v>
+        <v>79</v>
       </c>
       <c r="P55">
         <f>IF(E55=[1]Sheet1!E55,1,0)</f>
@@ -4943,10 +4943,10 @@
     </row>
     <row r="56" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A56" s="3" t="s">
-        <v>141</v>
+        <v>142</v>
       </c>
       <c r="B56" s="3" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>21</v>
@@ -4955,23 +4955,23 @@
         <v>65</v>
       </c>
       <c r="E56" s="3">
-        <v>0.58899999999999997</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G56" s="3">
-        <v>0.47120000000000001</v>
+        <v>6.4000000000000003E-3</v>
       </c>
       <c r="H56" s="3">
-        <v>0.58899999999999997</v>
+        <v>8.0000000000000002E-3</v>
       </c>
       <c r="I56" s="3">
-        <v>0.70679999999999998</v>
+        <v>9.5999999999999992E-3</v>
       </c>
       <c r="J56" s="3"/>
       <c r="K56" s="3" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="P56">
         <f>IF(E56=[1]Sheet1!E56,1,0)</f>
@@ -4996,7 +4996,7 @@
     </row>
     <row r="57" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A57" s="3" t="s">
-        <v>142</v>
+        <v>118</v>
       </c>
       <c r="B57" s="3" t="s">
         <v>154</v>
@@ -5005,26 +5005,26 @@
         <v>21</v>
       </c>
       <c r="D57" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E57" s="3">
-        <v>8.0000000000000002E-3</v>
+        <v>67</v>
+      </c>
+      <c r="E57" s="5">
+        <v>9.9999999999999995E-7</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G57" s="3">
-        <v>6.4000000000000003E-3</v>
-      </c>
-      <c r="H57" s="3">
-        <v>8.0000000000000002E-3</v>
-      </c>
-      <c r="I57" s="3">
-        <v>9.5999999999999992E-3</v>
+      <c r="G57" s="5">
+        <v>7.9999999999999996E-7</v>
+      </c>
+      <c r="H57" s="5">
+        <v>9.9999999999999995E-7</v>
+      </c>
+      <c r="I57" s="5">
+        <v>1.1999999999999999E-6</v>
       </c>
       <c r="J57" s="3"/>
       <c r="K57" s="3" t="s">
-        <v>80</v>
+        <v>101</v>
       </c>
       <c r="P57">
         <f>IF(E57=[1]Sheet1!E57,1,0)</f>
@@ -5049,7 +5049,7 @@
     </row>
     <row r="58" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A58" s="3" t="s">
-        <v>118</v>
+        <v>143</v>
       </c>
       <c r="B58" s="3" t="s">
         <v>154</v>
@@ -5058,26 +5058,26 @@
         <v>21</v>
       </c>
       <c r="D58" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E58" s="5">
-        <v>9.9999999999999995E-7</v>
+        <v>65</v>
+      </c>
+      <c r="E58" s="3">
+        <v>7.51E-2</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G58" s="5">
-        <v>7.9999999999999996E-7</v>
-      </c>
-      <c r="H58" s="5">
-        <v>9.9999999999999995E-7</v>
-      </c>
-      <c r="I58" s="5">
-        <v>1.1999999999999999E-6</v>
+      <c r="G58" s="3">
+        <v>6.0080000000000001E-2</v>
+      </c>
+      <c r="H58" s="3">
+        <v>7.51E-2</v>
+      </c>
+      <c r="I58" s="3">
+        <v>9.0119999999999895E-2</v>
       </c>
       <c r="J58" s="3"/>
       <c r="K58" s="3" t="s">
-        <v>101</v>
+        <v>81</v>
       </c>
       <c r="P58">
         <f>IF(E58=[1]Sheet1!E58,1,0)</f>
@@ -5102,7 +5102,7 @@
     </row>
     <row r="59" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A59" s="3" t="s">
-        <v>143</v>
+        <v>119</v>
       </c>
       <c r="B59" s="3" t="s">
         <v>154</v>
@@ -5111,26 +5111,26 @@
         <v>21</v>
       </c>
       <c r="D59" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E59" s="3">
-        <v>7.51E-2</v>
+        <v>13</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G59" s="3">
-        <v>6.0080000000000001E-2</v>
+        <v>10.4</v>
       </c>
       <c r="H59" s="3">
-        <v>7.51E-2</v>
+        <v>13</v>
       </c>
       <c r="I59" s="3">
-        <v>9.0119999999999895E-2</v>
+        <v>15.6</v>
       </c>
       <c r="J59" s="3"/>
       <c r="K59" s="3" t="s">
-        <v>81</v>
+        <v>102</v>
       </c>
       <c r="P59">
         <f>IF(E59=[1]Sheet1!E59,1,0)</f>
@@ -5155,7 +5155,7 @@
     </row>
     <row r="60" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A60" s="3" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B60" s="3" t="s">
         <v>154</v>
@@ -5167,23 +5167,23 @@
         <v>67</v>
       </c>
       <c r="E60" s="3">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G60" s="3">
-        <v>10.4</v>
+        <v>20</v>
       </c>
       <c r="H60" s="3">
-        <v>13</v>
+        <v>25</v>
       </c>
       <c r="I60" s="3">
-        <v>15.6</v>
+        <v>30</v>
       </c>
       <c r="J60" s="3"/>
       <c r="K60" s="3" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="P60">
         <f>IF(E60=[1]Sheet1!E60,1,0)</f>
@@ -5208,7 +5208,7 @@
     </row>
     <row r="61" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A61" s="3" t="s">
-        <v>120</v>
+        <v>144</v>
       </c>
       <c r="B61" s="3" t="s">
         <v>154</v>
@@ -5217,26 +5217,26 @@
         <v>21</v>
       </c>
       <c r="D61" s="3" t="s">
-        <v>67</v>
+        <v>65</v>
       </c>
       <c r="E61" s="3">
-        <v>25</v>
+        <v>3.9899999999999996E-3</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G61" s="3">
-        <v>20</v>
+        <v>3.192E-3</v>
       </c>
       <c r="H61" s="3">
-        <v>25</v>
+        <v>3.9899999999999996E-3</v>
       </c>
       <c r="I61" s="3">
-        <v>30</v>
+        <v>4.7879999999999997E-3</v>
       </c>
       <c r="J61" s="3"/>
       <c r="K61" s="3" t="s">
-        <v>103</v>
+        <v>82</v>
       </c>
       <c r="P61">
         <f>IF(E61=[1]Sheet1!E61,1,0)</f>
@@ -5261,10 +5261,10 @@
     </row>
     <row r="62" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A62" s="3" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
       <c r="B62" s="3" t="s">
-        <v>154</v>
+        <v>156</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>21</v>
@@ -5273,23 +5273,23 @@
         <v>65</v>
       </c>
       <c r="E62" s="3">
-        <v>3.9899999999999996E-3</v>
+        <v>0.06</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G62" s="3">
-        <v>3.192E-3</v>
+        <v>4.8000000000000001E-2</v>
       </c>
       <c r="H62" s="3">
-        <v>3.9899999999999996E-3</v>
+        <v>0.06</v>
       </c>
       <c r="I62" s="3">
-        <v>4.7879999999999997E-3</v>
+        <v>7.1999999999999995E-2</v>
       </c>
       <c r="J62" s="3"/>
       <c r="K62" s="3" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="P62">
         <f>IF(E62=[1]Sheet1!E62,1,0)</f>
@@ -5297,7 +5297,7 @@
       </c>
       <c r="Q62">
         <f>IF(F62=[1]Sheet1!F62,1,0)</f>
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="R62">
         <f>IF(G62=[1]Sheet1!G62,1,0)</f>
@@ -5314,10 +5314,10 @@
     </row>
     <row r="63" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A63" s="3" t="s">
-        <v>145</v>
+        <v>146</v>
       </c>
       <c r="B63" s="3" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>21</v>
@@ -5326,23 +5326,23 @@
         <v>65</v>
       </c>
       <c r="E63" s="3">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G63" s="3">
-        <v>4.8000000000000001E-2</v>
+        <v>1.6E-2</v>
       </c>
       <c r="H63" s="3">
-        <v>0.06</v>
+        <v>0.02</v>
       </c>
       <c r="I63" s="3">
-        <v>7.1999999999999995E-2</v>
+        <v>2.4E-2</v>
       </c>
       <c r="J63" s="3"/>
       <c r="K63" s="3" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="P63">
         <f>IF(E63=[1]Sheet1!E63,1,0)</f>
@@ -5367,10 +5367,10 @@
     </row>
     <row r="64" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A64" s="3" t="s">
-        <v>146</v>
+        <v>158</v>
       </c>
       <c r="B64" s="3" t="s">
-        <v>157</v>
+        <v>178</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>21</v>
@@ -5379,23 +5379,26 @@
         <v>65</v>
       </c>
       <c r="E64" s="3">
-        <v>0.02</v>
+        <v>5.81</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>66</v>
       </c>
-      <c r="G64" s="3">
-        <v>1.6E-2</v>
-      </c>
-      <c r="H64" s="3">
-        <v>0.02</v>
-      </c>
-      <c r="I64" s="3">
-        <v>2.4E-2</v>
+      <c r="G64" s="5">
+        <f>E64*0.8</f>
+        <v>4.6479999999999997</v>
+      </c>
+      <c r="H64" s="5">
+        <f>E64</f>
+        <v>5.81</v>
+      </c>
+      <c r="I64" s="5">
+        <f>1.2*E64</f>
+        <v>6.9719999999999995</v>
       </c>
       <c r="J64" s="3"/>
       <c r="K64" s="3" t="s">
-        <v>84</v>
+        <v>159</v>
       </c>
       <c r="P64">
         <f>IF(E64=[1]Sheet1!E64,1,0)</f>
@@ -5420,7 +5423,7 @@
     </row>
     <row r="65" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A65" s="3" t="s">
-        <v>158</v>
+        <v>160</v>
       </c>
       <c r="B65" s="3" t="s">
         <v>178</v>
@@ -5429,29 +5432,29 @@
         <v>21</v>
       </c>
       <c r="D65" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E65" s="3">
-        <v>5.81</v>
+        <v>67</v>
+      </c>
+      <c r="E65" s="5">
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G65" s="5">
         <f>E65*0.8</f>
-        <v>4.6479999999999997</v>
+        <v>3.9999999999999998E-7</v>
       </c>
       <c r="H65" s="5">
         <f>E65</f>
-        <v>5.81</v>
+        <v>4.9999999999999998E-7</v>
       </c>
       <c r="I65" s="5">
         <f>1.2*E65</f>
-        <v>6.9719999999999995</v>
+        <v>5.9999999999999997E-7</v>
       </c>
       <c r="J65" s="3"/>
       <c r="K65" s="3" t="s">
-        <v>159</v>
+        <v>161</v>
       </c>
       <c r="P65">
         <f>IF(E65=[1]Sheet1!E65,1,0)</f>
@@ -5476,38 +5479,38 @@
     </row>
     <row r="66" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A66" s="3" t="s">
-        <v>160</v>
+        <v>162</v>
       </c>
       <c r="B66" s="3" t="s">
-        <v>178</v>
+        <v>179</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D66" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E66" s="5">
-        <v>4.9999999999999998E-7</v>
+        <v>65</v>
+      </c>
+      <c r="E66" s="3">
+        <v>4.8</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G66" s="5">
-        <f>E66*0.8</f>
-        <v>3.9999999999999998E-7</v>
+        <f t="shared" ref="G67:G74" si="2">E66*0.8</f>
+        <v>3.84</v>
       </c>
       <c r="H66" s="5">
-        <f>E66</f>
-        <v>4.9999999999999998E-7</v>
+        <f t="shared" ref="H67:H74" si="3">E66</f>
+        <v>4.8</v>
       </c>
       <c r="I66" s="5">
-        <f>1.2*E66</f>
-        <v>5.9999999999999997E-7</v>
+        <f t="shared" ref="I67:I74" si="4">1.2*E66</f>
+        <v>5.76</v>
       </c>
       <c r="J66" s="3"/>
       <c r="K66" s="3" t="s">
-        <v>161</v>
+        <v>163</v>
       </c>
       <c r="P66">
         <f>IF(E66=[1]Sheet1!E66,1,0)</f>
@@ -5532,7 +5535,7 @@
     </row>
     <row r="67" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A67" s="3" t="s">
-        <v>162</v>
+        <v>164</v>
       </c>
       <c r="B67" s="3" t="s">
         <v>179</v>
@@ -5541,29 +5544,29 @@
         <v>21</v>
       </c>
       <c r="D67" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E67" s="3">
-        <v>4.8</v>
+        <v>67</v>
+      </c>
+      <c r="E67" s="5">
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G67" s="5">
-        <f t="shared" ref="G68:G75" si="2">E67*0.8</f>
-        <v>3.84</v>
+        <f t="shared" si="2"/>
+        <v>2.1120000000000004E-4</v>
       </c>
       <c r="H67" s="5">
-        <f t="shared" ref="H68:H75" si="3">E67</f>
-        <v>4.8</v>
+        <f t="shared" si="3"/>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="I67" s="5">
-        <f t="shared" ref="I68:I75" si="4">1.2*E67</f>
-        <v>5.76</v>
+        <f t="shared" si="4"/>
+        <v>3.168E-4</v>
       </c>
       <c r="J67" s="3"/>
       <c r="K67" s="3" t="s">
-        <v>163</v>
+        <v>165</v>
       </c>
       <c r="P67">
         <f>IF(E67=[1]Sheet1!E67,1,0)</f>
@@ -5588,38 +5591,38 @@
     </row>
     <row r="68" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A68" s="3" t="s">
-        <v>164</v>
+        <v>166</v>
       </c>
       <c r="B68" s="3" t="s">
-        <v>179</v>
+        <v>180</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D68" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E68" s="5">
-        <v>2.6400000000000002E-4</v>
+        <v>65</v>
+      </c>
+      <c r="E68" s="3">
+        <v>4.8</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G68" s="5">
         <f t="shared" si="2"/>
-        <v>2.1120000000000004E-4</v>
+        <v>3.84</v>
       </c>
       <c r="H68" s="5">
         <f t="shared" si="3"/>
-        <v>2.6400000000000002E-4</v>
+        <v>4.8</v>
       </c>
       <c r="I68" s="5">
         <f t="shared" si="4"/>
-        <v>3.168E-4</v>
+        <v>5.76</v>
       </c>
       <c r="J68" s="3"/>
       <c r="K68" s="3" t="s">
-        <v>165</v>
+        <v>167</v>
       </c>
       <c r="P68">
         <f>IF(E68=[1]Sheet1!E68,1,0)</f>
@@ -5644,7 +5647,7 @@
     </row>
     <row r="69" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A69" s="3" t="s">
-        <v>166</v>
+        <v>168</v>
       </c>
       <c r="B69" s="3" t="s">
         <v>180</v>
@@ -5653,29 +5656,29 @@
         <v>21</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>65</v>
-      </c>
-      <c r="E69" s="3">
-        <v>4.8</v>
+        <v>67</v>
+      </c>
+      <c r="E69" s="5">
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G69" s="5">
         <f t="shared" si="2"/>
-        <v>3.84</v>
+        <v>2.1120000000000004E-4</v>
       </c>
       <c r="H69" s="5">
         <f t="shared" si="3"/>
-        <v>4.8</v>
+        <v>2.6400000000000002E-4</v>
       </c>
       <c r="I69" s="5">
         <f t="shared" si="4"/>
-        <v>5.76</v>
+        <v>3.168E-4</v>
       </c>
       <c r="J69" s="3"/>
       <c r="K69" s="3" t="s">
-        <v>167</v>
+        <v>169</v>
       </c>
       <c r="P69">
         <f>IF(E69=[1]Sheet1!E69,1,0)</f>
@@ -5700,38 +5703,38 @@
     </row>
     <row r="70" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A70" s="3" t="s">
-        <v>168</v>
+        <v>170</v>
       </c>
       <c r="B70" s="3" t="s">
-        <v>180</v>
+        <v>181</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>21</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E70" s="5">
-        <v>2.6400000000000002E-4</v>
+        <v>65</v>
+      </c>
+      <c r="E70" s="3">
+        <v>2.82</v>
       </c>
       <c r="F70" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G70" s="5">
         <f t="shared" si="2"/>
-        <v>2.1120000000000004E-4</v>
+        <v>2.2559999999999998</v>
       </c>
       <c r="H70" s="5">
         <f t="shared" si="3"/>
-        <v>2.6400000000000002E-4</v>
+        <v>2.82</v>
       </c>
       <c r="I70" s="5">
         <f t="shared" si="4"/>
-        <v>3.168E-4</v>
+        <v>3.3839999999999999</v>
       </c>
       <c r="J70" s="3"/>
       <c r="K70" s="3" t="s">
-        <v>169</v>
+        <v>171</v>
       </c>
       <c r="P70">
         <f>IF(E70=[1]Sheet1!E70,1,0)</f>
@@ -5756,7 +5759,7 @@
     </row>
     <row r="71" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A71" s="3" t="s">
-        <v>170</v>
+        <v>172</v>
       </c>
       <c r="B71" s="3" t="s">
         <v>181</v>
@@ -5768,26 +5771,26 @@
         <v>65</v>
       </c>
       <c r="E71" s="3">
-        <v>2.82</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="F71" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G71" s="5">
         <f t="shared" si="2"/>
-        <v>2.2559999999999998</v>
+        <v>1.0000000000000002E-2</v>
       </c>
       <c r="H71" s="5">
         <f t="shared" si="3"/>
-        <v>2.82</v>
+        <v>1.2500000000000001E-2</v>
       </c>
       <c r="I71" s="5">
         <f t="shared" si="4"/>
-        <v>3.3839999999999999</v>
+        <v>1.4999999999999999E-2</v>
       </c>
       <c r="J71" s="3"/>
       <c r="K71" s="3" t="s">
-        <v>171</v>
+        <v>173</v>
       </c>
       <c r="P71">
         <f>IF(E71=[1]Sheet1!E71,1,0)</f>
@@ -5812,7 +5815,7 @@
     </row>
     <row r="72" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A72" s="3" t="s">
-        <v>172</v>
+        <v>174</v>
       </c>
       <c r="B72" s="3" t="s">
         <v>181</v>
@@ -5821,29 +5824,29 @@
         <v>21</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="E72" s="3">
-        <v>1.2500000000000001E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="F72" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G72" s="5">
         <f t="shared" si="2"/>
-        <v>1.0000000000000002E-2</v>
+        <v>2.7200000000000002E-2</v>
       </c>
       <c r="H72" s="5">
         <f t="shared" si="3"/>
-        <v>1.2500000000000001E-2</v>
+        <v>3.4000000000000002E-2</v>
       </c>
       <c r="I72" s="5">
         <f t="shared" si="4"/>
-        <v>1.4999999999999999E-2</v>
+        <v>4.0800000000000003E-2</v>
       </c>
       <c r="J72" s="3"/>
       <c r="K72" s="3" t="s">
-        <v>173</v>
+        <v>175</v>
       </c>
       <c r="P72">
         <f>IF(E72=[1]Sheet1!E72,1,0)</f>
@@ -5868,7 +5871,7 @@
     </row>
     <row r="73" spans="1:20" x14ac:dyDescent="0.35">
       <c r="A73" s="3" t="s">
-        <v>174</v>
+        <v>176</v>
       </c>
       <c r="B73" s="3" t="s">
         <v>181</v>
@@ -5880,26 +5883,26 @@
         <v>67</v>
       </c>
       <c r="E73" s="3">
-        <v>3.4000000000000002E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="F73" s="3" t="s">
         <v>66</v>
       </c>
       <c r="G73" s="5">
         <f t="shared" si="2"/>
-        <v>2.7200000000000002E-2</v>
+        <v>4.5600000000000002E-2</v>
       </c>
       <c r="H73" s="5">
         <f t="shared" si="3"/>
-        <v>3.4000000000000002E-2</v>
+        <v>5.7000000000000002E-2</v>
       </c>
       <c r="I73" s="5">
         <f t="shared" si="4"/>
-        <v>4.0800000000000003E-2</v>
+        <v>6.8400000000000002E-2</v>
       </c>
       <c r="J73" s="3"/>
       <c r="K73" s="3" t="s">
-        <v>175</v>
+        <v>177</v>
       </c>
       <c r="P73">
         <f>IF(E73=[1]Sheet1!E73,1,0)</f>
@@ -5919,62 +5922,6 @@
       </c>
       <c r="T73">
         <f>IF(I73=[1]Sheet1!I73,1,0)</f>
-        <v>0</v>
-      </c>
-    </row>
-    <row r="74" spans="1:20" x14ac:dyDescent="0.35">
-      <c r="A74" s="3" t="s">
-        <v>176</v>
-      </c>
-      <c r="B74" s="3" t="s">
-        <v>181</v>
-      </c>
-      <c r="C74" s="3" t="s">
-        <v>21</v>
-      </c>
-      <c r="D74" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="E74" s="3">
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>66</v>
-      </c>
-      <c r="G74" s="5">
-        <f t="shared" si="2"/>
-        <v>4.5600000000000002E-2</v>
-      </c>
-      <c r="H74" s="5">
-        <f t="shared" si="3"/>
-        <v>5.7000000000000002E-2</v>
-      </c>
-      <c r="I74" s="5">
-        <f t="shared" si="4"/>
-        <v>6.8400000000000002E-2</v>
-      </c>
-      <c r="J74" s="3"/>
-      <c r="K74" s="3" t="s">
-        <v>177</v>
-      </c>
-      <c r="P74">
-        <f>IF(E74=[1]Sheet1!E74,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="Q74">
-        <f>IF(F74=[1]Sheet1!F74,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="R74">
-        <f>IF(G74=[1]Sheet1!G74,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="S74">
-        <f>IF(H74=[1]Sheet1!H74,1,0)</f>
-        <v>0</v>
-      </c>
-      <c r="T74">
-        <f>IF(I74=[1]Sheet1!I74,1,0)</f>
         <v>0</v>
       </c>
     </row>

--- a/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
+++ b/biorefineries/isobutanol/analyses/full/parameter_distributions/parameter-distributions_corn_IBO_EtOH_B.xlsx
@@ -435,7 +435,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K83"/>
+  <dimension ref="A1:K76"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="40.81640625" customWidth="1" min="1" max="1"/>
@@ -1880,7 +1880,7 @@
     <row r="32">
       <c r="A32" s="3" t="inlineStr">
         <is>
-          <t>K_2</t>
+          <t>K_2i</t>
         </is>
       </c>
       <c r="B32" s="3" t="inlineStr">
@@ -1898,39 +1898,39 @@
           <t>g_per_l</t>
         </is>
       </c>
-      <c r="E32" s="5" t="n">
-        <v>2e-05</v>
+      <c r="E32" s="3" t="n">
+        <v>0.101</v>
       </c>
       <c r="F32" s="3" t="inlineStr">
         <is>
           <t>triangular</t>
         </is>
       </c>
-      <c r="G32" s="5" t="n">
-        <v>1.6e-05</v>
-      </c>
-      <c r="H32" s="5" t="n">
-        <v>2e-05</v>
-      </c>
-      <c r="I32" s="5" t="n">
-        <v>2.4e-05</v>
+      <c r="G32" s="3" t="n">
+        <v>0.08080000000000001</v>
+      </c>
+      <c r="H32" s="3" t="n">
+        <v>0.101</v>
+      </c>
+      <c r="I32" s="3" t="n">
+        <v>0.1212</v>
       </c>
       <c r="J32" s="3" t="n"/>
       <c r="K32" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.K_2 = x</t>
+          <t>V406.nsk_kinetic_model._te.K_2i = x</t>
         </is>
       </c>
     </row>
     <row r="33">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>K_2i</t>
+          <t>._k_3</t>
         </is>
       </c>
       <c r="B33" s="3" t="inlineStr">
         <is>
-          <t>Kinetics: TCA Cycle</t>
+          <t>Kinetics: Pyruvate-to-Acetaldehyde</t>
         </is>
       </c>
       <c r="C33" s="3" t="inlineStr">
@@ -1940,11 +1940,11 @@
       </c>
       <c r="D33" s="3" t="inlineStr">
         <is>
-          <t>g_per_l</t>
+          <t>g_per_l_per_h</t>
         </is>
       </c>
       <c r="E33" s="3" t="n">
-        <v>0.101</v>
+        <v>5.81</v>
       </c>
       <c r="F33" s="3" t="inlineStr">
         <is>
@@ -1952,25 +1952,25 @@
         </is>
       </c>
       <c r="G33" s="3" t="n">
-        <v>0.08080000000000001</v>
+        <v>4.648</v>
       </c>
       <c r="H33" s="3" t="n">
-        <v>0.101</v>
+        <v>5.81</v>
       </c>
       <c r="I33" s="3" t="n">
-        <v>0.1212</v>
+        <v>6.972</v>
       </c>
       <c r="J33" s="3" t="n"/>
       <c r="K33" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.K_2i = x</t>
+          <t>V406.nsk_kinetic_model._te.k_3 = x</t>
         </is>
       </c>
     </row>
     <row r="34">
       <c r="A34" s="3" t="inlineStr">
         <is>
-          <t>._k_3</t>
+          <t>K_3</t>
         </is>
       </c>
       <c r="B34" s="3" t="inlineStr">
@@ -1985,42 +1985,42 @@
       </c>
       <c r="D34" s="3" t="inlineStr">
         <is>
-          <t>g_per_l_per_h</t>
-        </is>
-      </c>
-      <c r="E34" s="3" t="n">
-        <v>5.81</v>
+          <t>g_per_l</t>
+        </is>
+      </c>
+      <c r="E34" s="5" t="n">
+        <v>5e-07</v>
       </c>
       <c r="F34" s="3" t="inlineStr">
         <is>
           <t>triangular</t>
         </is>
       </c>
-      <c r="G34" s="3" t="n">
-        <v>4.648</v>
-      </c>
-      <c r="H34" s="3" t="n">
-        <v>5.81</v>
-      </c>
-      <c r="I34" s="3" t="n">
-        <v>6.972</v>
+      <c r="G34" s="5" t="n">
+        <v>4e-07</v>
+      </c>
+      <c r="H34" s="5" t="n">
+        <v>5e-07</v>
+      </c>
+      <c r="I34" s="5" t="n">
+        <v>6e-07</v>
       </c>
       <c r="J34" s="3" t="n"/>
       <c r="K34" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_3 = x</t>
+          <t>V406.nsk_kinetic_model._te.K_3 = x</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="3" t="inlineStr">
         <is>
-          <t>K_3</t>
+          <t>._k_4</t>
         </is>
       </c>
       <c r="B35" s="3" t="inlineStr">
         <is>
-          <t>Kinetics: Pyruvate-to-Acetaldehyde</t>
+          <t>Kinetics: Acetaldehyde-to-Acetate</t>
         </is>
       </c>
       <c r="C35" s="3" t="inlineStr">
@@ -2030,37 +2030,37 @@
       </c>
       <c r="D35" s="3" t="inlineStr">
         <is>
-          <t>g_per_l</t>
-        </is>
-      </c>
-      <c r="E35" s="5" t="n">
-        <v>5e-07</v>
+          <t>g_per_l_per_h</t>
+        </is>
+      </c>
+      <c r="E35" s="3" t="n">
+        <v>4.8</v>
       </c>
       <c r="F35" s="3" t="inlineStr">
         <is>
           <t>triangular</t>
         </is>
       </c>
-      <c r="G35" s="5" t="n">
-        <v>4e-07</v>
-      </c>
-      <c r="H35" s="5" t="n">
-        <v>5e-07</v>
-      </c>
-      <c r="I35" s="5" t="n">
-        <v>6e-07</v>
+      <c r="G35" s="3" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="H35" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I35" s="3" t="n">
+        <v>5.76</v>
       </c>
       <c r="J35" s="3" t="n"/>
       <c r="K35" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.K_3 = x</t>
+          <t>V406.nsk_kinetic_model._te.k_4 = x</t>
         </is>
       </c>
     </row>
     <row r="36">
       <c r="A36" s="3" t="inlineStr">
         <is>
-          <t>._k_4</t>
+          <t>._k_4ie</t>
         </is>
       </c>
       <c r="B36" s="3" t="inlineStr">
@@ -2079,7 +2079,7 @@
         </is>
       </c>
       <c r="E36" s="3" t="n">
-        <v>4.8</v>
+        <v>0.04</v>
       </c>
       <c r="F36" s="3" t="inlineStr">
         <is>
@@ -2087,25 +2087,25 @@
         </is>
       </c>
       <c r="G36" s="3" t="n">
-        <v>3.84</v>
+        <v>0.032</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>4.8</v>
+        <v>0.04</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>5.76</v>
+        <v>0.048</v>
       </c>
       <c r="J36" s="3" t="n"/>
       <c r="K36" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_4 = x</t>
+          <t>V406.nsk_kinetic_model._te.k_4ie = x</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="3" t="inlineStr">
         <is>
-          <t>._k_4ie</t>
+          <t>._k_4ia</t>
         </is>
       </c>
       <c r="B37" s="3" t="inlineStr">
@@ -2124,7 +2124,7 @@
         </is>
       </c>
       <c r="E37" s="3" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="F37" s="3" t="inlineStr">
         <is>
@@ -2132,25 +2132,25 @@
         </is>
       </c>
       <c r="G37" s="3" t="n">
-        <v>0.032</v>
+        <v>0.096</v>
       </c>
       <c r="H37" s="3" t="n">
-        <v>0.04</v>
+        <v>0.12</v>
       </c>
       <c r="I37" s="3" t="n">
-        <v>0.048</v>
+        <v>0.144</v>
       </c>
       <c r="J37" s="3" t="n"/>
       <c r="K37" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_4ie = x</t>
+          <t>V406.nsk_kinetic_model._te.k_4ia = x</t>
         </is>
       </c>
     </row>
     <row r="38">
       <c r="A38" s="3" t="inlineStr">
         <is>
-          <t>._k_4ia</t>
+          <t>._k_4ii</t>
         </is>
       </c>
       <c r="B38" s="3" t="inlineStr">
@@ -2169,33 +2169,33 @@
         </is>
       </c>
       <c r="E38" s="3" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F38" s="3" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G38" s="3" t="n">
         <v>0.12</v>
       </c>
-      <c r="F38" s="3" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G38" s="3" t="n">
-        <v>0.096</v>
-      </c>
       <c r="H38" s="3" t="n">
-        <v>0.12</v>
+        <v>0.15</v>
       </c>
       <c r="I38" s="3" t="n">
-        <v>0.144</v>
+        <v>0.18</v>
       </c>
       <c r="J38" s="3" t="n"/>
       <c r="K38" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_4ia = x</t>
+          <t>V406.nsk_kinetic_model._te.k_4ii = x</t>
         </is>
       </c>
     </row>
     <row r="39">
       <c r="A39" s="3" t="inlineStr">
         <is>
-          <t>._k_4ii</t>
+          <t>K_4</t>
         </is>
       </c>
       <c r="B39" s="3" t="inlineStr">
@@ -2210,11 +2210,11 @@
       </c>
       <c r="D39" s="3" t="inlineStr">
         <is>
-          <t>g_per_l_per_h</t>
+          <t>g_per_l</t>
         </is>
       </c>
       <c r="E39" s="3" t="n">
-        <v>0.15</v>
+        <v>0.000264</v>
       </c>
       <c r="F39" s="3" t="inlineStr">
         <is>
@@ -2222,30 +2222,30 @@
         </is>
       </c>
       <c r="G39" s="3" t="n">
-        <v>0.12</v>
+        <v>0.0002112</v>
       </c>
       <c r="H39" s="3" t="n">
-        <v>0.15</v>
+        <v>0.000264</v>
       </c>
       <c r="I39" s="3" t="n">
-        <v>0.18</v>
+        <v>0.0003168</v>
       </c>
       <c r="J39" s="3" t="n"/>
       <c r="K39" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_4ii = x</t>
+          <t>V406.nsk_kinetic_model._te.K_4 = x</t>
         </is>
       </c>
     </row>
     <row r="40">
       <c r="A40" s="3" t="inlineStr">
         <is>
-          <t>K_4</t>
+          <t>._k_5</t>
         </is>
       </c>
       <c r="B40" s="3" t="inlineStr">
         <is>
-          <t>Kinetics: Acetaldehyde-to-Acetate</t>
+          <t>Kinetics: Acetate respiration</t>
         </is>
       </c>
       <c r="C40" s="3" t="inlineStr">
@@ -2255,11 +2255,11 @@
       </c>
       <c r="D40" s="3" t="inlineStr">
         <is>
-          <t>g_per_l</t>
+          <t>g_per_l_per_h</t>
         </is>
       </c>
       <c r="E40" s="3" t="n">
-        <v>0.000264</v>
+        <v>0.0104</v>
       </c>
       <c r="F40" s="3" t="inlineStr">
         <is>
@@ -2267,25 +2267,25 @@
         </is>
       </c>
       <c r="G40" s="3" t="n">
-        <v>0.0002112</v>
+        <v>0.008319999999999999</v>
       </c>
       <c r="H40" s="3" t="n">
-        <v>0.000264</v>
+        <v>0.0104</v>
       </c>
       <c r="I40" s="3" t="n">
-        <v>0.0003168</v>
+        <v>0.01248</v>
       </c>
       <c r="J40" s="3" t="n"/>
       <c r="K40" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.K_4 = x</t>
+          <t>V406.nsk_kinetic_model._te.k_5 = x</t>
         </is>
       </c>
     </row>
     <row r="41">
       <c r="A41" s="3" t="inlineStr">
         <is>
-          <t>._k_5</t>
+          <t>K_5</t>
         </is>
       </c>
       <c r="B41" s="3" t="inlineStr">
@@ -2300,11 +2300,11 @@
       </c>
       <c r="D41" s="3" t="inlineStr">
         <is>
-          <t>g_per_l_per_h</t>
+          <t>g_per_l</t>
         </is>
       </c>
       <c r="E41" s="3" t="n">
-        <v>0.0104</v>
+        <v>0.0102</v>
       </c>
       <c r="F41" s="3" t="inlineStr">
         <is>
@@ -2312,25 +2312,25 @@
         </is>
       </c>
       <c r="G41" s="3" t="n">
-        <v>0.008319999999999999</v>
+        <v>0.008160000000000001</v>
       </c>
       <c r="H41" s="3" t="n">
-        <v>0.0104</v>
+        <v>0.0102</v>
       </c>
       <c r="I41" s="3" t="n">
-        <v>0.01248</v>
+        <v>0.01224</v>
       </c>
       <c r="J41" s="3" t="n"/>
       <c r="K41" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_5 = x</t>
+          <t>V406.nsk_kinetic_model._te.K_5 = x</t>
         </is>
       </c>
     </row>
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>K_5</t>
+          <t>._k_5e</t>
         </is>
       </c>
       <c r="B42" s="3" t="inlineStr">
@@ -2345,11 +2345,11 @@
       </c>
       <c r="D42" s="3" t="inlineStr">
         <is>
-          <t>g_per_l</t>
+          <t>g_per_l_per_h</t>
         </is>
       </c>
       <c r="E42" s="3" t="n">
-        <v>0.0102</v>
+        <v>0.775</v>
       </c>
       <c r="F42" s="3" t="inlineStr">
         <is>
@@ -2357,25 +2357,25 @@
         </is>
       </c>
       <c r="G42" s="3" t="n">
-        <v>0.008160000000000001</v>
+        <v>0.6200000000000001</v>
       </c>
       <c r="H42" s="3" t="n">
-        <v>0.0102</v>
+        <v>0.775</v>
       </c>
       <c r="I42" s="3" t="n">
-        <v>0.01224</v>
+        <v>0.9299999999999999</v>
       </c>
       <c r="J42" s="3" t="n"/>
       <c r="K42" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.K_5 = x</t>
+          <t>V406.nsk_kinetic_model._te.k_5e = x</t>
         </is>
       </c>
     </row>
     <row r="43">
       <c r="A43" s="3" t="inlineStr">
         <is>
-          <t>._k_5e</t>
+          <t>K_5e</t>
         </is>
       </c>
       <c r="B43" s="3" t="inlineStr">
@@ -2390,11 +2390,11 @@
       </c>
       <c r="D43" s="3" t="inlineStr">
         <is>
-          <t>g_per_l_per_h</t>
+          <t>g_per_l</t>
         </is>
       </c>
       <c r="E43" s="3" t="n">
-        <v>0.775</v>
+        <v>0.1</v>
       </c>
       <c r="F43" s="3" t="inlineStr">
         <is>
@@ -2402,25 +2402,25 @@
         </is>
       </c>
       <c r="G43" s="3" t="n">
-        <v>0.6200000000000001</v>
+        <v>0.08000000000000002</v>
       </c>
       <c r="H43" s="3" t="n">
-        <v>0.775</v>
+        <v>0.1</v>
       </c>
       <c r="I43" s="3" t="n">
-        <v>0.9299999999999999</v>
+        <v>0.12</v>
       </c>
       <c r="J43" s="3" t="n"/>
       <c r="K43" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_5e = x</t>
+          <t>V406.nsk_kinetic_model._te.K_5e = x</t>
         </is>
       </c>
     </row>
     <row r="44">
       <c r="A44" s="3" t="inlineStr">
         <is>
-          <t>K_5e</t>
+          <t>K_5i</t>
         </is>
       </c>
       <c r="B44" s="3" t="inlineStr">
@@ -2439,7 +2439,7 @@
         </is>
       </c>
       <c r="E44" s="3" t="n">
-        <v>0.1</v>
+        <v>440</v>
       </c>
       <c r="F44" s="3" t="inlineStr">
         <is>
@@ -2447,30 +2447,30 @@
         </is>
       </c>
       <c r="G44" s="3" t="n">
-        <v>0.08000000000000002</v>
+        <v>352</v>
       </c>
       <c r="H44" s="3" t="n">
-        <v>0.1</v>
+        <v>440</v>
       </c>
       <c r="I44" s="3" t="n">
-        <v>0.12</v>
+        <v>528</v>
       </c>
       <c r="J44" s="3" t="n"/>
       <c r="K44" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.K_5e = x</t>
+          <t>V406.nsk_kinetic_model._te.K_5i = x</t>
         </is>
       </c>
     </row>
     <row r="45">
       <c r="A45" s="3" t="inlineStr">
         <is>
-          <t>K_5i</t>
+          <t>._k_6</t>
         </is>
       </c>
       <c r="B45" s="3" t="inlineStr">
         <is>
-          <t>Kinetics: Acetate respiration</t>
+          <t>Kinetics: Acetaldyhede-to-Ethanol</t>
         </is>
       </c>
       <c r="C45" s="3" t="inlineStr">
@@ -2480,11 +2480,11 @@
       </c>
       <c r="D45" s="3" t="inlineStr">
         <is>
-          <t>g_per_l</t>
+          <t>g_per_l_per_h</t>
         </is>
       </c>
       <c r="E45" s="3" t="n">
-        <v>440</v>
+        <v>2.82</v>
       </c>
       <c r="F45" s="3" t="inlineStr">
         <is>
@@ -2492,25 +2492,25 @@
         </is>
       </c>
       <c r="G45" s="3" t="n">
-        <v>352</v>
+        <v>2.256</v>
       </c>
       <c r="H45" s="3" t="n">
-        <v>440</v>
+        <v>2.82</v>
       </c>
       <c r="I45" s="3" t="n">
-        <v>528</v>
+        <v>3.384</v>
       </c>
       <c r="J45" s="3" t="n"/>
       <c r="K45" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.K_5i = x</t>
+          <t>V406.nsk_kinetic_model._te.k_6 = x</t>
         </is>
       </c>
     </row>
     <row r="46">
       <c r="A46" s="3" t="inlineStr">
         <is>
-          <t>._k_6</t>
+          <t>K_6</t>
         </is>
       </c>
       <c r="B46" s="3" t="inlineStr">
@@ -2525,11 +2525,11 @@
       </c>
       <c r="D46" s="3" t="inlineStr">
         <is>
-          <t>g_per_l_per_h</t>
+          <t>g_per_l</t>
         </is>
       </c>
       <c r="E46" s="3" t="n">
-        <v>2.82</v>
+        <v>0.034</v>
       </c>
       <c r="F46" s="3" t="inlineStr">
         <is>
@@ -2537,25 +2537,25 @@
         </is>
       </c>
       <c r="G46" s="3" t="n">
-        <v>2.256</v>
+        <v>0.0272</v>
       </c>
       <c r="H46" s="3" t="n">
-        <v>2.82</v>
+        <v>0.034</v>
       </c>
       <c r="I46" s="3" t="n">
-        <v>3.384</v>
+        <v>0.0408</v>
       </c>
       <c r="J46" s="3" t="n"/>
       <c r="K46" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_6 = x</t>
+          <t>V406.nsk_kinetic_model._te.K_6 = x</t>
         </is>
       </c>
     </row>
     <row r="47">
       <c r="A47" s="3" t="inlineStr">
         <is>
-          <t>._k_6r</t>
+          <t>K_6e</t>
         </is>
       </c>
       <c r="B47" s="3" t="inlineStr">
@@ -2570,11 +2570,11 @@
       </c>
       <c r="D47" s="3" t="inlineStr">
         <is>
-          <t>g_per_l_per_h</t>
+          <t>g_per_l</t>
         </is>
       </c>
       <c r="E47" s="3" t="n">
-        <v>0.0125</v>
+        <v>0.057</v>
       </c>
       <c r="F47" s="3" t="inlineStr">
         <is>
@@ -2582,203 +2582,203 @@
         </is>
       </c>
       <c r="G47" s="3" t="n">
-        <v>0.01</v>
+        <v>0.0456</v>
       </c>
       <c r="H47" s="3" t="n">
-        <v>0.0125</v>
+        <v>0.057</v>
       </c>
       <c r="I47" s="3" t="n">
-        <v>0.015</v>
+        <v>0.0684</v>
       </c>
       <c r="J47" s="3" t="n"/>
       <c r="K47" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_6r = x</t>
+          <t>V406.nsk_kinetic_model._te.K_6e = x</t>
         </is>
       </c>
     </row>
     <row r="48">
-      <c r="A48" s="3" t="inlineStr">
-        <is>
-          <t>K_6</t>
-        </is>
-      </c>
-      <c r="B48" s="3" t="inlineStr">
+      <c r="A48" t="inlineStr">
+        <is>
+          <t>._k_6ia</t>
+        </is>
+      </c>
+      <c r="B48" t="inlineStr">
         <is>
           <t>Kinetics: Acetaldyhede-to-Ethanol</t>
         </is>
       </c>
-      <c r="C48" s="3" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D48" s="3" t="inlineStr">
-        <is>
-          <t>g_per_l</t>
-        </is>
-      </c>
-      <c r="E48" s="3" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="F48" s="3" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G48" s="3" t="n">
-        <v>0.0272</v>
-      </c>
-      <c r="H48" s="3" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="I48" s="3" t="n">
-        <v>0.0408</v>
-      </c>
-      <c r="J48" s="3" t="n"/>
-      <c r="K48" s="3" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.K_6 = x</t>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>g_per_l_per_h</t>
+        </is>
+      </c>
+      <c r="E48" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F48" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G48" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="H48" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I48" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.k_6ia = x</t>
         </is>
       </c>
     </row>
     <row r="49">
-      <c r="A49" s="3" t="inlineStr">
-        <is>
-          <t>K_6e</t>
-        </is>
-      </c>
-      <c r="B49" s="3" t="inlineStr">
+      <c r="A49" t="inlineStr">
+        <is>
+          <t>._k_6ii</t>
+        </is>
+      </c>
+      <c r="B49" t="inlineStr">
         <is>
           <t>Kinetics: Acetaldyhede-to-Ethanol</t>
         </is>
       </c>
-      <c r="C49" s="3" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D49" s="3" t="inlineStr">
-        <is>
-          <t>g_per_l</t>
-        </is>
-      </c>
-      <c r="E49" s="3" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="F49" s="3" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G49" s="3" t="n">
-        <v>0.0456</v>
-      </c>
-      <c r="H49" s="3" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="I49" s="3" t="n">
-        <v>0.0684</v>
-      </c>
-      <c r="J49" s="3" t="n"/>
-      <c r="K49" s="3" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.K_6e = x</t>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>g_per_l_per_h</t>
+        </is>
+      </c>
+      <c r="E49" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="F49" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G49" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="H49" t="n">
+        <v>0.075</v>
+      </c>
+      <c r="I49" t="n">
+        <v>0.09</v>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.k_6ii = x</t>
         </is>
       </c>
     </row>
     <row r="50">
-      <c r="A50" t="inlineStr">
-        <is>
-          <t>._k_6ia</t>
-        </is>
-      </c>
-      <c r="B50" t="inlineStr">
-        <is>
-          <t>Kinetics: Acetaldyhede-to-Ethanol</t>
-        </is>
-      </c>
-      <c r="C50" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D50" t="inlineStr">
+      <c r="A50" s="3" t="inlineStr">
+        <is>
+          <t>._k_7</t>
+        </is>
+      </c>
+      <c r="B50" s="3" t="inlineStr">
+        <is>
+          <t>Kinetics: Glucose-to-Biomass</t>
+        </is>
+      </c>
+      <c r="C50" s="3" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D50" s="3" t="inlineStr">
         <is>
           <t>g_per_l_per_h</t>
         </is>
       </c>
-      <c r="E50" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G50" t="n">
+      <c r="E50" s="3" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="F50" s="3" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G50" s="3" t="n">
+        <v>0.9624000000000001</v>
+      </c>
+      <c r="H50" s="3" t="n">
+        <v>1.203</v>
+      </c>
+      <c r="I50" s="3" t="n">
+        <v>1.4436</v>
+      </c>
+      <c r="J50" s="3" t="n"/>
+      <c r="K50" s="3" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.k_7 = x</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" s="3" t="inlineStr">
+        <is>
+          <t>._k_7ie</t>
+        </is>
+      </c>
+      <c r="B51" s="3" t="inlineStr">
+        <is>
+          <t>Kinetics: Glucose-to-Biomass</t>
+        </is>
+      </c>
+      <c r="C51" s="3" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D51" s="3" t="inlineStr">
+        <is>
+          <t>g_per_l_per_h</t>
+        </is>
+      </c>
+      <c r="E51" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F51" s="3" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G51" s="3" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="H51" s="3" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I51" s="3" t="n">
         <v>0.048</v>
       </c>
-      <c r="H50" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I50" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="K50" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.k_6ia = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="inlineStr">
-        <is>
-          <t>._k_6ii</t>
-        </is>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>Kinetics: Acetaldyhede-to-Ethanol</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>g_per_l_per_h</t>
-        </is>
-      </c>
-      <c r="E51" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="F51" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G51" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="H51" t="n">
-        <v>0.075</v>
-      </c>
-      <c r="I51" t="n">
-        <v>0.09</v>
-      </c>
-      <c r="K51" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.k_6ii = x</t>
+      <c r="J51" s="3" t="n"/>
+      <c r="K51" s="3" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.k_7ie = x</t>
         </is>
       </c>
     </row>
     <row r="52">
       <c r="A52" s="3" t="inlineStr">
         <is>
-          <t>._k_7</t>
+          <t>._k_7ia</t>
         </is>
       </c>
       <c r="B52" s="3" t="inlineStr">
@@ -2797,7 +2797,7 @@
         </is>
       </c>
       <c r="E52" s="3" t="n">
-        <v>1.203</v>
+        <v>0.12</v>
       </c>
       <c r="F52" s="3" t="inlineStr">
         <is>
@@ -2805,25 +2805,25 @@
         </is>
       </c>
       <c r="G52" s="3" t="n">
-        <v>0.9624000000000001</v>
+        <v>0.096</v>
       </c>
       <c r="H52" s="3" t="n">
-        <v>1.203</v>
+        <v>0.12</v>
       </c>
       <c r="I52" s="3" t="n">
-        <v>1.4436</v>
+        <v>0.144</v>
       </c>
       <c r="J52" s="3" t="n"/>
       <c r="K52" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_7 = x</t>
+          <t>V406.nsk_kinetic_model._te.k_7ia = x</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" s="3" t="inlineStr">
         <is>
-          <t>._k_7ie</t>
+          <t>._k_7ii</t>
         </is>
       </c>
       <c r="B53" s="3" t="inlineStr">
@@ -2842,7 +2842,7 @@
         </is>
       </c>
       <c r="E53" s="3" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="F53" s="3" t="inlineStr">
         <is>
@@ -2850,25 +2850,25 @@
         </is>
       </c>
       <c r="G53" s="3" t="n">
-        <v>0.032</v>
+        <v>0.12</v>
       </c>
       <c r="H53" s="3" t="n">
-        <v>0.04</v>
+        <v>0.15</v>
       </c>
       <c r="I53" s="3" t="n">
-        <v>0.048</v>
+        <v>0.18</v>
       </c>
       <c r="J53" s="3" t="n"/>
       <c r="K53" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_7ie = x</t>
+          <t>V406.nsk_kinetic_model._te.k_7ii = x</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" s="3" t="inlineStr">
         <is>
-          <t>._k_7ia</t>
+          <t>K_7</t>
         </is>
       </c>
       <c r="B54" s="3" t="inlineStr">
@@ -2883,11 +2883,11 @@
       </c>
       <c r="D54" s="3" t="inlineStr">
         <is>
-          <t>g_per_l_per_h</t>
+          <t>g_per_l</t>
         </is>
       </c>
       <c r="E54" s="3" t="n">
-        <v>0.12</v>
+        <v>0.0101</v>
       </c>
       <c r="F54" s="3" t="inlineStr">
         <is>
@@ -2895,30 +2895,30 @@
         </is>
       </c>
       <c r="G54" s="3" t="n">
-        <v>0.096</v>
+        <v>0.00808</v>
       </c>
       <c r="H54" s="3" t="n">
-        <v>0.12</v>
+        <v>0.0101</v>
       </c>
       <c r="I54" s="3" t="n">
-        <v>0.144</v>
+        <v>0.01212</v>
       </c>
       <c r="J54" s="3" t="n"/>
       <c r="K54" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_7ia = x</t>
+          <t>V406.nsk_kinetic_model._te.K_7 = x</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" s="3" t="inlineStr">
         <is>
-          <t>._k_7ii</t>
+          <t>._k_8</t>
         </is>
       </c>
       <c r="B55" s="3" t="inlineStr">
         <is>
-          <t>Kinetics: Glucose-to-Biomass</t>
+          <t>Kinetics: Acetate-to-Biomass</t>
         </is>
       </c>
       <c r="C55" s="3" t="inlineStr">
@@ -2932,7 +2932,7 @@
         </is>
       </c>
       <c r="E55" s="3" t="n">
-        <v>0.15</v>
+        <v>0.589</v>
       </c>
       <c r="F55" s="3" t="inlineStr">
         <is>
@@ -2940,30 +2940,30 @@
         </is>
       </c>
       <c r="G55" s="3" t="n">
-        <v>0.12</v>
+        <v>0.4712</v>
       </c>
       <c r="H55" s="3" t="n">
-        <v>0.15</v>
+        <v>0.589</v>
       </c>
       <c r="I55" s="3" t="n">
-        <v>0.18</v>
+        <v>0.7068</v>
       </c>
       <c r="J55" s="3" t="n"/>
       <c r="K55" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_7ii = x</t>
+          <t>V406.nsk_kinetic_model._te.k_8 = x</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" s="3" t="inlineStr">
         <is>
-          <t>K_7</t>
+          <t>._k_9</t>
         </is>
       </c>
       <c r="B56" s="3" t="inlineStr">
         <is>
-          <t>Kinetics: Glucose-to-Biomass</t>
+          <t>Kinetics: Acetalhdyde compartment formation</t>
         </is>
       </c>
       <c r="C56" s="3" t="inlineStr">
@@ -2973,11 +2973,11 @@
       </c>
       <c r="D56" s="3" t="inlineStr">
         <is>
-          <t>g_per_l</t>
+          <t>g_per_l_per_h</t>
         </is>
       </c>
       <c r="E56" s="3" t="n">
-        <v>0.0101</v>
+        <v>0.008</v>
       </c>
       <c r="F56" s="3" t="inlineStr">
         <is>
@@ -2985,30 +2985,30 @@
         </is>
       </c>
       <c r="G56" s="3" t="n">
-        <v>0.00808</v>
+        <v>0.0064</v>
       </c>
       <c r="H56" s="3" t="n">
-        <v>0.0101</v>
+        <v>0.008</v>
       </c>
       <c r="I56" s="3" t="n">
-        <v>0.01212</v>
+        <v>0.009599999999999999</v>
       </c>
       <c r="J56" s="3" t="n"/>
       <c r="K56" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.K_7 = x</t>
+          <t>V406.nsk_kinetic_model._te.k_9 = x</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" s="3" t="inlineStr">
         <is>
-          <t>._k_8</t>
+          <t>._k_9e</t>
         </is>
       </c>
       <c r="B57" s="3" t="inlineStr">
         <is>
-          <t>Kinetics: Acetate-to-Biomass</t>
+          <t>Kinetics: Acetalhdyde compartment formation</t>
         </is>
       </c>
       <c r="C57" s="3" t="inlineStr">
@@ -3022,7 +3022,7 @@
         </is>
       </c>
       <c r="E57" s="3" t="n">
-        <v>0.589</v>
+        <v>0.0751</v>
       </c>
       <c r="F57" s="3" t="inlineStr">
         <is>
@@ -3030,25 +3030,25 @@
         </is>
       </c>
       <c r="G57" s="3" t="n">
-        <v>0.4712</v>
+        <v>0.06008</v>
       </c>
       <c r="H57" s="3" t="n">
-        <v>0.589</v>
+        <v>0.0751</v>
       </c>
       <c r="I57" s="3" t="n">
-        <v>0.7068</v>
+        <v>0.09011999999999999</v>
       </c>
       <c r="J57" s="3" t="n"/>
       <c r="K57" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_8 = x</t>
+          <t>V406.nsk_kinetic_model._te.k_9e = x</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" s="3" t="inlineStr">
         <is>
-          <t>._k_9</t>
+          <t>K_9e</t>
         </is>
       </c>
       <c r="B58" s="3" t="inlineStr">
@@ -3063,11 +3063,11 @@
       </c>
       <c r="D58" s="3" t="inlineStr">
         <is>
-          <t>g_per_l_per_h</t>
+          <t>g_per_l</t>
         </is>
       </c>
       <c r="E58" s="3" t="n">
-        <v>0.008</v>
+        <v>13</v>
       </c>
       <c r="F58" s="3" t="inlineStr">
         <is>
@@ -3075,25 +3075,25 @@
         </is>
       </c>
       <c r="G58" s="3" t="n">
-        <v>0.0064</v>
+        <v>10.4</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>0.008</v>
+        <v>13</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>0.009599999999999999</v>
+        <v>15.6</v>
       </c>
       <c r="J58" s="3" t="n"/>
       <c r="K58" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_9 = x</t>
+          <t>V406.nsk_kinetic_model._te.K_9e = x</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" s="3" t="inlineStr">
         <is>
-          <t>K_9</t>
+          <t>K_9i</t>
         </is>
       </c>
       <c r="B59" s="3" t="inlineStr">
@@ -3111,34 +3111,34 @@
           <t>g_per_l</t>
         </is>
       </c>
-      <c r="E59" s="5" t="n">
-        <v>1e-06</v>
+      <c r="E59" s="3" t="n">
+        <v>25</v>
       </c>
       <c r="F59" s="3" t="inlineStr">
         <is>
           <t>triangular</t>
         </is>
       </c>
-      <c r="G59" s="5" t="n">
-        <v>8e-07</v>
-      </c>
-      <c r="H59" s="5" t="n">
-        <v>1e-06</v>
-      </c>
-      <c r="I59" s="5" t="n">
-        <v>1.2e-06</v>
+      <c r="G59" s="3" t="n">
+        <v>20</v>
+      </c>
+      <c r="H59" s="3" t="n">
+        <v>25</v>
+      </c>
+      <c r="I59" s="3" t="n">
+        <v>30</v>
       </c>
       <c r="J59" s="3" t="n"/>
       <c r="K59" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.K_9 = x</t>
+          <t>V406.nsk_kinetic_model._te.K_9i = x</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>._k_9e</t>
+          <t>._k_9c</t>
         </is>
       </c>
       <c r="B60" s="3" t="inlineStr">
@@ -3157,7 +3157,7 @@
         </is>
       </c>
       <c r="E60" s="3" t="n">
-        <v>0.0751</v>
+        <v>0.00399</v>
       </c>
       <c r="F60" s="3" t="inlineStr">
         <is>
@@ -3165,30 +3165,30 @@
         </is>
       </c>
       <c r="G60" s="3" t="n">
-        <v>0.06008</v>
+        <v>0.003192</v>
       </c>
       <c r="H60" s="3" t="n">
-        <v>0.0751</v>
+        <v>0.00399</v>
       </c>
       <c r="I60" s="3" t="n">
-        <v>0.09011999999999999</v>
+        <v>0.004788</v>
       </c>
       <c r="J60" s="3" t="n"/>
       <c r="K60" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_9e = x</t>
+          <t>V406.nsk_kinetic_model._te.k_9c = x</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" s="3" t="inlineStr">
         <is>
-          <t>K_9e</t>
+          <t>._k_10</t>
         </is>
       </c>
       <c r="B61" s="3" t="inlineStr">
         <is>
-          <t>Kinetics: Acetalhdyde compartment formation</t>
+          <t>Kinetics: Active compartment degradation</t>
         </is>
       </c>
       <c r="C61" s="3" t="inlineStr">
@@ -3198,11 +3198,11 @@
       </c>
       <c r="D61" s="3" t="inlineStr">
         <is>
-          <t>g_per_l</t>
+          <t>g_per_l_per_h</t>
         </is>
       </c>
       <c r="E61" s="3" t="n">
-        <v>13</v>
+        <v>0.06</v>
       </c>
       <c r="F61" s="3" t="inlineStr">
         <is>
@@ -3210,429 +3210,432 @@
         </is>
       </c>
       <c r="G61" s="3" t="n">
-        <v>10.4</v>
+        <v>0.048</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>13</v>
+        <v>0.06</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>15.6</v>
+        <v>0.07199999999999999</v>
       </c>
       <c r="J61" s="3" t="n"/>
       <c r="K61" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.K_9e = x</t>
+          <t>V406.nsk_kinetic_model._te.k_10 = x</t>
         </is>
       </c>
     </row>
     <row r="62">
-      <c r="A62" s="3" t="inlineStr">
-        <is>
-          <t>K_9i</t>
-        </is>
-      </c>
-      <c r="B62" s="3" t="inlineStr">
-        <is>
-          <t>Kinetics: Acetalhdyde compartment formation</t>
-        </is>
-      </c>
-      <c r="C62" s="3" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D62" s="3" t="inlineStr">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>._k_10ie</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>Kinetics: Active compartment degradation</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D62" t="inlineStr">
+        <is>
+          <t>g_per_l_per_h</t>
+        </is>
+      </c>
+      <c r="E62" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G62" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="H62" t="n">
+        <v>0.04</v>
+      </c>
+      <c r="I62" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="K62" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.k_10ie = x</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>._k_10ia</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>Kinetics: Active compartment degradation</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D63" t="inlineStr">
+        <is>
+          <t>g_per_l_per_h</t>
+        </is>
+      </c>
+      <c r="E63" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G63" t="n">
+        <v>0.096</v>
+      </c>
+      <c r="H63" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="I63" t="n">
+        <v>0.144</v>
+      </c>
+      <c r="K63" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.k_10ia = x</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>._k_10ii</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>Kinetics: Active compartment degradation</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>g_per_l_per_h</t>
+        </is>
+      </c>
+      <c r="E64" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G64" t="n">
+        <v>0.12</v>
+      </c>
+      <c r="H64" t="n">
+        <v>0.15</v>
+      </c>
+      <c r="I64" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="K64" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.k_10ii = x</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" s="3" t="inlineStr">
+        <is>
+          <t>._k_11</t>
+        </is>
+      </c>
+      <c r="B65" s="3" t="inlineStr">
+        <is>
+          <t>Kinetics: Acetaldehyde compartment degradation</t>
+        </is>
+      </c>
+      <c r="C65" s="3" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D65" s="3" t="inlineStr">
+        <is>
+          <t>g_per_l_per_h</t>
+        </is>
+      </c>
+      <c r="E65" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="F65" s="3" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G65" s="3" t="n">
+        <v>0.016</v>
+      </c>
+      <c r="H65" s="3" t="n">
+        <v>0.02</v>
+      </c>
+      <c r="I65" s="3" t="n">
+        <v>0.024</v>
+      </c>
+      <c r="J65" s="3" t="n"/>
+      <c r="K65" s="3" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.k_11 = x</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" s="3" t="inlineStr">
+        <is>
+          <t>._k_13</t>
+        </is>
+      </c>
+      <c r="B66" s="3" t="inlineStr">
+        <is>
+          <t>Kinetics: Pyruvate-to-Acetolactate</t>
+        </is>
+      </c>
+      <c r="C66" s="3" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D66" s="3" t="inlineStr">
+        <is>
+          <t>g_per_l_per_h</t>
+        </is>
+      </c>
+      <c r="E66" s="3" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="F66" s="3" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G66" s="5" t="n">
+        <v>4.648</v>
+      </c>
+      <c r="H66" s="5" t="n">
+        <v>5.81</v>
+      </c>
+      <c r="I66" s="5" t="n">
+        <v>6.972</v>
+      </c>
+      <c r="J66" s="3" t="n"/>
+      <c r="K66" s="3" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.k_13 = x</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" s="3" t="inlineStr">
+        <is>
+          <t>K_13</t>
+        </is>
+      </c>
+      <c r="B67" s="3" t="inlineStr">
+        <is>
+          <t>Kinetics: Pyruvate-to-Acetolactate</t>
+        </is>
+      </c>
+      <c r="C67" s="3" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D67" s="3" t="inlineStr">
         <is>
           <t>g_per_l</t>
         </is>
       </c>
-      <c r="E62" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="F62" s="3" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G62" s="3" t="n">
-        <v>20</v>
-      </c>
-      <c r="H62" s="3" t="n">
-        <v>25</v>
-      </c>
-      <c r="I62" s="3" t="n">
-        <v>30</v>
-      </c>
-      <c r="J62" s="3" t="n"/>
-      <c r="K62" s="3" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.K_9i = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="63">
-      <c r="A63" s="3" t="inlineStr">
-        <is>
-          <t>._k_9c</t>
-        </is>
-      </c>
-      <c r="B63" s="3" t="inlineStr">
-        <is>
-          <t>Kinetics: Acetalhdyde compartment formation</t>
-        </is>
-      </c>
-      <c r="C63" s="3" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D63" s="3" t="inlineStr">
+      <c r="E67" s="5" t="n">
+        <v>5e-07</v>
+      </c>
+      <c r="F67" s="3" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G67" s="5" t="n">
+        <v>4e-07</v>
+      </c>
+      <c r="H67" s="5" t="n">
+        <v>5e-07</v>
+      </c>
+      <c r="I67" s="5" t="n">
+        <v>6e-07</v>
+      </c>
+      <c r="J67" s="3" t="n"/>
+      <c r="K67" s="3" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.K_13 = x</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" s="3" t="inlineStr">
+        <is>
+          <t>._k_14</t>
+        </is>
+      </c>
+      <c r="B68" s="3" t="inlineStr">
+        <is>
+          <t>Kinetics: Acetolactate-to-DHI</t>
+        </is>
+      </c>
+      <c r="C68" s="3" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D68" s="3" t="inlineStr">
         <is>
           <t>g_per_l_per_h</t>
         </is>
       </c>
-      <c r="E63" s="3" t="n">
-        <v>0.00399</v>
-      </c>
-      <c r="F63" s="3" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G63" s="3" t="n">
-        <v>0.003192</v>
-      </c>
-      <c r="H63" s="3" t="n">
-        <v>0.00399</v>
-      </c>
-      <c r="I63" s="3" t="n">
-        <v>0.004788</v>
-      </c>
-      <c r="J63" s="3" t="n"/>
-      <c r="K63" s="3" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.k_9c = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="64">
-      <c r="A64" s="3" t="inlineStr">
-        <is>
-          <t>._k_10</t>
-        </is>
-      </c>
-      <c r="B64" s="3" t="inlineStr">
-        <is>
-          <t>Kinetics: Active compartment degradation</t>
-        </is>
-      </c>
-      <c r="C64" s="3" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D64" s="3" t="inlineStr">
+      <c r="E68" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F68" s="3" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G68" s="5" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="H68" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I68" s="5" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="J68" s="3" t="n"/>
+      <c r="K68" s="3" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.k_14 = x</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" s="3" t="inlineStr">
+        <is>
+          <t>K_14</t>
+        </is>
+      </c>
+      <c r="B69" s="3" t="inlineStr">
+        <is>
+          <t>Kinetics: Acetolactate-to-DHI</t>
+        </is>
+      </c>
+      <c r="C69" s="3" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D69" s="3" t="inlineStr">
+        <is>
+          <t>g_per_l</t>
+        </is>
+      </c>
+      <c r="E69" s="5" t="n">
+        <v>0.000264</v>
+      </c>
+      <c r="F69" s="3" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G69" s="5" t="n">
+        <v>0.0002112</v>
+      </c>
+      <c r="H69" s="5" t="n">
+        <v>0.000264</v>
+      </c>
+      <c r="I69" s="5" t="n">
+        <v>0.0003168</v>
+      </c>
+      <c r="J69" s="3" t="n"/>
+      <c r="K69" s="3" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.K_14 = x</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" s="3" t="inlineStr">
+        <is>
+          <t>._k_15</t>
+        </is>
+      </c>
+      <c r="B70" s="3" t="inlineStr">
+        <is>
+          <t>Kinetics: DHI-to-Ketoisovalerate</t>
+        </is>
+      </c>
+      <c r="C70" s="3" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D70" s="3" t="inlineStr">
         <is>
           <t>g_per_l_per_h</t>
         </is>
       </c>
-      <c r="E64" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F64" s="3" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G64" s="3" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="H64" s="3" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I64" s="3" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="J64" s="3" t="n"/>
-      <c r="K64" s="3" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.k_10 = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="65">
-      <c r="A65" t="inlineStr">
-        <is>
-          <t>._k_10ie</t>
-        </is>
-      </c>
-      <c r="B65" t="inlineStr">
-        <is>
-          <t>Kinetics: Active compartment degradation</t>
-        </is>
-      </c>
-      <c r="C65" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D65" t="inlineStr">
-        <is>
-          <t>g_per_l_per_h</t>
-        </is>
-      </c>
-      <c r="E65" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="F65" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G65" t="n">
-        <v>0.032</v>
-      </c>
-      <c r="H65" t="n">
-        <v>0.04</v>
-      </c>
-      <c r="I65" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="K65" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.k_10ie = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="66">
-      <c r="A66" t="inlineStr">
-        <is>
-          <t>._k_10ia</t>
-        </is>
-      </c>
-      <c r="B66" t="inlineStr">
-        <is>
-          <t>Kinetics: Active compartment degradation</t>
-        </is>
-      </c>
-      <c r="C66" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D66" t="inlineStr">
-        <is>
-          <t>g_per_l_per_h</t>
-        </is>
-      </c>
-      <c r="E66" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="F66" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G66" t="n">
-        <v>0.096</v>
-      </c>
-      <c r="H66" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="I66" t="n">
-        <v>0.144</v>
-      </c>
-      <c r="K66" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.k_10ia = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="67">
-      <c r="A67" t="inlineStr">
-        <is>
-          <t>._k_10ii</t>
-        </is>
-      </c>
-      <c r="B67" t="inlineStr">
-        <is>
-          <t>Kinetics: Active compartment degradation</t>
-        </is>
-      </c>
-      <c r="C67" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D67" t="inlineStr">
-        <is>
-          <t>g_per_l_per_h</t>
-        </is>
-      </c>
-      <c r="E67" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="F67" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G67" t="n">
-        <v>0.12</v>
-      </c>
-      <c r="H67" t="n">
-        <v>0.15</v>
-      </c>
-      <c r="I67" t="n">
-        <v>0.18</v>
-      </c>
-      <c r="K67" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.k_10ii = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="68">
-      <c r="A68" t="inlineStr">
-        <is>
-          <t>P_10e</t>
-        </is>
-      </c>
-      <c r="B68" t="inlineStr">
-        <is>
-          <t>Kinetics: Active compartment degradation</t>
-        </is>
-      </c>
-      <c r="C68" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D68" t="inlineStr">
-        <is>
-          <t>g_per_l</t>
-        </is>
-      </c>
-      <c r="E68" t="n">
-        <v>100</v>
-      </c>
-      <c r="F68" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G68" t="n">
-        <v>80</v>
-      </c>
-      <c r="H68" t="n">
-        <v>100</v>
-      </c>
-      <c r="I68" t="n">
-        <v>120</v>
-      </c>
-      <c r="K68" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.P_10e = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="69">
-      <c r="A69" t="inlineStr">
-        <is>
-          <t>P_10a</t>
-        </is>
-      </c>
-      <c r="B69" t="inlineStr">
-        <is>
-          <t>Kinetics: Active compartment degradation</t>
-        </is>
-      </c>
-      <c r="C69" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D69" t="inlineStr">
-        <is>
-          <t>g_per_l</t>
-        </is>
-      </c>
-      <c r="E69" t="n">
-        <v>5</v>
-      </c>
-      <c r="F69" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G69" t="n">
-        <v>4</v>
-      </c>
-      <c r="H69" t="n">
-        <v>5</v>
-      </c>
-      <c r="I69" t="n">
-        <v>6</v>
-      </c>
-      <c r="K69" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.P_10a = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="70">
-      <c r="A70" t="inlineStr">
-        <is>
-          <t>P_10i</t>
-        </is>
-      </c>
-      <c r="B70" t="inlineStr">
-        <is>
-          <t>Kinetics: Active compartment degradation</t>
-        </is>
-      </c>
-      <c r="C70" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D70" t="inlineStr">
-        <is>
-          <t>g_per_l</t>
-        </is>
-      </c>
-      <c r="E70" t="n">
-        <v>25</v>
-      </c>
-      <c r="F70" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G70" t="n">
-        <v>20</v>
-      </c>
-      <c r="H70" t="n">
-        <v>25</v>
-      </c>
-      <c r="I70" t="n">
-        <v>30</v>
-      </c>
-      <c r="K70" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.P_10i = x</t>
+      <c r="E70" s="3" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="F70" s="3" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G70" s="5" t="n">
+        <v>3.84</v>
+      </c>
+      <c r="H70" s="5" t="n">
+        <v>4.8</v>
+      </c>
+      <c r="I70" s="5" t="n">
+        <v>5.76</v>
+      </c>
+      <c r="J70" s="3" t="n"/>
+      <c r="K70" s="3" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.k_15 = x</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" s="3" t="inlineStr">
         <is>
-          <t>._k_11</t>
+          <t>K_15</t>
         </is>
       </c>
       <c r="B71" s="3" t="inlineStr">
         <is>
-          <t>Kinetics: Acetaldehyde compartment degradation</t>
+          <t>Kinetics: DHI-to-Ketoisovalerate</t>
         </is>
       </c>
       <c r="C71" s="3" t="inlineStr">
@@ -3642,42 +3645,42 @@
       </c>
       <c r="D71" s="3" t="inlineStr">
         <is>
-          <t>g_per_l_per_h</t>
-        </is>
-      </c>
-      <c r="E71" s="3" t="n">
-        <v>0.02</v>
+          <t>g_per_l</t>
+        </is>
+      </c>
+      <c r="E71" s="5" t="n">
+        <v>0.000264</v>
       </c>
       <c r="F71" s="3" t="inlineStr">
         <is>
           <t>triangular</t>
         </is>
       </c>
-      <c r="G71" s="3" t="n">
-        <v>0.016</v>
-      </c>
-      <c r="H71" s="3" t="n">
-        <v>0.02</v>
-      </c>
-      <c r="I71" s="3" t="n">
-        <v>0.024</v>
+      <c r="G71" s="5" t="n">
+        <v>0.0002112</v>
+      </c>
+      <c r="H71" s="5" t="n">
+        <v>0.000264</v>
+      </c>
+      <c r="I71" s="5" t="n">
+        <v>0.0003168</v>
       </c>
       <c r="J71" s="3" t="n"/>
       <c r="K71" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_11 = x</t>
+          <t>V406.nsk_kinetic_model._te.K_15 = x</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" s="3" t="inlineStr">
         <is>
-          <t>._k_13</t>
+          <t>._k_16</t>
         </is>
       </c>
       <c r="B72" s="3" t="inlineStr">
         <is>
-          <t>Kinetics: Pyruvate-to-Acetolactate</t>
+          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
         </is>
       </c>
       <c r="C72" s="3" t="inlineStr">
@@ -3691,7 +3694,7 @@
         </is>
       </c>
       <c r="E72" s="3" t="n">
-        <v>5.81</v>
+        <v>2.82</v>
       </c>
       <c r="F72" s="3" t="inlineStr">
         <is>
@@ -3699,30 +3702,30 @@
         </is>
       </c>
       <c r="G72" s="5" t="n">
-        <v>4.648</v>
+        <v>2.256</v>
       </c>
       <c r="H72" s="5" t="n">
-        <v>5.81</v>
+        <v>2.82</v>
       </c>
       <c r="I72" s="5" t="n">
-        <v>6.972</v>
+        <v>3.384</v>
       </c>
       <c r="J72" s="3" t="n"/>
       <c r="K72" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_13 = x</t>
+          <t>V406.nsk_kinetic_model._te.k_16 = x</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" s="3" t="inlineStr">
         <is>
-          <t>K_13</t>
+          <t>K_16</t>
         </is>
       </c>
       <c r="B73" s="3" t="inlineStr">
         <is>
-          <t>Kinetics: Pyruvate-to-Acetolactate</t>
+          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
         </is>
       </c>
       <c r="C73" s="3" t="inlineStr">
@@ -3735,8 +3738,8 @@
           <t>g_per_l</t>
         </is>
       </c>
-      <c r="E73" s="5" t="n">
-        <v>5e-07</v>
+      <c r="E73" s="3" t="n">
+        <v>0.034</v>
       </c>
       <c r="F73" s="3" t="inlineStr">
         <is>
@@ -3744,30 +3747,30 @@
         </is>
       </c>
       <c r="G73" s="5" t="n">
-        <v>4e-07</v>
+        <v>0.0272</v>
       </c>
       <c r="H73" s="5" t="n">
-        <v>5e-07</v>
+        <v>0.034</v>
       </c>
       <c r="I73" s="5" t="n">
-        <v>6e-07</v>
+        <v>0.0408</v>
       </c>
       <c r="J73" s="3" t="n"/>
       <c r="K73" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.K_13 = x</t>
+          <t>V406.nsk_kinetic_model._te.K_16 = x</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" s="3" t="inlineStr">
         <is>
-          <t>._k_14</t>
+          <t>K_16i</t>
         </is>
       </c>
       <c r="B74" s="3" t="inlineStr">
         <is>
-          <t>Kinetics: Acetolactate-to-DHI</t>
+          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
         </is>
       </c>
       <c r="C74" s="3" t="inlineStr">
@@ -3777,11 +3780,11 @@
       </c>
       <c r="D74" s="3" t="inlineStr">
         <is>
-          <t>g_per_l_per_h</t>
+          <t>g_per_l</t>
         </is>
       </c>
       <c r="E74" s="3" t="n">
-        <v>4.8</v>
+        <v>0.057</v>
       </c>
       <c r="F74" s="3" t="inlineStr">
         <is>
@@ -3789,419 +3792,104 @@
         </is>
       </c>
       <c r="G74" s="5" t="n">
-        <v>3.84</v>
+        <v>0.0456</v>
       </c>
       <c r="H74" s="5" t="n">
-        <v>4.8</v>
+        <v>0.057</v>
       </c>
       <c r="I74" s="5" t="n">
-        <v>5.76</v>
+        <v>0.0684</v>
       </c>
       <c r="J74" s="3" t="n"/>
       <c r="K74" s="3" t="inlineStr">
         <is>
-          <t>V406.nsk_kinetic_model._te.k_14 = x</t>
+          <t>V406.nsk_kinetic_model._te.K_16i = x</t>
         </is>
       </c>
     </row>
     <row r="75">
-      <c r="A75" s="3" t="inlineStr">
-        <is>
-          <t>K_14</t>
-        </is>
-      </c>
-      <c r="B75" s="3" t="inlineStr">
-        <is>
-          <t>Kinetics: Acetolactate-to-DHI</t>
-        </is>
-      </c>
-      <c r="C75" s="3" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D75" s="3" t="inlineStr">
-        <is>
-          <t>g_per_l</t>
-        </is>
-      </c>
-      <c r="E75" s="5" t="n">
-        <v>0.000264</v>
-      </c>
-      <c r="F75" s="3" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G75" s="5" t="n">
-        <v>0.0002112</v>
-      </c>
-      <c r="H75" s="5" t="n">
-        <v>0.000264</v>
-      </c>
-      <c r="I75" s="5" t="n">
-        <v>0.0003168</v>
-      </c>
-      <c r="J75" s="3" t="n"/>
-      <c r="K75" s="3" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.K_14 = x</t>
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>._k_16ia</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D75" t="inlineStr">
+        <is>
+          <t>g_per_l_per_h</t>
+        </is>
+      </c>
+      <c r="E75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G75" t="n">
+        <v>0.048</v>
+      </c>
+      <c r="H75" t="n">
+        <v>0.06</v>
+      </c>
+      <c r="I75" t="n">
+        <v>0.07199999999999999</v>
+      </c>
+      <c r="K75" t="inlineStr">
+        <is>
+          <t>V406.nsk_kinetic_model._te.k_16ia = x</t>
         </is>
       </c>
     </row>
     <row r="76">
-      <c r="A76" s="3" t="inlineStr">
-        <is>
-          <t>._k_15</t>
-        </is>
-      </c>
-      <c r="B76" s="3" t="inlineStr">
-        <is>
-          <t>Kinetics: DHI-to-Ketoisovalerate</t>
-        </is>
-      </c>
-      <c r="C76" s="3" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D76" s="3" t="inlineStr">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>._k_16ie</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>coupled</t>
+        </is>
+      </c>
+      <c r="D76" t="inlineStr">
         <is>
           <t>g_per_l_per_h</t>
         </is>
       </c>
-      <c r="E76" s="3" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="F76" s="3" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G76" s="5" t="n">
-        <v>3.84</v>
-      </c>
-      <c r="H76" s="5" t="n">
-        <v>4.8</v>
-      </c>
-      <c r="I76" s="5" t="n">
-        <v>5.76</v>
-      </c>
-      <c r="J76" s="3" t="n"/>
-      <c r="K76" s="3" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.k_15 = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="77">
-      <c r="A77" s="3" t="inlineStr">
-        <is>
-          <t>K_15</t>
-        </is>
-      </c>
-      <c r="B77" s="3" t="inlineStr">
-        <is>
-          <t>Kinetics: DHI-to-Ketoisovalerate</t>
-        </is>
-      </c>
-      <c r="C77" s="3" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D77" s="3" t="inlineStr">
-        <is>
-          <t>g_per_l</t>
-        </is>
-      </c>
-      <c r="E77" s="5" t="n">
-        <v>0.000264</v>
-      </c>
-      <c r="F77" s="3" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G77" s="5" t="n">
-        <v>0.0002112</v>
-      </c>
-      <c r="H77" s="5" t="n">
-        <v>0.000264</v>
-      </c>
-      <c r="I77" s="5" t="n">
-        <v>0.0003168</v>
-      </c>
-      <c r="J77" s="3" t="n"/>
-      <c r="K77" s="3" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.K_15 = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="78">
-      <c r="A78" s="3" t="inlineStr">
-        <is>
-          <t>._k_16</t>
-        </is>
-      </c>
-      <c r="B78" s="3" t="inlineStr">
-        <is>
-          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
-        </is>
-      </c>
-      <c r="C78" s="3" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D78" s="3" t="inlineStr">
-        <is>
-          <t>g_per_l_per_h</t>
-        </is>
-      </c>
-      <c r="E78" s="3" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="F78" s="3" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G78" s="5" t="n">
-        <v>2.256</v>
-      </c>
-      <c r="H78" s="5" t="n">
-        <v>2.82</v>
-      </c>
-      <c r="I78" s="5" t="n">
-        <v>3.384</v>
-      </c>
-      <c r="J78" s="3" t="n"/>
-      <c r="K78" s="3" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.k_16 = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="79">
-      <c r="A79" s="3" t="inlineStr">
-        <is>
-          <t>._k_16r</t>
-        </is>
-      </c>
-      <c r="B79" s="3" t="inlineStr">
-        <is>
-          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
-        </is>
-      </c>
-      <c r="C79" s="3" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D79" s="3" t="inlineStr">
-        <is>
-          <t>g_per_l_per_h</t>
-        </is>
-      </c>
-      <c r="E79" s="3" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="F79" s="3" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G79" s="5" t="n">
-        <v>0.01</v>
-      </c>
-      <c r="H79" s="5" t="n">
-        <v>0.0125</v>
-      </c>
-      <c r="I79" s="5" t="n">
-        <v>0.015</v>
-      </c>
-      <c r="J79" s="3" t="n"/>
-      <c r="K79" s="3" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.k_16r = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="80">
-      <c r="A80" s="3" t="inlineStr">
-        <is>
-          <t>K_16</t>
-        </is>
-      </c>
-      <c r="B80" s="3" t="inlineStr">
-        <is>
-          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
-        </is>
-      </c>
-      <c r="C80" s="3" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D80" s="3" t="inlineStr">
-        <is>
-          <t>g_per_l</t>
-        </is>
-      </c>
-      <c r="E80" s="3" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="F80" s="3" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G80" s="5" t="n">
-        <v>0.0272</v>
-      </c>
-      <c r="H80" s="5" t="n">
-        <v>0.034</v>
-      </c>
-      <c r="I80" s="5" t="n">
-        <v>0.0408</v>
-      </c>
-      <c r="J80" s="3" t="n"/>
-      <c r="K80" s="3" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.K_16 = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="81">
-      <c r="A81" s="3" t="inlineStr">
-        <is>
-          <t>K_16i</t>
-        </is>
-      </c>
-      <c r="B81" s="3" t="inlineStr">
-        <is>
-          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
-        </is>
-      </c>
-      <c r="C81" s="3" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D81" s="3" t="inlineStr">
-        <is>
-          <t>g_per_l</t>
-        </is>
-      </c>
-      <c r="E81" s="3" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="F81" s="3" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G81" s="5" t="n">
-        <v>0.0456</v>
-      </c>
-      <c r="H81" s="5" t="n">
-        <v>0.057</v>
-      </c>
-      <c r="I81" s="5" t="n">
-        <v>0.0684</v>
-      </c>
-      <c r="J81" s="3" t="n"/>
-      <c r="K81" s="3" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.K_16i = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="82">
-      <c r="A82" t="inlineStr">
-        <is>
-          <t>._k_16ia</t>
-        </is>
-      </c>
-      <c r="B82" t="inlineStr">
-        <is>
-          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
-        </is>
-      </c>
-      <c r="C82" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D82" t="inlineStr">
-        <is>
-          <t>g_per_l_per_h</t>
-        </is>
-      </c>
-      <c r="E82" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="F82" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G82" t="n">
-        <v>0.048</v>
-      </c>
-      <c r="H82" t="n">
-        <v>0.06</v>
-      </c>
-      <c r="I82" t="n">
-        <v>0.07199999999999999</v>
-      </c>
-      <c r="K82" t="inlineStr">
-        <is>
-          <t>V406.nsk_kinetic_model._te.k_16ia = x</t>
-        </is>
-      </c>
-    </row>
-    <row r="83">
-      <c r="A83" t="inlineStr">
-        <is>
-          <t>._k_16ie</t>
-        </is>
-      </c>
-      <c r="B83" t="inlineStr">
-        <is>
-          <t>Kinetics: Ketoisovalerate-to-Isobutanol</t>
-        </is>
-      </c>
-      <c r="C83" t="inlineStr">
-        <is>
-          <t>coupled</t>
-        </is>
-      </c>
-      <c r="D83" t="inlineStr">
-        <is>
-          <t>g_per_l_per_h</t>
-        </is>
-      </c>
-      <c r="E83" t="n">
+      <c r="E76" t="n">
         <v>0.02</v>
       </c>
-      <c r="F83" t="inlineStr">
-        <is>
-          <t>triangular</t>
-        </is>
-      </c>
-      <c r="G83" t="n">
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>triangular</t>
+        </is>
+      </c>
+      <c r="G76" t="n">
         <v>0.016</v>
       </c>
-      <c r="H83" t="n">
+      <c r="H76" t="n">
         <v>0.02</v>
       </c>
-      <c r="I83" t="n">
+      <c r="I76" t="n">
         <v>0.024</v>
       </c>
-      <c r="K83" t="inlineStr">
+      <c r="K76" t="inlineStr">
         <is>
           <t>V406.nsk_kinetic_model._te.k_16ie = x</t>
         </is>
